--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="767" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79B38FE5-D8E7-4FC7-8BA0-BE581C8D6A69}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3569F7CB-BB43-43E3-9220-220AB4DCFFEB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1439,47 +1439,47 @@
       </c>
       <c r="H3" s="14">
         <f t="shared" ref="H3:R3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" s="14">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q3" s="14">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3" s="14">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="1">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
@@ -3151,11 +3151,15 @@
       <c r="D28" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="E28" s="11">
+        <v>7</v>
+      </c>
+      <c r="F28" s="11">
+        <v>1</v>
+      </c>
       <c r="G28" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="H28" s="24" t="s">
         <v>46</v>
@@ -6286,7 +6290,7 @@
       <c r="F76" s="43"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6392,59 +6396,59 @@
       </c>
       <c r="S77" s="28">
         <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="T77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="U77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="V77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="W77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="Y77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="Z77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AB77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AC77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AD77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AE77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AF77" s="28">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6501,59 +6505,59 @@
       </c>
       <c r="S78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3569F7CB-BB43-43E3-9220-220AB4DCFFEB}"/>
+  <xr:revisionPtr revIDLastSave="772" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FA3B9F-65DB-43FC-9057-3D547343C990}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -842,58 +842,11 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -901,6 +854,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -933,6 +888,51 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1272,15 +1272,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1358,17 +1358,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="65"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
@@ -1376,13 +1376,13 @@
         <v>114</v>
       </c>
       <c r="J2" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="L2" s="30" t="s">
         <v>107</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>111</v>
       </c>
       <c r="M2" s="29" t="s">
         <v>102</v>
@@ -1393,14 +1393,14 @@
       <c r="O2" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="30" t="s">
+      <c r="P2" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="29" t="s">
+      <c r="R2" s="29" t="s">
         <v>113</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>112</v>
       </c>
       <c r="S2" s="29"/>
       <c r="T2" s="29"/>
@@ -1430,116 +1430,116 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="53"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f t="shared" ref="H3:R3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <v>8</v>
+      </c>
+      <c r="I3" s="14">
+        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
         <v>7</v>
       </c>
-      <c r="I3" s="14">
+      <c r="J3" s="14">
+        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
+        <v>7</v>
+      </c>
+      <c r="K3" s="14">
+        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
+        <v>7</v>
+      </c>
+      <c r="L3" s="14">
+        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+        <v>6</v>
+      </c>
+      <c r="M3" s="14">
+        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
+        <v>6</v>
+      </c>
+      <c r="N3" s="14">
+        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="O3" s="14">
+        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="P3" s="14">
+        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
+        <v>4</v>
+      </c>
+      <c r="R3" s="14">
+        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
+        <v>4</v>
+      </c>
+      <c r="S3" s="14">
+        <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="J3" s="14">
+        <v>0</v>
+      </c>
+      <c r="U3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="K3" s="14">
+        <v>0</v>
+      </c>
+      <c r="V3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="L3" s="14">
+        <v>0</v>
+      </c>
+      <c r="W3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="M3" s="14">
+        <v>0</v>
+      </c>
+      <c r="X3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="P3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Q3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="R3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="S3" s="14">
-        <f t="shared" ref="S3:AF3" si="1">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
         <v>0</v>
       </c>
-      <c r="T3" s="14">
-        <f t="shared" si="1"/>
+      <c r="AD3" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U3" s="14">
-        <f t="shared" si="1"/>
+      <c r="AE3" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V3" s="14">
-        <f t="shared" si="1"/>
+      <c r="AF3" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="37" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G51" si="2">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
+        <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
         <v>L</v>
       </c>
       <c r="H4" s="24" t="s">
@@ -1570,10 +1570,10 @@
       <c r="J4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="23" t="s">
+      <c r="K4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M4" s="23" t="s">
@@ -1585,10 +1585,10 @@
       <c r="O4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="23" t="s">
+      <c r="P4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R4" s="23" t="s">
@@ -1610,7 +1610,7 @@
       <c r="AF4" s="23"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H5" s="24" t="s">
@@ -1639,10 +1639,10 @@
       <c r="J5" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="23" t="s">
+      <c r="K5" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M5" s="23" t="s">
@@ -1654,10 +1654,10 @@
       <c r="O5" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="23" t="s">
+      <c r="P5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R5" s="23" t="s">
@@ -1679,7 +1679,7 @@
       <c r="AF5" s="23"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
+      <c r="A6" s="38"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1692,7 +1692,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H6" s="24" t="s">
@@ -1702,14 +1702,14 @@
         <v>46</v>
       </c>
       <c r="J6" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="K6" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>10</v>
-      </c>
       <c r="M6" s="23" t="s">
         <v>46</v>
       </c>
@@ -1719,10 +1719,10 @@
       <c r="O6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P6" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q6" s="23" t="s">
+      <c r="P6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R6" s="23" t="s">
@@ -1744,7 +1744,7 @@
       <c r="AF6" s="23"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1757,7 +1757,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -1767,12 +1767,12 @@
         <v>10</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M7" s="23" t="s">
@@ -1784,11 +1784,11 @@
       <c r="O7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P7" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q7" s="23" t="s">
-        <v>46</v>
+      <c r="P7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R7" s="23" t="s">
         <v>46</v>
@@ -1809,7 +1809,7 @@
       <c r="AF7" s="23"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H8" s="24" t="s">
@@ -1834,10 +1834,10 @@
       <c r="J8" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="23" t="s">
+      <c r="K8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L8" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M8" s="23" t="s">
@@ -1849,10 +1849,10 @@
       <c r="O8" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q8" s="23" t="s">
+      <c r="P8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R8" s="23" t="s">
@@ -1874,7 +1874,7 @@
       <c r="AF8" s="23"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+      <c r="A9" s="39"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1887,7 +1887,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H9" s="24" t="s">
@@ -1899,10 +1899,10 @@
       <c r="J9" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L9" s="23" t="s">
+      <c r="K9" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L9" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M9" s="23" t="s">
@@ -1914,14 +1914,14 @@
       <c r="O9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q9" s="23" t="s">
+      <c r="P9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S9" s="23"/>
       <c r="T9" s="23"/>
@@ -1939,7 +1939,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H10" s="24" t="s">
@@ -1970,11 +1970,11 @@
       <c r="J10" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="23" t="s">
-        <v>10</v>
+      <c r="K10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M10" s="23" t="s">
         <v>46</v>
@@ -1985,14 +1985,14 @@
       <c r="O10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q10" s="23" t="s">
+      <c r="P10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S10" s="23"/>
       <c r="T10" s="23"/>
@@ -2010,7 +2010,7 @@
       <c r="AF10" s="23"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H11" s="24" t="s">
@@ -2039,10 +2039,10 @@
       <c r="J11" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L11" s="23" t="s">
+      <c r="K11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L11" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M11" s="23" t="s">
@@ -2054,10 +2054,10 @@
       <c r="O11" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="23" t="s">
+      <c r="P11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R11" s="23" t="s">
@@ -2079,7 +2079,7 @@
       <c r="AF11" s="23"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2092,7 +2092,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H12" s="24" t="s">
@@ -2102,12 +2102,12 @@
         <v>46</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L12" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M12" s="23" t="s">
@@ -2119,14 +2119,14 @@
       <c r="O12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="23" t="s">
-        <v>46</v>
+      <c r="P12" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R12" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
@@ -2144,7 +2144,7 @@
       <c r="AF12" s="23"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2157,7 +2157,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H13" s="24" t="s">
@@ -2167,12 +2167,12 @@
         <v>46</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M13" s="23" t="s">
@@ -2184,10 +2184,10 @@
       <c r="O13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="23" t="s">
+      <c r="P13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R13" s="23" t="s">
@@ -2209,7 +2209,7 @@
       <c r="AF13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H14" s="24" t="s">
@@ -2234,10 +2234,10 @@
       <c r="J14" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="23" t="s">
+      <c r="K14" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M14" s="23" t="s">
@@ -2249,14 +2249,14 @@
       <c r="O14" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q14" s="23" t="s">
-        <v>10</v>
+      <c r="P14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q14" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R14" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
@@ -2274,7 +2274,7 @@
       <c r="AF14" s="23"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2287,7 +2287,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -2297,12 +2297,12 @@
         <v>104</v>
       </c>
       <c r="J15" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K15" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L15" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="24" t="s">
         <v>10</v>
       </c>
       <c r="M15" s="23" t="s">
@@ -2314,14 +2314,14 @@
       <c r="O15" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q15" s="23" t="s">
+      <c r="P15" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R15" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
@@ -2339,7 +2339,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="45" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2358,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H16" s="24" t="s">
@@ -2370,11 +2370,11 @@
       <c r="J16" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="23" t="s">
-        <v>10</v>
+      <c r="K16" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M16" s="23" t="s">
         <v>46</v>
@@ -2385,11 +2385,11 @@
       <c r="O16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q16" s="23" t="s">
-        <v>46</v>
+      <c r="P16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q16" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R16" s="23" t="s">
         <v>46</v>
@@ -2410,7 +2410,7 @@
       <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
       <c r="H17" s="24" t="s">
@@ -2439,10 +2439,10 @@
       <c r="J17" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L17" s="23" t="s">
+      <c r="K17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -2454,10 +2454,10 @@
       <c r="O17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q17" s="23" t="s">
+      <c r="P17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R17" s="23" t="s">
@@ -2479,7 +2479,7 @@
       <c r="AF17" s="23"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2492,7 +2492,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H18" s="24" t="s">
@@ -2502,13 +2502,13 @@
         <v>104</v>
       </c>
       <c r="J18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L18" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M18" s="23" t="s">
         <v>104</v>
@@ -2519,10 +2519,10 @@
       <c r="O18" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P18" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q18" s="23" t="s">
+      <c r="P18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q18" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R18" s="23" t="s">
@@ -2544,7 +2544,7 @@
       <c r="AF18" s="23"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2557,7 +2557,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H19" s="24" t="s">
@@ -2569,10 +2569,10 @@
       <c r="J19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" s="23" t="s">
+      <c r="K19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M19" s="23" t="s">
@@ -2584,10 +2584,10 @@
       <c r="O19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q19" s="23" t="s">
+      <c r="P19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R19" s="23" t="s">
@@ -2609,7 +2609,7 @@
       <c r="AF19" s="23"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2622,7 +2622,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H20" s="24" t="s">
@@ -2632,13 +2632,13 @@
         <v>104</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L20" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L20" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M20" s="23" t="s">
         <v>104</v>
@@ -2649,10 +2649,10 @@
       <c r="O20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q20" s="23" t="s">
+      <c r="P20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R20" s="23" t="s">
@@ -2674,7 +2674,7 @@
       <c r="AF20" s="23"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2687,7 +2687,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H21" s="24" t="s">
@@ -2699,10 +2699,10 @@
       <c r="J21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21" s="23" t="s">
+      <c r="K21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M21" s="23" t="s">
@@ -2714,10 +2714,10 @@
       <c r="O21" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q21" s="23" t="s">
+      <c r="P21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R21" s="23" t="s">
@@ -2739,7 +2739,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="42" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2758,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H22" s="24" t="s">
@@ -2770,11 +2770,11 @@
       <c r="J22" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="23" t="s">
-        <v>10</v>
+      <c r="K22" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M22" s="23" t="s">
         <v>46</v>
@@ -2785,14 +2785,14 @@
       <c r="O22" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q22" s="23" t="s">
+      <c r="P22" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R22" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S22" s="23"/>
       <c r="T22" s="23"/>
@@ -2810,7 +2810,7 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+      <c r="A23" s="38"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H23" s="24" t="s">
@@ -2839,11 +2839,11 @@
       <c r="J23" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L23" s="23" t="s">
-        <v>10</v>
+      <c r="K23" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>104</v>
@@ -2854,14 +2854,14 @@
       <c r="O23" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P23" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q23" s="23" t="s">
-        <v>10</v>
+      <c r="P23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q23" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R23" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
@@ -2879,7 +2879,7 @@
       <c r="AF23" s="23"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
+      <c r="A24" s="38"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2892,7 +2892,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H24" s="24" t="s">
@@ -2902,13 +2902,13 @@
         <v>46</v>
       </c>
       <c r="J24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L24" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L24" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M24" s="23" t="s">
         <v>46</v>
@@ -2919,11 +2919,11 @@
       <c r="O24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q24" s="23" t="s">
-        <v>46</v>
+      <c r="P24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q24" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R24" s="23" t="s">
         <v>46</v>
@@ -2944,7 +2944,7 @@
       <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+      <c r="A25" s="38"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2957,7 +2957,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H25" s="24" t="s">
@@ -2967,12 +2967,12 @@
         <v>10</v>
       </c>
       <c r="J25" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L25" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L25" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M25" s="23" t="s">
@@ -2984,11 +2984,11 @@
       <c r="O25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P25" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q25" s="23" t="s">
-        <v>10</v>
+      <c r="P25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R25" s="23" t="s">
         <v>10</v>
@@ -3009,7 +3009,7 @@
       <c r="AF25" s="23"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3022,7 +3022,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H26" s="24" t="s">
@@ -3034,11 +3034,11 @@
       <c r="J26" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L26" s="23" t="s">
-        <v>10</v>
+      <c r="K26" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M26" s="23" t="s">
         <v>10</v>
@@ -3049,14 +3049,14 @@
       <c r="O26" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P26" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q26" s="23" t="s">
+      <c r="P26" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
@@ -3074,7 +3074,7 @@
       <c r="AF26" s="23"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3087,7 +3087,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H27" s="24" t="s">
@@ -3099,11 +3099,11 @@
       <c r="J27" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L27" s="23" t="s">
-        <v>10</v>
+      <c r="K27" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M27" s="23" t="s">
         <v>46</v>
@@ -3114,11 +3114,11 @@
       <c r="O27" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q27" s="23" t="s">
-        <v>46</v>
+      <c r="P27" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q27" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R27" s="23" t="s">
         <v>46</v>
@@ -3139,7 +3139,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3158,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H28" s="24" t="s">
@@ -3170,10 +3170,10 @@
       <c r="J28" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L28" s="23" t="s">
+      <c r="K28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M28" s="23" t="s">
@@ -3185,10 +3185,10 @@
       <c r="O28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q28" s="23" t="s">
+      <c r="P28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R28" s="23" t="s">
@@ -3210,7 +3210,7 @@
       <c r="AF28" s="23"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
+      <c r="A29" s="38"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3223,7 +3223,7 @@
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H29" s="24" t="s">
@@ -3233,13 +3233,13 @@
         <v>46</v>
       </c>
       <c r="J29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L29" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M29" s="23" t="s">
         <v>104</v>
@@ -3250,11 +3250,11 @@
       <c r="O29" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q29" s="23" t="s">
-        <v>10</v>
+      <c r="P29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R29" s="23" t="s">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       <c r="AF29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3288,7 +3288,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H30" s="24" t="s">
@@ -3300,10 +3300,10 @@
       <c r="J30" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L30" s="23" t="s">
+      <c r="K30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M30" s="23" t="s">
@@ -3315,10 +3315,10 @@
       <c r="O30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q30" s="23" t="s">
+      <c r="P30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R30" s="23" t="s">
@@ -3340,7 +3340,7 @@
       <c r="AF30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H31" s="24" t="s">
@@ -3365,11 +3365,11 @@
       <c r="J31" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L31" s="23" t="s">
-        <v>104</v>
+      <c r="K31" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L31" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M31" s="23" t="s">
         <v>46</v>
@@ -3380,10 +3380,10 @@
       <c r="O31" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q31" s="23" t="s">
+      <c r="P31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q31" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R31" s="23" t="s">
@@ -3405,7 +3405,7 @@
       <c r="AF31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
+      <c r="A32" s="38"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3418,7 +3418,7 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H32" s="24" t="s">
@@ -3428,13 +3428,13 @@
         <v>104</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K32" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L32" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="K32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L32" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M32" s="23" t="s">
         <v>104</v>
@@ -3445,11 +3445,11 @@
       <c r="O32" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q32" s="23" t="s">
-        <v>104</v>
+      <c r="P32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q32" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R32" s="23" t="s">
         <v>104</v>
@@ -3470,7 +3470,7 @@
       <c r="AF32" s="23"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3483,7 +3483,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H33" s="24" t="s">
@@ -3495,10 +3495,10 @@
       <c r="J33" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K33" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L33" s="23" t="s">
+      <c r="K33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L33" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M33" s="23" t="s">
@@ -3510,11 +3510,11 @@
       <c r="O33" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P33" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q33" s="23" t="s">
-        <v>104</v>
+      <c r="P33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q33" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R33" s="23" t="s">
         <v>104</v>
@@ -3535,7 +3535,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3547,11 +3547,15 @@
       <c r="D34" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
+      <c r="E34" s="12">
+        <v>2</v>
+      </c>
+      <c r="F34" s="12">
+        <v>2</v>
+      </c>
       <c r="G34" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
+        <f t="shared" si="1"/>
+        <v>E</v>
       </c>
       <c r="H34" s="24" t="s">
         <v>10</v>
@@ -3560,13 +3564,13 @@
         <v>104</v>
       </c>
       <c r="J34" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K34" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L34" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="K34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L34" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M34" s="23" t="s">
         <v>10</v>
@@ -3577,14 +3581,14 @@
       <c r="O34" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P34" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q34" s="23" t="s">
+      <c r="P34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R34" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S34" s="23"/>
       <c r="T34" s="23"/>
@@ -3602,7 +3606,7 @@
       <c r="AF34" s="23"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
+      <c r="A35" s="38"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3615,7 +3619,7 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H35" s="24" t="s">
@@ -3627,10 +3631,10 @@
       <c r="J35" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L35" s="23" t="s">
+      <c r="K35" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L35" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M35" s="23" t="s">
@@ -3642,14 +3646,14 @@
       <c r="O35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q35" s="23" t="s">
+      <c r="P35" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S35" s="23"/>
       <c r="T35" s="23"/>
@@ -3667,7 +3671,7 @@
       <c r="AF35" s="23"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
+      <c r="A36" s="38"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3680,7 +3684,7 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H36" s="24" t="s">
@@ -3690,13 +3694,13 @@
         <v>46</v>
       </c>
       <c r="J36" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K36" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L36" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="K36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L36" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M36" s="23" t="s">
         <v>46</v>
@@ -3707,10 +3711,10 @@
       <c r="O36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q36" s="23" t="s">
+      <c r="P36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q36" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R36" s="23" t="s">
@@ -3732,7 +3736,7 @@
       <c r="AF36" s="23"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
+      <c r="A37" s="38"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3745,7 +3749,7 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H37" s="24" t="s">
@@ -3757,10 +3761,10 @@
       <c r="J37" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L37" s="23" t="s">
+      <c r="K37" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M37" s="23" t="s">
@@ -3772,14 +3776,14 @@
       <c r="O37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q37" s="23" t="s">
+      <c r="P37" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R37" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S37" s="23"/>
       <c r="T37" s="23"/>
@@ -3797,7 +3801,7 @@
       <c r="AF37" s="23"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
+      <c r="A38" s="38"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3810,7 +3814,7 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H38" s="24" t="s">
@@ -3822,11 +3826,11 @@
       <c r="J38" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="K38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L38" s="23" t="s">
-        <v>46</v>
+      <c r="K38" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L38" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M38" s="23" t="s">
         <v>46</v>
@@ -3837,14 +3841,14 @@
       <c r="O38" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q38" s="23" t="s">
+      <c r="P38" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q38" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R38" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S38" s="23"/>
       <c r="T38" s="23"/>
@@ -3862,7 +3866,7 @@
       <c r="AF38" s="23"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="40"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3875,7 +3879,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H39" s="24" t="s">
@@ -3885,13 +3889,13 @@
         <v>10</v>
       </c>
       <c r="J39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L39" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="K39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L39" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M39" s="23" t="s">
         <v>104</v>
@@ -3902,14 +3906,14 @@
       <c r="O39" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q39" s="23" t="s">
+      <c r="P39" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R39" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S39" s="23"/>
       <c r="T39" s="23"/>
@@ -3927,7 +3931,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3942,7 +3946,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H40" s="24" t="s">
@@ -3954,10 +3958,10 @@
       <c r="J40" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L40" s="23" t="s">
+      <c r="K40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L40" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M40" s="23" t="s">
@@ -3969,11 +3973,11 @@
       <c r="O40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P40" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q40" s="23" t="s">
-        <v>46</v>
+      <c r="P40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q40" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R40" s="23" t="s">
         <v>46</v>
@@ -3994,7 +3998,7 @@
       <c r="AF40" s="23"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
+      <c r="A41" s="38"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4007,7 +4011,7 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H41" s="24" t="s">
@@ -4017,13 +4021,13 @@
         <v>46</v>
       </c>
       <c r="J41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K41" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L41" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="K41" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L41" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M41" s="23" t="s">
         <v>104</v>
@@ -4034,11 +4038,11 @@
       <c r="O41" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q41" s="23" t="s">
-        <v>46</v>
+      <c r="P41" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q41" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R41" s="23" t="s">
         <v>46</v>
@@ -4059,7 +4063,7 @@
       <c r="AF41" s="23"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4072,7 +4076,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H42" s="24" t="s">
@@ -4084,10 +4088,10 @@
       <c r="J42" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L42" s="23" t="s">
+      <c r="K42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M42" s="23" t="s">
@@ -4099,10 +4103,10 @@
       <c r="O42" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q42" s="23" t="s">
+      <c r="P42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R42" s="23" t="s">
@@ -4124,7 +4128,7 @@
       <c r="AF42" s="23"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
+      <c r="A43" s="38"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4137,7 +4141,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H43" s="24" t="s">
@@ -4149,11 +4153,11 @@
       <c r="J43" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K43" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L43" s="23" t="s">
-        <v>10</v>
+      <c r="K43" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L43" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M43" s="23" t="s">
         <v>104</v>
@@ -4164,11 +4168,11 @@
       <c r="O43" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q43" s="23" t="s">
-        <v>104</v>
+      <c r="P43" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q43" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R43" s="23" t="s">
         <v>104</v>
@@ -4189,7 +4193,7 @@
       <c r="AF43" s="23"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
+      <c r="A44" s="38"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4202,7 +4206,7 @@
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H44" s="24" t="s">
@@ -4214,10 +4218,10 @@
       <c r="J44" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K44" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L44" s="23" t="s">
+      <c r="K44" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L44" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M44" s="23" t="s">
@@ -4229,10 +4233,10 @@
       <c r="O44" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="23" t="s">
+      <c r="P44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R44" s="23" t="s">
@@ -4254,7 +4258,7 @@
       <c r="AF44" s="23"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="40"/>
+      <c r="A45" s="39"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4267,7 +4271,7 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H45" s="24" t="s">
@@ -4279,10 +4283,10 @@
       <c r="J45" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L45" s="23" t="s">
+      <c r="K45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M45" s="23" t="s">
@@ -4294,10 +4298,10 @@
       <c r="O45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q45" s="23" t="s">
+      <c r="P45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R45" s="23" t="s">
@@ -4319,7 +4323,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4334,7 +4338,7 @@
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H46" s="24" t="s">
@@ -4346,10 +4350,10 @@
       <c r="J46" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L46" s="23" t="s">
+      <c r="K46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M46" s="23" t="s">
@@ -4361,10 +4365,10 @@
       <c r="O46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q46" s="23" t="s">
+      <c r="P46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R46" s="23" t="s">
@@ -4386,7 +4390,7 @@
       <c r="AF46" s="23"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39"/>
+      <c r="A47" s="38"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4399,7 +4403,7 @@
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H47" s="24" t="s">
@@ -4411,10 +4415,10 @@
       <c r="J47" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L47" s="23" t="s">
+      <c r="K47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M47" s="23" t="s">
@@ -4426,10 +4430,10 @@
       <c r="O47" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q47" s="23" t="s">
+      <c r="P47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R47" s="23" t="s">
@@ -4451,7 +4455,7 @@
       <c r="AF47" s="23"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4464,7 +4468,7 @@
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H48" s="24" t="s">
@@ -4476,10 +4480,10 @@
       <c r="J48" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L48" s="23" t="s">
+      <c r="K48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M48" s="23" t="s">
@@ -4491,10 +4495,10 @@
       <c r="O48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q48" s="23" t="s">
+      <c r="P48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R48" s="23" t="s">
@@ -4516,7 +4520,7 @@
       <c r="AF48" s="23"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4529,7 +4533,7 @@
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H49" s="24" t="s">
@@ -4541,10 +4545,10 @@
       <c r="J49" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L49" s="23" t="s">
+      <c r="K49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M49" s="23" t="s">
@@ -4556,10 +4560,10 @@
       <c r="O49" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q49" s="23" t="s">
+      <c r="P49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R49" s="23" t="s">
@@ -4581,7 +4585,7 @@
       <c r="AF49" s="23"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4594,7 +4598,7 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H50" s="24" t="s">
@@ -4606,11 +4610,11 @@
       <c r="J50" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="K50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L50" s="23" t="s">
-        <v>104</v>
+      <c r="K50" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L50" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M50" s="23" t="s">
         <v>10</v>
@@ -4621,10 +4625,10 @@
       <c r="O50" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q50" s="23" t="s">
+      <c r="P50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R50" s="23" t="s">
@@ -4646,7 +4650,7 @@
       <c r="AF50" s="23"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4659,7 +4663,7 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H51" s="24" t="s">
@@ -4669,12 +4673,12 @@
         <v>104</v>
       </c>
       <c r="J51" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L51" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L51" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M51" s="23" t="s">
@@ -4686,10 +4690,10 @@
       <c r="O51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P51" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q51" s="23" t="s">
+      <c r="P51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q51" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R51" s="23" t="s">
@@ -4711,7 +4715,7 @@
       <c r="AF51" s="23"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="60" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4726,7 +4730,7 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15" t="str">
-        <f t="shared" ref="G52:G75" si="3">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
+        <f t="shared" ref="G52:G75" si="2">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
       <c r="H52" s="26" t="s">
@@ -4736,13 +4740,13 @@
         <v>10</v>
       </c>
       <c r="J52" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L52" s="25" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="K52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L52" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M52" s="25" t="s">
         <v>46</v>
@@ -4753,11 +4757,11 @@
       <c r="O52" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P52" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q52" s="25" t="s">
-        <v>46</v>
+      <c r="P52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q52" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="R52" s="25" t="s">
         <v>46</v>
@@ -4778,7 +4782,7 @@
       <c r="AF52" s="25"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
+      <c r="A53" s="61"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4791,7 +4795,7 @@
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H53" s="26" t="s">
@@ -4801,12 +4805,12 @@
         <v>104</v>
       </c>
       <c r="J53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K53" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L53" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="K53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L53" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M53" s="25" t="s">
@@ -4818,10 +4822,10 @@
       <c r="O53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q53" s="25" t="s">
+      <c r="P53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q53" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R53" s="25" t="s">
@@ -4843,7 +4847,7 @@
       <c r="AF53" s="25"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4856,7 +4860,7 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H54" s="26" t="s">
@@ -4868,10 +4872,10 @@
       <c r="J54" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L54" s="25" t="s">
+      <c r="K54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M54" s="25" t="s">
@@ -4883,10 +4887,10 @@
       <c r="O54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q54" s="25" t="s">
+      <c r="P54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R54" s="25" t="s">
@@ -4908,7 +4912,7 @@
       <c r="AF54" s="25"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4921,7 +4925,7 @@
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H55" s="26" t="s">
@@ -4931,13 +4935,13 @@
         <v>10</v>
       </c>
       <c r="J55" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L55" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="K55" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L55" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M55" s="25" t="s">
         <v>46</v>
@@ -4948,14 +4952,14 @@
       <c r="O55" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P55" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q55" s="25" t="s">
-        <v>10</v>
+      <c r="P55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q55" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="R55" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S55" s="25"/>
       <c r="T55" s="25"/>
@@ -4974,7 +4978,7 @@
       <c r="AK55" s="31"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -4987,7 +4991,7 @@
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H56" s="26" t="s">
@@ -4999,11 +5003,11 @@
       <c r="J56" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="K56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L56" s="25" t="s">
-        <v>46</v>
+      <c r="K56" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L56" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M56" s="25" t="s">
         <v>104</v>
@@ -5014,11 +5018,11 @@
       <c r="O56" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q56" s="25" t="s">
-        <v>104</v>
+      <c r="P56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q56" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="R56" s="25" t="s">
         <v>104</v>
@@ -5039,7 +5043,7 @@
       <c r="AF56" s="25"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="47"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5052,7 +5056,7 @@
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H57" s="26" t="s">
@@ -5062,13 +5066,13 @@
         <v>46</v>
       </c>
       <c r="J57" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K57" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L57" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="K57" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L57" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="M57" s="25" t="s">
         <v>46</v>
@@ -5079,14 +5083,14 @@
       <c r="O57" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P57" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q57" s="25" t="s">
+      <c r="P57" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q57" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R57" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S57" s="25"/>
       <c r="T57" s="25"/>
@@ -5104,7 +5108,7 @@
       <c r="AF57" s="25"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48" t="s">
+      <c r="A58" s="63" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5119,7 +5123,7 @@
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
       <c r="G58" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H58" s="26" t="s">
@@ -5131,10 +5135,10 @@
       <c r="J58" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L58" s="25" t="s">
+      <c r="K58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M58" s="25" t="s">
@@ -5146,10 +5150,10 @@
       <c r="O58" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q58" s="25" t="s">
+      <c r="P58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R58" s="25" t="s">
@@ -5171,7 +5175,7 @@
       <c r="AF58" s="25"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="49"/>
+      <c r="A59" s="64"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5184,7 +5188,7 @@
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H59" s="26" t="s">
@@ -5196,10 +5200,10 @@
       <c r="J59" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L59" s="25" t="s">
+      <c r="K59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L59" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M59" s="25" t="s">
@@ -5211,11 +5215,11 @@
       <c r="O59" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P59" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q59" s="25" t="s">
-        <v>46</v>
+      <c r="P59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q59" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="R59" s="25" t="s">
         <v>46</v>
@@ -5236,7 +5240,7 @@
       <c r="AF59" s="25"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="49"/>
+      <c r="A60" s="64"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5249,7 +5253,7 @@
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H60" s="26" t="s">
@@ -5259,12 +5263,12 @@
         <v>46</v>
       </c>
       <c r="J60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K60" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="L60" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="K60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M60" s="25" t="s">
@@ -5276,10 +5280,10 @@
       <c r="O60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q60" s="25" t="s">
+      <c r="P60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R60" s="25" t="s">
@@ -5301,7 +5305,7 @@
       <c r="AF60" s="25"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+      <c r="A61" s="64"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5314,7 +5318,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H61" s="26" t="s">
@@ -5324,13 +5328,13 @@
         <v>104</v>
       </c>
       <c r="J61" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="K61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L61" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="K61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L61" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="M61" s="25" t="s">
         <v>10</v>
@@ -5341,11 +5345,11 @@
       <c r="O61" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q61" s="25" t="s">
-        <v>104</v>
+      <c r="P61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q61" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="R61" s="25" t="s">
         <v>104</v>
@@ -5366,7 +5370,7 @@
       <c r="AF61" s="25"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="49"/>
+      <c r="A62" s="64"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5379,7 +5383,7 @@
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H62" s="26" t="s">
@@ -5391,10 +5395,10 @@
       <c r="J62" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="K62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L62" s="25" t="s">
+      <c r="K62" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L62" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M62" s="25" t="s">
@@ -5406,14 +5410,14 @@
       <c r="O62" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P62" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q62" s="25" t="s">
-        <v>104</v>
+      <c r="P62" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q62" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="R62" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S62" s="25"/>
       <c r="T62" s="25"/>
@@ -5431,7 +5435,7 @@
       <c r="AF62" s="25"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="50"/>
+      <c r="A63" s="65"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5444,7 +5448,7 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H63" s="26" t="s">
@@ -5456,10 +5460,10 @@
       <c r="J63" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="K63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L63" s="25" t="s">
+      <c r="K63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M63" s="25" t="s">
@@ -5471,10 +5475,10 @@
       <c r="O63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q63" s="25" t="s">
+      <c r="P63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R63" s="25" t="s">
@@ -5496,7 +5500,7 @@
       <c r="AF63" s="25"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="51" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5511,7 +5515,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H64" s="26" t="s">
@@ -5523,10 +5527,10 @@
       <c r="J64" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L64" s="25" t="s">
+      <c r="K64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M64" s="25" t="s">
@@ -5538,10 +5542,10 @@
       <c r="O64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q64" s="25" t="s">
+      <c r="P64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R64" s="25" t="s">
@@ -5563,7 +5567,7 @@
       <c r="AF64" s="25"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5576,7 +5580,7 @@
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H65" s="26" t="s">
@@ -5588,10 +5592,10 @@
       <c r="J65" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="K65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L65" s="25" t="s">
+      <c r="K65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M65" s="25" t="s">
@@ -5603,10 +5607,10 @@
       <c r="O65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q65" s="25" t="s">
+      <c r="P65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R65" s="25" t="s">
@@ -5628,7 +5632,7 @@
       <c r="AF65" s="25"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5641,7 +5645,7 @@
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H66" s="26" t="s">
@@ -5653,10 +5657,10 @@
       <c r="J66" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L66" s="25" t="s">
+      <c r="K66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M66" s="25" t="s">
@@ -5668,10 +5672,10 @@
       <c r="O66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q66" s="25" t="s">
+      <c r="P66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R66" s="25" t="s">
@@ -5693,7 +5697,7 @@
       <c r="AF66" s="25"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5706,7 +5710,7 @@
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H67" s="26" t="s">
@@ -5718,11 +5722,11 @@
       <c r="J67" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L67" s="25" t="s">
-        <v>104</v>
+      <c r="K67" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L67" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="M67" s="25" t="s">
         <v>46</v>
@@ -5733,10 +5737,10 @@
       <c r="O67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q67" s="25" t="s">
+      <c r="P67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q67" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R67" s="25" t="s">
@@ -5758,7 +5762,7 @@
       <c r="AF67" s="25"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5771,7 +5775,7 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H68" s="26" t="s">
@@ -5781,13 +5785,13 @@
         <v>10</v>
       </c>
       <c r="J68" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K68" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="L68" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="K68" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L68" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M68" s="25" t="s">
         <v>104</v>
@@ -5798,14 +5802,14 @@
       <c r="O68" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P68" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q68" s="25" t="s">
-        <v>104</v>
+      <c r="P68" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q68" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="R68" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S68" s="25"/>
       <c r="T68" s="25"/>
@@ -5823,7 +5827,7 @@
       <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="34"/>
+      <c r="A69" s="53"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5836,7 +5840,7 @@
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H69" s="26" t="s">
@@ -5848,11 +5852,11 @@
       <c r="J69" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="K69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L69" s="25" t="s">
-        <v>46</v>
+      <c r="K69" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L69" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M69" s="25" t="s">
         <v>10</v>
@@ -5863,11 +5867,11 @@
       <c r="O69" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P69" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q69" s="25" t="s">
-        <v>10</v>
+      <c r="P69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q69" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="R69" s="25" t="s">
         <v>10</v>
@@ -5888,7 +5892,7 @@
       <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="54" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5903,7 +5907,7 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
       <c r="G70" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H70" s="26" t="s">
@@ -5915,11 +5919,11 @@
       <c r="J70" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K70" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L70" s="25" t="s">
-        <v>10</v>
+      <c r="K70" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L70" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="M70" s="25" t="s">
         <v>10</v>
@@ -5930,14 +5934,14 @@
       <c r="O70" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P70" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q70" s="25" t="s">
-        <v>10</v>
+      <c r="P70" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q70" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="R70" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S70" s="25"/>
       <c r="T70" s="25"/>
@@ -5955,7 +5959,7 @@
       <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
+      <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5968,7 +5972,7 @@
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
       <c r="G71" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H71" s="26" t="s">
@@ -5980,11 +5984,11 @@
       <c r="J71" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="K71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L71" s="25" t="s">
-        <v>10</v>
+      <c r="K71" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L71" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M71" s="25" t="s">
         <v>10</v>
@@ -5995,14 +5999,14 @@
       <c r="O71" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P71" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q71" s="25" t="s">
-        <v>46</v>
+      <c r="P71" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q71" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="R71" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="S71" s="25"/>
       <c r="T71" s="25"/>
@@ -6020,7 +6024,7 @@
       <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
+      <c r="A72" s="55"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6033,7 +6037,7 @@
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
       <c r="G72" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H72" s="26" t="s">
@@ -6045,10 +6049,10 @@
       <c r="J72" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L72" s="25" t="s">
+      <c r="K72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M72" s="25" t="s">
@@ -6060,10 +6064,10 @@
       <c r="O72" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q72" s="25" t="s">
+      <c r="P72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R72" s="25" t="s">
@@ -6085,7 +6089,7 @@
       <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
+      <c r="A73" s="55"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6098,7 +6102,7 @@
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H73" s="26" t="s">
@@ -6108,12 +6112,12 @@
         <v>104</v>
       </c>
       <c r="J73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K73" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L73" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="K73" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L73" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M73" s="25" t="s">
@@ -6125,14 +6129,14 @@
       <c r="O73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P73" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q73" s="25" t="s">
-        <v>104</v>
+      <c r="P73" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q73" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="R73" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S73" s="25"/>
       <c r="T73" s="25"/>
@@ -6150,7 +6154,7 @@
       <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
+      <c r="A74" s="55"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6163,7 +6167,7 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H74" s="26" t="s">
@@ -6173,13 +6177,13 @@
         <v>10</v>
       </c>
       <c r="J74" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L74" s="25" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="K74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L74" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="M74" s="25" t="s">
         <v>104</v>
@@ -6190,10 +6194,10 @@
       <c r="O74" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q74" s="25" t="s">
+      <c r="P74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R74" s="25" t="s">
@@ -6215,7 +6219,7 @@
       <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="56"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6228,7 +6232,7 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H75" s="26" t="s">
@@ -6238,12 +6242,12 @@
         <v>104</v>
       </c>
       <c r="J75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K75" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="L75" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="K75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L75" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M75" s="25" t="s">
@@ -6255,14 +6259,14 @@
       <c r="O75" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q75" s="25" t="s">
+      <c r="P75" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q75" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R75" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S75" s="25"/>
       <c r="T75" s="25"/>
@@ -6283,14 +6287,14 @@
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="41" t="s">
+      <c r="D76" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="42"/>
-      <c r="F76" s="43"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6299,13 +6303,13 @@
         <v>186</v>
       </c>
       <c r="J76" s="26">
+        <v>201</v>
+      </c>
+      <c r="K76" s="25">
+        <v>222</v>
+      </c>
+      <c r="L76" s="26">
         <v>185</v>
-      </c>
-      <c r="K76" s="26">
-        <v>201</v>
-      </c>
-      <c r="L76" s="25">
-        <v>222</v>
       </c>
       <c r="M76" s="25">
         <v>172</v>
@@ -6316,14 +6320,14 @@
       <c r="O76" s="25">
         <v>190</v>
       </c>
-      <c r="P76" s="26">
+      <c r="P76" s="25">
+        <v>169</v>
+      </c>
+      <c r="Q76" s="26">
         <v>180</v>
       </c>
-      <c r="Q76" s="25">
+      <c r="R76" s="25">
         <v>197</v>
-      </c>
-      <c r="R76" s="25">
-        <v>169</v>
       </c>
       <c r="S76" s="25"/>
       <c r="T76" s="25"/>
@@ -6344,111 +6348,111 @@
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="44" t="s">
+      <c r="D77" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="43"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="34"/>
       <c r="H77" s="28">
-        <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
+        <f>SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(I78:I81)</f>
         <v>0</v>
       </c>
       <c r="J77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(J78:J81)</f>
         <v>0</v>
       </c>
       <c r="K77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(K78:K81)</f>
         <v>0</v>
       </c>
       <c r="L77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(L78:L81)</f>
         <v>0</v>
       </c>
       <c r="M77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(M78:M81)</f>
         <v>0</v>
       </c>
       <c r="N77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(N78:N81)</f>
         <v>0</v>
       </c>
       <c r="O77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(O78:O81)</f>
         <v>0</v>
       </c>
       <c r="P77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(P78:P81)</f>
         <v>0</v>
       </c>
       <c r="Q77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(Q78:Q81)</f>
         <v>0</v>
       </c>
       <c r="R77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(R78:R81)</f>
         <v>0</v>
       </c>
       <c r="S77" s="28">
-        <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
-        <v>73</v>
+        <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
+        <v>69</v>
       </c>
       <c r="T77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="U77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="V77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="W77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="X77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="Y77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="Z77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="AA77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="AB77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="AC77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="AD77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="AE77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="AF77" s="28">
-        <f t="shared" si="5"/>
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6460,104 +6464,104 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="6">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="6"/>
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6569,103 +6573,103 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="7">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -6678,103 +6682,103 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="8">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -6787,103 +6791,103 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="9">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7755,6 +7759,13 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7766,13 +7777,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -842,58 +842,11 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -901,6 +854,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -933,6 +888,51 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1272,15 +1272,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1358,17 +1358,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="65"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
@@ -1430,10 +1430,10 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="53"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
@@ -1539,7 +1539,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="37" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1610,7 +1610,7 @@
       <c r="AF4" s="23"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="AF5" s="23"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
+      <c r="A6" s="38"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1744,7 +1744,7 @@
       <c r="AF6" s="23"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="AF7" s="23"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1874,7 +1874,7 @@
       <c r="AF8" s="23"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+      <c r="A9" s="39"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -2010,7 +2010,7 @@
       <c r="AF10" s="23"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2079,7 +2079,7 @@
       <c r="AF11" s="23"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2144,7 +2144,7 @@
       <c r="AF12" s="23"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="AF13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="AF14" s="23"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2339,7 +2339,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="45" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2410,7 +2410,7 @@
       <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2479,7 +2479,7 @@
       <c r="AF17" s="23"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2544,7 +2544,7 @@
       <c r="AF18" s="23"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2609,7 +2609,7 @@
       <c r="AF19" s="23"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2674,7 +2674,7 @@
       <c r="AF20" s="23"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2739,7 +2739,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="42" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2810,7 +2810,7 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+      <c r="A23" s="38"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2879,7 +2879,7 @@
       <c r="AF23" s="23"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
+      <c r="A24" s="38"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2944,7 +2944,7 @@
       <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+      <c r="A25" s="38"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -3009,7 +3009,7 @@
       <c r="AF25" s="23"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3074,7 +3074,7 @@
       <c r="AF26" s="23"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3139,7 +3139,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3210,7 +3210,7 @@
       <c r="AF28" s="23"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
+      <c r="A29" s="38"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="AF29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3344,7 +3344,7 @@
       <c r="AF30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3409,7 +3409,7 @@
       <c r="AF31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
+      <c r="A32" s="38"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3474,7 +3474,7 @@
       <c r="AF32" s="23"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3539,7 +3539,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3610,7 +3610,7 @@
       <c r="AF34" s="23"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
+      <c r="A35" s="38"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3675,7 +3675,7 @@
       <c r="AF35" s="23"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
+      <c r="A36" s="38"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3740,7 +3740,7 @@
       <c r="AF36" s="23"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
+      <c r="A37" s="38"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3805,7 +3805,7 @@
       <c r="AF37" s="23"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
+      <c r="A38" s="38"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3870,7 +3870,7 @@
       <c r="AF38" s="23"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="40"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3935,7 +3935,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -4002,7 +4002,7 @@
       <c r="AF40" s="23"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
+      <c r="A41" s="38"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4067,7 +4067,7 @@
       <c r="AF41" s="23"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4132,7 +4132,7 @@
       <c r="AF42" s="23"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
+      <c r="A43" s="38"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4197,7 +4197,7 @@
       <c r="AF43" s="23"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
+      <c r="A44" s="38"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4262,7 +4262,7 @@
       <c r="AF44" s="23"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="40"/>
+      <c r="A45" s="39"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4327,7 +4327,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4394,7 +4394,7 @@
       <c r="AF46" s="23"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39"/>
+      <c r="A47" s="38"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4459,7 +4459,7 @@
       <c r="AF47" s="23"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="AF48" s="23"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4589,7 +4589,7 @@
       <c r="AF49" s="23"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4654,7 +4654,7 @@
       <c r="AF50" s="23"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4719,7 +4719,7 @@
       <c r="AF51" s="23"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="60" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4786,7 +4786,7 @@
       <c r="AF52" s="25"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
+      <c r="A53" s="61"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4851,7 +4851,7 @@
       <c r="AF53" s="25"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4916,7 +4916,7 @@
       <c r="AF54" s="25"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4982,7 +4982,7 @@
       <c r="AK55" s="31"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5047,7 +5047,7 @@
       <c r="AF56" s="25"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="47"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5112,7 +5112,7 @@
       <c r="AF57" s="25"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48" t="s">
+      <c r="A58" s="63" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5179,7 +5179,7 @@
       <c r="AF58" s="25"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="49"/>
+      <c r="A59" s="64"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5244,7 +5244,7 @@
       <c r="AF59" s="25"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="49"/>
+      <c r="A60" s="64"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5309,7 +5309,7 @@
       <c r="AF60" s="25"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+      <c r="A61" s="64"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5374,7 +5374,7 @@
       <c r="AF61" s="25"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="49"/>
+      <c r="A62" s="64"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5439,7 +5439,7 @@
       <c r="AF62" s="25"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="50"/>
+      <c r="A63" s="65"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5504,7 +5504,7 @@
       <c r="AF63" s="25"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="51" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5571,7 +5571,7 @@
       <c r="AF64" s="25"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5636,7 +5636,7 @@
       <c r="AF65" s="25"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5701,7 +5701,7 @@
       <c r="AF66" s="25"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5766,7 +5766,7 @@
       <c r="AF67" s="25"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5831,7 +5831,7 @@
       <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="34"/>
+      <c r="A69" s="53"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5896,7 +5896,7 @@
       <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="54" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5963,7 +5963,7 @@
       <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
+      <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6028,7 +6028,7 @@
       <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
+      <c r="A72" s="55"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6093,7 +6093,7 @@
       <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
+      <c r="A73" s="55"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6158,7 +6158,7 @@
       <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
+      <c r="A74" s="55"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6223,7 +6223,7 @@
       <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="56"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6291,11 +6291,11 @@
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="41" t="s">
+      <c r="D76" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="42"/>
-      <c r="F76" s="43"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
         <v>34</v>
@@ -6352,12 +6352,12 @@
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="44" t="s">
+      <c r="D77" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="43"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="34"/>
       <c r="H77" s="28">
         <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
         <v>0</v>
@@ -7763,6 +7763,13 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7774,13 +7781,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="772" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FA3B9F-65DB-43FC-9057-3D547343C990}"/>
+  <xr:revisionPtr revIDLastSave="774" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{347B884D-3869-4E25-8178-22204B9CB31A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1438,103 +1438,103 @@
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <f t="shared" ref="H3:R3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
         <v>8</v>
       </c>
       <c r="I3" s="14">
-        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="J3" s="14">
-        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="K3" s="14">
-        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="L3" s="14">
-        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="M3" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N3" s="14">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M3" s="14">
-        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
-        <v>6</v>
-      </c>
-      <c r="N3" s="14">
-        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+      <c r="O3" s="14">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O3" s="14">
-        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
+      <c r="P3" s="14">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="P3" s="14">
-        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
+      <c r="Q3" s="14">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q3" s="14">
-        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
+      <c r="R3" s="14">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="R3" s="14">
-        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
-        <v>4</v>
-      </c>
       <c r="S3" s="14">
-        <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
+        <f t="shared" ref="S3:AF3" si="1">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="T3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
+        <f t="shared" ref="G4:G51" si="2">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
         <v>L</v>
       </c>
       <c r="H4" s="24" t="s">
@@ -1627,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H5" s="24" t="s">
@@ -1692,7 +1692,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H6" s="24" t="s">
@@ -1757,7 +1757,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -1822,7 +1822,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H8" s="24" t="s">
@@ -1887,7 +1887,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H9" s="24" t="s">
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H10" s="24" t="s">
@@ -2027,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H11" s="24" t="s">
@@ -2092,7 +2092,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H12" s="24" t="s">
@@ -2157,7 +2157,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H13" s="24" t="s">
@@ -2222,7 +2222,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H14" s="24" t="s">
@@ -2287,7 +2287,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -2358,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H16" s="24" t="s">
@@ -2427,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>V</v>
       </c>
       <c r="H17" s="24" t="s">
@@ -2492,7 +2492,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H18" s="24" t="s">
@@ -2557,7 +2557,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H19" s="24" t="s">
@@ -2622,7 +2622,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H20" s="24" t="s">
@@ -2687,7 +2687,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H21" s="24" t="s">
@@ -2758,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H22" s="24" t="s">
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H23" s="24" t="s">
@@ -2892,7 +2892,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H24" s="24" t="s">
@@ -2957,7 +2957,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H25" s="24" t="s">
@@ -3022,7 +3022,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H26" s="24" t="s">
@@ -3087,7 +3087,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H27" s="24" t="s">
@@ -3158,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H28" s="24" t="s">
@@ -3220,11 +3220,15 @@
       <c r="D29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="E29" s="11">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11">
+        <v>2</v>
+      </c>
       <c r="G29" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+        <f t="shared" si="2"/>
+        <v>V</v>
       </c>
       <c r="H29" s="24" t="s">
         <v>10</v>
@@ -3288,7 +3292,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H30" s="24" t="s">
@@ -3353,7 +3357,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H31" s="24" t="s">
@@ -3418,7 +3422,7 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H32" s="24" t="s">
@@ -3483,7 +3487,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H33" s="24" t="s">
@@ -3554,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H34" s="24" t="s">
@@ -3619,7 +3623,7 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H35" s="24" t="s">
@@ -3684,7 +3688,7 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H36" s="24" t="s">
@@ -3749,7 +3753,7 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H37" s="24" t="s">
@@ -3814,7 +3818,7 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H38" s="24" t="s">
@@ -3879,7 +3883,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H39" s="24" t="s">
@@ -3946,7 +3950,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H40" s="24" t="s">
@@ -4011,7 +4015,7 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H41" s="24" t="s">
@@ -4076,7 +4080,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H42" s="24" t="s">
@@ -4141,7 +4145,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H43" s="24" t="s">
@@ -4206,7 +4210,7 @@
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H44" s="24" t="s">
@@ -4271,7 +4275,7 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H45" s="24" t="s">
@@ -4338,7 +4342,7 @@
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H46" s="24" t="s">
@@ -4403,7 +4407,7 @@
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H47" s="24" t="s">
@@ -4468,7 +4472,7 @@
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H48" s="24" t="s">
@@ -4533,7 +4537,7 @@
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H49" s="24" t="s">
@@ -4598,7 +4602,7 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H50" s="24" t="s">
@@ -4663,7 +4667,7 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H51" s="24" t="s">
@@ -4730,7 +4734,7 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15" t="str">
-        <f t="shared" ref="G52:G75" si="2">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
+        <f t="shared" ref="G52:G75" si="3">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
       <c r="H52" s="26" t="s">
@@ -4795,7 +4799,7 @@
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H53" s="26" t="s">
@@ -4860,7 +4864,7 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H54" s="26" t="s">
@@ -4925,7 +4929,7 @@
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H55" s="26" t="s">
@@ -4991,7 +4995,7 @@
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H56" s="26" t="s">
@@ -5056,7 +5060,7 @@
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H57" s="26" t="s">
@@ -5123,7 +5127,7 @@
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
       <c r="G58" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H58" s="26" t="s">
@@ -5188,7 +5192,7 @@
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H59" s="26" t="s">
@@ -5253,7 +5257,7 @@
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H60" s="26" t="s">
@@ -5318,7 +5322,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H61" s="26" t="s">
@@ -5383,7 +5387,7 @@
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H62" s="26" t="s">
@@ -5448,7 +5452,7 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H63" s="26" t="s">
@@ -5515,7 +5519,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H64" s="26" t="s">
@@ -5580,7 +5584,7 @@
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H65" s="26" t="s">
@@ -5645,7 +5649,7 @@
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H66" s="26" t="s">
@@ -5710,7 +5714,7 @@
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H67" s="26" t="s">
@@ -5775,7 +5779,7 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H68" s="26" t="s">
@@ -5840,7 +5844,7 @@
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H69" s="26" t="s">
@@ -5907,7 +5911,7 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
       <c r="G70" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H70" s="26" t="s">
@@ -5972,7 +5976,7 @@
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
       <c r="G71" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H71" s="26" t="s">
@@ -6037,7 +6041,7 @@
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
       <c r="G72" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H72" s="26" t="s">
@@ -6102,7 +6106,7 @@
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H73" s="26" t="s">
@@ -6167,7 +6171,7 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H74" s="26" t="s">
@@ -6232,7 +6236,7 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H75" s="26" t="s">
@@ -6294,7 +6298,7 @@
       <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6355,104 +6359,104 @@
       <c r="F77" s="33"/>
       <c r="G77" s="34"/>
       <c r="H77" s="28">
-        <f>SUM(H78:H81)</f>
+        <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
-        <f>SUM(I78:I81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J77" s="28">
-        <f>SUM(J78:J81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K77" s="28">
-        <f>SUM(K78:K81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L77" s="28">
-        <f>SUM(L78:L81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M77" s="28">
-        <f>SUM(M78:M81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N77" s="28">
-        <f>SUM(N78:N81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O77" s="28">
-        <f>SUM(O78:O81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P77" s="28">
-        <f>SUM(P78:P81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q77" s="28">
-        <f>SUM(Q78:Q81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R77" s="28">
-        <f>SUM(R78:R81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S77" s="28">
-        <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
-        <v>69</v>
+        <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
+        <v>66</v>
       </c>
       <c r="T77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="U77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="V77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="W77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="X77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="Y77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="Z77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="AA77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="AB77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="AC77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="AD77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="AE77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
       <c r="AF77" s="28">
-        <f t="shared" si="3"/>
-        <v>69</v>
+        <f t="shared" si="5"/>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6464,104 +6468,104 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="6">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="4"/>
-        <v>69</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6573,104 +6577,104 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="7">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6682,103 +6686,103 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="8">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -6791,103 +6795,103 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="9">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="774" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{347B884D-3869-4E25-8178-22204B9CB31A}"/>
+  <xr:revisionPtr revIDLastSave="780" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E98E93CE-030E-4543-B6F3-FF4E69C4C62E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -842,11 +842,58 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -854,8 +901,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -888,51 +933,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1272,15 +1272,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1358,17 +1358,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="65"/>
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
@@ -1430,10 +1430,10 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="36"/>
+      <c r="F3" s="53"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
@@ -1455,15 +1455,15 @@
       </c>
       <c r="L3" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O3" s="14">
         <f t="shared" si="0"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Q3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" s="14">
         <f t="shared" si="0"/>
@@ -1539,7 +1539,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="54" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1610,7 +1610,7 @@
       <c r="AF4" s="23"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="38"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="AF5" s="23"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1744,7 +1744,7 @@
       <c r="AF6" s="23"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="AF7" s="23"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="38"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1874,7 +1874,7 @@
       <c r="AF8" s="23"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="59" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -2010,7 +2010,7 @@
       <c r="AF10" s="23"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="38"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2079,7 +2079,7 @@
       <c r="AF11" s="23"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="38"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2144,7 +2144,7 @@
       <c r="AF12" s="23"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="AF13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+      <c r="A14" s="39"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="AF14" s="23"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="39"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2339,7 +2339,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="60" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2410,7 +2410,7 @@
       <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2479,7 +2479,7 @@
       <c r="AF17" s="23"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2544,7 +2544,7 @@
       <c r="AF18" s="23"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="38"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2609,7 +2609,7 @@
       <c r="AF19" s="23"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="38"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2674,7 +2674,7 @@
       <c r="AF20" s="23"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2739,7 +2739,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="57" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2810,7 +2810,7 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2879,7 +2879,7 @@
       <c r="AF23" s="23"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2944,7 +2944,7 @@
       <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="38"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -3009,7 +3009,7 @@
       <c r="AF25" s="23"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3074,7 +3074,7 @@
       <c r="AF26" s="23"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3139,7 +3139,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="58" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3210,7 +3210,7 @@
       <c r="AF28" s="23"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="38"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3220,15 +3220,11 @@
       <c r="D29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="11">
-        <v>1</v>
-      </c>
-      <c r="F29" s="11">
-        <v>2</v>
-      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>V</v>
+        <v>-</v>
       </c>
       <c r="H29" s="24" t="s">
         <v>10</v>
@@ -3279,7 +3275,7 @@
       <c r="AF29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3344,7 +3340,7 @@
       <c r="AF30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="38"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3409,7 +3405,7 @@
       <c r="AF31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="38"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3474,7 +3470,7 @@
       <c r="AF32" s="23"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="39"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3539,7 +3535,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="56" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3610,7 +3606,7 @@
       <c r="AF34" s="23"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="38"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3675,7 +3671,7 @@
       <c r="AF35" s="23"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="38"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3740,7 +3736,7 @@
       <c r="AF36" s="23"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="38"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3805,7 +3801,7 @@
       <c r="AF37" s="23"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="38"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3870,7 +3866,7 @@
       <c r="AF38" s="23"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="39"/>
+      <c r="A39" s="40"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3935,7 +3931,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="55" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -4002,7 +3998,7 @@
       <c r="AF40" s="23"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="38"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4067,7 +4063,7 @@
       <c r="AF41" s="23"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="38"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4132,7 +4128,7 @@
       <c r="AF42" s="23"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="38"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4197,7 +4193,7 @@
       <c r="AF43" s="23"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="38"/>
+      <c r="A44" s="39"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4262,7 +4258,7 @@
       <c r="AF44" s="23"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="39"/>
+      <c r="A45" s="40"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4327,7 +4323,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="57" t="s">
+      <c r="A46" s="38" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4394,7 +4390,7 @@
       <c r="AF46" s="23"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="38"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4459,7 +4455,7 @@
       <c r="AF47" s="23"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4524,7 +4520,7 @@
       <c r="AF48" s="23"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="38"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4589,7 +4585,7 @@
       <c r="AF49" s="23"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4654,7 +4650,7 @@
       <c r="AF50" s="23"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="39"/>
+      <c r="A51" s="40"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4719,7 +4715,7 @@
       <c r="AF51" s="23"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="45" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4786,7 +4782,7 @@
       <c r="AF52" s="25"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="61"/>
+      <c r="A53" s="46"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4851,7 +4847,7 @@
       <c r="AF53" s="25"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="61"/>
+      <c r="A54" s="46"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4916,7 +4912,7 @@
       <c r="AF54" s="25"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="61"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4982,7 +4978,7 @@
       <c r="AK55" s="31"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="61"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5047,7 +5043,7 @@
       <c r="AF56" s="25"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="62"/>
+      <c r="A57" s="47"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5112,7 +5108,7 @@
       <c r="AF57" s="25"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="48" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5179,7 +5175,7 @@
       <c r="AF58" s="25"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="64"/>
+      <c r="A59" s="49"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5244,7 +5240,7 @@
       <c r="AF59" s="25"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="64"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5309,7 +5305,7 @@
       <c r="AF60" s="25"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="64"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5374,7 +5370,7 @@
       <c r="AF61" s="25"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="64"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5439,7 +5435,7 @@
       <c r="AF62" s="25"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="65"/>
+      <c r="A63" s="50"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5504,7 +5500,7 @@
       <c r="AF63" s="25"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="51" t="s">
+      <c r="A64" s="32" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5571,7 +5567,7 @@
       <c r="AF64" s="25"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="52"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5636,7 +5632,7 @@
       <c r="AF65" s="25"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="52"/>
+      <c r="A66" s="33"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5701,7 +5697,7 @@
       <c r="AF66" s="25"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="52"/>
+      <c r="A67" s="33"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5766,7 +5762,7 @@
       <c r="AF67" s="25"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="52"/>
+      <c r="A68" s="33"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5831,7 +5827,7 @@
       <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="53"/>
+      <c r="A69" s="34"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5896,7 +5892,7 @@
       <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="54" t="s">
+      <c r="A70" s="35" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5963,7 +5959,7 @@
       <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
+      <c r="A71" s="36"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6028,7 +6024,7 @@
       <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="55"/>
+      <c r="A72" s="36"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6093,7 +6089,7 @@
       <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="55"/>
+      <c r="A73" s="36"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6158,7 +6154,7 @@
       <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="55"/>
+      <c r="A74" s="36"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6223,7 +6219,7 @@
       <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="56"/>
+      <c r="A75" s="37"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6291,14 +6287,14 @@
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="58" t="s">
+      <c r="D76" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="33"/>
-      <c r="F76" s="34"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="43"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6352,12 +6348,12 @@
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="59" t="s">
+      <c r="D77" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="34"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="43"/>
       <c r="H77" s="28">
         <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
         <v>0</v>
@@ -6404,59 +6400,59 @@
       </c>
       <c r="S77" s="28">
         <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="T77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="V77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="W77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Y77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Z77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AB77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AC77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AD77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AE77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AF77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6513,59 +6509,59 @@
       </c>
       <c r="S78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6622,59 +6618,59 @@
       </c>
       <c r="S79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="T79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="U79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="V79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="W79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="X79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Z79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AA79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AB79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AC79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AD79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AE79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AF79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -7763,13 +7759,6 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7781,6 +7770,13 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="774" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{347B884D-3869-4E25-8178-22204B9CB31A}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A4B4EDA-FF16-4029-9588-22B038EC5556}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -377,13 +377,13 @@
     <t>JORGE</t>
   </si>
   <si>
-    <t>Ivan</t>
-  </si>
-  <si>
     <t>Armandin</t>
   </si>
   <si>
     <t>Brenda</t>
+  </si>
+  <si>
+    <t>Ivan</t>
   </si>
 </sst>
 </file>
@@ -842,11 +842,58 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -854,8 +901,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -889,51 +934,6 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,10 +963,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1272,15 +1268,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1358,22 +1354,22 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="65"/>
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J2" s="30" t="s">
         <v>108</v>
@@ -1391,7 +1387,7 @@
         <v>109</v>
       </c>
       <c r="O2" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P2" s="29" t="s">
         <v>112</v>
@@ -1400,7 +1396,7 @@
         <v>105</v>
       </c>
       <c r="R2" s="29" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S2" s="29"/>
       <c r="T2" s="29"/>
@@ -1430,10 +1426,10 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="36"/>
+      <c r="F3" s="53"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
@@ -1455,15 +1451,15 @@
       </c>
       <c r="L3" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O3" s="14">
         <f t="shared" si="0"/>
@@ -1475,7 +1471,7 @@
       </c>
       <c r="Q3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" s="14">
         <f t="shared" si="0"/>
@@ -1539,7 +1535,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="54" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1610,7 +1606,7 @@
       <c r="AF4" s="23"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="38"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1679,7 +1675,7 @@
       <c r="AF5" s="23"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1744,7 +1740,7 @@
       <c r="AF6" s="23"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1809,7 +1805,7 @@
       <c r="AF7" s="23"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="38"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1874,7 +1870,7 @@
       <c r="AF8" s="23"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1939,7 +1935,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="59" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -2010,7 +2006,7 @@
       <c r="AF10" s="23"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="38"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2079,7 +2075,7 @@
       <c r="AF11" s="23"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="38"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2144,7 +2140,7 @@
       <c r="AF12" s="23"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2209,7 +2205,7 @@
       <c r="AF13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+      <c r="A14" s="39"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2274,7 +2270,7 @@
       <c r="AF14" s="23"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="39"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2339,7 +2335,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="60" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2410,7 +2406,7 @@
       <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2479,7 +2475,7 @@
       <c r="AF17" s="23"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2544,7 +2540,7 @@
       <c r="AF18" s="23"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="38"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2609,7 +2605,7 @@
       <c r="AF19" s="23"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="38"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2674,7 +2670,7 @@
       <c r="AF20" s="23"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2739,7 +2735,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="57" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2810,7 +2806,7 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2879,7 +2875,7 @@
       <c r="AF23" s="23"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2944,7 +2940,7 @@
       <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="38"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -3009,7 +3005,7 @@
       <c r="AF25" s="23"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3074,7 +3070,7 @@
       <c r="AF26" s="23"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3139,7 +3135,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="58" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3210,7 +3206,7 @@
       <c r="AF28" s="23"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="38"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3220,15 +3216,11 @@
       <c r="D29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="11">
-        <v>1</v>
-      </c>
-      <c r="F29" s="11">
-        <v>2</v>
-      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>V</v>
+        <v>-</v>
       </c>
       <c r="H29" s="24" t="s">
         <v>10</v>
@@ -3279,7 +3271,7 @@
       <c r="AF29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3344,7 +3336,7 @@
       <c r="AF30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="38"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3409,7 +3401,7 @@
       <c r="AF31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="38"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3474,7 +3466,7 @@
       <c r="AF32" s="23"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="39"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3539,7 +3531,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="56" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3610,7 +3602,7 @@
       <c r="AF34" s="23"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="38"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3675,7 +3667,7 @@
       <c r="AF35" s="23"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="38"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3740,7 +3732,7 @@
       <c r="AF36" s="23"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="38"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3805,7 +3797,7 @@
       <c r="AF37" s="23"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="38"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3870,7 +3862,7 @@
       <c r="AF38" s="23"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="39"/>
+      <c r="A39" s="40"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3935,7 +3927,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="55" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -4002,7 +3994,7 @@
       <c r="AF40" s="23"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="38"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4067,7 +4059,7 @@
       <c r="AF41" s="23"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="38"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4132,7 +4124,7 @@
       <c r="AF42" s="23"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="38"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4197,7 +4189,7 @@
       <c r="AF43" s="23"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="38"/>
+      <c r="A44" s="39"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4262,7 +4254,7 @@
       <c r="AF44" s="23"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="39"/>
+      <c r="A45" s="40"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4327,7 +4319,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="57" t="s">
+      <c r="A46" s="38" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4394,7 +4386,7 @@
       <c r="AF46" s="23"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="38"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4459,7 +4451,7 @@
       <c r="AF47" s="23"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4524,7 +4516,7 @@
       <c r="AF48" s="23"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="38"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4589,7 +4581,7 @@
       <c r="AF49" s="23"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4654,7 +4646,7 @@
       <c r="AF50" s="23"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="39"/>
+      <c r="A51" s="40"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4719,7 +4711,7 @@
       <c r="AF51" s="23"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="45" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4786,7 +4778,7 @@
       <c r="AF52" s="25"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="61"/>
+      <c r="A53" s="46"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4851,7 +4843,7 @@
       <c r="AF53" s="25"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="61"/>
+      <c r="A54" s="46"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4916,7 +4908,7 @@
       <c r="AF54" s="25"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="61"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4982,7 +4974,7 @@
       <c r="AK55" s="31"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="61"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5047,7 +5039,7 @@
       <c r="AF56" s="25"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="62"/>
+      <c r="A57" s="47"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5112,7 +5104,7 @@
       <c r="AF57" s="25"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="48" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5179,7 +5171,7 @@
       <c r="AF58" s="25"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="64"/>
+      <c r="A59" s="49"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5244,7 +5236,7 @@
       <c r="AF59" s="25"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="64"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5309,7 +5301,7 @@
       <c r="AF60" s="25"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="64"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5374,7 +5366,7 @@
       <c r="AF61" s="25"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="64"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5439,7 +5431,7 @@
       <c r="AF62" s="25"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="65"/>
+      <c r="A63" s="50"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5504,7 +5496,7 @@
       <c r="AF63" s="25"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="51" t="s">
+      <c r="A64" s="32" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5571,7 +5563,7 @@
       <c r="AF64" s="25"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="52"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5636,7 +5628,7 @@
       <c r="AF65" s="25"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="52"/>
+      <c r="A66" s="33"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5701,7 +5693,7 @@
       <c r="AF66" s="25"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="52"/>
+      <c r="A67" s="33"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5766,7 +5758,7 @@
       <c r="AF67" s="25"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="52"/>
+      <c r="A68" s="33"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5831,7 +5823,7 @@
       <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="53"/>
+      <c r="A69" s="34"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5896,7 +5888,7 @@
       <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="54" t="s">
+      <c r="A70" s="35" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5963,7 +5955,7 @@
       <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
+      <c r="A71" s="36"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6028,7 +6020,7 @@
       <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="55"/>
+      <c r="A72" s="36"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6093,7 +6085,7 @@
       <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="55"/>
+      <c r="A73" s="36"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6158,7 +6150,7 @@
       <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="55"/>
+      <c r="A74" s="36"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6223,7 +6215,7 @@
       <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="56"/>
+      <c r="A75" s="37"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6291,14 +6283,14 @@
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="58" t="s">
+      <c r="D76" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="33"/>
-      <c r="F76" s="34"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="43"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6352,12 +6344,12 @@
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="59" t="s">
+      <c r="D77" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="34"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="43"/>
       <c r="H77" s="28">
         <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
         <v>0</v>
@@ -6404,59 +6396,59 @@
       </c>
       <c r="S77" s="28">
         <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="T77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="V77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="W77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Y77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Z77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AB77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AC77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AD77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AE77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AF77" s="28">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6513,59 +6505,59 @@
       </c>
       <c r="S78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6622,59 +6614,59 @@
       </c>
       <c r="S79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="T79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="U79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="V79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="W79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="X79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Z79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AA79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AB79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AC79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AD79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AE79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AF79" s="3">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -7763,13 +7755,6 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7781,6 +7766,13 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A4B4EDA-FF16-4029-9588-22B038EC5556}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B283F66-6F1F-4008-B4AD-C56CD7D054F4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -842,58 +842,11 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -901,6 +854,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -934,6 +889,51 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,6 +963,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1268,15 +1272,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1354,17 +1358,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="65"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
@@ -1426,10 +1430,10 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="53"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
@@ -1439,7 +1443,7 @@
       </c>
       <c r="I3" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" s="14">
         <f t="shared" si="0"/>
@@ -1535,7 +1539,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="37" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1606,7 +1610,7 @@
       <c r="AF4" s="23"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1675,7 +1679,7 @@
       <c r="AF5" s="23"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
+      <c r="A6" s="38"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1740,7 +1744,7 @@
       <c r="AF6" s="23"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1805,7 +1809,7 @@
       <c r="AF7" s="23"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1870,7 +1874,7 @@
       <c r="AF8" s="23"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+      <c r="A9" s="39"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1935,7 +1939,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -2006,7 +2010,7 @@
       <c r="AF10" s="23"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2075,7 +2079,7 @@
       <c r="AF11" s="23"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2140,7 +2144,7 @@
       <c r="AF12" s="23"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2205,7 +2209,7 @@
       <c r="AF13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2270,7 +2274,7 @@
       <c r="AF14" s="23"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2335,7 +2339,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="45" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2406,7 +2410,7 @@
       <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2475,7 +2479,7 @@
       <c r="AF17" s="23"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2540,7 +2544,7 @@
       <c r="AF18" s="23"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2605,7 +2609,7 @@
       <c r="AF19" s="23"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2670,7 +2674,7 @@
       <c r="AF20" s="23"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2735,7 +2739,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="42" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2806,7 +2810,7 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+      <c r="A23" s="38"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2875,7 +2879,7 @@
       <c r="AF23" s="23"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
+      <c r="A24" s="38"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2940,7 +2944,7 @@
       <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+      <c r="A25" s="38"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -3005,7 +3009,7 @@
       <c r="AF25" s="23"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3070,7 +3074,7 @@
       <c r="AF26" s="23"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3135,7 +3139,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3206,7 +3210,7 @@
       <c r="AF28" s="23"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
+      <c r="A29" s="38"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3216,11 +3220,15 @@
       <c r="D29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="E29" s="11">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11">
+        <v>0</v>
+      </c>
       <c r="G29" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="H29" s="24" t="s">
         <v>10</v>
@@ -3271,7 +3279,7 @@
       <c r="AF29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3336,7 +3344,7 @@
       <c r="AF30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3401,7 +3409,7 @@
       <c r="AF31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
+      <c r="A32" s="38"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3466,7 +3474,7 @@
       <c r="AF32" s="23"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3531,7 +3539,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3602,7 +3610,7 @@
       <c r="AF34" s="23"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
+      <c r="A35" s="38"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3667,7 +3675,7 @@
       <c r="AF35" s="23"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
+      <c r="A36" s="38"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3732,7 +3740,7 @@
       <c r="AF36" s="23"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
+      <c r="A37" s="38"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3797,7 +3805,7 @@
       <c r="AF37" s="23"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
+      <c r="A38" s="38"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3862,7 +3870,7 @@
       <c r="AF38" s="23"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="40"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3927,7 +3935,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3994,7 +4002,7 @@
       <c r="AF40" s="23"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
+      <c r="A41" s="38"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4059,7 +4067,7 @@
       <c r="AF41" s="23"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4124,7 +4132,7 @@
       <c r="AF42" s="23"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
+      <c r="A43" s="38"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4189,7 +4197,7 @@
       <c r="AF43" s="23"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
+      <c r="A44" s="38"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4254,7 +4262,7 @@
       <c r="AF44" s="23"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="40"/>
+      <c r="A45" s="39"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4319,7 +4327,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4386,7 +4394,7 @@
       <c r="AF46" s="23"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39"/>
+      <c r="A47" s="38"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4451,7 +4459,7 @@
       <c r="AF47" s="23"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4516,7 +4524,7 @@
       <c r="AF48" s="23"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4581,7 +4589,7 @@
       <c r="AF49" s="23"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4646,7 +4654,7 @@
       <c r="AF50" s="23"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4711,7 +4719,7 @@
       <c r="AF51" s="23"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="60" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4778,7 +4786,7 @@
       <c r="AF52" s="25"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
+      <c r="A53" s="61"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4843,7 +4851,7 @@
       <c r="AF53" s="25"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4908,7 +4916,7 @@
       <c r="AF54" s="25"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4974,7 +4982,7 @@
       <c r="AK55" s="31"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5039,7 +5047,7 @@
       <c r="AF56" s="25"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="47"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5104,7 +5112,7 @@
       <c r="AF57" s="25"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48" t="s">
+      <c r="A58" s="63" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5171,7 +5179,7 @@
       <c r="AF58" s="25"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="49"/>
+      <c r="A59" s="64"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5236,7 +5244,7 @@
       <c r="AF59" s="25"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="49"/>
+      <c r="A60" s="64"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5301,7 +5309,7 @@
       <c r="AF60" s="25"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+      <c r="A61" s="64"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5366,7 +5374,7 @@
       <c r="AF61" s="25"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="49"/>
+      <c r="A62" s="64"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5431,7 +5439,7 @@
       <c r="AF62" s="25"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="50"/>
+      <c r="A63" s="65"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5496,7 +5504,7 @@
       <c r="AF63" s="25"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="51" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5563,7 +5571,7 @@
       <c r="AF64" s="25"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5628,7 +5636,7 @@
       <c r="AF65" s="25"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5693,7 +5701,7 @@
       <c r="AF66" s="25"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5758,7 +5766,7 @@
       <c r="AF67" s="25"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5823,7 +5831,7 @@
       <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="34"/>
+      <c r="A69" s="53"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5888,7 +5896,7 @@
       <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="54" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5955,7 +5963,7 @@
       <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
+      <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6020,7 +6028,7 @@
       <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
+      <c r="A72" s="55"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6085,7 +6093,7 @@
       <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
+      <c r="A73" s="55"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6150,7 +6158,7 @@
       <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
+      <c r="A74" s="55"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6215,7 +6223,7 @@
       <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="56"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6283,14 +6291,14 @@
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="41" t="s">
+      <c r="D76" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="42"/>
-      <c r="F76" s="43"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6344,12 +6352,12 @@
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="44" t="s">
+      <c r="D77" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="43"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="34"/>
       <c r="H77" s="28">
         <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
         <v>0</v>
@@ -6396,59 +6404,59 @@
       </c>
       <c r="S77" s="28">
         <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="W77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AC77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AD77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AE77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF77" s="28">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6505,59 +6513,59 @@
       </c>
       <c r="S78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -7755,6 +7763,13 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7766,13 +7781,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B283F66-6F1F-4008-B4AD-C56CD7D054F4}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{520E5BCB-4E6B-4D5A-92E7-DE5306A6C5B5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -842,11 +842,58 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -854,8 +901,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -888,51 +933,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1271,16 +1271,16 @@
     <col min="15" max="32" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1357,18 +1357,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="65"/>
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
@@ -1417,7 +1417,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1430,116 +1430,116 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="36"/>
+      <c r="F3" s="53"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f t="shared" ref="H3:R3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <v>9</v>
+      </c>
+      <c r="I3" s="14">
+        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
+        <v>9</v>
+      </c>
+      <c r="J3" s="14">
+        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
         <v>8</v>
       </c>
-      <c r="I3" s="14">
+      <c r="K3" s="14">
+        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
+        <v>8</v>
+      </c>
+      <c r="L3" s="14">
+        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+        <v>7</v>
+      </c>
+      <c r="M3" s="14">
+        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
+        <v>7</v>
+      </c>
+      <c r="N3" s="14">
+        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+        <v>6</v>
+      </c>
+      <c r="O3" s="14">
+        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
+        <v>6</v>
+      </c>
+      <c r="P3" s="14">
+        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="R3" s="14">
+        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="S3" s="14">
+        <f>SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="14">
+        <f t="shared" ref="S3:AF3" si="0">SUM(IF(T4=$G$4,1,0)+IF(T5=$G$5,1,0)+IF(T6=$G$6,1,0)+IF(T7=$G$7,1,0)+IF(T8=$G$8,1,0)+IF(T9=$G$9,1,0)+IF(T10=$G$10,1,0)+IF(T11=$G$11,1,0)+IF(T12=$G$12,1,0)+IF(T13=$G$13,1,0)+IF(T14=$G$14,1,0)+IF(T15=$G$15,1,0)+IF(T16=$G$16,1,0)+IF(T17=$G$17,1,0)+IF(T18=$G$18,1,0)+IF(T19=$G$19,1,0)+IF(T20=$G$20,1,0)+IF(T21=$G$21,1,0)+IF(T22=$G$22,1,0)+IF(T23=$G$23,1,0)+IF(T24=$G$24,1,0)+IF(T25=$G$25,1,0)+IF(T26=$G$26,1,0)+IF(T27=$G$27,1,0)+IF(T28=$G$28,1,0)+IF(T29=$G$29,1,0)+IF(T30=$G$30,1,0)+IF(T31=$G$31,1,0)+IF(T32=$G$32,1,0)+IF(T33=$G$33,1,0)+IF(T34=$G$34,1,0)+IF(T35=$G$35,1,0)+IF(T36=$G$36,1,0)+IF(T37=$G$37,1,0)+IF(T38=$G$38,1,0)+IF(T39=$G$39,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="14">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="J3" s="14">
+        <v>0</v>
+      </c>
+      <c r="V3" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="K3" s="14">
+        <v>0</v>
+      </c>
+      <c r="W3" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="L3" s="14">
+        <v>0</v>
+      </c>
+      <c r="X3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="M3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="N3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="P3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Q3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="R3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="S3" s="14">
-        <f t="shared" ref="S3:AF3" si="1">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
         <v>0</v>
       </c>
-      <c r="T3" s="14">
-        <f t="shared" si="1"/>
+      <c r="AE3" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U3" s="14">
-        <f t="shared" si="1"/>
+      <c r="AF3" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="54" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G51" si="2">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
+        <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
         <v>L</v>
       </c>
       <c r="H4" s="24" t="s">
@@ -1610,7 +1610,7 @@
       <c r="AF4" s="23"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="38"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H5" s="24" t="s">
@@ -1679,7 +1679,7 @@
       <c r="AF5" s="23"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1692,7 +1692,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H6" s="24" t="s">
@@ -1744,7 +1744,7 @@
       <c r="AF6" s="23"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1757,7 +1757,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -1809,7 +1809,7 @@
       <c r="AF7" s="23"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="38"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H8" s="24" t="s">
@@ -1874,7 +1874,7 @@
       <c r="AF8" s="23"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1887,7 +1887,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H9" s="24" t="s">
@@ -1939,7 +1939,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="59" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H10" s="24" t="s">
@@ -2010,7 +2010,7 @@
       <c r="AF10" s="23"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="38"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H11" s="24" t="s">
@@ -2079,7 +2079,7 @@
       <c r="AF11" s="23"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="38"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2092,7 +2092,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H12" s="24" t="s">
@@ -2144,7 +2144,7 @@
       <c r="AF12" s="23"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2157,7 +2157,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H13" s="24" t="s">
@@ -2209,7 +2209,7 @@
       <c r="AF13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+      <c r="A14" s="39"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H14" s="24" t="s">
@@ -2274,7 +2274,7 @@
       <c r="AF14" s="23"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="39"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2287,7 +2287,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -2339,7 +2339,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="60" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2358,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H16" s="24" t="s">
@@ -2410,7 +2410,7 @@
       <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
       <c r="H17" s="24" t="s">
@@ -2479,7 +2479,7 @@
       <c r="AF17" s="23"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2492,7 +2492,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H18" s="24" t="s">
@@ -2544,7 +2544,7 @@
       <c r="AF18" s="23"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="38"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2557,7 +2557,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H19" s="24" t="s">
@@ -2609,7 +2609,7 @@
       <c r="AF19" s="23"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="38"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2622,7 +2622,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H20" s="24" t="s">
@@ -2674,7 +2674,7 @@
       <c r="AF20" s="23"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2687,7 +2687,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H21" s="24" t="s">
@@ -2739,7 +2739,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="57" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2758,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H22" s="24" t="s">
@@ -2810,7 +2810,7 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H23" s="24" t="s">
@@ -2879,7 +2879,7 @@
       <c r="AF23" s="23"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2892,7 +2892,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H24" s="24" t="s">
@@ -2944,7 +2944,7 @@
       <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="38"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2957,7 +2957,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H25" s="24" t="s">
@@ -3009,7 +3009,7 @@
       <c r="AF25" s="23"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3022,7 +3022,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H26" s="24" t="s">
@@ -3074,7 +3074,7 @@
       <c r="AF26" s="23"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3087,7 +3087,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H27" s="24" t="s">
@@ -3139,7 +3139,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="58" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3158,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H28" s="24" t="s">
@@ -3210,7 +3210,7 @@
       <c r="AF28" s="23"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="38"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H29" s="24" t="s">
@@ -3279,7 +3279,7 @@
       <c r="AF29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3292,7 +3292,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H30" s="24" t="s">
@@ -3344,7 +3344,7 @@
       <c r="AF30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="38"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3357,7 +3357,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H31" s="24" t="s">
@@ -3409,7 +3409,7 @@
       <c r="AF31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="38"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3422,7 +3422,7 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H32" s="24" t="s">
@@ -3474,7 +3474,7 @@
       <c r="AF32" s="23"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="39"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3487,7 +3487,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H33" s="24" t="s">
@@ -3539,7 +3539,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="56" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3558,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H34" s="24" t="s">
@@ -3610,7 +3610,7 @@
       <c r="AF34" s="23"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="38"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3620,11 +3620,15 @@
       <c r="D35" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
+      <c r="E35" s="12">
+        <v>4</v>
+      </c>
+      <c r="F35" s="12">
+        <v>1</v>
+      </c>
       <c r="G35" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
+        <f t="shared" si="1"/>
+        <v>L</v>
       </c>
       <c r="H35" s="24" t="s">
         <v>46</v>
@@ -3675,7 +3679,7 @@
       <c r="AF35" s="23"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="38"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3688,7 +3692,7 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H36" s="24" t="s">
@@ -3740,7 +3744,7 @@
       <c r="AF36" s="23"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="38"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3753,7 +3757,7 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H37" s="24" t="s">
@@ -3805,7 +3809,7 @@
       <c r="AF37" s="23"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="38"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3818,7 +3822,7 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H38" s="24" t="s">
@@ -3870,7 +3874,7 @@
       <c r="AF38" s="23"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="39"/>
+      <c r="A39" s="40"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3883,7 +3887,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H39" s="24" t="s">
@@ -3935,7 +3939,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="55" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3950,7 +3954,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H40" s="24" t="s">
@@ -4002,7 +4006,7 @@
       <c r="AF40" s="23"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="38"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4015,7 +4019,7 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H41" s="24" t="s">
@@ -4067,7 +4071,7 @@
       <c r="AF41" s="23"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="38"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4080,7 +4084,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H42" s="24" t="s">
@@ -4132,7 +4136,7 @@
       <c r="AF42" s="23"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="38"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4145,7 +4149,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H43" s="24" t="s">
@@ -4197,7 +4201,7 @@
       <c r="AF43" s="23"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="38"/>
+      <c r="A44" s="39"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4210,7 +4214,7 @@
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H44" s="24" t="s">
@@ -4262,7 +4266,7 @@
       <c r="AF44" s="23"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="39"/>
+      <c r="A45" s="40"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4275,7 +4279,7 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H45" s="24" t="s">
@@ -4327,7 +4331,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="57" t="s">
+      <c r="A46" s="38" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4342,7 +4346,7 @@
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H46" s="24" t="s">
@@ -4394,7 +4398,7 @@
       <c r="AF46" s="23"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="38"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4407,7 +4411,7 @@
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H47" s="24" t="s">
@@ -4459,7 +4463,7 @@
       <c r="AF47" s="23"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4472,7 +4476,7 @@
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H48" s="24" t="s">
@@ -4524,7 +4528,7 @@
       <c r="AF48" s="23"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="38"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4537,7 +4541,7 @@
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H49" s="24" t="s">
@@ -4589,7 +4593,7 @@
       <c r="AF49" s="23"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4602,7 +4606,7 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H50" s="24" t="s">
@@ -4654,7 +4658,7 @@
       <c r="AF50" s="23"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="39"/>
+      <c r="A51" s="40"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4667,7 +4671,7 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H51" s="24" t="s">
@@ -4719,7 +4723,7 @@
       <c r="AF51" s="23"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="45" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4734,7 +4738,7 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15" t="str">
-        <f t="shared" ref="G52:G75" si="3">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
+        <f t="shared" ref="G52:G75" si="2">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
       <c r="H52" s="26" t="s">
@@ -4786,7 +4790,7 @@
       <c r="AF52" s="25"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="61"/>
+      <c r="A53" s="46"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4799,7 +4803,7 @@
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H53" s="26" t="s">
@@ -4851,7 +4855,7 @@
       <c r="AF53" s="25"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="61"/>
+      <c r="A54" s="46"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4864,7 +4868,7 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H54" s="26" t="s">
@@ -4916,7 +4920,7 @@
       <c r="AF54" s="25"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="61"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4929,7 +4933,7 @@
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H55" s="26" t="s">
@@ -4982,7 +4986,7 @@
       <c r="AK55" s="31"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="61"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -4995,7 +4999,7 @@
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H56" s="26" t="s">
@@ -5047,7 +5051,7 @@
       <c r="AF56" s="25"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="62"/>
+      <c r="A57" s="47"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5060,7 +5064,7 @@
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H57" s="26" t="s">
@@ -5112,7 +5116,7 @@
       <c r="AF57" s="25"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="48" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5127,7 +5131,7 @@
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
       <c r="G58" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H58" s="26" t="s">
@@ -5179,7 +5183,7 @@
       <c r="AF58" s="25"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="64"/>
+      <c r="A59" s="49"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5192,7 +5196,7 @@
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H59" s="26" t="s">
@@ -5244,7 +5248,7 @@
       <c r="AF59" s="25"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="64"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5257,7 +5261,7 @@
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H60" s="26" t="s">
@@ -5309,7 +5313,7 @@
       <c r="AF60" s="25"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="64"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5322,7 +5326,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H61" s="26" t="s">
@@ -5374,7 +5378,7 @@
       <c r="AF61" s="25"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="64"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5387,7 +5391,7 @@
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H62" s="26" t="s">
@@ -5439,7 +5443,7 @@
       <c r="AF62" s="25"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="65"/>
+      <c r="A63" s="50"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5452,7 +5456,7 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H63" s="26" t="s">
@@ -5504,7 +5508,7 @@
       <c r="AF63" s="25"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="51" t="s">
+      <c r="A64" s="32" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5519,7 +5523,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H64" s="26" t="s">
@@ -5571,7 +5575,7 @@
       <c r="AF64" s="25"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="52"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5584,7 +5588,7 @@
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H65" s="26" t="s">
@@ -5636,7 +5640,7 @@
       <c r="AF65" s="25"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="52"/>
+      <c r="A66" s="33"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5649,7 +5653,7 @@
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H66" s="26" t="s">
@@ -5701,7 +5705,7 @@
       <c r="AF66" s="25"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="52"/>
+      <c r="A67" s="33"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5714,7 +5718,7 @@
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H67" s="26" t="s">
@@ -5766,7 +5770,7 @@
       <c r="AF67" s="25"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="52"/>
+      <c r="A68" s="33"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5779,7 +5783,7 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H68" s="26" t="s">
@@ -5831,7 +5835,7 @@
       <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="53"/>
+      <c r="A69" s="34"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5844,7 +5848,7 @@
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H69" s="26" t="s">
@@ -5896,7 +5900,7 @@
       <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="54" t="s">
+      <c r="A70" s="35" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5911,7 +5915,7 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
       <c r="G70" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H70" s="26" t="s">
@@ -5963,7 +5967,7 @@
       <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
+      <c r="A71" s="36"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5976,7 +5980,7 @@
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
       <c r="G71" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H71" s="26" t="s">
@@ -6028,7 +6032,7 @@
       <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="55"/>
+      <c r="A72" s="36"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6041,7 +6045,7 @@
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
       <c r="G72" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H72" s="26" t="s">
@@ -6093,7 +6097,7 @@
       <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="55"/>
+      <c r="A73" s="36"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6106,7 +6110,7 @@
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H73" s="26" t="s">
@@ -6158,7 +6162,7 @@
       <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="55"/>
+      <c r="A74" s="36"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6171,7 +6175,7 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H74" s="26" t="s">
@@ -6223,7 +6227,7 @@
       <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="56"/>
+      <c r="A75" s="37"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6236,7 +6240,7 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H75" s="26" t="s">
@@ -6291,14 +6295,14 @@
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="58" t="s">
+      <c r="D76" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="33"/>
-      <c r="F76" s="34"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="43"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6352,111 +6356,111 @@
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="59" t="s">
+      <c r="D77" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="34"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="43"/>
       <c r="H77" s="28">
-        <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
+        <f>SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(I78:I81)</f>
         <v>0</v>
       </c>
       <c r="J77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(J78:J81)</f>
         <v>0</v>
       </c>
       <c r="K77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(K78:K81)</f>
         <v>0</v>
       </c>
       <c r="L77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(L78:L81)</f>
         <v>0</v>
       </c>
       <c r="M77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(M78:M81)</f>
         <v>0</v>
       </c>
       <c r="N77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(N78:N81)</f>
         <v>0</v>
       </c>
       <c r="O77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(O78:O81)</f>
         <v>0</v>
       </c>
       <c r="P77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(P78:P81)</f>
         <v>0</v>
       </c>
       <c r="Q77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(Q78:Q81)</f>
         <v>0</v>
       </c>
       <c r="R77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(R78:R81)</f>
         <v>0</v>
       </c>
       <c r="S77" s="28">
-        <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
-        <v>68</v>
+        <f>SUM(S78:S81)</f>
+        <v>63</v>
       </c>
       <c r="T77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" ref="S77:AF77" si="3">SUM(T78:T81)</f>
+        <v>63</v>
       </c>
       <c r="U77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="V77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="W77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="X77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="Y77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="Z77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="AA77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="AB77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="AC77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="AD77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="AE77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="AF77" s="28">
-        <f t="shared" si="5"/>
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6468,104 +6472,104 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="6">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="6"/>
-        <v>68</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6577,104 +6581,104 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="7">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6686,103 +6690,103 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="8">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -6795,103 +6799,103 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="9">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7758,18 +7762,11 @@
       <c r="G124" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H2:R77">
-    <sortCondition descending="1" ref="H3:R3"/>
-    <sortCondition descending="1" ref="H77:R77"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H2:S77">
+    <sortCondition descending="1" ref="H3:S3"/>
+    <sortCondition descending="1" ref="H77:S77"/>
   </sortState>
   <mergeCells count="18">
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7781,6 +7778,13 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{520E5BCB-4E6B-4D5A-92E7-DE5306A6C5B5}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9BF7E63-D030-4F11-A7E6-4A6C6A9739B8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
@@ -842,58 +842,11 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -901,6 +854,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -934,6 +889,51 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,10 +963,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1257,30 +1253,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.6640625" customWidth="1"/>
-    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="32" width="5.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="32" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1357,18 +1353,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+    <row r="2" spans="1:32" ht="143.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="65"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
@@ -1417,7 +1413,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1430,116 +1426,116 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="53"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <f t="shared" ref="H3:S3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
         <v>9</v>
       </c>
       <c r="I3" s="14">
-        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="J3" s="14">
-        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="K3" s="14">
-        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="L3" s="14">
-        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="M3" s="14">
-        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N3" s="14">
-        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O3" s="14">
-        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="P3" s="14">
-        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q3" s="14">
-        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="R3" s="14">
-        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="S3" s="14">
-        <f>SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="T3" s="14">
-        <f t="shared" ref="S3:AF3" si="0">SUM(IF(T4=$G$4,1,0)+IF(T5=$G$5,1,0)+IF(T6=$G$6,1,0)+IF(T7=$G$7,1,0)+IF(T8=$G$8,1,0)+IF(T9=$G$9,1,0)+IF(T10=$G$10,1,0)+IF(T11=$G$11,1,0)+IF(T12=$G$12,1,0)+IF(T13=$G$13,1,0)+IF(T14=$G$14,1,0)+IF(T15=$G$15,1,0)+IF(T16=$G$16,1,0)+IF(T17=$G$17,1,0)+IF(T18=$G$18,1,0)+IF(T19=$G$19,1,0)+IF(T20=$G$20,1,0)+IF(T21=$G$21,1,0)+IF(T22=$G$22,1,0)+IF(T23=$G$23,1,0)+IF(T24=$G$24,1,0)+IF(T25=$G$25,1,0)+IF(T26=$G$26,1,0)+IF(T27=$G$27,1,0)+IF(T28=$G$28,1,0)+IF(T29=$G$29,1,0)+IF(T30=$G$30,1,0)+IF(T31=$G$31,1,0)+IF(T32=$G$32,1,0)+IF(T33=$G$33,1,0)+IF(T34=$G$34,1,0)+IF(T35=$G$35,1,0)+IF(T36=$G$36,1,0)+IF(T37=$G$37,1,0)+IF(T38=$G$38,1,0)+IF(T39=$G$39,1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="U3" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="T3" s="14">
+        <f t="shared" ref="T3:AF3" si="1">SUM(IF(T4=$G$4,1,0)+IF(T5=$G$5,1,0)+IF(T6=$G$6,1,0)+IF(T7=$G$7,1,0)+IF(T8=$G$8,1,0)+IF(T9=$G$9,1,0)+IF(T10=$G$10,1,0)+IF(T11=$G$11,1,0)+IF(T12=$G$12,1,0)+IF(T13=$G$13,1,0)+IF(T14=$G$14,1,0)+IF(T15=$G$15,1,0)+IF(T16=$G$16,1,0)+IF(T17=$G$17,1,0)+IF(T18=$G$18,1,0)+IF(T19=$G$19,1,0)+IF(T20=$G$20,1,0)+IF(T21=$G$21,1,0)+IF(T22=$G$22,1,0)+IF(T23=$G$23,1,0)+IF(T24=$G$24,1,0)+IF(T25=$G$25,1,0)+IF(T26=$G$26,1,0)+IF(T27=$G$27,1,0)+IF(T28=$G$28,1,0)+IF(T29=$G$29,1,0)+IF(T30=$G$30,1,0)+IF(T31=$G$31,1,0)+IF(T32=$G$32,1,0)+IF(T33=$G$33,1,0)+IF(T34=$G$34,1,0)+IF(T35=$G$35,1,0)+IF(T36=$G$36,1,0)+IF(T37=$G$37,1,0)+IF(T38=$G$38,1,0)+IF(T39=$G$39,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="V3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
+    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1558,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
+        <f t="shared" ref="G4:G51" si="2">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
         <v>L</v>
       </c>
       <c r="H4" s="24" t="s">
@@ -1609,8 +1605,8 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
+    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="38"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1627,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H5" s="24" t="s">
@@ -1678,8 +1674,8 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
+    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="38"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1692,7 +1688,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H6" s="24" t="s">
@@ -1743,8 +1739,8 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
+    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="38"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1757,7 +1753,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -1808,8 +1804,8 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
+    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="38"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1822,7 +1818,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H8" s="24" t="s">
@@ -1873,8 +1869,8 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="39"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1887,7 +1883,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H9" s="24" t="s">
@@ -1938,8 +1934,8 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="59" t="s">
+    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1958,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H10" s="24" t="s">
@@ -2009,8 +2005,8 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
+    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="38"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2027,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H11" s="24" t="s">
@@ -2078,8 +2074,8 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
+    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="38"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2092,7 +2088,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H12" s="24" t="s">
@@ -2143,8 +2139,8 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
+    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="38"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2157,7 +2153,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H13" s="24" t="s">
@@ -2208,8 +2204,8 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
+    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="38"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2222,7 +2218,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H14" s="24" t="s">
@@ -2273,8 +2269,8 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="39"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2287,7 +2283,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -2338,8 +2334,8 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2358,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H16" s="24" t="s">
@@ -2409,8 +2405,8 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
+    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="38"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2427,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>V</v>
       </c>
       <c r="H17" s="24" t="s">
@@ -2478,8 +2474,8 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
+    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="38"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2492,7 +2488,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H18" s="24" t="s">
@@ -2543,8 +2539,8 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
+    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="38"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2557,7 +2553,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H19" s="24" t="s">
@@ -2608,8 +2604,8 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
+    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="38"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2622,7 +2618,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H20" s="24" t="s">
@@ -2673,8 +2669,8 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="39"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2687,7 +2683,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H21" s="24" t="s">
@@ -2738,8 +2734,8 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="57" t="s">
+    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="42" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2758,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H22" s="24" t="s">
@@ -2809,8 +2805,8 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="38"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2827,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H23" s="24" t="s">
@@ -2878,8 +2874,8 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
+    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="38"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2892,7 +2888,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H24" s="24" t="s">
@@ -2943,8 +2939,8 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2957,7 +2953,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H25" s="24" t="s">
@@ -3008,8 +3004,8 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="38"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3022,7 +3018,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H26" s="24" t="s">
@@ -3073,8 +3069,8 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="39"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3087,7 +3083,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H27" s="24" t="s">
@@ -3138,8 +3134,8 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="58" t="s">
+    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3158,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H28" s="24" t="s">
@@ -3209,8 +3205,8 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
+    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="38"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3227,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H29" s="24" t="s">
@@ -3278,8 +3274,8 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
+    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="38"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3292,7 +3288,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H30" s="24" t="s">
@@ -3343,8 +3339,8 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
+    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="38"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3357,7 +3353,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H31" s="24" t="s">
@@ -3408,8 +3404,8 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
+    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="38"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3422,7 +3418,7 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H32" s="24" t="s">
@@ -3473,8 +3469,8 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="39"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3487,7 +3483,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H33" s="24" t="s">
@@ -3538,8 +3534,8 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56" t="s">
+    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3558,7 +3554,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H34" s="24" t="s">
@@ -3609,8 +3605,8 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
+    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="38"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3627,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H35" s="24" t="s">
@@ -3678,8 +3674,8 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
+    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="38"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3692,7 +3688,7 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H36" s="24" t="s">
@@ -3743,8 +3739,8 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
+    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="38"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3757,7 +3753,7 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H37" s="24" t="s">
@@ -3808,8 +3804,8 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
+    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="38"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3822,7 +3818,7 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H38" s="24" t="s">
@@ -3873,8 +3869,8 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="40"/>
+    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="39"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3887,7 +3883,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H39" s="24" t="s">
@@ -3938,8 +3934,8 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="55" t="s">
+    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3954,7 +3950,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H40" s="24" t="s">
@@ -4005,8 +4001,8 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
+    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="38"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4019,7 +4015,7 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H41" s="24" t="s">
@@ -4070,8 +4066,8 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
+    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="38"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4084,7 +4080,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H42" s="24" t="s">
@@ -4135,8 +4131,8 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
+    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="38"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4149,7 +4145,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H43" s="24" t="s">
@@ -4200,8 +4196,8 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
+    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="38"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4214,7 +4210,7 @@
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H44" s="24" t="s">
@@ -4265,8 +4261,8 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="40"/>
+    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="39"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4279,7 +4275,7 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H45" s="24" t="s">
@@ -4330,8 +4326,8 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="38" t="s">
+    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4343,11 +4339,15 @@
       <c r="D46" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
       <c r="G46" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+        <f t="shared" si="2"/>
+        <v>E</v>
       </c>
       <c r="H46" s="24" t="s">
         <v>46</v>
@@ -4397,8 +4397,8 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39"/>
+    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="38"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4411,7 +4411,7 @@
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H47" s="24" t="s">
@@ -4462,8 +4462,8 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="38"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4476,7 +4476,7 @@
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H48" s="24" t="s">
@@ -4527,8 +4527,8 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="38"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4541,7 +4541,7 @@
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H49" s="24" t="s">
@@ -4592,8 +4592,8 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="38"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4606,7 +4606,7 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H50" s="24" t="s">
@@ -4657,8 +4657,8 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="39"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4671,7 +4671,7 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H51" s="24" t="s">
@@ -4722,8 +4722,8 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="60" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4738,7 +4738,7 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15" t="str">
-        <f t="shared" ref="G52:G75" si="2">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
+        <f t="shared" ref="G52:G75" si="3">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
       <c r="H52" s="26" t="s">
@@ -4789,8 +4789,8 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
+    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="61"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4803,7 +4803,7 @@
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H53" s="26" t="s">
@@ -4854,8 +4854,8 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
+    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="61"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4868,7 +4868,7 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H54" s="26" t="s">
@@ -4919,8 +4919,8 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
+    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="61"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4933,7 +4933,7 @@
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H55" s="26" t="s">
@@ -4985,8 +4985,8 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
+    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="61"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -4999,7 +4999,7 @@
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H56" s="26" t="s">
@@ -5050,8 +5050,8 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="47"/>
+    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="62"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H57" s="26" t="s">
@@ -5115,8 +5115,8 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48" t="s">
+    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="63" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5131,7 +5131,7 @@
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
       <c r="G58" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H58" s="26" t="s">
@@ -5182,8 +5182,8 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="49"/>
+    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="64"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5196,7 +5196,7 @@
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H59" s="26" t="s">
@@ -5247,8 +5247,8 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="49"/>
+    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="64"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5261,7 +5261,7 @@
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H60" s="26" t="s">
@@ -5312,8 +5312,8 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="64"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5326,7 +5326,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H61" s="26" t="s">
@@ -5377,8 +5377,8 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="49"/>
+    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="64"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5391,7 +5391,7 @@
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H62" s="26" t="s">
@@ -5442,8 +5442,8 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="50"/>
+    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="65"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5456,7 +5456,7 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H63" s="26" t="s">
@@ -5507,8 +5507,8 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="32" t="s">
+    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="51" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5523,7 +5523,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H64" s="26" t="s">
@@ -5574,8 +5574,8 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
+    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="52"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5588,7 +5588,7 @@
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H65" s="26" t="s">
@@ -5639,8 +5639,8 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
+    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="52"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5653,7 +5653,7 @@
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H66" s="26" t="s">
@@ -5704,8 +5704,8 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
+    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="52"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5718,7 +5718,7 @@
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H67" s="26" t="s">
@@ -5769,8 +5769,8 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
+    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="52"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5783,7 +5783,7 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H68" s="26" t="s">
@@ -5834,8 +5834,8 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="34"/>
+    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="53"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5848,7 +5848,7 @@
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H69" s="26" t="s">
@@ -5899,8 +5899,8 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="35" t="s">
+    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="54" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5915,7 +5915,7 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
       <c r="G70" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H70" s="26" t="s">
@@ -5966,8 +5966,8 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
+    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5980,7 +5980,7 @@
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
       <c r="G71" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H71" s="26" t="s">
@@ -6031,8 +6031,8 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
+    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="55"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6045,7 +6045,7 @@
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
       <c r="G72" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H72" s="26" t="s">
@@ -6096,8 +6096,8 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
+    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="55"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6110,7 +6110,7 @@
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H73" s="26" t="s">
@@ -6161,8 +6161,8 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
+    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="55"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6175,7 +6175,7 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H74" s="26" t="s">
@@ -6226,8 +6226,8 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="56"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6240,7 +6240,7 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H75" s="26" t="s">
@@ -6291,15 +6291,15 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="41" t="s">
+      <c r="D76" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="42"/>
-      <c r="F76" s="43"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
         <v>37</v>
@@ -6352,118 +6352,118 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="44" t="s">
+      <c r="D77" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="43"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="34"/>
       <c r="H77" s="28">
-        <f>SUM(H78:H81)</f>
+        <f t="shared" ref="H77:S77" si="4">SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
-        <f>SUM(I78:I81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J77" s="28">
-        <f>SUM(J78:J81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K77" s="28">
-        <f>SUM(K78:K81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L77" s="28">
-        <f>SUM(L78:L81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M77" s="28">
-        <f>SUM(M78:M81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N77" s="28">
-        <f>SUM(N78:N81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O77" s="28">
-        <f>SUM(O78:O81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P77" s="28">
-        <f>SUM(P78:P81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q77" s="28">
-        <f>SUM(Q78:Q81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R77" s="28">
-        <f>SUM(R78:R81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S77" s="28">
-        <f>SUM(S78:S81)</f>
+        <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="T77" s="28">
-        <f t="shared" ref="S77:AF77" si="3">SUM(T78:T81)</f>
+        <f t="shared" ref="T77:AF77" si="5">SUM(T78:T81)</f>
         <v>63</v>
       </c>
       <c r="U77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="V77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="W77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="X77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="Y77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="Z77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="AA77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="AB77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="AC77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="AD77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="AE77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="AF77" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
     </row>
-    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6472,107 +6472,107 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="6">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6581,107 +6581,107 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="7">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6690,107 +6690,107 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="8">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6799,107 +6799,107 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="9">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6933,7 +6933,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -6967,7 +6967,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7001,7 +7001,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7035,7 +7035,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7069,7 +7069,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7103,7 +7103,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7137,7 +7137,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7171,7 +7171,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7205,7 +7205,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7239,7 +7239,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7273,7 +7273,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7307,7 +7307,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7341,7 +7341,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7375,7 +7375,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7409,7 +7409,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7443,7 +7443,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7477,7 +7477,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7511,7 +7511,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7545,7 +7545,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7554,7 +7554,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7563,7 +7563,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7572,7 +7572,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7581,7 +7581,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7590,7 +7590,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7599,7 +7599,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7608,7 +7608,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7617,7 +7617,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7626,7 +7626,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7635,7 +7635,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7644,7 +7644,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7653,7 +7653,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7662,7 +7662,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7671,7 +7671,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7680,7 +7680,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7689,7 +7689,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7698,7 +7698,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7707,7 +7707,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7716,7 +7716,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7725,7 +7725,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7734,7 +7734,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7743,7 +7743,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7752,7 +7752,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7767,6 +7767,13 @@
     <sortCondition descending="1" ref="H77:S77"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7778,13 +7785,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -7799,14 +7799,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="15" width="11.44140625" customWidth="1"/>
+    <col min="1" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="15" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>16</v>
@@ -7853,7 +7853,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -7898,7 +7898,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -7943,7 +7943,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -7988,7 +7988,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -8033,7 +8033,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -8078,7 +8078,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -8123,7 +8123,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -8168,7 +8168,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -8213,7 +8213,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -8258,7 +8258,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -8303,7 +8303,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>16</v>
@@ -8348,7 +8348,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>16</v>
@@ -8393,7 +8393,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
@@ -8438,7 +8438,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -8483,7 +8483,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
@@ -8528,7 +8528,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>16</v>
@@ -8573,7 +8573,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
@@ -8618,7 +8618,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>16</v>
@@ -8663,7 +8663,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>16</v>
@@ -8708,7 +8708,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>16</v>
@@ -8753,7 +8753,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -8798,7 +8798,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -8843,7 +8843,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>16</v>
@@ -8888,7 +8888,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>16</v>
@@ -8933,7 +8933,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -8978,7 +8978,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>16</v>
@@ -9023,7 +9023,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>16</v>
@@ -9068,7 +9068,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>16</v>
@@ -9113,7 +9113,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>16</v>
@@ -9158,7 +9158,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>16</v>
@@ -9203,7 +9203,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>16</v>
@@ -9248,7 +9248,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>16</v>
@@ -9293,7 +9293,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>16</v>
@@ -9338,7 +9338,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>16</v>
@@ -9383,7 +9383,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>16</v>
@@ -9428,7 +9428,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>16</v>
@@ -9473,7 +9473,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>16</v>
@@ -9518,7 +9518,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>16</v>
@@ -9563,7 +9563,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>16</v>
@@ -9608,7 +9608,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>16</v>
@@ -9653,7 +9653,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>16</v>
@@ -9698,7 +9698,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>16</v>
@@ -9743,7 +9743,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>16</v>
@@ -9788,7 +9788,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>16</v>
@@ -9833,7 +9833,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>16</v>
@@ -9878,7 +9878,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>16</v>
@@ -9923,7 +9923,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>16</v>
@@ -9968,7 +9968,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>16</v>
@@ -10013,7 +10013,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>16</v>
@@ -10058,7 +10058,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>16</v>
@@ -10103,7 +10103,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>16</v>
@@ -10148,7 +10148,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>16</v>
@@ -10193,7 +10193,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>16</v>
@@ -10238,7 +10238,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>16</v>
@@ -10283,7 +10283,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>16</v>
@@ -10328,7 +10328,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>16</v>
@@ -10373,7 +10373,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>16</v>
@@ -10418,7 +10418,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>16</v>
@@ -10463,7 +10463,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>16</v>
@@ -10508,7 +10508,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>16</v>
@@ -10553,7 +10553,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>16</v>
@@ -10598,7 +10598,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>16</v>
@@ -10643,7 +10643,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>16</v>
@@ -10688,7 +10688,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>16</v>
@@ -10733,7 +10733,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>16</v>
@@ -10778,7 +10778,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>16</v>
@@ -10823,7 +10823,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>16</v>
@@ -10868,7 +10868,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>16</v>
@@ -10913,7 +10913,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>16</v>
@@ -10958,7 +10958,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>16</v>
@@ -11003,7 +11003,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>16</v>
@@ -11048,7 +11048,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>16</v>
@@ -11093,7 +11093,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>16</v>
@@ -11138,7 +11138,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>16</v>
@@ -11183,7 +11183,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>16</v>
@@ -11228,7 +11228,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>16</v>
@@ -11273,7 +11273,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>16</v>
@@ -11318,7 +11318,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>16</v>
@@ -11363,7 +11363,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>16</v>
@@ -11408,7 +11408,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>16</v>
@@ -11453,7 +11453,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>16</v>
@@ -11498,7 +11498,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>16</v>
@@ -11543,7 +11543,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>16</v>
@@ -11588,7 +11588,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>16</v>
@@ -11633,7 +11633,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>16</v>
@@ -11678,7 +11678,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>16</v>
@@ -11723,7 +11723,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>16</v>
@@ -11768,7 +11768,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>16</v>
@@ -11813,7 +11813,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>16</v>
@@ -11858,7 +11858,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>16</v>
@@ -11903,7 +11903,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>16</v>
@@ -11948,7 +11948,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>16</v>
@@ -11993,7 +11993,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>16</v>
@@ -12038,7 +12038,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>16</v>
@@ -12083,7 +12083,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>16</v>
@@ -12128,7 +12128,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>16</v>
@@ -12173,7 +12173,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>16</v>
@@ -12218,7 +12218,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>16</v>
@@ -12263,7 +12263,7 @@
         <v>SI(G28-H28=-100;0;</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12289,9 +12289,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="11" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12302,26 +12302,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" customWidth="1"/>
-    <col min="2" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="2" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="11" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -12329,61 +12329,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -12391,7 +12391,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -12399,19 +12399,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -12419,19 +12419,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -12439,19 +12439,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -12459,13 +12459,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -12473,229 +12473,229 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="1"/>
     </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="1"/>
     </row>
-    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="1"/>
     </row>
-    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="1"/>
     </row>
-    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="1"/>
     </row>
-    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="1"/>
     </row>
-    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="1"/>
     </row>
-    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="1"/>
     </row>
-    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="1"/>
     </row>
-    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="1"/>
     </row>
   </sheetData>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9BF7E63-D030-4F11-A7E6-4A6C6A9739B8}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6A08344-E9E1-47B0-BADC-B098CA9ADB93}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
@@ -965,6 +965,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -1253,21 +1257,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.7109375" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="32" width="5.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.77734375" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="32" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>101</v>
       </c>
@@ -1353,7 +1359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="143.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>47</v>
       </c>
@@ -1413,7 +1419,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1434,107 +1440,107 @@
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f t="shared" ref="H3:S3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
         <v>9</v>
       </c>
       <c r="I3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
         <v>9</v>
       </c>
       <c r="J3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
         <v>8</v>
       </c>
       <c r="K3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
         <v>8</v>
       </c>
       <c r="L3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
         <v>7</v>
       </c>
       <c r="M3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
         <v>7</v>
       </c>
       <c r="N3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
         <v>6</v>
       </c>
       <c r="O3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
         <v>6</v>
       </c>
       <c r="P3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
         <v>5</v>
       </c>
       <c r="Q3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
         <v>5</v>
       </c>
       <c r="R3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
         <v>5</v>
       </c>
       <c r="S3" s="14">
-        <f t="shared" si="0"/>
+        <f>SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="T3" s="14">
-        <f t="shared" ref="T3:AF3" si="1">SUM(IF(T4=$G$4,1,0)+IF(T5=$G$5,1,0)+IF(T6=$G$6,1,0)+IF(T7=$G$7,1,0)+IF(T8=$G$8,1,0)+IF(T9=$G$9,1,0)+IF(T10=$G$10,1,0)+IF(T11=$G$11,1,0)+IF(T12=$G$12,1,0)+IF(T13=$G$13,1,0)+IF(T14=$G$14,1,0)+IF(T15=$G$15,1,0)+IF(T16=$G$16,1,0)+IF(T17=$G$17,1,0)+IF(T18=$G$18,1,0)+IF(T19=$G$19,1,0)+IF(T20=$G$20,1,0)+IF(T21=$G$21,1,0)+IF(T22=$G$22,1,0)+IF(T23=$G$23,1,0)+IF(T24=$G$24,1,0)+IF(T25=$G$25,1,0)+IF(T26=$G$26,1,0)+IF(T27=$G$27,1,0)+IF(T28=$G$28,1,0)+IF(T29=$G$29,1,0)+IF(T30=$G$30,1,0)+IF(T31=$G$31,1,0)+IF(T32=$G$32,1,0)+IF(T33=$G$33,1,0)+IF(T34=$G$34,1,0)+IF(T35=$G$35,1,0)+IF(T36=$G$36,1,0)+IF(T37=$G$37,1,0)+IF(T38=$G$38,1,0)+IF(T39=$G$39,1,0))</f>
+        <f>SUM(IF(T4=$G$4,1,0)+IF(T5=$G$5,1,0)+IF(T6=$G$6,1,0)+IF(T7=$G$7,1,0)+IF(T8=$G$8,1,0)+IF(T9=$G$9,1,0)+IF(T10=$G$10,1,0)+IF(T11=$G$11,1,0)+IF(T12=$G$12,1,0)+IF(T13=$G$13,1,0)+IF(T14=$G$14,1,0)+IF(T15=$G$15,1,0)+IF(T16=$G$16,1,0)+IF(T17=$G$17,1,0)+IF(T18=$G$18,1,0)+IF(T19=$G$19,1,0)+IF(T20=$G$20,1,0)+IF(T21=$G$21,1,0)+IF(T22=$G$22,1,0)+IF(T23=$G$23,1,0)+IF(T24=$G$24,1,0)+IF(T25=$G$25,1,0)+IF(T26=$G$26,1,0)+IF(T27=$G$27,1,0)+IF(T28=$G$28,1,0)+IF(T29=$G$29,1,0)+IF(T30=$G$30,1,0)+IF(T31=$G$31,1,0)+IF(T32=$G$32,1,0)+IF(T33=$G$33,1,0)+IF(T34=$G$34,1,0)+IF(T35=$G$35,1,0)+IF(T36=$G$36,1,0)+IF(T37=$G$37,1,0)+IF(T38=$G$38,1,0)+IF(T39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="U3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(U4=$G$4,1,0)+IF(U5=$G$5,1,0)+IF(U6=$G$6,1,0)+IF(U7=$G$7,1,0)+IF(U8=$G$8,1,0)+IF(U9=$G$9,1,0)+IF(U10=$G$10,1,0)+IF(U11=$G$11,1,0)+IF(U12=$G$12,1,0)+IF(U13=$G$13,1,0)+IF(U14=$G$14,1,0)+IF(U15=$G$15,1,0)+IF(U16=$G$16,1,0)+IF(U17=$G$17,1,0)+IF(U18=$G$18,1,0)+IF(U19=$G$19,1,0)+IF(U20=$G$20,1,0)+IF(U21=$G$21,1,0)+IF(U22=$G$22,1,0)+IF(U23=$G$23,1,0)+IF(U24=$G$24,1,0)+IF(U25=$G$25,1,0)+IF(U26=$G$26,1,0)+IF(U27=$G$27,1,0)+IF(U28=$G$28,1,0)+IF(U29=$G$29,1,0)+IF(U30=$G$30,1,0)+IF(U31=$G$31,1,0)+IF(U32=$G$32,1,0)+IF(U33=$G$33,1,0)+IF(U34=$G$34,1,0)+IF(U35=$G$35,1,0)+IF(U36=$G$36,1,0)+IF(U37=$G$37,1,0)+IF(U38=$G$38,1,0)+IF(U39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="V3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(V4=$G$4,1,0)+IF(V5=$G$5,1,0)+IF(V6=$G$6,1,0)+IF(V7=$G$7,1,0)+IF(V8=$G$8,1,0)+IF(V9=$G$9,1,0)+IF(V10=$G$10,1,0)+IF(V11=$G$11,1,0)+IF(V12=$G$12,1,0)+IF(V13=$G$13,1,0)+IF(V14=$G$14,1,0)+IF(V15=$G$15,1,0)+IF(V16=$G$16,1,0)+IF(V17=$G$17,1,0)+IF(V18=$G$18,1,0)+IF(V19=$G$19,1,0)+IF(V20=$G$20,1,0)+IF(V21=$G$21,1,0)+IF(V22=$G$22,1,0)+IF(V23=$G$23,1,0)+IF(V24=$G$24,1,0)+IF(V25=$G$25,1,0)+IF(V26=$G$26,1,0)+IF(V27=$G$27,1,0)+IF(V28=$G$28,1,0)+IF(V29=$G$29,1,0)+IF(V30=$G$30,1,0)+IF(V31=$G$31,1,0)+IF(V32=$G$32,1,0)+IF(V33=$G$33,1,0)+IF(V34=$G$34,1,0)+IF(V35=$G$35,1,0)+IF(V36=$G$36,1,0)+IF(V37=$G$37,1,0)+IF(V38=$G$38,1,0)+IF(V39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="W3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(W4=$G$4,1,0)+IF(W5=$G$5,1,0)+IF(W6=$G$6,1,0)+IF(W7=$G$7,1,0)+IF(W8=$G$8,1,0)+IF(W9=$G$9,1,0)+IF(W10=$G$10,1,0)+IF(W11=$G$11,1,0)+IF(W12=$G$12,1,0)+IF(W13=$G$13,1,0)+IF(W14=$G$14,1,0)+IF(W15=$G$15,1,0)+IF(W16=$G$16,1,0)+IF(W17=$G$17,1,0)+IF(W18=$G$18,1,0)+IF(W19=$G$19,1,0)+IF(W20=$G$20,1,0)+IF(W21=$G$21,1,0)+IF(W22=$G$22,1,0)+IF(W23=$G$23,1,0)+IF(W24=$G$24,1,0)+IF(W25=$G$25,1,0)+IF(W26=$G$26,1,0)+IF(W27=$G$27,1,0)+IF(W28=$G$28,1,0)+IF(W29=$G$29,1,0)+IF(W30=$G$30,1,0)+IF(W31=$G$31,1,0)+IF(W32=$G$32,1,0)+IF(W33=$G$33,1,0)+IF(W34=$G$34,1,0)+IF(W35=$G$35,1,0)+IF(W36=$G$36,1,0)+IF(W37=$G$37,1,0)+IF(W38=$G$38,1,0)+IF(W39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="X3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(X4=$G$4,1,0)+IF(X5=$G$5,1,0)+IF(X6=$G$6,1,0)+IF(X7=$G$7,1,0)+IF(X8=$G$8,1,0)+IF(X9=$G$9,1,0)+IF(X10=$G$10,1,0)+IF(X11=$G$11,1,0)+IF(X12=$G$12,1,0)+IF(X13=$G$13,1,0)+IF(X14=$G$14,1,0)+IF(X15=$G$15,1,0)+IF(X16=$G$16,1,0)+IF(X17=$G$17,1,0)+IF(X18=$G$18,1,0)+IF(X19=$G$19,1,0)+IF(X20=$G$20,1,0)+IF(X21=$G$21,1,0)+IF(X22=$G$22,1,0)+IF(X23=$G$23,1,0)+IF(X24=$G$24,1,0)+IF(X25=$G$25,1,0)+IF(X26=$G$26,1,0)+IF(X27=$G$27,1,0)+IF(X28=$G$28,1,0)+IF(X29=$G$29,1,0)+IF(X30=$G$30,1,0)+IF(X31=$G$31,1,0)+IF(X32=$G$32,1,0)+IF(X33=$G$33,1,0)+IF(X34=$G$34,1,0)+IF(X35=$G$35,1,0)+IF(X36=$G$36,1,0)+IF(X37=$G$37,1,0)+IF(X38=$G$38,1,0)+IF(X39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="Y3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(Y4=$G$4,1,0)+IF(Y5=$G$5,1,0)+IF(Y6=$G$6,1,0)+IF(Y7=$G$7,1,0)+IF(Y8=$G$8,1,0)+IF(Y9=$G$9,1,0)+IF(Y10=$G$10,1,0)+IF(Y11=$G$11,1,0)+IF(Y12=$G$12,1,0)+IF(Y13=$G$13,1,0)+IF(Y14=$G$14,1,0)+IF(Y15=$G$15,1,0)+IF(Y16=$G$16,1,0)+IF(Y17=$G$17,1,0)+IF(Y18=$G$18,1,0)+IF(Y19=$G$19,1,0)+IF(Y20=$G$20,1,0)+IF(Y21=$G$21,1,0)+IF(Y22=$G$22,1,0)+IF(Y23=$G$23,1,0)+IF(Y24=$G$24,1,0)+IF(Y25=$G$25,1,0)+IF(Y26=$G$26,1,0)+IF(Y27=$G$27,1,0)+IF(Y28=$G$28,1,0)+IF(Y29=$G$29,1,0)+IF(Y30=$G$30,1,0)+IF(Y31=$G$31,1,0)+IF(Y32=$G$32,1,0)+IF(Y33=$G$33,1,0)+IF(Y34=$G$34,1,0)+IF(Y35=$G$35,1,0)+IF(Y36=$G$36,1,0)+IF(Y37=$G$37,1,0)+IF(Y38=$G$38,1,0)+IF(Y39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="Z3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(Z4=$G$4,1,0)+IF(Z5=$G$5,1,0)+IF(Z6=$G$6,1,0)+IF(Z7=$G$7,1,0)+IF(Z8=$G$8,1,0)+IF(Z9=$G$9,1,0)+IF(Z10=$G$10,1,0)+IF(Z11=$G$11,1,0)+IF(Z12=$G$12,1,0)+IF(Z13=$G$13,1,0)+IF(Z14=$G$14,1,0)+IF(Z15=$G$15,1,0)+IF(Z16=$G$16,1,0)+IF(Z17=$G$17,1,0)+IF(Z18=$G$18,1,0)+IF(Z19=$G$19,1,0)+IF(Z20=$G$20,1,0)+IF(Z21=$G$21,1,0)+IF(Z22=$G$22,1,0)+IF(Z23=$G$23,1,0)+IF(Z24=$G$24,1,0)+IF(Z25=$G$25,1,0)+IF(Z26=$G$26,1,0)+IF(Z27=$G$27,1,0)+IF(Z28=$G$28,1,0)+IF(Z29=$G$29,1,0)+IF(Z30=$G$30,1,0)+IF(Z31=$G$31,1,0)+IF(Z32=$G$32,1,0)+IF(Z33=$G$33,1,0)+IF(Z34=$G$34,1,0)+IF(Z35=$G$35,1,0)+IF(Z36=$G$36,1,0)+IF(Z37=$G$37,1,0)+IF(Z38=$G$38,1,0)+IF(Z39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="AA3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(AA4=$G$4,1,0)+IF(AA5=$G$5,1,0)+IF(AA6=$G$6,1,0)+IF(AA7=$G$7,1,0)+IF(AA8=$G$8,1,0)+IF(AA9=$G$9,1,0)+IF(AA10=$G$10,1,0)+IF(AA11=$G$11,1,0)+IF(AA12=$G$12,1,0)+IF(AA13=$G$13,1,0)+IF(AA14=$G$14,1,0)+IF(AA15=$G$15,1,0)+IF(AA16=$G$16,1,0)+IF(AA17=$G$17,1,0)+IF(AA18=$G$18,1,0)+IF(AA19=$G$19,1,0)+IF(AA20=$G$20,1,0)+IF(AA21=$G$21,1,0)+IF(AA22=$G$22,1,0)+IF(AA23=$G$23,1,0)+IF(AA24=$G$24,1,0)+IF(AA25=$G$25,1,0)+IF(AA26=$G$26,1,0)+IF(AA27=$G$27,1,0)+IF(AA28=$G$28,1,0)+IF(AA29=$G$29,1,0)+IF(AA30=$G$30,1,0)+IF(AA31=$G$31,1,0)+IF(AA32=$G$32,1,0)+IF(AA33=$G$33,1,0)+IF(AA34=$G$34,1,0)+IF(AA35=$G$35,1,0)+IF(AA36=$G$36,1,0)+IF(AA37=$G$37,1,0)+IF(AA38=$G$38,1,0)+IF(AA39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="AB3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(AB4=$G$4,1,0)+IF(AB5=$G$5,1,0)+IF(AB6=$G$6,1,0)+IF(AB7=$G$7,1,0)+IF(AB8=$G$8,1,0)+IF(AB9=$G$9,1,0)+IF(AB10=$G$10,1,0)+IF(AB11=$G$11,1,0)+IF(AB12=$G$12,1,0)+IF(AB13=$G$13,1,0)+IF(AB14=$G$14,1,0)+IF(AB15=$G$15,1,0)+IF(AB16=$G$16,1,0)+IF(AB17=$G$17,1,0)+IF(AB18=$G$18,1,0)+IF(AB19=$G$19,1,0)+IF(AB20=$G$20,1,0)+IF(AB21=$G$21,1,0)+IF(AB22=$G$22,1,0)+IF(AB23=$G$23,1,0)+IF(AB24=$G$24,1,0)+IF(AB25=$G$25,1,0)+IF(AB26=$G$26,1,0)+IF(AB27=$G$27,1,0)+IF(AB28=$G$28,1,0)+IF(AB29=$G$29,1,0)+IF(AB30=$G$30,1,0)+IF(AB31=$G$31,1,0)+IF(AB32=$G$32,1,0)+IF(AB33=$G$33,1,0)+IF(AB34=$G$34,1,0)+IF(AB35=$G$35,1,0)+IF(AB36=$G$36,1,0)+IF(AB37=$G$37,1,0)+IF(AB38=$G$38,1,0)+IF(AB39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="AC3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(AC4=$G$4,1,0)+IF(AC5=$G$5,1,0)+IF(AC6=$G$6,1,0)+IF(AC7=$G$7,1,0)+IF(AC8=$G$8,1,0)+IF(AC9=$G$9,1,0)+IF(AC10=$G$10,1,0)+IF(AC11=$G$11,1,0)+IF(AC12=$G$12,1,0)+IF(AC13=$G$13,1,0)+IF(AC14=$G$14,1,0)+IF(AC15=$G$15,1,0)+IF(AC16=$G$16,1,0)+IF(AC17=$G$17,1,0)+IF(AC18=$G$18,1,0)+IF(AC19=$G$19,1,0)+IF(AC20=$G$20,1,0)+IF(AC21=$G$21,1,0)+IF(AC22=$G$22,1,0)+IF(AC23=$G$23,1,0)+IF(AC24=$G$24,1,0)+IF(AC25=$G$25,1,0)+IF(AC26=$G$26,1,0)+IF(AC27=$G$27,1,0)+IF(AC28=$G$28,1,0)+IF(AC29=$G$29,1,0)+IF(AC30=$G$30,1,0)+IF(AC31=$G$31,1,0)+IF(AC32=$G$32,1,0)+IF(AC33=$G$33,1,0)+IF(AC34=$G$34,1,0)+IF(AC35=$G$35,1,0)+IF(AC36=$G$36,1,0)+IF(AC37=$G$37,1,0)+IF(AC38=$G$38,1,0)+IF(AC39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="AD3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(AD4=$G$4,1,0)+IF(AD5=$G$5,1,0)+IF(AD6=$G$6,1,0)+IF(AD7=$G$7,1,0)+IF(AD8=$G$8,1,0)+IF(AD9=$G$9,1,0)+IF(AD10=$G$10,1,0)+IF(AD11=$G$11,1,0)+IF(AD12=$G$12,1,0)+IF(AD13=$G$13,1,0)+IF(AD14=$G$14,1,0)+IF(AD15=$G$15,1,0)+IF(AD16=$G$16,1,0)+IF(AD17=$G$17,1,0)+IF(AD18=$G$18,1,0)+IF(AD19=$G$19,1,0)+IF(AD20=$G$20,1,0)+IF(AD21=$G$21,1,0)+IF(AD22=$G$22,1,0)+IF(AD23=$G$23,1,0)+IF(AD24=$G$24,1,0)+IF(AD25=$G$25,1,0)+IF(AD26=$G$26,1,0)+IF(AD27=$G$27,1,0)+IF(AD28=$G$28,1,0)+IF(AD29=$G$29,1,0)+IF(AD30=$G$30,1,0)+IF(AD31=$G$31,1,0)+IF(AD32=$G$32,1,0)+IF(AD33=$G$33,1,0)+IF(AD34=$G$34,1,0)+IF(AD35=$G$35,1,0)+IF(AD36=$G$36,1,0)+IF(AD37=$G$37,1,0)+IF(AD38=$G$38,1,0)+IF(AD39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="AE3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(AE4=$G$4,1,0)+IF(AE5=$G$5,1,0)+IF(AE6=$G$6,1,0)+IF(AE7=$G$7,1,0)+IF(AE8=$G$8,1,0)+IF(AE9=$G$9,1,0)+IF(AE10=$G$10,1,0)+IF(AE11=$G$11,1,0)+IF(AE12=$G$12,1,0)+IF(AE13=$G$13,1,0)+IF(AE14=$G$14,1,0)+IF(AE15=$G$15,1,0)+IF(AE16=$G$16,1,0)+IF(AE17=$G$17,1,0)+IF(AE18=$G$18,1,0)+IF(AE19=$G$19,1,0)+IF(AE20=$G$20,1,0)+IF(AE21=$G$21,1,0)+IF(AE22=$G$22,1,0)+IF(AE23=$G$23,1,0)+IF(AE24=$G$24,1,0)+IF(AE25=$G$25,1,0)+IF(AE26=$G$26,1,0)+IF(AE27=$G$27,1,0)+IF(AE28=$G$28,1,0)+IF(AE29=$G$29,1,0)+IF(AE30=$G$30,1,0)+IF(AE31=$G$31,1,0)+IF(AE32=$G$32,1,0)+IF(AE33=$G$33,1,0)+IF(AE34=$G$34,1,0)+IF(AE35=$G$35,1,0)+IF(AE36=$G$36,1,0)+IF(AE37=$G$37,1,0)+IF(AE38=$G$38,1,0)+IF(AE39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="AF3" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(AF4=$G$4,1,0)+IF(AF5=$G$5,1,0)+IF(AF6=$G$6,1,0)+IF(AF7=$G$7,1,0)+IF(AF8=$G$8,1,0)+IF(AF9=$G$9,1,0)+IF(AF10=$G$10,1,0)+IF(AF11=$G$11,1,0)+IF(AF12=$G$12,1,0)+IF(AF13=$G$13,1,0)+IF(AF14=$G$14,1,0)+IF(AF15=$G$15,1,0)+IF(AF16=$G$16,1,0)+IF(AF17=$G$17,1,0)+IF(AF18=$G$18,1,0)+IF(AF19=$G$19,1,0)+IF(AF20=$G$20,1,0)+IF(AF21=$G$21,1,0)+IF(AF22=$G$22,1,0)+IF(AF23=$G$23,1,0)+IF(AF24=$G$24,1,0)+IF(AF25=$G$25,1,0)+IF(AF26=$G$26,1,0)+IF(AF27=$G$27,1,0)+IF(AF28=$G$28,1,0)+IF(AF29=$G$29,1,0)+IF(AF30=$G$30,1,0)+IF(AF31=$G$31,1,0)+IF(AF32=$G$32,1,0)+IF(AF33=$G$33,1,0)+IF(AF34=$G$34,1,0)+IF(AF35=$G$35,1,0)+IF(AF36=$G$36,1,0)+IF(AF37=$G$37,1,0)+IF(AF38=$G$38,1,0)+IF(AF39=$G$39,1,0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
         <v>6</v>
       </c>
@@ -1554,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G51" si="2">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
+        <f t="shared" ref="G4:G51" si="0">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
         <v>L</v>
       </c>
       <c r="H4" s="24" t="s">
@@ -1605,7 +1611,7 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="38"/>
       <c r="B5" s="7">
         <v>2</v>
@@ -1623,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>L</v>
       </c>
       <c r="H5" s="24" t="s">
@@ -1674,7 +1680,7 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="38"/>
       <c r="B6" s="7">
         <v>3</v>
@@ -1688,7 +1694,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H6" s="24" t="s">
@@ -1739,7 +1745,7 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="38"/>
       <c r="B7" s="7">
         <v>4</v>
@@ -1753,7 +1759,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -1804,7 +1810,7 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="38"/>
       <c r="B8" s="7">
         <v>5</v>
@@ -1818,7 +1824,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H8" s="24" t="s">
@@ -1869,7 +1875,7 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="39"/>
       <c r="B9" s="7">
         <v>6</v>
@@ -1883,7 +1889,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H9" s="24" t="s">
@@ -1934,7 +1940,7 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
@@ -1954,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>E</v>
       </c>
       <c r="H10" s="24" t="s">
@@ -2005,7 +2011,7 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="38"/>
       <c r="B11" s="7">
         <v>8</v>
@@ -2023,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>E</v>
       </c>
       <c r="H11" s="24" t="s">
@@ -2074,7 +2080,7 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="38"/>
       <c r="B12" s="7">
         <v>9</v>
@@ -2088,7 +2094,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H12" s="24" t="s">
@@ -2139,7 +2145,7 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="38"/>
       <c r="B13" s="7">
         <v>10</v>
@@ -2153,7 +2159,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H13" s="24" t="s">
@@ -2204,7 +2210,7 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="38"/>
       <c r="B14" s="7">
         <v>11</v>
@@ -2218,7 +2224,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H14" s="24" t="s">
@@ -2269,7 +2275,7 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="39"/>
       <c r="B15" s="7">
         <v>12</v>
@@ -2283,7 +2289,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -2334,7 +2340,7 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="45" t="s">
         <v>8</v>
       </c>
@@ -2354,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>E</v>
       </c>
       <c r="H16" s="24" t="s">
@@ -2405,7 +2411,7 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="38"/>
       <c r="B17" s="7">
         <v>14</v>
@@ -2423,7 +2429,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>V</v>
       </c>
       <c r="H17" s="24" t="s">
@@ -2474,7 +2480,7 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="38"/>
       <c r="B18" s="7">
         <v>15</v>
@@ -2488,7 +2494,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H18" s="24" t="s">
@@ -2539,7 +2545,7 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="38"/>
       <c r="B19" s="7">
         <v>16</v>
@@ -2553,7 +2559,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H19" s="24" t="s">
@@ -2604,7 +2610,7 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="38"/>
       <c r="B20" s="7">
         <v>17</v>
@@ -2618,7 +2624,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H20" s="24" t="s">
@@ -2669,7 +2675,7 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="39"/>
       <c r="B21" s="7">
         <v>18</v>
@@ -2683,7 +2689,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H21" s="24" t="s">
@@ -2734,7 +2740,7 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="42" t="s">
         <v>9</v>
       </c>
@@ -2754,7 +2760,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>L</v>
       </c>
       <c r="H22" s="24" t="s">
@@ -2805,7 +2811,7 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="38"/>
       <c r="B23" s="7">
         <v>20</v>
@@ -2823,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>L</v>
       </c>
       <c r="H23" s="24" t="s">
@@ -2874,7 +2880,7 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="38"/>
       <c r="B24" s="7">
         <v>21</v>
@@ -2888,7 +2894,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H24" s="24" t="s">
@@ -2939,7 +2945,7 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="38"/>
       <c r="B25" s="7">
         <v>22</v>
@@ -2953,7 +2959,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H25" s="24" t="s">
@@ -3004,7 +3010,7 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="38"/>
       <c r="B26" s="7">
         <v>23</v>
@@ -3018,7 +3024,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H26" s="24" t="s">
@@ -3069,7 +3075,7 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="39"/>
       <c r="B27" s="7">
         <v>24</v>
@@ -3083,7 +3089,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H27" s="24" t="s">
@@ -3134,7 +3140,7 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="43" t="s">
         <v>10</v>
       </c>
@@ -3154,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>L</v>
       </c>
       <c r="H28" s="24" t="s">
@@ -3205,7 +3211,7 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="38"/>
       <c r="B29" s="7">
         <v>26</v>
@@ -3223,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>L</v>
       </c>
       <c r="H29" s="24" t="s">
@@ -3274,7 +3280,7 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="38"/>
       <c r="B30" s="7">
         <v>27</v>
@@ -3288,7 +3294,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H30" s="24" t="s">
@@ -3339,7 +3345,7 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="38"/>
       <c r="B31" s="7">
         <v>28</v>
@@ -3353,7 +3359,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H31" s="24" t="s">
@@ -3404,7 +3410,7 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="38"/>
       <c r="B32" s="7">
         <v>29</v>
@@ -3418,7 +3424,7 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H32" s="24" t="s">
@@ -3469,7 +3475,7 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="39"/>
       <c r="B33" s="7">
         <v>30</v>
@@ -3483,7 +3489,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H33" s="24" t="s">
@@ -3534,7 +3540,7 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="41" t="s">
         <v>11</v>
       </c>
@@ -3554,7 +3560,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>E</v>
       </c>
       <c r="H34" s="24" t="s">
@@ -3605,7 +3611,7 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="38"/>
       <c r="B35" s="7">
         <v>32</v>
@@ -3623,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>L</v>
       </c>
       <c r="H35" s="24" t="s">
@@ -3674,7 +3680,7 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="38"/>
       <c r="B36" s="7">
         <v>33</v>
@@ -3688,7 +3694,7 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H36" s="24" t="s">
@@ -3739,7 +3745,7 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="38"/>
       <c r="B37" s="7">
         <v>34</v>
@@ -3753,7 +3759,7 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H37" s="24" t="s">
@@ -3804,7 +3810,7 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="38"/>
       <c r="B38" s="7">
         <v>35</v>
@@ -3818,7 +3824,7 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H38" s="24" t="s">
@@ -3869,7 +3875,7 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="39"/>
       <c r="B39" s="7">
         <v>36</v>
@@ -3883,7 +3889,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H39" s="24" t="s">
@@ -3934,7 +3940,7 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="40" t="s">
         <v>12</v>
       </c>
@@ -3947,11 +3953,15 @@
       <c r="D40" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
+      <c r="E40" s="13">
+        <v>1</v>
+      </c>
+      <c r="F40" s="13">
+        <v>1</v>
+      </c>
       <c r="G40" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
+        <f t="shared" si="0"/>
+        <v>E</v>
       </c>
       <c r="H40" s="24" t="s">
         <v>46</v>
@@ -4001,7 +4011,7 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="38"/>
       <c r="B41" s="7">
         <v>38</v>
@@ -4012,11 +4022,15 @@
       <c r="D41" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
+      <c r="E41" s="13">
+        <v>2</v>
+      </c>
+      <c r="F41" s="13">
+        <v>2</v>
+      </c>
       <c r="G41" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
+        <f t="shared" si="0"/>
+        <v>E</v>
       </c>
       <c r="H41" s="24" t="s">
         <v>46</v>
@@ -4066,7 +4080,7 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="38"/>
       <c r="B42" s="7">
         <v>39</v>
@@ -4080,7 +4094,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H42" s="24" t="s">
@@ -4131,7 +4145,7 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="38"/>
       <c r="B43" s="7">
         <v>40</v>
@@ -4145,7 +4159,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H43" s="24" t="s">
@@ -4196,7 +4210,7 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="38"/>
       <c r="B44" s="7">
         <v>41</v>
@@ -4210,7 +4224,7 @@
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H44" s="24" t="s">
@@ -4261,7 +4275,7 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="39"/>
       <c r="B45" s="7">
         <v>42</v>
@@ -4275,7 +4289,7 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H45" s="24" t="s">
@@ -4326,7 +4340,7 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="57" t="s">
         <v>13</v>
       </c>
@@ -4346,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>E</v>
       </c>
       <c r="H46" s="24" t="s">
@@ -4397,7 +4411,7 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="38"/>
       <c r="B47" s="7">
         <v>44</v>
@@ -4408,11 +4422,15 @@
       <c r="D47" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
+      <c r="E47" s="14">
+        <v>1</v>
+      </c>
+      <c r="F47" s="14">
+        <v>1</v>
+      </c>
       <c r="G47" s="14" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
+        <f t="shared" si="0"/>
+        <v>E</v>
       </c>
       <c r="H47" s="24" t="s">
         <v>104</v>
@@ -4462,7 +4480,7 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="38"/>
       <c r="B48" s="7">
         <v>45</v>
@@ -4476,7 +4494,7 @@
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H48" s="24" t="s">
@@ -4527,7 +4545,7 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="38"/>
       <c r="B49" s="7">
         <v>46</v>
@@ -4541,7 +4559,7 @@
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H49" s="24" t="s">
@@ -4592,7 +4610,7 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="38"/>
       <c r="B50" s="7">
         <v>47</v>
@@ -4606,7 +4624,7 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H50" s="24" t="s">
@@ -4657,7 +4675,7 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="39"/>
       <c r="B51" s="7">
         <v>48</v>
@@ -4671,7 +4689,7 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H51" s="24" t="s">
@@ -4722,7 +4740,7 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="60" t="s">
         <v>77</v>
       </c>
@@ -4738,7 +4756,7 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15" t="str">
-        <f t="shared" ref="G52:G75" si="3">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
+        <f t="shared" ref="G52:G75" si="1">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
       <c r="H52" s="26" t="s">
@@ -4789,7 +4807,7 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="61"/>
       <c r="B53" s="7">
         <v>50</v>
@@ -4803,7 +4821,7 @@
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H53" s="26" t="s">
@@ -4854,7 +4872,7 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="61"/>
       <c r="B54" s="7">
         <v>51</v>
@@ -4868,7 +4886,7 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H54" s="26" t="s">
@@ -4919,7 +4937,7 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="61"/>
       <c r="B55" s="7">
         <v>52</v>
@@ -4933,7 +4951,7 @@
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H55" s="26" t="s">
@@ -4985,7 +5003,7 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="61"/>
       <c r="B56" s="7">
         <v>53</v>
@@ -4999,7 +5017,7 @@
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H56" s="26" t="s">
@@ -5050,7 +5068,7 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="62"/>
       <c r="B57" s="7">
         <v>54</v>
@@ -5064,7 +5082,7 @@
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H57" s="26" t="s">
@@ -5115,7 +5133,7 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="63" t="s">
         <v>78</v>
       </c>
@@ -5131,7 +5149,7 @@
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
       <c r="G58" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H58" s="26" t="s">
@@ -5182,7 +5200,7 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="64"/>
       <c r="B59" s="7">
         <v>56</v>
@@ -5196,7 +5214,7 @@
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H59" s="26" t="s">
@@ -5247,7 +5265,7 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="64"/>
       <c r="B60" s="7">
         <v>57</v>
@@ -5261,7 +5279,7 @@
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H60" s="26" t="s">
@@ -5312,7 +5330,7 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="64"/>
       <c r="B61" s="7">
         <v>58</v>
@@ -5326,7 +5344,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H61" s="26" t="s">
@@ -5377,7 +5395,7 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="64"/>
       <c r="B62" s="7">
         <v>59</v>
@@ -5391,7 +5409,7 @@
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H62" s="26" t="s">
@@ -5442,7 +5460,7 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="65"/>
       <c r="B63" s="7">
         <v>60</v>
@@ -5456,7 +5474,7 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H63" s="26" t="s">
@@ -5507,7 +5525,7 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="51" t="s">
         <v>79</v>
       </c>
@@ -5523,7 +5541,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H64" s="26" t="s">
@@ -5574,7 +5592,7 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="52"/>
       <c r="B65" s="7">
         <v>62</v>
@@ -5588,7 +5606,7 @@
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H65" s="26" t="s">
@@ -5639,7 +5657,7 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="52"/>
       <c r="B66" s="7">
         <v>63</v>
@@ -5653,7 +5671,7 @@
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H66" s="26" t="s">
@@ -5704,7 +5722,7 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="52"/>
       <c r="B67" s="7">
         <v>64</v>
@@ -5718,7 +5736,7 @@
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H67" s="26" t="s">
@@ -5769,7 +5787,7 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="52"/>
       <c r="B68" s="7">
         <v>65</v>
@@ -5783,7 +5801,7 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H68" s="26" t="s">
@@ -5834,7 +5852,7 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="53"/>
       <c r="B69" s="7">
         <v>66</v>
@@ -5848,7 +5866,7 @@
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H69" s="26" t="s">
@@ -5899,7 +5917,7 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="54" t="s">
         <v>46</v>
       </c>
@@ -5915,7 +5933,7 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
       <c r="G70" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H70" s="26" t="s">
@@ -5966,7 +5984,7 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>68</v>
@@ -5980,7 +5998,7 @@
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
       <c r="G71" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H71" s="26" t="s">
@@ -6031,7 +6049,7 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="55"/>
       <c r="B72" s="7">
         <v>69</v>
@@ -6045,7 +6063,7 @@
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
       <c r="G72" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H72" s="26" t="s">
@@ -6096,7 +6114,7 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="55"/>
       <c r="B73" s="7">
         <v>70</v>
@@ -6110,7 +6128,7 @@
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H73" s="26" t="s">
@@ -6161,7 +6179,7 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="55"/>
       <c r="B74" s="7">
         <v>71</v>
@@ -6175,7 +6193,7 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H74" s="26" t="s">
@@ -6226,7 +6244,7 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="56"/>
       <c r="B75" s="7">
         <v>72</v>
@@ -6240,7 +6258,7 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H75" s="26" t="s">
@@ -6291,7 +6309,7 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
@@ -6302,7 +6320,7 @@
       <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6352,7 +6370,7 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
@@ -6363,107 +6381,107 @@
       <c r="F77" s="33"/>
       <c r="G77" s="34"/>
       <c r="H77" s="28">
-        <f t="shared" ref="H77:S77" si="4">SUM(H78:H81)</f>
+        <f>SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(I78:I81)</f>
         <v>0</v>
       </c>
       <c r="J77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(J78:J81)</f>
         <v>0</v>
       </c>
       <c r="K77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(K78:K81)</f>
         <v>0</v>
       </c>
       <c r="L77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(L78:L81)</f>
         <v>0</v>
       </c>
       <c r="M77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(M78:M81)</f>
         <v>0</v>
       </c>
       <c r="N77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(N78:N81)</f>
         <v>0</v>
       </c>
       <c r="O77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(O78:O81)</f>
         <v>0</v>
       </c>
       <c r="P77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(P78:P81)</f>
         <v>0</v>
       </c>
       <c r="Q77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(Q78:Q81)</f>
         <v>0</v>
       </c>
       <c r="R77" s="28">
-        <f t="shared" si="4"/>
+        <f>SUM(R78:R81)</f>
         <v>0</v>
       </c>
       <c r="S77" s="28">
-        <f t="shared" si="4"/>
-        <v>63</v>
+        <f>SUM(S78:S81)</f>
+        <v>55</v>
       </c>
       <c r="T77" s="28">
-        <f t="shared" ref="T77:AF77" si="5">SUM(T78:T81)</f>
-        <v>63</v>
+        <f>SUM(T78:T81)</f>
+        <v>55</v>
       </c>
       <c r="U77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(U78:U81)</f>
+        <v>55</v>
       </c>
       <c r="V77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(V78:V81)</f>
+        <v>55</v>
       </c>
       <c r="W77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(W78:W81)</f>
+        <v>55</v>
       </c>
       <c r="X77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(X78:X81)</f>
+        <v>55</v>
       </c>
       <c r="Y77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(Y78:Y81)</f>
+        <v>55</v>
       </c>
       <c r="Z77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(Z78:Z81)</f>
+        <v>55</v>
       </c>
       <c r="AA77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(AA78:AA81)</f>
+        <v>55</v>
       </c>
       <c r="AB77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(AB78:AB81)</f>
+        <v>55</v>
       </c>
       <c r="AC77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(AC78:AC81)</f>
+        <v>55</v>
       </c>
       <c r="AD77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(AD78:AD81)</f>
+        <v>55</v>
       </c>
       <c r="AE77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
+        <f>SUM(AE78:AE81)</f>
+        <v>55</v>
       </c>
       <c r="AF77" s="28">
-        <f t="shared" si="5"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+        <f>SUM(AF78:AF81)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6472,107 +6490,107 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="6">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="2">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6581,107 +6599,107 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="7">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="3">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="7"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6690,107 +6708,107 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="8">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="4">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6799,107 +6817,107 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="9">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="5">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6933,7 +6951,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -6967,7 +6985,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7001,7 +7019,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7035,7 +7053,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7069,7 +7087,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7103,7 +7121,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7137,7 +7155,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7171,7 +7189,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7205,7 +7223,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7239,7 +7257,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7273,7 +7291,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7307,7 +7325,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7341,7 +7359,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7375,7 +7393,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7409,7 +7427,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7443,7 +7461,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7477,7 +7495,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7511,7 +7529,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7545,7 +7563,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7554,7 +7572,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7563,7 +7581,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7572,7 +7590,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7581,7 +7599,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7590,7 +7608,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7599,7 +7617,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7608,7 +7626,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7617,7 +7635,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7626,7 +7644,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7635,7 +7653,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7644,7 +7662,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7653,7 +7671,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7662,7 +7680,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7671,7 +7689,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7680,7 +7698,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7689,7 +7707,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7698,7 +7716,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7707,7 +7725,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7716,7 +7734,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7725,7 +7743,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7734,7 +7752,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7743,7 +7761,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7752,7 +7770,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7762,9 +7780,9 @@
       <c r="G124" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H2:S77">
-    <sortCondition descending="1" ref="H3:S3"/>
-    <sortCondition descending="1" ref="H77:S77"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H2:AF77">
+    <sortCondition descending="1" ref="H3:AF3"/>
+    <sortCondition descending="1" ref="H77:AF77"/>
   </sortState>
   <mergeCells count="18">
     <mergeCell ref="A64:A69"/>
@@ -7799,14 +7817,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="15" width="11.42578125" customWidth="1"/>
+    <col min="1" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="15" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>16</v>
@@ -7853,7 +7871,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -7898,7 +7916,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -7943,7 +7961,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -7988,7 +8006,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -8033,7 +8051,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -8078,7 +8096,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -8123,7 +8141,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -8168,7 +8186,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -8213,7 +8231,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -8258,7 +8276,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -8303,7 +8321,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>16</v>
@@ -8348,7 +8366,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>16</v>
@@ -8393,7 +8411,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
@@ -8438,7 +8456,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -8483,7 +8501,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
@@ -8528,7 +8546,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>16</v>
@@ -8573,7 +8591,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
@@ -8618,7 +8636,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>16</v>
@@ -8663,7 +8681,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>16</v>
@@ -8708,7 +8726,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>16</v>
@@ -8753,7 +8771,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -8798,7 +8816,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -8843,7 +8861,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>16</v>
@@ -8888,7 +8906,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>16</v>
@@ -8933,7 +8951,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -8978,7 +8996,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>16</v>
@@ -9023,7 +9041,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>16</v>
@@ -9068,7 +9086,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>16</v>
@@ -9113,7 +9131,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>16</v>
@@ -9158,7 +9176,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>16</v>
@@ -9203,7 +9221,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>16</v>
@@ -9248,7 +9266,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>16</v>
@@ -9293,7 +9311,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>16</v>
@@ -9338,7 +9356,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>16</v>
@@ -9383,7 +9401,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>16</v>
@@ -9428,7 +9446,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>16</v>
@@ -9473,7 +9491,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>16</v>
@@ -9518,7 +9536,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>16</v>
@@ -9563,7 +9581,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>16</v>
@@ -9608,7 +9626,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>16</v>
@@ -9653,7 +9671,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>16</v>
@@ -9698,7 +9716,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>16</v>
@@ -9743,7 +9761,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>16</v>
@@ -9788,7 +9806,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>16</v>
@@ -9833,7 +9851,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>16</v>
@@ -9878,7 +9896,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>16</v>
@@ -9923,7 +9941,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>16</v>
@@ -9968,7 +9986,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>16</v>
@@ -10013,7 +10031,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>16</v>
@@ -10058,7 +10076,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>16</v>
@@ -10103,7 +10121,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>16</v>
@@ -10148,7 +10166,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>16</v>
@@ -10193,7 +10211,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>16</v>
@@ -10238,7 +10256,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>16</v>
@@ -10283,7 +10301,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>16</v>
@@ -10328,7 +10346,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>16</v>
@@ -10373,7 +10391,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>16</v>
@@ -10418,7 +10436,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>16</v>
@@ -10463,7 +10481,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>16</v>
@@ -10508,7 +10526,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>16</v>
@@ -10553,7 +10571,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>16</v>
@@ -10598,7 +10616,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>16</v>
@@ -10643,7 +10661,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>16</v>
@@ -10688,7 +10706,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>16</v>
@@ -10733,7 +10751,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>16</v>
@@ -10778,7 +10796,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>16</v>
@@ -10823,7 +10841,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>16</v>
@@ -10868,7 +10886,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>16</v>
@@ -10913,7 +10931,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>16</v>
@@ -10958,7 +10976,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>16</v>
@@ -11003,7 +11021,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>16</v>
@@ -11048,7 +11066,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>16</v>
@@ -11093,7 +11111,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>16</v>
@@ -11138,7 +11156,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>16</v>
@@ -11183,7 +11201,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>16</v>
@@ -11228,7 +11246,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>16</v>
@@ -11273,7 +11291,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>16</v>
@@ -11318,7 +11336,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>16</v>
@@ -11363,7 +11381,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>16</v>
@@ -11408,7 +11426,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>16</v>
@@ -11453,7 +11471,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>16</v>
@@ -11498,7 +11516,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>16</v>
@@ -11543,7 +11561,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>16</v>
@@ -11588,7 +11606,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>16</v>
@@ -11633,7 +11651,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>16</v>
@@ -11678,7 +11696,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>16</v>
@@ -11723,7 +11741,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>16</v>
@@ -11768,7 +11786,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>16</v>
@@ -11813,7 +11831,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>16</v>
@@ -11858,7 +11876,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>16</v>
@@ -11903,7 +11921,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>16</v>
@@ -11948,7 +11966,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>16</v>
@@ -11993,7 +12011,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>16</v>
@@ -12038,7 +12056,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>16</v>
@@ -12083,7 +12101,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>16</v>
@@ -12128,7 +12146,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>16</v>
@@ -12173,7 +12191,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>16</v>
@@ -12218,7 +12236,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>16</v>
@@ -12263,7 +12281,7 @@
         <v>SI(G28-H28=-100;0;</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12289,9 +12307,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="11" width="10.7109375" customWidth="1"/>
+    <col min="1" max="11" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12302,26 +12320,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="11" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="11" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -12329,61 +12347,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -12391,7 +12409,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -12399,19 +12417,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -12419,19 +12437,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -12439,19 +12457,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -12459,13 +12477,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -12473,229 +12491,229 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="1"/>
     </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1"/>
     </row>
-    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="1"/>
     </row>
-    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="1"/>
     </row>
-    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="1"/>
     </row>
-    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="1"/>
     </row>
-    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="1"/>
     </row>
-    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="1"/>
     </row>
-    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="1"/>
     </row>
-    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1"/>
     </row>
   </sheetData>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="14_{5A23C1EE-031E-437C-A77D-23726E51E3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6A08344-E9E1-47B0-BADC-B098CA9ADB93}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1875F05A-1114-4066-8DB0-2B98DE64359D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -458,7 +480,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -595,6 +617,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor rgb="FFD8D8D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -749,7 +777,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -934,6 +962,9 @@
     <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,10 +994,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1257,23 +1284,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" customWidth="1"/>
-    <col min="12" max="12" width="5.77734375" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" customWidth="1"/>
-    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="32" width="5.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.7109375" customWidth="1"/>
+    <col min="19" max="32" width="5.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>101</v>
       </c>
@@ -1292,28 +1318,28 @@
       <c r="J1" s="19">
         <v>3</v>
       </c>
-      <c r="K1" s="20">
+      <c r="K1" s="66">
         <v>4</v>
       </c>
-      <c r="L1" s="20">
+      <c r="L1" s="66">
         <v>5</v>
       </c>
-      <c r="M1" s="20">
+      <c r="M1" s="66">
         <v>6</v>
       </c>
-      <c r="N1" s="20">
+      <c r="N1" s="66">
         <v>7</v>
       </c>
-      <c r="O1" s="20">
+      <c r="O1" s="66">
         <v>8</v>
       </c>
-      <c r="P1" s="20">
+      <c r="P1" s="66">
         <v>9</v>
       </c>
-      <c r="Q1" s="20">
-        <v>10</v>
-      </c>
-      <c r="R1" s="20">
+      <c r="Q1" s="66">
+        <v>10</v>
+      </c>
+      <c r="R1" s="66">
         <v>11</v>
       </c>
       <c r="S1" s="20">
@@ -1359,7 +1385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" ht="143.25" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>47</v>
       </c>
@@ -1374,35 +1400,35 @@
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="K2" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="J2" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="M2" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="N2" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="M2" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="N2" s="30" t="s">
+      <c r="O2" s="30" t="s">
         <v>109</v>
-      </c>
-      <c r="O2" s="29" t="s">
-        <v>114</v>
       </c>
       <c r="P2" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="30" t="s">
+      <c r="Q2" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="R2" s="30" t="s">
         <v>105</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>115</v>
       </c>
       <c r="S2" s="29"/>
       <c r="T2" s="29"/>
@@ -1419,7 +1445,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1439,108 +1465,108 @@
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="14">
-        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+      <c r="H3" s="14" cm="1">
+        <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$75=H4:H75)*($G$4:$G$75&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="I3" s="14" cm="1">
+        <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$75=I4:I75)*($G$4:$G$75&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="J3" s="14" cm="1">
+        <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$75=J4:J75)*($G$4:$G$75&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="K3" s="14" cm="1">
+        <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$75=K4:K75)*($G$4:$G$75&lt;&gt;""))</f>
         <v>9</v>
       </c>
-      <c r="I3" s="14">
-        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
+      <c r="L3" s="14" cm="1">
+        <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$75=L4:L75)*($G$4:$G$75&lt;&gt;""))</f>
         <v>9</v>
       </c>
-      <c r="J3" s="14">
-        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
-        <v>8</v>
-      </c>
-      <c r="K3" s="14">
-        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
-        <v>8</v>
-      </c>
-      <c r="L3" s="14">
-        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+      <c r="M3" s="14" cm="1">
+        <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$75=M4:M75)*($G$4:$G$75&lt;&gt;""))</f>
+        <v>9</v>
+      </c>
+      <c r="N3" s="14" cm="1">
+        <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$75=N4:N75)*($G$4:$G$75&lt;&gt;""))</f>
         <v>7</v>
       </c>
-      <c r="M3" s="14">
-        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
+      <c r="O3" s="14" cm="1">
+        <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$75=O4:O75)*($G$4:$G$75&lt;&gt;""))</f>
         <v>7</v>
       </c>
-      <c r="N3" s="14">
-        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+      <c r="P3" s="14" cm="1">
+        <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$75=P4:P75)*($G$4:$G$75&lt;&gt;""))</f>
         <v>6</v>
       </c>
-      <c r="O3" s="14">
-        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
+      <c r="Q3" s="14" cm="1">
+        <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$75=Q4:Q75)*($G$4:$G$75&lt;&gt;""))</f>
         <v>6</v>
       </c>
-      <c r="P3" s="14">
-        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
+      <c r="R3" s="14" cm="1">
+        <f t="array" ref="R3">SUMPRODUCT(($G$4:$G$75=R4:R75)*($G$4:$G$75&lt;&gt;""))</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="14">
-        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
-        <v>5</v>
-      </c>
-      <c r="R3" s="14">
-        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
-        <v>5</v>
-      </c>
       <c r="S3" s="14">
-        <f>SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
+        <v>24</v>
       </c>
       <c r="T3" s="14">
-        <f>SUM(IF(T4=$G$4,1,0)+IF(T5=$G$5,1,0)+IF(T6=$G$6,1,0)+IF(T7=$G$7,1,0)+IF(T8=$G$8,1,0)+IF(T9=$G$9,1,0)+IF(T10=$G$10,1,0)+IF(T11=$G$11,1,0)+IF(T12=$G$12,1,0)+IF(T13=$G$13,1,0)+IF(T14=$G$14,1,0)+IF(T15=$G$15,1,0)+IF(T16=$G$16,1,0)+IF(T17=$G$17,1,0)+IF(T18=$G$18,1,0)+IF(T19=$G$19,1,0)+IF(T20=$G$20,1,0)+IF(T21=$G$21,1,0)+IF(T22=$G$22,1,0)+IF(T23=$G$23,1,0)+IF(T24=$G$24,1,0)+IF(T25=$G$25,1,0)+IF(T26=$G$26,1,0)+IF(T27=$G$27,1,0)+IF(T28=$G$28,1,0)+IF(T29=$G$29,1,0)+IF(T30=$G$30,1,0)+IF(T31=$G$31,1,0)+IF(T32=$G$32,1,0)+IF(T33=$G$33,1,0)+IF(T34=$G$34,1,0)+IF(T35=$G$35,1,0)+IF(T36=$G$36,1,0)+IF(T37=$G$37,1,0)+IF(T38=$G$38,1,0)+IF(T39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="U3" s="14">
-        <f>SUM(IF(U4=$G$4,1,0)+IF(U5=$G$5,1,0)+IF(U6=$G$6,1,0)+IF(U7=$G$7,1,0)+IF(U8=$G$8,1,0)+IF(U9=$G$9,1,0)+IF(U10=$G$10,1,0)+IF(U11=$G$11,1,0)+IF(U12=$G$12,1,0)+IF(U13=$G$13,1,0)+IF(U14=$G$14,1,0)+IF(U15=$G$15,1,0)+IF(U16=$G$16,1,0)+IF(U17=$G$17,1,0)+IF(U18=$G$18,1,0)+IF(U19=$G$19,1,0)+IF(U20=$G$20,1,0)+IF(U21=$G$21,1,0)+IF(U22=$G$22,1,0)+IF(U23=$G$23,1,0)+IF(U24=$G$24,1,0)+IF(U25=$G$25,1,0)+IF(U26=$G$26,1,0)+IF(U27=$G$27,1,0)+IF(U28=$G$28,1,0)+IF(U29=$G$29,1,0)+IF(U30=$G$30,1,0)+IF(U31=$G$31,1,0)+IF(U32=$G$32,1,0)+IF(U33=$G$33,1,0)+IF(U34=$G$34,1,0)+IF(U35=$G$35,1,0)+IF(U36=$G$36,1,0)+IF(U37=$G$37,1,0)+IF(U38=$G$38,1,0)+IF(U39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="V3" s="14">
-        <f>SUM(IF(V4=$G$4,1,0)+IF(V5=$G$5,1,0)+IF(V6=$G$6,1,0)+IF(V7=$G$7,1,0)+IF(V8=$G$8,1,0)+IF(V9=$G$9,1,0)+IF(V10=$G$10,1,0)+IF(V11=$G$11,1,0)+IF(V12=$G$12,1,0)+IF(V13=$G$13,1,0)+IF(V14=$G$14,1,0)+IF(V15=$G$15,1,0)+IF(V16=$G$16,1,0)+IF(V17=$G$17,1,0)+IF(V18=$G$18,1,0)+IF(V19=$G$19,1,0)+IF(V20=$G$20,1,0)+IF(V21=$G$21,1,0)+IF(V22=$G$22,1,0)+IF(V23=$G$23,1,0)+IF(V24=$G$24,1,0)+IF(V25=$G$25,1,0)+IF(V26=$G$26,1,0)+IF(V27=$G$27,1,0)+IF(V28=$G$28,1,0)+IF(V29=$G$29,1,0)+IF(V30=$G$30,1,0)+IF(V31=$G$31,1,0)+IF(V32=$G$32,1,0)+IF(V33=$G$33,1,0)+IF(V34=$G$34,1,0)+IF(V35=$G$35,1,0)+IF(V36=$G$36,1,0)+IF(V37=$G$37,1,0)+IF(V38=$G$38,1,0)+IF(V39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="W3" s="14">
-        <f>SUM(IF(W4=$G$4,1,0)+IF(W5=$G$5,1,0)+IF(W6=$G$6,1,0)+IF(W7=$G$7,1,0)+IF(W8=$G$8,1,0)+IF(W9=$G$9,1,0)+IF(W10=$G$10,1,0)+IF(W11=$G$11,1,0)+IF(W12=$G$12,1,0)+IF(W13=$G$13,1,0)+IF(W14=$G$14,1,0)+IF(W15=$G$15,1,0)+IF(W16=$G$16,1,0)+IF(W17=$G$17,1,0)+IF(W18=$G$18,1,0)+IF(W19=$G$19,1,0)+IF(W20=$G$20,1,0)+IF(W21=$G$21,1,0)+IF(W22=$G$22,1,0)+IF(W23=$G$23,1,0)+IF(W24=$G$24,1,0)+IF(W25=$G$25,1,0)+IF(W26=$G$26,1,0)+IF(W27=$G$27,1,0)+IF(W28=$G$28,1,0)+IF(W29=$G$29,1,0)+IF(W30=$G$30,1,0)+IF(W31=$G$31,1,0)+IF(W32=$G$32,1,0)+IF(W33=$G$33,1,0)+IF(W34=$G$34,1,0)+IF(W35=$G$35,1,0)+IF(W36=$G$36,1,0)+IF(W37=$G$37,1,0)+IF(W38=$G$38,1,0)+IF(W39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="X3" s="14">
-        <f>SUM(IF(X4=$G$4,1,0)+IF(X5=$G$5,1,0)+IF(X6=$G$6,1,0)+IF(X7=$G$7,1,0)+IF(X8=$G$8,1,0)+IF(X9=$G$9,1,0)+IF(X10=$G$10,1,0)+IF(X11=$G$11,1,0)+IF(X12=$G$12,1,0)+IF(X13=$G$13,1,0)+IF(X14=$G$14,1,0)+IF(X15=$G$15,1,0)+IF(X16=$G$16,1,0)+IF(X17=$G$17,1,0)+IF(X18=$G$18,1,0)+IF(X19=$G$19,1,0)+IF(X20=$G$20,1,0)+IF(X21=$G$21,1,0)+IF(X22=$G$22,1,0)+IF(X23=$G$23,1,0)+IF(X24=$G$24,1,0)+IF(X25=$G$25,1,0)+IF(X26=$G$26,1,0)+IF(X27=$G$27,1,0)+IF(X28=$G$28,1,0)+IF(X29=$G$29,1,0)+IF(X30=$G$30,1,0)+IF(X31=$G$31,1,0)+IF(X32=$G$32,1,0)+IF(X33=$G$33,1,0)+IF(X34=$G$34,1,0)+IF(X35=$G$35,1,0)+IF(X36=$G$36,1,0)+IF(X37=$G$37,1,0)+IF(X38=$G$38,1,0)+IF(X39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="Y3" s="14">
-        <f>SUM(IF(Y4=$G$4,1,0)+IF(Y5=$G$5,1,0)+IF(Y6=$G$6,1,0)+IF(Y7=$G$7,1,0)+IF(Y8=$G$8,1,0)+IF(Y9=$G$9,1,0)+IF(Y10=$G$10,1,0)+IF(Y11=$G$11,1,0)+IF(Y12=$G$12,1,0)+IF(Y13=$G$13,1,0)+IF(Y14=$G$14,1,0)+IF(Y15=$G$15,1,0)+IF(Y16=$G$16,1,0)+IF(Y17=$G$17,1,0)+IF(Y18=$G$18,1,0)+IF(Y19=$G$19,1,0)+IF(Y20=$G$20,1,0)+IF(Y21=$G$21,1,0)+IF(Y22=$G$22,1,0)+IF(Y23=$G$23,1,0)+IF(Y24=$G$24,1,0)+IF(Y25=$G$25,1,0)+IF(Y26=$G$26,1,0)+IF(Y27=$G$27,1,0)+IF(Y28=$G$28,1,0)+IF(Y29=$G$29,1,0)+IF(Y30=$G$30,1,0)+IF(Y31=$G$31,1,0)+IF(Y32=$G$32,1,0)+IF(Y33=$G$33,1,0)+IF(Y34=$G$34,1,0)+IF(Y35=$G$35,1,0)+IF(Y36=$G$36,1,0)+IF(Y37=$G$37,1,0)+IF(Y38=$G$38,1,0)+IF(Y39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="Z3" s="14">
-        <f>SUM(IF(Z4=$G$4,1,0)+IF(Z5=$G$5,1,0)+IF(Z6=$G$6,1,0)+IF(Z7=$G$7,1,0)+IF(Z8=$G$8,1,0)+IF(Z9=$G$9,1,0)+IF(Z10=$G$10,1,0)+IF(Z11=$G$11,1,0)+IF(Z12=$G$12,1,0)+IF(Z13=$G$13,1,0)+IF(Z14=$G$14,1,0)+IF(Z15=$G$15,1,0)+IF(Z16=$G$16,1,0)+IF(Z17=$G$17,1,0)+IF(Z18=$G$18,1,0)+IF(Z19=$G$19,1,0)+IF(Z20=$G$20,1,0)+IF(Z21=$G$21,1,0)+IF(Z22=$G$22,1,0)+IF(Z23=$G$23,1,0)+IF(Z24=$G$24,1,0)+IF(Z25=$G$25,1,0)+IF(Z26=$G$26,1,0)+IF(Z27=$G$27,1,0)+IF(Z28=$G$28,1,0)+IF(Z29=$G$29,1,0)+IF(Z30=$G$30,1,0)+IF(Z31=$G$31,1,0)+IF(Z32=$G$32,1,0)+IF(Z33=$G$33,1,0)+IF(Z34=$G$34,1,0)+IF(Z35=$G$35,1,0)+IF(Z36=$G$36,1,0)+IF(Z37=$G$37,1,0)+IF(Z38=$G$38,1,0)+IF(Z39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="AA3" s="14">
-        <f>SUM(IF(AA4=$G$4,1,0)+IF(AA5=$G$5,1,0)+IF(AA6=$G$6,1,0)+IF(AA7=$G$7,1,0)+IF(AA8=$G$8,1,0)+IF(AA9=$G$9,1,0)+IF(AA10=$G$10,1,0)+IF(AA11=$G$11,1,0)+IF(AA12=$G$12,1,0)+IF(AA13=$G$13,1,0)+IF(AA14=$G$14,1,0)+IF(AA15=$G$15,1,0)+IF(AA16=$G$16,1,0)+IF(AA17=$G$17,1,0)+IF(AA18=$G$18,1,0)+IF(AA19=$G$19,1,0)+IF(AA20=$G$20,1,0)+IF(AA21=$G$21,1,0)+IF(AA22=$G$22,1,0)+IF(AA23=$G$23,1,0)+IF(AA24=$G$24,1,0)+IF(AA25=$G$25,1,0)+IF(AA26=$G$26,1,0)+IF(AA27=$G$27,1,0)+IF(AA28=$G$28,1,0)+IF(AA29=$G$29,1,0)+IF(AA30=$G$30,1,0)+IF(AA31=$G$31,1,0)+IF(AA32=$G$32,1,0)+IF(AA33=$G$33,1,0)+IF(AA34=$G$34,1,0)+IF(AA35=$G$35,1,0)+IF(AA36=$G$36,1,0)+IF(AA37=$G$37,1,0)+IF(AA38=$G$38,1,0)+IF(AA39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="AB3" s="14">
-        <f>SUM(IF(AB4=$G$4,1,0)+IF(AB5=$G$5,1,0)+IF(AB6=$G$6,1,0)+IF(AB7=$G$7,1,0)+IF(AB8=$G$8,1,0)+IF(AB9=$G$9,1,0)+IF(AB10=$G$10,1,0)+IF(AB11=$G$11,1,0)+IF(AB12=$G$12,1,0)+IF(AB13=$G$13,1,0)+IF(AB14=$G$14,1,0)+IF(AB15=$G$15,1,0)+IF(AB16=$G$16,1,0)+IF(AB17=$G$17,1,0)+IF(AB18=$G$18,1,0)+IF(AB19=$G$19,1,0)+IF(AB20=$G$20,1,0)+IF(AB21=$G$21,1,0)+IF(AB22=$G$22,1,0)+IF(AB23=$G$23,1,0)+IF(AB24=$G$24,1,0)+IF(AB25=$G$25,1,0)+IF(AB26=$G$26,1,0)+IF(AB27=$G$27,1,0)+IF(AB28=$G$28,1,0)+IF(AB29=$G$29,1,0)+IF(AB30=$G$30,1,0)+IF(AB31=$G$31,1,0)+IF(AB32=$G$32,1,0)+IF(AB33=$G$33,1,0)+IF(AB34=$G$34,1,0)+IF(AB35=$G$35,1,0)+IF(AB36=$G$36,1,0)+IF(AB37=$G$37,1,0)+IF(AB38=$G$38,1,0)+IF(AB39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="AC3" s="14">
-        <f>SUM(IF(AC4=$G$4,1,0)+IF(AC5=$G$5,1,0)+IF(AC6=$G$6,1,0)+IF(AC7=$G$7,1,0)+IF(AC8=$G$8,1,0)+IF(AC9=$G$9,1,0)+IF(AC10=$G$10,1,0)+IF(AC11=$G$11,1,0)+IF(AC12=$G$12,1,0)+IF(AC13=$G$13,1,0)+IF(AC14=$G$14,1,0)+IF(AC15=$G$15,1,0)+IF(AC16=$G$16,1,0)+IF(AC17=$G$17,1,0)+IF(AC18=$G$18,1,0)+IF(AC19=$G$19,1,0)+IF(AC20=$G$20,1,0)+IF(AC21=$G$21,1,0)+IF(AC22=$G$22,1,0)+IF(AC23=$G$23,1,0)+IF(AC24=$G$24,1,0)+IF(AC25=$G$25,1,0)+IF(AC26=$G$26,1,0)+IF(AC27=$G$27,1,0)+IF(AC28=$G$28,1,0)+IF(AC29=$G$29,1,0)+IF(AC30=$G$30,1,0)+IF(AC31=$G$31,1,0)+IF(AC32=$G$32,1,0)+IF(AC33=$G$33,1,0)+IF(AC34=$G$34,1,0)+IF(AC35=$G$35,1,0)+IF(AC36=$G$36,1,0)+IF(AC37=$G$37,1,0)+IF(AC38=$G$38,1,0)+IF(AC39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="AD3" s="14">
-        <f>SUM(IF(AD4=$G$4,1,0)+IF(AD5=$G$5,1,0)+IF(AD6=$G$6,1,0)+IF(AD7=$G$7,1,0)+IF(AD8=$G$8,1,0)+IF(AD9=$G$9,1,0)+IF(AD10=$G$10,1,0)+IF(AD11=$G$11,1,0)+IF(AD12=$G$12,1,0)+IF(AD13=$G$13,1,0)+IF(AD14=$G$14,1,0)+IF(AD15=$G$15,1,0)+IF(AD16=$G$16,1,0)+IF(AD17=$G$17,1,0)+IF(AD18=$G$18,1,0)+IF(AD19=$G$19,1,0)+IF(AD20=$G$20,1,0)+IF(AD21=$G$21,1,0)+IF(AD22=$G$22,1,0)+IF(AD23=$G$23,1,0)+IF(AD24=$G$24,1,0)+IF(AD25=$G$25,1,0)+IF(AD26=$G$26,1,0)+IF(AD27=$G$27,1,0)+IF(AD28=$G$28,1,0)+IF(AD29=$G$29,1,0)+IF(AD30=$G$30,1,0)+IF(AD31=$G$31,1,0)+IF(AD32=$G$32,1,0)+IF(AD33=$G$33,1,0)+IF(AD34=$G$34,1,0)+IF(AD35=$G$35,1,0)+IF(AD36=$G$36,1,0)+IF(AD37=$G$37,1,0)+IF(AD38=$G$38,1,0)+IF(AD39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="AE3" s="14">
-        <f>SUM(IF(AE4=$G$4,1,0)+IF(AE5=$G$5,1,0)+IF(AE6=$G$6,1,0)+IF(AE7=$G$7,1,0)+IF(AE8=$G$8,1,0)+IF(AE9=$G$9,1,0)+IF(AE10=$G$10,1,0)+IF(AE11=$G$11,1,0)+IF(AE12=$G$12,1,0)+IF(AE13=$G$13,1,0)+IF(AE14=$G$14,1,0)+IF(AE15=$G$15,1,0)+IF(AE16=$G$16,1,0)+IF(AE17=$G$17,1,0)+IF(AE18=$G$18,1,0)+IF(AE19=$G$19,1,0)+IF(AE20=$G$20,1,0)+IF(AE21=$G$21,1,0)+IF(AE22=$G$22,1,0)+IF(AE23=$G$23,1,0)+IF(AE24=$G$24,1,0)+IF(AE25=$G$25,1,0)+IF(AE26=$G$26,1,0)+IF(AE27=$G$27,1,0)+IF(AE28=$G$28,1,0)+IF(AE29=$G$29,1,0)+IF(AE30=$G$30,1,0)+IF(AE31=$G$31,1,0)+IF(AE32=$G$32,1,0)+IF(AE33=$G$33,1,0)+IF(AE34=$G$34,1,0)+IF(AE35=$G$35,1,0)+IF(AE36=$G$36,1,0)+IF(AE37=$G$37,1,0)+IF(AE38=$G$38,1,0)+IF(AE39=$G$39,1,0))</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="AF3" s="14">
-        <f>SUM(IF(AF4=$G$4,1,0)+IF(AF5=$G$5,1,0)+IF(AF6=$G$6,1,0)+IF(AF7=$G$7,1,0)+IF(AF8=$G$8,1,0)+IF(AF9=$G$9,1,0)+IF(AF10=$G$10,1,0)+IF(AF11=$G$11,1,0)+IF(AF12=$G$12,1,0)+IF(AF13=$G$13,1,0)+IF(AF14=$G$14,1,0)+IF(AF15=$G$15,1,0)+IF(AF16=$G$16,1,0)+IF(AF17=$G$17,1,0)+IF(AF18=$G$18,1,0)+IF(AF19=$G$19,1,0)+IF(AF20=$G$20,1,0)+IF(AF21=$G$21,1,0)+IF(AF22=$G$22,1,0)+IF(AF23=$G$23,1,0)+IF(AF24=$G$24,1,0)+IF(AF25=$G$25,1,0)+IF(AF26=$G$26,1,0)+IF(AF27=$G$27,1,0)+IF(AF28=$G$28,1,0)+IF(AF29=$G$29,1,0)+IF(AF30=$G$30,1,0)+IF(AF31=$G$31,1,0)+IF(AF32=$G$32,1,0)+IF(AF33=$G$33,1,0)+IF(AF34=$G$34,1,0)+IF(AF35=$G$35,1,0)+IF(AF36=$G$36,1,0)+IF(AF37=$G$37,1,0)+IF(AF38=$G$38,1,0)+IF(AF39=$G$39,1,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
         <v>6</v>
       </c>
@@ -1560,22 +1586,22 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G51" si="0">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
+        <f>IF(OR(E4="",F4=""),"",IF(E4&gt;F4,"L",IF(E4&lt;F4,"V","E")))</f>
         <v>L</v>
       </c>
       <c r="H4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="24" t="s">
+      <c r="I4" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="24" t="s">
+      <c r="L4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M4" s="23" t="s">
@@ -1584,16 +1610,16 @@
       <c r="N4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="23" t="s">
+      <c r="O4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="23" t="s">
+      <c r="Q4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S4" s="23"/>
@@ -1611,7 +1637,7 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="B5" s="7">
         <v>2</v>
@@ -1629,40 +1655,40 @@
         <v>1</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G5:G68" si="1">IF(OR(E5="",F5=""),"",IF(E5&gt;F5,"L",IF(E5&lt;F5,"V","E")))</f>
         <v>L</v>
       </c>
       <c r="H5" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="24" t="s">
+      <c r="I5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="24" t="s">
+      <c r="L5" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N5" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="23" t="s">
-        <v>104</v>
+      <c r="O5" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="P5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R5" s="23" t="s">
+      <c r="Q5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R5" s="24" t="s">
         <v>10</v>
       </c>
       <c r="S5" s="23"/>
@@ -1680,7 +1706,7 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="B6" s="7">
         <v>3</v>
@@ -1694,40 +1720,40 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H6" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>104</v>
+      <c r="I6" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="M6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O6" s="23" t="s">
-        <v>46</v>
+      <c r="O6" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="P6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q6" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R6" s="23" t="s">
+      <c r="Q6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R6" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S6" s="23"/>
@@ -1745,7 +1771,7 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="B7" s="7">
         <v>4</v>
@@ -1759,22 +1785,22 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H7" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>10</v>
+      <c r="I7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M7" s="23" t="s">
@@ -1783,17 +1809,17 @@
       <c r="N7" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O7" s="23" t="s">
+      <c r="O7" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q7" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R7" s="23" t="s">
-        <v>46</v>
+      <c r="Q7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R7" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="S7" s="23"/>
       <c r="T7" s="23"/>
@@ -1810,7 +1836,7 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="38"/>
       <c r="B8" s="7">
         <v>5</v>
@@ -1824,40 +1850,40 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H8" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I8" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="24" t="s">
+      <c r="I8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O8" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="P8" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R8" s="23" t="s">
+      <c r="Q8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R8" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S8" s="23"/>
@@ -1875,7 +1901,7 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="39"/>
       <c r="B9" s="7">
         <v>6</v>
@@ -1889,40 +1915,40 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H9" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="24" t="s">
+      <c r="I9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L9" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N9" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="O9" s="23" t="s">
-        <v>10</v>
+      <c r="O9" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R9" s="23" t="s">
+      <c r="Q9" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R9" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S9" s="23"/>
@@ -1940,7 +1966,7 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
@@ -1959,41 +1985,41 @@
       <c r="F10" s="8">
         <v>1</v>
       </c>
-      <c r="G10" s="8" t="str">
-        <f t="shared" si="0"/>
+      <c r="G10" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>46</v>
+      <c r="I10" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K10" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="24" t="s">
+      <c r="L10" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M10" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O10" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="P10" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R10" s="23" t="s">
+      <c r="Q10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R10" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S10" s="23"/>
@@ -2011,7 +2037,7 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="7">
         <v>8</v>
@@ -2028,41 +2054,41 @@
       <c r="F11" s="8">
         <v>1</v>
       </c>
-      <c r="G11" s="8" t="str">
-        <f t="shared" si="0"/>
+      <c r="G11" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H11" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="24" t="s">
+      <c r="I11" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J11" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M11" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N11" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O11" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="P11" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R11" s="23" t="s">
+      <c r="Q11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S11" s="23"/>
@@ -2080,7 +2106,7 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="38"/>
       <c r="B12" s="7">
         <v>9</v>
@@ -2093,23 +2119,23 @@
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G12" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H12" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>10</v>
+      <c r="I12" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="24" t="s">
+      <c r="L12" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M12" s="23" t="s">
@@ -2118,17 +2144,17 @@
       <c r="N12" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="23" t="s">
+      <c r="O12" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P12" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R12" s="23" t="s">
-        <v>46</v>
+      <c r="Q12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R12" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
@@ -2145,7 +2171,7 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="38"/>
       <c r="B13" s="7">
         <v>10</v>
@@ -2158,23 +2184,23 @@
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
-      <c r="G13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G13" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H13" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>10</v>
+      <c r="I13" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="24" t="s">
+      <c r="L13" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M13" s="23" t="s">
@@ -2183,16 +2209,16 @@
       <c r="N13" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="23" t="s">
+      <c r="O13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R13" s="23" t="s">
+      <c r="Q13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S13" s="23"/>
@@ -2210,7 +2236,7 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="38"/>
       <c r="B14" s="7">
         <v>11</v>
@@ -2223,42 +2249,42 @@
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
-      <c r="G14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G14" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H14" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I14" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="24" t="s">
+      <c r="I14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M14" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="O14" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P14" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q14" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R14" s="23" t="s">
-        <v>10</v>
+      <c r="Q14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
@@ -2275,7 +2301,7 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="39"/>
       <c r="B15" s="7">
         <v>12</v>
@@ -2288,41 +2314,41 @@
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
-      <c r="G15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G15" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H15" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>104</v>
+      <c r="I15" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L15" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O15" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="O15" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="P15" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R15" s="23" t="s">
+      <c r="Q15" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R15" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S15" s="23"/>
@@ -2340,7 +2366,7 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="45" t="s">
         <v>8</v>
       </c>
@@ -2359,23 +2385,23 @@
       <c r="F16" s="9">
         <v>1</v>
       </c>
-      <c r="G16" s="9" t="str">
-        <f t="shared" si="0"/>
+      <c r="G16" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H16" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>46</v>
+      <c r="I16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M16" s="23" t="s">
@@ -2384,17 +2410,17 @@
       <c r="N16" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="23" t="s">
+      <c r="O16" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q16" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R16" s="23" t="s">
-        <v>46</v>
+      <c r="Q16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R16" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
@@ -2411,7 +2437,7 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="7">
         <v>14</v>
@@ -2428,23 +2454,23 @@
       <c r="F17" s="9">
         <v>1</v>
       </c>
-      <c r="G17" s="9" t="str">
-        <f t="shared" si="0"/>
+      <c r="G17" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
       <c r="H17" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J17" s="24" t="s">
+      <c r="I17" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="24" t="s">
+      <c r="L17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -2453,16 +2479,16 @@
       <c r="N17" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="O17" s="23" t="s">
+      <c r="O17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="P17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R17" s="23" t="s">
+      <c r="Q17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S17" s="23"/>
@@ -2480,7 +2506,7 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
       <c r="B18" s="7">
         <v>15</v>
@@ -2493,41 +2519,41 @@
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
-      <c r="G18" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G18" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H18" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>10</v>
+      <c r="I18" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>46</v>
+      <c r="L18" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N18" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O18" s="23" t="s">
+      <c r="O18" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q18" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R18" s="23" t="s">
+      <c r="Q18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R18" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S18" s="23"/>
@@ -2545,7 +2571,7 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="38"/>
       <c r="B19" s="7">
         <v>16</v>
@@ -2558,23 +2584,23 @@
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
-      <c r="G19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G19" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="24" t="s">
+      <c r="I19" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="24" t="s">
+      <c r="L19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M19" s="23" t="s">
@@ -2583,16 +2609,16 @@
       <c r="N19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O19" s="23" t="s">
+      <c r="O19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R19" s="23" t="s">
+      <c r="Q19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S19" s="23"/>
@@ -2610,7 +2636,7 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
       <c r="B20" s="7">
         <v>17</v>
@@ -2623,41 +2649,41 @@
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
-      <c r="G20" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G20" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H20" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J20" s="24" t="s">
+      <c r="I20" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L20" s="24" t="s">
-        <v>46</v>
+      <c r="L20" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O20" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="P20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R20" s="23" t="s">
+      <c r="Q20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S20" s="23"/>
@@ -2675,7 +2701,7 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="39"/>
       <c r="B21" s="7">
         <v>18</v>
@@ -2688,41 +2714,41 @@
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G21" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J21" s="24" t="s">
+      <c r="I21" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="24" t="s">
+      <c r="L21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O21" s="23" t="s">
-        <v>10</v>
+      <c r="O21" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="P21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R21" s="23" t="s">
+      <c r="Q21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S21" s="23"/>
@@ -2740,7 +2766,7 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="s">
         <v>9</v>
       </c>
@@ -2759,41 +2785,41 @@
       <c r="F22" s="10">
         <v>1</v>
       </c>
-      <c r="G22" s="10" t="str">
-        <f t="shared" si="0"/>
+      <c r="G22" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H22" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I22" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>46</v>
+      <c r="I22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L22" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="L22" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M22" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N22" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O22" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="O22" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P22" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R22" s="23" t="s">
+      <c r="Q22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R22" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S22" s="23"/>
@@ -2811,7 +2837,7 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="38"/>
       <c r="B23" s="7">
         <v>20</v>
@@ -2828,42 +2854,42 @@
       <c r="F23" s="10">
         <v>0</v>
       </c>
-      <c r="G23" s="10" t="str">
-        <f t="shared" si="0"/>
+      <c r="G23" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H23" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I23" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>46</v>
+      <c r="I23" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L23" s="24" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L23" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O23" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="O23" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="P23" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q23" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R23" s="23" t="s">
-        <v>10</v>
+      <c r="Q23" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
@@ -2880,7 +2906,7 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="38"/>
       <c r="B24" s="7">
         <v>21</v>
@@ -2893,23 +2919,23 @@
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
-      <c r="G24" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G24" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H24" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24" s="24" t="s">
-        <v>10</v>
+      <c r="I24" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L24" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="L24" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M24" s="23" t="s">
@@ -2918,17 +2944,17 @@
       <c r="N24" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O24" s="23" t="s">
+      <c r="O24" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R24" s="23" t="s">
-        <v>46</v>
+      <c r="Q24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R24" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
@@ -2945,7 +2971,7 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="38"/>
       <c r="B25" s="7">
         <v>22</v>
@@ -2958,42 +2984,42 @@
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
-      <c r="G25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G25" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H25" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>104</v>
+      <c r="I25" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L25" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M25" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O25" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="O25" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q25" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R25" s="23" t="s">
-        <v>10</v>
+      <c r="Q25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R25" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="S25" s="23"/>
       <c r="T25" s="23"/>
@@ -3010,7 +3036,7 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="38"/>
       <c r="B26" s="7">
         <v>23</v>
@@ -3023,41 +3049,41 @@
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
-      <c r="G26" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G26" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H26" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" s="24" t="s">
-        <v>104</v>
+      <c r="I26" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J26" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="24" t="s">
-        <v>104</v>
+      <c r="L26" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N26" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="O26" s="23" t="s">
+      <c r="O26" s="24" t="s">
         <v>104</v>
       </c>
       <c r="P26" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q26" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R26" s="23" t="s">
+      <c r="Q26" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R26" s="24" t="s">
         <v>10</v>
       </c>
       <c r="S26" s="23"/>
@@ -3075,7 +3101,7 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="39"/>
       <c r="B27" s="7">
         <v>24</v>
@@ -3088,42 +3114,42 @@
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
-      <c r="G27" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G27" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H27" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J27" s="24" t="s">
-        <v>104</v>
+      <c r="I27" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J27" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L27" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="L27" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N27" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O27" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O27" s="24" t="s">
         <v>10</v>
       </c>
       <c r="P27" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R27" s="23" t="s">
-        <v>46</v>
+      <c r="Q27" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R27" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="S27" s="23"/>
       <c r="T27" s="23"/>
@@ -3140,7 +3166,7 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="43" t="s">
         <v>10</v>
       </c>
@@ -3159,23 +3185,23 @@
       <c r="F28" s="11">
         <v>1</v>
       </c>
-      <c r="G28" s="11" t="str">
-        <f t="shared" si="0"/>
+      <c r="G28" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H28" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J28" s="24" t="s">
+      <c r="I28" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="24" t="s">
+      <c r="L28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M28" s="23" t="s">
@@ -3184,16 +3210,16 @@
       <c r="N28" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O28" s="23" t="s">
+      <c r="O28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R28" s="23" t="s">
+      <c r="Q28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S28" s="23"/>
@@ -3211,7 +3237,7 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="38"/>
       <c r="B29" s="7">
         <v>26</v>
@@ -3228,42 +3254,42 @@
       <c r="F29" s="11">
         <v>0</v>
       </c>
-      <c r="G29" s="11" t="str">
-        <f t="shared" si="0"/>
+      <c r="G29" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H29" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J29" s="24" t="s">
+      <c r="I29" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L29" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="L29" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N29" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="O29" s="23" t="s">
-        <v>10</v>
+      <c r="O29" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P29" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R29" s="23" t="s">
-        <v>10</v>
+      <c r="Q29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="S29" s="23"/>
       <c r="T29" s="23"/>
@@ -3280,7 +3306,7 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="38"/>
       <c r="B30" s="7">
         <v>27</v>
@@ -3293,23 +3319,23 @@
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G30" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H30" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J30" s="24" t="s">
+      <c r="I30" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="24" t="s">
+      <c r="L30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M30" s="23" t="s">
@@ -3318,16 +3344,16 @@
       <c r="N30" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O30" s="23" t="s">
+      <c r="O30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R30" s="23" t="s">
+      <c r="Q30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S30" s="23"/>
@@ -3345,7 +3371,7 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="38"/>
       <c r="B31" s="7">
         <v>28</v>
@@ -3358,41 +3384,41 @@
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G31" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H31" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J31" s="24" t="s">
-        <v>46</v>
+      <c r="I31" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K31" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L31" s="24" t="s">
+      <c r="L31" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N31" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O31" s="23" t="s">
-        <v>10</v>
+      <c r="O31" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="P31" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R31" s="23" t="s">
+      <c r="Q31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R31" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S31" s="23"/>
@@ -3410,7 +3436,7 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="38"/>
       <c r="B32" s="7">
         <v>29</v>
@@ -3423,42 +3449,42 @@
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G32" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H32" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J32" s="24" t="s">
+      <c r="I32" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L32" s="24" t="s">
-        <v>46</v>
+      <c r="L32" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O32" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O32" s="24" t="s">
         <v>10</v>
       </c>
       <c r="P32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R32" s="23" t="s">
-        <v>104</v>
+      <c r="Q32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R32" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="S32" s="23"/>
       <c r="T32" s="23"/>
@@ -3475,7 +3501,7 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="39"/>
       <c r="B33" s="7">
         <v>30</v>
@@ -3488,42 +3514,42 @@
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G33" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H33" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J33" s="24" t="s">
+      <c r="I33" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K33" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L33" s="24" t="s">
-        <v>104</v>
+      <c r="L33" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O33" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="O33" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="P33" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q33" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R33" s="23" t="s">
-        <v>104</v>
+      <c r="Q33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R33" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="S33" s="23"/>
       <c r="T33" s="23"/>
@@ -3540,7 +3566,7 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="41" t="s">
         <v>11</v>
       </c>
@@ -3559,41 +3585,41 @@
       <c r="F34" s="12">
         <v>2</v>
       </c>
-      <c r="G34" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="G34" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H34" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I34" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J34" s="24" t="s">
+      <c r="I34" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L34" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="L34" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N34" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O34" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O34" s="24" t="s">
         <v>104</v>
       </c>
       <c r="P34" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q34" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R34" s="23" t="s">
+      <c r="Q34" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R34" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S34" s="23"/>
@@ -3611,7 +3637,7 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="38"/>
       <c r="B35" s="7">
         <v>32</v>
@@ -3628,23 +3654,23 @@
       <c r="F35" s="12">
         <v>1</v>
       </c>
-      <c r="G35" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="G35" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H35" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J35" s="24" t="s">
+      <c r="I35" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L35" s="24" t="s">
+      <c r="L35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M35" s="23" t="s">
@@ -3653,16 +3679,16 @@
       <c r="N35" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O35" s="23" t="s">
+      <c r="O35" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P35" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R35" s="23" t="s">
+      <c r="Q35" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R35" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S35" s="23"/>
@@ -3680,7 +3706,7 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="38"/>
       <c r="B36" s="7">
         <v>33</v>
@@ -3693,41 +3719,41 @@
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
-      <c r="G36" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G36" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H36" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J36" s="24" t="s">
-        <v>10</v>
+      <c r="I36" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J36" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L36" s="24" t="s">
-        <v>104</v>
+      <c r="L36" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M36" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O36" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O36" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R36" s="23" t="s">
+      <c r="Q36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R36" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S36" s="23"/>
@@ -3745,7 +3771,7 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="38"/>
       <c r="B37" s="7">
         <v>34</v>
@@ -3758,23 +3784,23 @@
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
-      <c r="G37" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G37" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H37" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J37" s="24" t="s">
+      <c r="I37" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L37" s="24" t="s">
+      <c r="L37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M37" s="23" t="s">
@@ -3783,16 +3809,16 @@
       <c r="N37" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="O37" s="23" t="s">
+      <c r="O37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="P37" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R37" s="23" t="s">
+      <c r="Q37" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S37" s="23"/>
@@ -3810,7 +3836,7 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="38"/>
       <c r="B38" s="7">
         <v>35</v>
@@ -3823,41 +3849,41 @@
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
-      <c r="G38" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G38" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H38" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J38" s="24" t="s">
-        <v>10</v>
+      <c r="I38" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L38" s="24" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L38" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M38" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N38" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O38" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="O38" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P38" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R38" s="23" t="s">
+      <c r="Q38" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R38" s="24" t="s">
         <v>10</v>
       </c>
       <c r="S38" s="23"/>
@@ -3875,7 +3901,7 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="39"/>
       <c r="B39" s="7">
         <v>36</v>
@@ -3888,41 +3914,41 @@
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G39" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H39" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I39" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J39" s="24" t="s">
+      <c r="I39" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L39" s="24" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L39" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M39" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O39" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O39" s="24" t="s">
         <v>104</v>
       </c>
       <c r="P39" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R39" s="23" t="s">
+      <c r="Q39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R39" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S39" s="23"/>
@@ -3940,7 +3966,7 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="40" t="s">
         <v>12</v>
       </c>
@@ -3959,42 +3985,42 @@
       <c r="F40" s="13">
         <v>1</v>
       </c>
-      <c r="G40" s="13" t="str">
-        <f t="shared" si="0"/>
+      <c r="G40" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J40" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J40" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L40" s="24" t="s">
-        <v>46</v>
+      <c r="L40" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M40" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N40" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O40" s="23" t="s">
+      <c r="O40" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q40" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R40" s="23" t="s">
-        <v>46</v>
+      <c r="Q40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R40" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="S40" s="23"/>
       <c r="T40" s="23"/>
@@ -4011,7 +4037,7 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="38"/>
       <c r="B41" s="7">
         <v>38</v>
@@ -4028,42 +4054,42 @@
       <c r="F41" s="13">
         <v>2</v>
       </c>
-      <c r="G41" s="13" t="str">
-        <f t="shared" si="0"/>
+      <c r="G41" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J41" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L41" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="L41" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M41" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N41" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="O41" s="23" t="s">
-        <v>10</v>
+      <c r="O41" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P41" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R41" s="23" t="s">
-        <v>46</v>
+      <c r="Q41" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R41" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="S41" s="23"/>
       <c r="T41" s="23"/>
@@ -4080,7 +4106,7 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="38"/>
       <c r="B42" s="7">
         <v>39</v>
@@ -4093,23 +4119,23 @@
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
-      <c r="G42" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G42" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H42" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J42" s="24" t="s">
+      <c r="I42" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L42" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L42" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M42" s="23" t="s">
@@ -4118,16 +4144,16 @@
       <c r="N42" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O42" s="23" t="s">
+      <c r="O42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P42" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R42" s="23" t="s">
+      <c r="Q42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S42" s="23"/>
@@ -4145,7 +4171,7 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="38"/>
       <c r="B43" s="7">
         <v>40</v>
@@ -4158,42 +4184,42 @@
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
-      <c r="G43" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G43" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H43" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J43" s="24" t="s">
-        <v>46</v>
+      <c r="I43" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K43" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L43" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="L43" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M43" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O43" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="O43" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="P43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R43" s="23" t="s">
-        <v>104</v>
+      <c r="Q43" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R43" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="S43" s="23"/>
       <c r="T43" s="23"/>
@@ -4210,7 +4236,7 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
       <c r="B44" s="7">
         <v>41</v>
@@ -4223,41 +4249,41 @@
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
-      <c r="G44" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G44" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H44" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I44" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J44" s="24" t="s">
+      <c r="I44" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K44" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L44" s="24" t="s">
-        <v>104</v>
+      <c r="L44" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O44" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O44" s="24" t="s">
         <v>10</v>
       </c>
       <c r="P44" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R44" s="23" t="s">
+      <c r="Q44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R44" s="24" t="s">
         <v>10</v>
       </c>
       <c r="S44" s="23"/>
@@ -4275,7 +4301,7 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="39"/>
       <c r="B45" s="7">
         <v>42</v>
@@ -4288,23 +4314,23 @@
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
-      <c r="G45" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G45" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H45" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J45" s="24" t="s">
+      <c r="I45" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L45" s="24" t="s">
+      <c r="L45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M45" s="23" t="s">
@@ -4313,16 +4339,16 @@
       <c r="N45" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="O45" s="23" t="s">
+      <c r="O45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="P45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R45" s="23" t="s">
+      <c r="Q45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S45" s="23"/>
@@ -4340,7 +4366,7 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="57" t="s">
         <v>13</v>
       </c>
@@ -4359,23 +4385,23 @@
       <c r="F46" s="14">
         <v>0</v>
       </c>
-      <c r="G46" s="14" t="str">
-        <f t="shared" si="0"/>
+      <c r="G46" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H46" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J46" s="24" t="s">
+      <c r="I46" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="24" t="s">
+      <c r="L46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M46" s="23" t="s">
@@ -4384,16 +4410,16 @@
       <c r="N46" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O46" s="23" t="s">
+      <c r="O46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R46" s="23" t="s">
+      <c r="Q46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S46" s="23"/>
@@ -4411,7 +4437,7 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="38"/>
       <c r="B47" s="7">
         <v>44</v>
@@ -4428,41 +4454,41 @@
       <c r="F47" s="14">
         <v>1</v>
       </c>
-      <c r="G47" s="14" t="str">
-        <f t="shared" si="0"/>
+      <c r="G47" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H47" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J47" s="24" t="s">
+      <c r="I47" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L47" s="24" t="s">
+      <c r="L47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M47" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N47" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="O47" s="23" t="s">
-        <v>10</v>
+      <c r="O47" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R47" s="23" t="s">
+      <c r="Q47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S47" s="23"/>
@@ -4480,7 +4506,7 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="38"/>
       <c r="B48" s="7">
         <v>45</v>
@@ -4493,23 +4519,23 @@
       </c>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
-      <c r="G48" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G48" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H48" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J48" s="24" t="s">
+      <c r="I48" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L48" s="24" t="s">
+      <c r="L48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M48" s="23" t="s">
@@ -4518,16 +4544,16 @@
       <c r="N48" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O48" s="23" t="s">
+      <c r="O48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R48" s="23" t="s">
+      <c r="Q48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S48" s="23"/>
@@ -4545,7 +4571,7 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="38"/>
       <c r="B49" s="7">
         <v>46</v>
@@ -4558,23 +4584,23 @@
       </c>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
-      <c r="G49" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G49" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H49" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="I49" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J49" s="24" t="s">
+      <c r="I49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J49" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L49" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="L49" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M49" s="23" t="s">
@@ -4583,16 +4609,16 @@
       <c r="N49" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O49" s="23" t="s">
+      <c r="O49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="P49" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="Q49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="R49" s="23" t="s">
+      <c r="Q49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="S49" s="23"/>
@@ -4610,7 +4636,7 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="38"/>
       <c r="B50" s="7">
         <v>47</v>
@@ -4623,41 +4649,41 @@
       </c>
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
-      <c r="G50" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G50" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H50" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I50" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J50" s="24" t="s">
-        <v>10</v>
+      <c r="I50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J50" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K50" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L50" s="24" t="s">
+      <c r="L50" s="23" t="s">
         <v>10</v>
       </c>
       <c r="M50" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N50" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O50" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="O50" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="P50" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="Q50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R50" s="23" t="s">
+      <c r="Q50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R50" s="24" t="s">
         <v>10</v>
       </c>
       <c r="S50" s="23"/>
@@ -4675,7 +4701,7 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="39"/>
       <c r="B51" s="7">
         <v>48</v>
@@ -4688,41 +4714,41 @@
       </c>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
-      <c r="G51" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
+      <c r="G51" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H51" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J51" s="24" t="s">
-        <v>10</v>
+      <c r="I51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L51" s="24" t="s">
+      <c r="L51" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M51" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O51" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="O51" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="P51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Q51" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="R51" s="23" t="s">
+      <c r="Q51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R51" s="24" t="s">
         <v>104</v>
       </c>
       <c r="S51" s="23"/>
@@ -4740,7 +4766,7 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="60" t="s">
         <v>77</v>
       </c>
@@ -4753,44 +4779,48 @@
       <c r="D52" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15" t="str">
-        <f t="shared" ref="G52:G75" si="1">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
-        <v>-</v>
+      <c r="E52" s="15">
+        <v>3</v>
+      </c>
+      <c r="F52" s="15">
+        <v>1</v>
+      </c>
+      <c r="G52" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>L</v>
       </c>
       <c r="H52" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I52" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J52" s="26" t="s">
+      <c r="I52" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J52" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L52" s="26" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="L52" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="M52" s="25" t="s">
         <v>46</v>
       </c>
       <c r="N52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O52" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O52" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P52" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q52" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="R52" s="25" t="s">
-        <v>46</v>
+      <c r="Q52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R52" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="S52" s="25"/>
       <c r="T52" s="25"/>
@@ -4807,7 +4837,7 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="7">
         <v>50</v>
@@ -4820,23 +4850,23 @@
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
-      <c r="G53" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G53" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H53" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J53" s="26" t="s">
-        <v>46</v>
+      <c r="I53" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J53" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L53" s="26" t="s">
+      <c r="L53" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M53" s="25" t="s">
@@ -4845,16 +4875,16 @@
       <c r="N53" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O53" s="25" t="s">
+      <c r="O53" s="26" t="s">
         <v>104</v>
       </c>
       <c r="P53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="Q53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="R53" s="25" t="s">
+      <c r="Q53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R53" s="26" t="s">
         <v>104</v>
       </c>
       <c r="S53" s="25"/>
@@ -4872,7 +4902,7 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="61"/>
       <c r="B54" s="7">
         <v>51</v>
@@ -4885,23 +4915,23 @@
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
-      <c r="G54" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G54" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H54" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J54" s="26" t="s">
+      <c r="I54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L54" s="26" t="s">
+      <c r="L54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M54" s="25" t="s">
@@ -4910,16 +4940,16 @@
       <c r="N54" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O54" s="25" t="s">
+      <c r="O54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R54" s="25" t="s">
+      <c r="Q54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S54" s="25"/>
@@ -4937,7 +4967,7 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="7">
         <v>52</v>
@@ -4950,42 +4980,42 @@
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
-      <c r="G55" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G55" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H55" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J55" s="26" t="s">
-        <v>46</v>
+      <c r="I55" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J55" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K55" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L55" s="26" t="s">
-        <v>104</v>
+      <c r="L55" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="M55" s="25" t="s">
         <v>46</v>
       </c>
       <c r="N55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O55" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O55" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P55" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q55" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="R55" s="25" t="s">
-        <v>10</v>
+      <c r="Q55" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R55" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="S55" s="25"/>
       <c r="T55" s="25"/>
@@ -5003,7 +5033,7 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="61"/>
       <c r="B56" s="7">
         <v>53</v>
@@ -5016,42 +5046,42 @@
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
-      <c r="G56" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G56" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H56" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="I56" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J56" s="26" t="s">
-        <v>104</v>
+      <c r="I56" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J56" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L56" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L56" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M56" s="25" t="s">
         <v>104</v>
       </c>
       <c r="N56" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="O56" s="25" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="O56" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="P56" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="Q56" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="R56" s="25" t="s">
-        <v>104</v>
+      <c r="Q56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R56" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="S56" s="25"/>
       <c r="T56" s="25"/>
@@ -5068,7 +5098,7 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="62"/>
       <c r="B57" s="7">
         <v>54</v>
@@ -5081,41 +5111,41 @@
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
-      <c r="G57" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G57" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H57" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I57" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J57" s="26" t="s">
-        <v>104</v>
+      <c r="I57" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J57" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K57" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L57" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="L57" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M57" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N57" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="O57" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O57" s="26" t="s">
         <v>10</v>
       </c>
       <c r="P57" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="Q57" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R57" s="25" t="s">
+      <c r="Q57" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R57" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S57" s="25"/>
@@ -5133,7 +5163,7 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="63" t="s">
         <v>78</v>
       </c>
@@ -5148,23 +5178,23 @@
       </c>
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
-      <c r="G58" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G58" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H58" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I58" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J58" s="26" t="s">
+      <c r="I58" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J58" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L58" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L58" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M58" s="25" t="s">
@@ -5173,16 +5203,16 @@
       <c r="N58" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O58" s="25" t="s">
+      <c r="O58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P58" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R58" s="25" t="s">
+      <c r="Q58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S58" s="25"/>
@@ -5200,7 +5230,7 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="64"/>
       <c r="B59" s="7">
         <v>56</v>
@@ -5213,42 +5243,42 @@
       </c>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
-      <c r="G59" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G59" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H59" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J59" s="26" t="s">
+      <c r="I59" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L59" s="26" t="s">
+      <c r="L59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M59" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N59" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O59" s="25" t="s">
-        <v>10</v>
+      <c r="O59" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="P59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q59" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="R59" s="25" t="s">
-        <v>46</v>
+      <c r="Q59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R59" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="S59" s="25"/>
       <c r="T59" s="25"/>
@@ -5265,7 +5295,7 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="64"/>
       <c r="B60" s="7">
         <v>57</v>
@@ -5278,23 +5308,23 @@
       </c>
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
-      <c r="G60" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G60" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H60" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J60" s="26" t="s">
-        <v>10</v>
+      <c r="I60" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J60" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L60" s="26" t="s">
+      <c r="L60" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M60" s="25" t="s">
@@ -5303,16 +5333,16 @@
       <c r="N60" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O60" s="25" t="s">
+      <c r="O60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R60" s="25" t="s">
+      <c r="Q60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S60" s="25"/>
@@ -5330,7 +5360,7 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="64"/>
       <c r="B61" s="7">
         <v>58</v>
@@ -5343,42 +5373,42 @@
       </c>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
-      <c r="G61" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G61" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H61" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J61" s="26" t="s">
-        <v>46</v>
+      <c r="I61" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J61" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K61" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L61" s="26" t="s">
+      <c r="L61" s="25" t="s">
         <v>10</v>
       </c>
       <c r="M61" s="25" t="s">
         <v>10</v>
       </c>
       <c r="N61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O61" s="25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="O61" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="P61" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="Q61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R61" s="25" t="s">
-        <v>104</v>
+      <c r="Q61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R61" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="S61" s="25"/>
       <c r="T61" s="25"/>
@@ -5395,7 +5425,7 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="64"/>
       <c r="B62" s="7">
         <v>59</v>
@@ -5408,42 +5438,42 @@
       </c>
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
-      <c r="G62" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G62" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H62" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J62" s="26" t="s">
+      <c r="I62" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J62" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L62" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L62" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M62" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N62" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O62" s="25" t="s">
-        <v>10</v>
+      <c r="O62" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="P62" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="Q62" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="R62" s="25" t="s">
-        <v>104</v>
+      <c r="Q62" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R62" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="S62" s="25"/>
       <c r="T62" s="25"/>
@@ -5460,7 +5490,7 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="65"/>
       <c r="B63" s="7">
         <v>60</v>
@@ -5473,23 +5503,23 @@
       </c>
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
-      <c r="G63" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G63" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H63" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="I63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J63" s="26" t="s">
+      <c r="I63" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L63" s="26" t="s">
+      <c r="L63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M63" s="25" t="s">
@@ -5498,16 +5528,16 @@
       <c r="N63" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O63" s="25" t="s">
+      <c r="O63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="P63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="Q63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="R63" s="25" t="s">
+      <c r="Q63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="S63" s="25"/>
@@ -5525,7 +5555,7 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="51" t="s">
         <v>79</v>
       </c>
@@ -5540,23 +5570,23 @@
       </c>
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
-      <c r="G64" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G64" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H64" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J64" s="26" t="s">
+      <c r="I64" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L64" s="26" t="s">
+      <c r="L64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M64" s="25" t="s">
@@ -5565,16 +5595,16 @@
       <c r="N64" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O64" s="25" t="s">
+      <c r="O64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R64" s="25" t="s">
+      <c r="Q64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S64" s="25"/>
@@ -5592,7 +5622,7 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="52"/>
       <c r="B65" s="7">
         <v>62</v>
@@ -5605,23 +5635,23 @@
       </c>
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
-      <c r="G65" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G65" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H65" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="I65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J65" s="26" t="s">
+      <c r="I65" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L65" s="26" t="s">
+      <c r="L65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M65" s="25" t="s">
@@ -5630,16 +5660,16 @@
       <c r="N65" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O65" s="25" t="s">
+      <c r="O65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="P65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="Q65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="R65" s="25" t="s">
+      <c r="Q65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="S65" s="25"/>
@@ -5657,7 +5687,7 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="52"/>
       <c r="B66" s="7">
         <v>63</v>
@@ -5670,23 +5700,23 @@
       </c>
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
-      <c r="G66" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G66" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H66" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J66" s="26" t="s">
+      <c r="I66" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L66" s="26" t="s">
+      <c r="L66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M66" s="25" t="s">
@@ -5695,16 +5725,16 @@
       <c r="N66" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O66" s="25" t="s">
+      <c r="O66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R66" s="25" t="s">
+      <c r="Q66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S66" s="25"/>
@@ -5722,7 +5752,7 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="52"/>
       <c r="B67" s="7">
         <v>64</v>
@@ -5735,23 +5765,23 @@
       </c>
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
-      <c r="G67" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G67" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H67" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J67" s="26" t="s">
-        <v>46</v>
+      <c r="I67" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J67" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K67" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L67" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="L67" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M67" s="25" t="s">
@@ -5760,16 +5790,16 @@
       <c r="N67" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O67" s="25" t="s">
+      <c r="O67" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R67" s="25" t="s">
+      <c r="Q67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R67" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S67" s="25"/>
@@ -5787,7 +5817,7 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="52"/>
       <c r="B68" s="7">
         <v>65</v>
@@ -5800,23 +5830,23 @@
       </c>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
-      <c r="G68" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G68" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="H68" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I68" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J68" s="26" t="s">
-        <v>10</v>
+      <c r="I68" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J68" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L68" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L68" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M68" s="25" t="s">
@@ -5825,17 +5855,17 @@
       <c r="N68" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O68" s="25" t="s">
+      <c r="O68" s="26" t="s">
         <v>104</v>
       </c>
       <c r="P68" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="Q68" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R68" s="25" t="s">
-        <v>104</v>
+      <c r="Q68" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R68" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="S68" s="25"/>
       <c r="T68" s="25"/>
@@ -5852,7 +5882,7 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="53"/>
       <c r="B69" s="7">
         <v>66</v>
@@ -5865,24 +5895,24 @@
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
-      <c r="G69" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G69" s="7" t="str">
+        <f t="shared" ref="G69:G75" si="2">IF(OR(E69="",F69=""),"",IF(E69&gt;F69,"L",IF(E69&lt;F69,"V","E")))</f>
+        <v/>
       </c>
       <c r="H69" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I69" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J69" s="26" t="s">
-        <v>104</v>
+      <c r="I69" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J69" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L69" s="26" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L69" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="M69" s="25" t="s">
         <v>10</v>
@@ -5890,17 +5920,17 @@
       <c r="N69" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O69" s="25" t="s">
-        <v>10</v>
+      <c r="O69" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="P69" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="Q69" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R69" s="25" t="s">
-        <v>10</v>
+      <c r="Q69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R69" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="S69" s="25"/>
       <c r="T69" s="25"/>
@@ -5917,7 +5947,7 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="54" t="s">
         <v>46</v>
       </c>
@@ -5932,42 +5962,42 @@
       </c>
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
-      <c r="G70" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G70" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="H70" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="I70" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J70" s="26" t="s">
-        <v>46</v>
+      <c r="I70" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J70" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L70" s="26" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L70" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="M70" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N70" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O70" s="25" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="O70" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="P70" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q70" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="R70" s="25" t="s">
-        <v>10</v>
+      <c r="Q70" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R70" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="S70" s="25"/>
       <c r="T70" s="25"/>
@@ -5984,7 +6014,7 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>68</v>
@@ -5997,24 +6027,24 @@
       </c>
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
-      <c r="G71" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G71" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="H71" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I71" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J71" s="26" t="s">
-        <v>104</v>
+      <c r="I71" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J71" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L71" s="26" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="L71" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="M71" s="25" t="s">
         <v>10</v>
@@ -6022,17 +6052,17 @@
       <c r="N71" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O71" s="25" t="s">
-        <v>10</v>
+      <c r="O71" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="P71" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="Q71" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="R71" s="25" t="s">
-        <v>46</v>
+      <c r="Q71" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R71" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="S71" s="25"/>
       <c r="T71" s="25"/>
@@ -6049,7 +6079,7 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="55"/>
       <c r="B72" s="7">
         <v>69</v>
@@ -6062,23 +6092,23 @@
       </c>
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
-      <c r="G72" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G72" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="H72" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I72" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J72" s="26" t="s">
+      <c r="I72" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J72" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L72" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L72" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M72" s="25" t="s">
@@ -6087,16 +6117,16 @@
       <c r="N72" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O72" s="25" t="s">
+      <c r="O72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P72" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Q72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R72" s="25" t="s">
+      <c r="Q72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S72" s="25"/>
@@ -6114,7 +6144,7 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="55"/>
       <c r="B73" s="7">
         <v>70</v>
@@ -6127,23 +6157,23 @@
       </c>
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
-      <c r="G73" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G73" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="H73" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="I73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J73" s="26" t="s">
-        <v>46</v>
+      <c r="I73" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J73" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L73" s="26" t="s">
+      <c r="L73" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M73" s="25" t="s">
@@ -6152,17 +6182,17 @@
       <c r="N73" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="O73" s="25" t="s">
+      <c r="O73" s="26" t="s">
         <v>104</v>
       </c>
       <c r="P73" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="Q73" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="R73" s="25" t="s">
-        <v>104</v>
+      <c r="Q73" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R73" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="S73" s="25"/>
       <c r="T73" s="25"/>
@@ -6179,7 +6209,7 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="55"/>
       <c r="B74" s="7">
         <v>71</v>
@@ -6192,41 +6222,41 @@
       </c>
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
-      <c r="G74" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G74" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="H74" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="I74" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J74" s="26" t="s">
+      <c r="I74" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J74" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L74" s="26" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="L74" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="M74" s="25" t="s">
         <v>104</v>
       </c>
       <c r="N74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O74" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="P74" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="Q74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="R74" s="25" t="s">
+      <c r="Q74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="S74" s="25"/>
@@ -6244,7 +6274,7 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="56"/>
       <c r="B75" s="7">
         <v>72</v>
@@ -6257,23 +6287,23 @@
       </c>
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
-      <c r="G75" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+      <c r="G75" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="H75" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I75" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J75" s="26" t="s">
-        <v>10</v>
+      <c r="I75" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J75" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L75" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="L75" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M75" s="25" t="s">
@@ -6282,16 +6312,16 @@
       <c r="N75" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="O75" s="25" t="s">
+      <c r="O75" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P75" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="Q75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="R75" s="25" t="s">
+      <c r="Q75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R75" s="26" t="s">
         <v>46</v>
       </c>
       <c r="S75" s="25"/>
@@ -6309,7 +6339,7 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
@@ -6320,40 +6350,40 @@
       <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
       </c>
-      <c r="I76" s="25">
+      <c r="I76" s="26">
+        <v>201</v>
+      </c>
+      <c r="J76" s="25">
+        <v>222</v>
+      </c>
+      <c r="K76" s="25">
         <v>186</v>
       </c>
-      <c r="J76" s="26">
-        <v>201</v>
-      </c>
-      <c r="K76" s="25">
-        <v>222</v>
-      </c>
-      <c r="L76" s="26">
+      <c r="L76" s="25">
+        <v>172</v>
+      </c>
+      <c r="M76" s="25">
+        <v>190</v>
+      </c>
+      <c r="N76" s="26">
         <v>185</v>
       </c>
-      <c r="M76" s="25">
-        <v>172</v>
-      </c>
-      <c r="N76" s="26">
+      <c r="O76" s="26">
         <v>162</v>
-      </c>
-      <c r="O76" s="25">
-        <v>190</v>
       </c>
       <c r="P76" s="25">
         <v>169</v>
       </c>
-      <c r="Q76" s="26">
+      <c r="Q76" s="25">
+        <v>197</v>
+      </c>
+      <c r="R76" s="26">
         <v>180</v>
-      </c>
-      <c r="R76" s="25">
-        <v>197</v>
       </c>
       <c r="S76" s="25"/>
       <c r="T76" s="25"/>
@@ -6370,7 +6400,7 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
@@ -6381,107 +6411,107 @@
       <c r="F77" s="33"/>
       <c r="G77" s="34"/>
       <c r="H77" s="28">
-        <f>SUM(H78:H81)</f>
+        <f t="shared" ref="H77:R77" si="3">SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
-        <f>SUM(I78:I81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J77" s="28">
-        <f>SUM(J78:J81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K77" s="28">
-        <f>SUM(K78:K81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L77" s="28">
-        <f>SUM(L78:L81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M77" s="28">
-        <f>SUM(M78:M81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N77" s="28">
-        <f>SUM(N78:N81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O77" s="28">
-        <f>SUM(O78:O81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P77" s="28">
-        <f>SUM(P78:P81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q77" s="28">
-        <f>SUM(Q78:Q81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R77" s="28">
-        <f>SUM(R78:R81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S77" s="28">
-        <f>SUM(S78:S81)</f>
-        <v>55</v>
+        <f t="shared" ref="S77:AF77" si="4">SUM(S78:S81)</f>
+        <v>51</v>
       </c>
       <c r="T77" s="28">
-        <f>SUM(T78:T81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="U77" s="28">
-        <f>SUM(U78:U81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="V77" s="28">
-        <f>SUM(V78:V81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="W77" s="28">
-        <f>SUM(W78:W81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="X77" s="28">
-        <f>SUM(X78:X81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="Y77" s="28">
-        <f>SUM(Y78:Y81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="Z77" s="28">
-        <f>SUM(Z78:Z81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="AA77" s="28">
-        <f>SUM(AA78:AA81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="AB77" s="28">
-        <f>SUM(AB78:AB81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="AC77" s="28">
-        <f>SUM(AC78:AC81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="AD77" s="28">
-        <f>SUM(AD78:AD81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="AE77" s="28">
-        <f>SUM(AE78:AE81)</f>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="AF77" s="28">
-        <f>SUM(AF78:AF81)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6490,107 +6520,107 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="2">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="5">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6599,107 +6629,107 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="3">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="6">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="3"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6708,107 +6738,107 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="4">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="7">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6817,107 +6847,107 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="5">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="8">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6951,7 +6981,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -6985,7 +7015,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7019,7 +7049,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7053,7 +7083,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7087,7 +7117,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7121,7 +7151,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7155,7 +7185,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7189,7 +7219,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7223,7 +7253,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7257,7 +7287,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7291,7 +7321,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7325,7 +7355,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7359,7 +7389,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7393,7 +7423,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7427,7 +7457,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7461,7 +7491,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7495,7 +7525,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7529,7 +7559,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7563,7 +7593,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7572,7 +7602,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7581,7 +7611,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7590,7 +7620,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7599,7 +7629,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7608,7 +7638,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7617,7 +7647,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7626,7 +7656,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7635,7 +7665,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7644,7 +7674,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7653,7 +7683,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7662,7 +7692,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7671,7 +7701,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7680,7 +7710,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7689,7 +7719,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7698,7 +7728,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7707,7 +7737,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7716,7 +7746,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7725,7 +7755,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7734,7 +7764,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7743,7 +7773,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7752,7 +7782,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7761,7 +7791,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7770,7 +7800,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7780,9 +7810,9 @@
       <c r="G124" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H2:AF77">
-    <sortCondition descending="1" ref="H3:AF3"/>
-    <sortCondition descending="1" ref="H77:AF77"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H2:R77">
+    <sortCondition descending="1" ref="H3:R3"/>
+    <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
     <mergeCell ref="A64:A69"/>
@@ -7817,14 +7847,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="15" width="11.44140625" customWidth="1"/>
+    <col min="1" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="15" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>16</v>
@@ -7871,7 +7901,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -7916,7 +7946,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -7961,7 +7991,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -8006,7 +8036,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -8051,7 +8081,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -8096,7 +8126,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -8141,7 +8171,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -8186,7 +8216,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -8231,7 +8261,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -8276,7 +8306,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -8321,7 +8351,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>16</v>
@@ -8366,7 +8396,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>16</v>
@@ -8411,7 +8441,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
@@ -8456,7 +8486,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -8501,7 +8531,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
@@ -8546,7 +8576,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>16</v>
@@ -8591,7 +8621,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
@@ -8636,7 +8666,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>16</v>
@@ -8681,7 +8711,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>16</v>
@@ -8726,7 +8756,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>16</v>
@@ -8771,7 +8801,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -8816,7 +8846,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -8861,7 +8891,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>16</v>
@@ -8906,7 +8936,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>16</v>
@@ -8951,7 +8981,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -8996,7 +9026,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>16</v>
@@ -9041,7 +9071,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>16</v>
@@ -9086,7 +9116,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>16</v>
@@ -9131,7 +9161,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>16</v>
@@ -9176,7 +9206,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>16</v>
@@ -9221,7 +9251,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>16</v>
@@ -9266,7 +9296,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>16</v>
@@ -9311,7 +9341,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>16</v>
@@ -9356,7 +9386,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>16</v>
@@ -9401,7 +9431,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>16</v>
@@ -9446,7 +9476,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>16</v>
@@ -9491,7 +9521,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>16</v>
@@ -9536,7 +9566,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>16</v>
@@ -9581,7 +9611,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>16</v>
@@ -9626,7 +9656,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>16</v>
@@ -9671,7 +9701,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>16</v>
@@ -9716,7 +9746,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>16</v>
@@ -9761,7 +9791,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>16</v>
@@ -9806,7 +9836,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>16</v>
@@ -9851,7 +9881,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>16</v>
@@ -9896,7 +9926,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>16</v>
@@ -9941,7 +9971,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>16</v>
@@ -9986,7 +10016,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>16</v>
@@ -10031,7 +10061,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>16</v>
@@ -10076,7 +10106,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>16</v>
@@ -10121,7 +10151,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>16</v>
@@ -10166,7 +10196,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>16</v>
@@ -10211,7 +10241,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>16</v>
@@ -10256,7 +10286,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>16</v>
@@ -10301,7 +10331,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>16</v>
@@ -10346,7 +10376,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>16</v>
@@ -10391,7 +10421,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>16</v>
@@ -10436,7 +10466,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>16</v>
@@ -10481,7 +10511,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>16</v>
@@ -10526,7 +10556,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>16</v>
@@ -10571,7 +10601,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>16</v>
@@ -10616,7 +10646,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>16</v>
@@ -10661,7 +10691,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>16</v>
@@ -10706,7 +10736,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>16</v>
@@ -10751,7 +10781,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>16</v>
@@ -10796,7 +10826,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>16</v>
@@ -10841,7 +10871,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>16</v>
@@ -10886,7 +10916,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>16</v>
@@ -10931,7 +10961,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>16</v>
@@ -10976,7 +11006,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>16</v>
@@ -11021,7 +11051,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>16</v>
@@ -11066,7 +11096,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>16</v>
@@ -11111,7 +11141,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>16</v>
@@ -11156,7 +11186,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>16</v>
@@ -11201,7 +11231,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>16</v>
@@ -11246,7 +11276,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>16</v>
@@ -11291,7 +11321,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>16</v>
@@ -11336,7 +11366,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>16</v>
@@ -11381,7 +11411,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>16</v>
@@ -11426,7 +11456,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>16</v>
@@ -11471,7 +11501,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>16</v>
@@ -11516,7 +11546,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>16</v>
@@ -11561,7 +11591,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>16</v>
@@ -11606,7 +11636,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>16</v>
@@ -11651,7 +11681,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>16</v>
@@ -11696,7 +11726,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>16</v>
@@ -11741,7 +11771,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>16</v>
@@ -11786,7 +11816,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>16</v>
@@ -11831,7 +11861,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>16</v>
@@ -11876,7 +11906,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>16</v>
@@ -11921,7 +11951,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>16</v>
@@ -11966,7 +11996,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>16</v>
@@ -12011,7 +12041,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>16</v>
@@ -12056,7 +12086,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>16</v>
@@ -12101,7 +12131,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>16</v>
@@ -12146,7 +12176,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>16</v>
@@ -12191,7 +12221,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>16</v>
@@ -12236,7 +12266,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>16</v>
@@ -12281,7 +12311,7 @@
         <v>SI(G28-H28=-100;0;</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12307,9 +12337,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="11" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12320,26 +12350,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" customWidth="1"/>
-    <col min="2" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="2" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="11" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -12347,61 +12377,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -12409,7 +12439,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -12417,19 +12447,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -12437,19 +12467,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -12457,19 +12487,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -12477,13 +12507,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -12491,229 +12521,229 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="1"/>
     </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="1"/>
     </row>
-    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="1"/>
     </row>
-    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="1"/>
     </row>
-    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="1"/>
     </row>
-    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="1"/>
     </row>
-    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="1"/>
     </row>
-    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="1"/>
     </row>
-    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="1"/>
     </row>
-    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="1"/>
     </row>
   </sheetData>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1875F05A-1114-4066-8DB0-2B98DE64359D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E8C2455-946D-4A6F-9D1C-A4E63580ACE8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
@@ -870,11 +870,61 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -882,8 +932,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -917,54 +965,6 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -994,6 +994,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1284,31 +1288,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.7109375" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="5.7109375" customWidth="1"/>
-    <col min="19" max="32" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.6640625" customWidth="1"/>
+    <col min="19" max="32" width="5.6640625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1318,28 +1322,28 @@
       <c r="J1" s="19">
         <v>3</v>
       </c>
-      <c r="K1" s="66">
+      <c r="K1" s="32">
         <v>4</v>
       </c>
-      <c r="L1" s="66">
+      <c r="L1" s="32">
         <v>5</v>
       </c>
-      <c r="M1" s="66">
+      <c r="M1" s="32">
         <v>6</v>
       </c>
-      <c r="N1" s="66">
+      <c r="N1" s="32">
         <v>7</v>
       </c>
-      <c r="O1" s="66">
+      <c r="O1" s="32">
         <v>8</v>
       </c>
-      <c r="P1" s="66">
+      <c r="P1" s="32">
         <v>9</v>
       </c>
-      <c r="Q1" s="66">
-        <v>10</v>
-      </c>
-      <c r="R1" s="66">
+      <c r="Q1" s="32">
+        <v>10</v>
+      </c>
+      <c r="R1" s="32">
         <v>11</v>
       </c>
       <c r="S1" s="20">
@@ -1385,35 +1389,35 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="143.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48" t="s">
+      <c r="B2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="30" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="J2" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="29" t="s">
-        <v>111</v>
-      </c>
       <c r="K2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="M2" s="29" t="s">
         <v>113</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="M2" s="29" t="s">
-        <v>114</v>
       </c>
       <c r="N2" s="30" t="s">
         <v>107</v>
@@ -1445,7 +1449,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1458,56 +1462,56 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="36"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$75=H4:H75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3" s="14" cm="1">
         <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$75=I4:I75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3" s="14" cm="1">
         <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$75=J4:J75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" s="14" cm="1">
         <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$75=K4:K75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L3" s="14" cm="1">
         <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$75=L4:L75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M3" s="14" cm="1">
         <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$75=M4:M75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" s="14" cm="1">
         <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$75=N4:N75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O3" s="14" cm="1">
         <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$75=O4:O75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P3" s="14" cm="1">
         <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$75=P4:P75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="14" cm="1">
         <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$75=Q4:Q75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R3" s="14" cm="1">
         <f t="array" ref="R3">SUMPRODUCT(($G$4:$G$75=R4:R75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
@@ -1566,8 +1570,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="55" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1589,13 +1593,13 @@
         <f>IF(OR(E4="",F4=""),"",IF(E4&gt;F4,"L",IF(E4&lt;F4,"V","E")))</f>
         <v>L</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K4" s="23" t="s">
@@ -1637,8 +1641,8 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
+    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="40"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1658,23 +1662,23 @@
         <f t="shared" ref="G5:G68" si="1">IF(OR(E5="",F5=""),"",IF(E5&gt;F5,"L",IF(E5&lt;F5,"V","E")))</f>
         <v>L</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I5" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K5" s="23" t="s">
         <v>46</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N5" s="24" t="s">
         <v>46</v>
@@ -1706,8 +1710,8 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="38"/>
+    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="40"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1723,14 +1727,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H6" s="24" t="s">
-        <v>46</v>
+      <c r="H6" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>46</v>
@@ -1771,8 +1775,8 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="38"/>
+    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="40"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1788,23 +1792,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H7" s="24" t="s">
-        <v>10</v>
+      <c r="H7" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I7" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>46</v>
+      <c r="J7" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N7" s="24" t="s">
         <v>46</v>
@@ -1836,8 +1840,8 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="38"/>
+    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="40"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1853,23 +1857,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N8" s="24" t="s">
         <v>104</v>
@@ -1901,8 +1905,8 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
+    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="41"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1918,20 +1922,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H9" s="24" t="s">
-        <v>46</v>
+      <c r="H9" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M9" s="23" t="s">
         <v>10</v>
@@ -1966,8 +1970,8 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="60" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1989,23 +1993,23 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L10" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N10" s="24" t="s">
         <v>46</v>
@@ -2037,8 +2041,8 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="38"/>
+    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="40"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2058,23 +2062,23 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H11" s="24" t="s">
-        <v>10</v>
+      <c r="H11" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L11" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N11" s="24" t="s">
         <v>104</v>
@@ -2106,8 +2110,8 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="38"/>
+    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="40"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2123,14 +2127,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K12" s="23" t="s">
         <v>46</v>
@@ -2171,8 +2175,8 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
+    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="40"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2188,14 +2192,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K13" s="23" t="s">
         <v>46</v>
@@ -2236,8 +2240,8 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="38"/>
+    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="40"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2253,23 +2257,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="H14" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I14" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="23" t="s">
+      <c r="J14" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L14" s="23" t="s">
         <v>10</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N14" s="24" t="s">
         <v>46</v>
@@ -2301,8 +2305,8 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
+    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="41"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2318,23 +2322,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H15" s="24" t="s">
-        <v>46</v>
+      <c r="H15" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J15" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N15" s="24" t="s">
         <v>10</v>
@@ -2366,8 +2370,8 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
+    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="61" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2389,14 +2393,14 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H16" s="24" t="s">
-        <v>46</v>
+      <c r="H16" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I16" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="23" t="s">
-        <v>10</v>
+      <c r="J16" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>46</v>
@@ -2437,8 +2441,8 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="38"/>
+    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="40"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2458,13 +2462,13 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I17" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="23" t="s">
+      <c r="J17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -2506,8 +2510,8 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="38"/>
+    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="40"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2523,23 +2527,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J18" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K18" s="23" t="s">
         <v>104</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N18" s="24" t="s">
         <v>46</v>
@@ -2571,8 +2575,8 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="38"/>
+    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="40"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2588,13 +2592,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J19" s="23" t="s">
+      <c r="J19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K19" s="23" t="s">
@@ -2636,8 +2640,8 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="38"/>
+    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="40"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2653,13 +2657,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H20" s="24" t="s">
+      <c r="H20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I20" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J20" s="23" t="s">
+      <c r="J20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -2701,8 +2705,8 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
+    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="41"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2718,23 +2722,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="23" t="s">
+      <c r="J21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N21" s="24" t="s">
         <v>46</v>
@@ -2766,8 +2770,8 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="42" t="s">
+    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="58" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2789,23 +2793,23 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H22" s="24" t="s">
-        <v>46</v>
+      <c r="H22" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I22" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J22" s="23" t="s">
-        <v>10</v>
+      <c r="J22" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L22" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N22" s="24" t="s">
         <v>46</v>
@@ -2837,8 +2841,8 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
+    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="40"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2858,20 +2862,20 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H23" s="24" t="s">
-        <v>104</v>
+      <c r="H23" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>46</v>
@@ -2906,8 +2910,8 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="38"/>
+    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="40"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2923,14 +2927,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H24" s="24" t="s">
-        <v>46</v>
+      <c r="H24" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J24" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K24" s="23" t="s">
         <v>46</v>
@@ -2971,8 +2975,8 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="38"/>
+    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="40"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2988,14 +2992,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H25" s="24" t="s">
-        <v>10</v>
+      <c r="H25" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J25" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="K25" s="23" t="s">
         <v>10</v>
@@ -3036,8 +3040,8 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="38"/>
+    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="40"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3053,23 +3057,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H26" s="24" t="s">
+      <c r="H26" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J26" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J26" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="K26" s="23" t="s">
         <v>10</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N26" s="24" t="s">
         <v>104</v>
@@ -3101,8 +3105,8 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="39"/>
+    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="41"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3118,23 +3122,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="H27" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J27" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J27" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="K27" s="23" t="s">
         <v>46</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N27" s="24" t="s">
         <v>104</v>
@@ -3166,8 +3170,8 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="43" t="s">
+    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="59" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3189,13 +3193,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I28" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="23" t="s">
+      <c r="J28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -3237,8 +3241,8 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="38"/>
+    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="40"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3258,23 +3262,23 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H29" s="24" t="s">
+      <c r="H29" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I29" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J29" s="23" t="s">
+      <c r="J29" s="24" t="s">
         <v>10</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N29" s="24" t="s">
         <v>104</v>
@@ -3306,8 +3310,8 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="38"/>
+    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="40"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3323,13 +3327,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H30" s="24" t="s">
+      <c r="H30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J30" s="23" t="s">
+      <c r="J30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -3371,8 +3375,8 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="38"/>
+    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="40"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3388,23 +3392,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H31" s="24" t="s">
-        <v>10</v>
+      <c r="H31" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J31" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="J31" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="K31" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N31" s="24" t="s">
         <v>46</v>
@@ -3436,8 +3440,8 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="38"/>
+    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="40"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3453,23 +3457,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H32" s="24" t="s">
-        <v>10</v>
+      <c r="H32" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J32" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K32" s="23" t="s">
         <v>104</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N32" s="24" t="s">
         <v>46</v>
@@ -3501,8 +3505,8 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="39"/>
+    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="41"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3518,20 +3522,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H33" s="24" t="s">
+      <c r="H33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I33" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="23" t="s">
+      <c r="J33" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M33" s="23" t="s">
         <v>104</v>
@@ -3566,8 +3570,8 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="41" t="s">
+    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="57" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3589,20 +3593,20 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H34" s="24" t="s">
+      <c r="H34" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I34" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J34" s="23" t="s">
+      <c r="J34" s="24" t="s">
         <v>10</v>
       </c>
       <c r="K34" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M34" s="23" t="s">
         <v>104</v>
@@ -3637,8 +3641,8 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="38"/>
+    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="40"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3658,13 +3662,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H35" s="24" t="s">
+      <c r="H35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I35" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J35" s="23" t="s">
+      <c r="J35" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K35" s="23" t="s">
@@ -3706,8 +3710,8 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
+    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="40"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3723,14 +3727,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H36" s="24" t="s">
+      <c r="H36" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I36" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J36" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J36" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K36" s="23" t="s">
         <v>46</v>
@@ -3771,8 +3775,8 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="38"/>
+    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="40"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3788,13 +3792,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H37" s="24" t="s">
+      <c r="H37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I37" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J37" s="23" t="s">
+      <c r="J37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="23" t="s">
@@ -3836,8 +3840,8 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="38"/>
+    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="40"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3853,20 +3857,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H38" s="24" t="s">
+      <c r="H38" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J38" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J38" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M38" s="23" t="s">
         <v>10</v>
@@ -3901,8 +3905,8 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="39"/>
+    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="41"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3918,23 +3922,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H39" s="24" t="s">
+      <c r="H39" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I39" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J39" s="23" t="s">
+      <c r="J39" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K39" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L39" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M39" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N39" s="24" t="s">
         <v>10</v>
@@ -3966,8 +3970,8 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
+    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="56" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3989,20 +3993,20 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H40" s="24" t="s">
-        <v>104</v>
+      <c r="H40" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J40" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="J40" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M40" s="23" t="s">
         <v>46</v>
@@ -4037,8 +4041,8 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="38"/>
+    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="40"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4058,23 +4062,23 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H41" s="24" t="s">
-        <v>104</v>
+      <c r="H41" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J41" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="J41" s="24" t="s">
         <v>10</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M41" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N41" s="24" t="s">
         <v>104</v>
@@ -4106,8 +4110,8 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="38"/>
+    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="40"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4123,23 +4127,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H42" s="24" t="s">
+      <c r="H42" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I42" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J42" s="23" t="s">
+      <c r="J42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L42" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M42" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N42" s="24" t="s">
         <v>46</v>
@@ -4171,8 +4175,8 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="38"/>
+    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="40"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4188,23 +4192,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H43" s="24" t="s">
+      <c r="H43" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J43" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J43" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="K43" s="23" t="s">
         <v>104</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="M43" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N43" s="24" t="s">
         <v>46</v>
@@ -4236,8 +4240,8 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="38"/>
+    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="40"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4253,23 +4257,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H44" s="24" t="s">
-        <v>46</v>
+      <c r="H44" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J44" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N44" s="24" t="s">
         <v>104</v>
@@ -4301,8 +4305,8 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="39"/>
+    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="41"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4318,13 +4322,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H45" s="24" t="s">
+      <c r="H45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I45" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J45" s="23" t="s">
+      <c r="J45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -4366,8 +4370,8 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="57" t="s">
+    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="39" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4389,13 +4393,13 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H46" s="24" t="s">
+      <c r="H46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I46" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J46" s="23" t="s">
+      <c r="J46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K46" s="23" t="s">
@@ -4437,8 +4441,8 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="38"/>
+    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="40"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4458,23 +4462,23 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H47" s="24" t="s">
+      <c r="H47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I47" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J47" s="23" t="s">
+      <c r="J47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M47" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N47" s="24" t="s">
         <v>104</v>
@@ -4506,8 +4510,8 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="38"/>
+    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="40"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4523,13 +4527,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H48" s="24" t="s">
+      <c r="H48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I48" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J48" s="23" t="s">
+      <c r="J48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K48" s="23" t="s">
@@ -4571,8 +4575,8 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="38"/>
+    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="40"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4588,23 +4592,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H49" s="24" t="s">
+      <c r="H49" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I49" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J49" s="23" t="s">
+      <c r="J49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L49" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M49" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N49" s="24" t="s">
         <v>46</v>
@@ -4636,8 +4640,8 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="38"/>
+    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="40"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4653,23 +4657,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H50" s="24" t="s">
-        <v>10</v>
+      <c r="H50" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I50" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J50" s="23" t="s">
-        <v>104</v>
+      <c r="J50" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K50" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L50" s="23" t="s">
         <v>10</v>
       </c>
       <c r="M50" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N50" s="24" t="s">
         <v>10</v>
@@ -4701,8 +4705,8 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="39"/>
+    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="41"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4718,14 +4722,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H51" s="24" t="s">
-        <v>10</v>
+      <c r="H51" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I51" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J51" s="23" t="s">
-        <v>104</v>
+      <c r="J51" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K51" s="23" t="s">
         <v>104</v>
@@ -4766,8 +4770,8 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="60" t="s">
+    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="46" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4789,23 +4793,23 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H52" s="26" t="s">
+      <c r="H52" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I52" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J52" s="25" t="s">
+      <c r="J52" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L52" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M52" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N52" s="26" t="s">
         <v>104</v>
@@ -4837,8 +4841,8 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="61"/>
+    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="47"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4848,20 +4852,24 @@
       <c r="D53" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
+      <c r="E53" s="15">
+        <v>1</v>
+      </c>
+      <c r="F53" s="15">
+        <v>4</v>
+      </c>
       <c r="G53" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H53" s="26" t="s">
-        <v>10</v>
+        <v>V</v>
+      </c>
+      <c r="H53" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I53" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J53" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="J53" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="K53" s="25" t="s">
         <v>104</v>
@@ -4902,8 +4910,8 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="61"/>
+    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="47"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4919,13 +4927,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H54" s="26" t="s">
+      <c r="H54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I54" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J54" s="25" t="s">
+      <c r="J54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K54" s="25" t="s">
@@ -4967,8 +4975,8 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="61"/>
+    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="47"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4984,23 +4992,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H55" s="26" t="s">
-        <v>46</v>
+      <c r="H55" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I55" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J55" s="25" t="s">
-        <v>10</v>
+      <c r="J55" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="K55" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L55" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M55" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N55" s="26" t="s">
         <v>104</v>
@@ -5033,8 +5041,8 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="61"/>
+    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="47"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5050,23 +5058,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H56" s="26" t="s">
-        <v>104</v>
+      <c r="H56" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="I56" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J56" s="25" t="s">
-        <v>46</v>
+      <c r="J56" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L56" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M56" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N56" s="26" t="s">
         <v>104</v>
@@ -5098,8 +5106,8 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="62"/>
+    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="48"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5115,23 +5123,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H57" s="26" t="s">
+      <c r="H57" s="25" t="s">
         <v>10</v>
       </c>
       <c r="I57" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J57" s="25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J57" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="K57" s="25" t="s">
         <v>46</v>
       </c>
       <c r="L57" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M57" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N57" s="26" t="s">
         <v>46</v>
@@ -5163,8 +5171,8 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="63" t="s">
+    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="49" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5176,29 +5184,33 @@
       <c r="D58" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
+      <c r="E58" s="16">
+        <v>3</v>
+      </c>
+      <c r="F58" s="16">
+        <v>0</v>
+      </c>
       <c r="G58" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H58" s="26" t="s">
+        <v>L</v>
+      </c>
+      <c r="H58" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I58" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J58" s="25" t="s">
+      <c r="J58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K58" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L58" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N58" s="26" t="s">
         <v>46</v>
@@ -5230,8 +5242,8 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="64"/>
+    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="50"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5247,23 +5259,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H59" s="26" t="s">
+      <c r="H59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I59" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J59" s="25" t="s">
+      <c r="J59" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="L59" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M59" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N59" s="26" t="s">
         <v>46</v>
@@ -5295,8 +5307,8 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="64"/>
+    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="50"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5312,14 +5324,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H60" s="26" t="s">
+      <c r="H60" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I60" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J60" s="25" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J60" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="K60" s="25" t="s">
         <v>46</v>
@@ -5360,8 +5372,8 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="64"/>
+    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="50"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5377,23 +5389,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H61" s="26" t="s">
-        <v>10</v>
+      <c r="H61" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J61" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="J61" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L61" s="25" t="s">
         <v>10</v>
       </c>
       <c r="M61" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N61" s="26" t="s">
         <v>10</v>
@@ -5425,8 +5437,8 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="64"/>
+    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="50"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5442,20 +5454,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H62" s="26" t="s">
-        <v>10</v>
+      <c r="H62" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J62" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="J62" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L62" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M62" s="25" t="s">
         <v>10</v>
@@ -5490,8 +5502,8 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="65"/>
+    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="51"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5507,13 +5519,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H63" s="26" t="s">
+      <c r="H63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="I63" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J63" s="25" t="s">
+      <c r="J63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K63" s="25" t="s">
@@ -5555,8 +5567,8 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="51" t="s">
+    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="33" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5574,13 +5586,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H64" s="26" t="s">
+      <c r="H64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I64" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J64" s="25" t="s">
+      <c r="J64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K64" s="25" t="s">
@@ -5622,8 +5634,8 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="52"/>
+    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="34"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5639,13 +5651,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H65" s="26" t="s">
+      <c r="H65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="I65" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J65" s="25" t="s">
+      <c r="J65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K65" s="25" t="s">
@@ -5687,8 +5699,8 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="52"/>
+    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="34"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5704,13 +5716,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H66" s="26" t="s">
+      <c r="H66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I66" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J66" s="25" t="s">
+      <c r="J66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K66" s="25" t="s">
@@ -5752,8 +5764,8 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="52"/>
+    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="34"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5769,14 +5781,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H67" s="26" t="s">
-        <v>46</v>
+      <c r="H67" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I67" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J67" s="25" t="s">
-        <v>104</v>
+      <c r="J67" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="K67" s="25" t="s">
         <v>46</v>
@@ -5817,8 +5829,8 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="52"/>
+    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="34"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5834,23 +5846,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H68" s="26" t="s">
-        <v>10</v>
+      <c r="H68" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="I68" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J68" s="25" t="s">
-        <v>46</v>
+      <c r="J68" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L68" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M68" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N68" s="26" t="s">
         <v>104</v>
@@ -5882,8 +5894,8 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="53"/>
+    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="35"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5899,23 +5911,23 @@
         <f t="shared" ref="G69:G75" si="2">IF(OR(E69="",F69=""),"",IF(E69&gt;F69,"L",IF(E69&lt;F69,"V","E")))</f>
         <v/>
       </c>
-      <c r="H69" s="26" t="s">
-        <v>10</v>
+      <c r="H69" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="I69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J69" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="J69" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L69" s="25" t="s">
         <v>10</v>
       </c>
       <c r="M69" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N69" s="26" t="s">
         <v>104</v>
@@ -5947,8 +5959,8 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="54" t="s">
+    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="36" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5966,20 +5978,20 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H70" s="26" t="s">
-        <v>104</v>
+      <c r="H70" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I70" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J70" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="J70" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L70" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M70" s="25" t="s">
         <v>46</v>
@@ -6014,8 +6026,8 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="55"/>
+    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="37"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6031,23 +6043,23 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H71" s="26" t="s">
-        <v>46</v>
+      <c r="H71" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J71" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="J71" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="K71" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L71" s="25" t="s">
         <v>10</v>
       </c>
       <c r="M71" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N71" s="26" t="s">
         <v>104</v>
@@ -6079,8 +6091,8 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="55"/>
+    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="37"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6096,23 +6108,23 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H72" s="26" t="s">
+      <c r="H72" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I72" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J72" s="25" t="s">
+      <c r="J72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L72" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N72" s="26" t="s">
         <v>46</v>
@@ -6144,8 +6156,8 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="55"/>
+    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="37"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6161,14 +6173,14 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H73" s="26" t="s">
+      <c r="H73" s="25" t="s">
         <v>104</v>
       </c>
       <c r="I73" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J73" s="25" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="J73" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="K73" s="25" t="s">
         <v>104</v>
@@ -6209,8 +6221,8 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="55"/>
+    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="37"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6226,23 +6238,23 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H74" s="26" t="s">
+      <c r="H74" s="25" t="s">
         <v>104</v>
       </c>
       <c r="I74" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J74" s="25" t="s">
+      <c r="J74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L74" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M74" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N74" s="26" t="s">
         <v>46</v>
@@ -6274,8 +6286,8 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="56"/>
+    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="38"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6291,23 +6303,23 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H75" s="26" t="s">
+      <c r="H75" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I75" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J75" s="25" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J75" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="K75" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L75" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M75" s="25" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N75" s="26" t="s">
         <v>46</v>
@@ -6339,36 +6351,36 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="58" t="s">
+      <c r="D76" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="33"/>
-      <c r="F76" s="34"/>
+      <c r="E76" s="43"/>
+      <c r="F76" s="44"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>49</v>
-      </c>
-      <c r="H76" s="26">
+        <v>57</v>
+      </c>
+      <c r="H76" s="25">
+        <v>222</v>
+      </c>
+      <c r="I76" s="26">
         <v>179</v>
       </c>
-      <c r="I76" s="26">
+      <c r="J76" s="26">
         <v>201</v>
       </c>
-      <c r="J76" s="25">
-        <v>222</v>
-      </c>
       <c r="K76" s="25">
+        <v>172</v>
+      </c>
+      <c r="L76" s="25">
+        <v>190</v>
+      </c>
+      <c r="M76" s="25">
         <v>186</v>
-      </c>
-      <c r="L76" s="25">
-        <v>172</v>
-      </c>
-      <c r="M76" s="25">
-        <v>190</v>
       </c>
       <c r="N76" s="26">
         <v>185</v>
@@ -6400,118 +6412,118 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="59" t="s">
+      <c r="D77" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="34"/>
+      <c r="E77" s="43"/>
+      <c r="F77" s="43"/>
+      <c r="G77" s="44"/>
       <c r="H77" s="28">
-        <f t="shared" ref="H77:R77" si="3">SUM(H78:H81)</f>
+        <f>SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
+        <f>SUM(I78:I81)</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="28">
+        <f>SUM(J78:J81)</f>
+        <v>0</v>
+      </c>
+      <c r="K77" s="28">
+        <f>SUM(K78:K81)</f>
+        <v>0</v>
+      </c>
+      <c r="L77" s="28">
+        <f>SUM(L78:L81)</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="28">
+        <f>SUM(M78:M81)</f>
+        <v>0</v>
+      </c>
+      <c r="N77" s="28">
+        <f>SUM(N78:N81)</f>
+        <v>0</v>
+      </c>
+      <c r="O77" s="28">
+        <f>SUM(O78:O81)</f>
+        <v>0</v>
+      </c>
+      <c r="P77" s="28">
+        <f>SUM(P78:P81)</f>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="28">
+        <f>SUM(Q78:Q81)</f>
+        <v>0</v>
+      </c>
+      <c r="R77" s="28">
+        <f>SUM(R78:R81)</f>
+        <v>0</v>
+      </c>
+      <c r="S77" s="28">
+        <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
+        <v>43</v>
+      </c>
+      <c r="T77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="28">
+        <v>43</v>
+      </c>
+      <c r="U77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="28">
+        <v>43</v>
+      </c>
+      <c r="V77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L77" s="28">
+        <v>43</v>
+      </c>
+      <c r="W77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="28">
+        <v>43</v>
+      </c>
+      <c r="X77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="28">
+        <v>43</v>
+      </c>
+      <c r="Y77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="28">
+        <v>43</v>
+      </c>
+      <c r="Z77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="28">
+        <v>43</v>
+      </c>
+      <c r="AA77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="28">
+        <v>43</v>
+      </c>
+      <c r="AB77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="28">
+        <v>43</v>
+      </c>
+      <c r="AC77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S77" s="28">
-        <f t="shared" ref="S77:AF77" si="4">SUM(S78:S81)</f>
-        <v>51</v>
-      </c>
-      <c r="T77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="U77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="V77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="W77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="X77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="Y77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="Z77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="AA77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="AB77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-      <c r="AC77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AD77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
+        <f t="shared" si="3"/>
+        <v>43</v>
       </c>
       <c r="AE77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
+        <f t="shared" si="3"/>
+        <v>43</v>
       </c>
       <c r="AF77" s="28">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6520,107 +6532,107 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="5">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6629,107 +6641,107 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="6">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="6"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6738,107 +6750,107 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="7">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6847,107 +6859,107 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="8">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6981,7 +6993,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7015,7 +7027,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7049,7 +7061,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7083,7 +7095,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7117,7 +7129,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7151,7 +7163,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7185,7 +7197,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7219,7 +7231,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7253,7 +7265,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7287,7 +7299,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7321,7 +7333,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7355,7 +7367,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7389,7 +7401,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7423,7 +7435,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7457,7 +7469,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7491,7 +7503,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7525,7 +7537,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7559,7 +7571,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7593,7 +7605,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7602,7 +7614,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7611,7 +7623,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7620,7 +7632,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7629,7 +7641,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7638,7 +7650,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7647,7 +7659,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7656,7 +7668,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7665,7 +7677,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7674,7 +7686,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7683,7 +7695,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7692,7 +7704,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7701,7 +7713,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7710,7 +7722,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7719,7 +7731,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7728,7 +7740,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7737,7 +7749,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7746,7 +7758,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7755,7 +7767,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7764,7 +7776,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7773,7 +7785,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7782,7 +7794,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7791,7 +7803,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7800,7 +7812,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7815,13 +7827,6 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7833,6 +7838,13 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -7847,14 +7859,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="15" width="11.42578125" customWidth="1"/>
+    <col min="1" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="15" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>16</v>
@@ -7901,7 +7913,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -7946,7 +7958,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -7991,7 +8003,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -8036,7 +8048,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -8081,7 +8093,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -8126,7 +8138,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -8171,7 +8183,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -8216,7 +8228,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -8261,7 +8273,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -8306,7 +8318,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -8351,7 +8363,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>16</v>
@@ -8396,7 +8408,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>16</v>
@@ -8441,7 +8453,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
@@ -8486,7 +8498,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -8531,7 +8543,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
@@ -8576,7 +8588,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>16</v>
@@ -8621,7 +8633,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
@@ -8666,7 +8678,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>16</v>
@@ -8711,7 +8723,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>16</v>
@@ -8756,7 +8768,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>16</v>
@@ -8801,7 +8813,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -8846,7 +8858,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -8891,7 +8903,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>16</v>
@@ -8936,7 +8948,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>16</v>
@@ -8981,7 +8993,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -9026,7 +9038,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>16</v>
@@ -9071,7 +9083,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>16</v>
@@ -9116,7 +9128,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>16</v>
@@ -9161,7 +9173,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>16</v>
@@ -9206,7 +9218,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>16</v>
@@ -9251,7 +9263,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>16</v>
@@ -9296,7 +9308,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>16</v>
@@ -9341,7 +9353,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>16</v>
@@ -9386,7 +9398,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>16</v>
@@ -9431,7 +9443,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>16</v>
@@ -9476,7 +9488,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>16</v>
@@ -9521,7 +9533,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>16</v>
@@ -9566,7 +9578,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>16</v>
@@ -9611,7 +9623,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>16</v>
@@ -9656,7 +9668,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>16</v>
@@ -9701,7 +9713,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>16</v>
@@ -9746,7 +9758,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>16</v>
@@ -9791,7 +9803,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>16</v>
@@ -9836,7 +9848,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>16</v>
@@ -9881,7 +9893,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>16</v>
@@ -9926,7 +9938,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>16</v>
@@ -9971,7 +9983,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>16</v>
@@ -10016,7 +10028,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>16</v>
@@ -10061,7 +10073,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>16</v>
@@ -10106,7 +10118,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>16</v>
@@ -10151,7 +10163,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>16</v>
@@ -10196,7 +10208,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>16</v>
@@ -10241,7 +10253,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>16</v>
@@ -10286,7 +10298,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>16</v>
@@ -10331,7 +10343,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>16</v>
@@ -10376,7 +10388,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>16</v>
@@ -10421,7 +10433,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>16</v>
@@ -10466,7 +10478,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>16</v>
@@ -10511,7 +10523,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>16</v>
@@ -10556,7 +10568,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>16</v>
@@ -10601,7 +10613,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>16</v>
@@ -10646,7 +10658,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>16</v>
@@ -10691,7 +10703,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>16</v>
@@ -10736,7 +10748,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>16</v>
@@ -10781,7 +10793,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>16</v>
@@ -10826,7 +10838,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>16</v>
@@ -10871,7 +10883,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>16</v>
@@ -10916,7 +10928,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>16</v>
@@ -10961,7 +10973,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>16</v>
@@ -11006,7 +11018,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>16</v>
@@ -11051,7 +11063,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>16</v>
@@ -11096,7 +11108,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>16</v>
@@ -11141,7 +11153,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>16</v>
@@ -11186,7 +11198,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>16</v>
@@ -11231,7 +11243,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>16</v>
@@ -11276,7 +11288,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>16</v>
@@ -11321,7 +11333,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>16</v>
@@ -11366,7 +11378,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>16</v>
@@ -11411,7 +11423,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>16</v>
@@ -11456,7 +11468,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>16</v>
@@ -11501,7 +11513,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>16</v>
@@ -11546,7 +11558,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>16</v>
@@ -11591,7 +11603,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>16</v>
@@ -11636,7 +11648,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>16</v>
@@ -11681,7 +11693,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>16</v>
@@ -11726,7 +11738,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>16</v>
@@ -11771,7 +11783,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>16</v>
@@ -11816,7 +11828,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>16</v>
@@ -11861,7 +11873,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>16</v>
@@ -11906,7 +11918,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>16</v>
@@ -11951,7 +11963,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>16</v>
@@ -11996,7 +12008,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>16</v>
@@ -12041,7 +12053,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>16</v>
@@ -12086,7 +12098,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>16</v>
@@ -12131,7 +12143,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>16</v>
@@ -12176,7 +12188,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>16</v>
@@ -12221,7 +12233,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>16</v>
@@ -12266,7 +12278,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>16</v>
@@ -12311,7 +12323,7 @@
         <v>SI(G28-H28=-100;0;</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12337,9 +12349,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="11" width="10.7109375" customWidth="1"/>
+    <col min="1" max="11" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12350,26 +12362,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="11" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="11" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -12377,61 +12389,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -12439,7 +12451,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -12447,19 +12459,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -12467,19 +12479,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -12487,19 +12499,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -12507,13 +12519,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -12521,229 +12533,229 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="1"/>
     </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1"/>
     </row>
-    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="1"/>
     </row>
-    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="1"/>
     </row>
-    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="1"/>
     </row>
-    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="1"/>
     </row>
-    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="1"/>
     </row>
-    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="1"/>
     </row>
-    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="1"/>
     </row>
-    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1"/>
     </row>
   </sheetData>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E8C2455-946D-4A6F-9D1C-A4E63580ACE8}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0515CD9-3561-4DE0-9CAA-E6558E43F67B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1411,13 +1411,13 @@
         <v>108</v>
       </c>
       <c r="K2" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="M2" s="29" t="s">
         <v>114</v>
-      </c>
-      <c r="M2" s="29" t="s">
-        <v>113</v>
       </c>
       <c r="N2" s="30" t="s">
         <v>107</v>
@@ -1471,47 +1471,47 @@
       </c>
       <c r="H3" s="14" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$75=H4:H75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3" s="14" cm="1">
         <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$75=I4:I75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J3" s="14" cm="1">
         <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$75=J4:J75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K3" s="14" cm="1">
         <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$75=K4:K75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L3" s="14" cm="1">
         <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$75=L4:L75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M3" s="14" cm="1">
         <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$75=M4:M75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N3" s="14" cm="1">
         <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$75=N4:N75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O3" s="14" cm="1">
         <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$75=O4:O75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P3" s="14" cm="1">
         <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$75=P4:P75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q3" s="14" cm="1">
         <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$75=Q4:Q75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R3" s="14" cm="1">
         <f t="array" ref="R3">SUMPRODUCT(($G$4:$G$75=R4:R75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
@@ -1675,10 +1675,10 @@
         <v>46</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N5" s="24" t="s">
         <v>46</v>
@@ -1802,13 +1802,13 @@
         <v>10</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N7" s="24" t="s">
         <v>46</v>
@@ -1867,13 +1867,13 @@
         <v>104</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N8" s="24" t="s">
         <v>104</v>
@@ -1932,10 +1932,10 @@
         <v>104</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M9" s="23" t="s">
         <v>10</v>
@@ -2003,13 +2003,13 @@
         <v>46</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L10" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N10" s="24" t="s">
         <v>46</v>
@@ -2072,13 +2072,13 @@
         <v>104</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L11" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N11" s="24" t="s">
         <v>104</v>
@@ -2267,13 +2267,13 @@
         <v>46</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L14" s="23" t="s">
         <v>10</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N14" s="24" t="s">
         <v>46</v>
@@ -2332,13 +2332,13 @@
         <v>104</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N15" s="24" t="s">
         <v>10</v>
@@ -2540,10 +2540,10 @@
         <v>104</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N18" s="24" t="s">
         <v>46</v>
@@ -2735,10 +2735,10 @@
         <v>46</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N21" s="24" t="s">
         <v>46</v>
@@ -2803,13 +2803,13 @@
         <v>46</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L22" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N22" s="24" t="s">
         <v>46</v>
@@ -2872,10 +2872,10 @@
         <v>46</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>46</v>
@@ -3070,10 +3070,10 @@
         <v>10</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N26" s="24" t="s">
         <v>104</v>
@@ -3135,10 +3135,10 @@
         <v>46</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N27" s="24" t="s">
         <v>104</v>
@@ -3272,13 +3272,13 @@
         <v>10</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N29" s="24" t="s">
         <v>104</v>
@@ -3402,13 +3402,13 @@
         <v>46</v>
       </c>
       <c r="K31" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N31" s="24" t="s">
         <v>46</v>
@@ -3470,10 +3470,10 @@
         <v>104</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N32" s="24" t="s">
         <v>46</v>
@@ -3532,10 +3532,10 @@
         <v>104</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M33" s="23" t="s">
         <v>104</v>
@@ -3603,10 +3603,10 @@
         <v>10</v>
       </c>
       <c r="K34" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M34" s="23" t="s">
         <v>104</v>
@@ -3867,10 +3867,10 @@
         <v>10</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M38" s="23" t="s">
         <v>10</v>
@@ -3932,13 +3932,13 @@
         <v>104</v>
       </c>
       <c r="K39" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L39" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M39" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N39" s="24" t="s">
         <v>10</v>
@@ -4003,10 +4003,10 @@
         <v>46</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M40" s="23" t="s">
         <v>46</v>
@@ -4072,13 +4072,13 @@
         <v>10</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M41" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N41" s="24" t="s">
         <v>104</v>
@@ -4137,13 +4137,13 @@
         <v>46</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L42" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M42" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N42" s="24" t="s">
         <v>46</v>
@@ -4205,10 +4205,10 @@
         <v>104</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="M43" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N43" s="24" t="s">
         <v>46</v>
@@ -4267,13 +4267,13 @@
         <v>104</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N44" s="24" t="s">
         <v>104</v>
@@ -4475,10 +4475,10 @@
         <v>104</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M47" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N47" s="24" t="s">
         <v>104</v>
@@ -4602,13 +4602,13 @@
         <v>46</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L49" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M49" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N49" s="24" t="s">
         <v>46</v>
@@ -4667,13 +4667,13 @@
         <v>10</v>
       </c>
       <c r="K50" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L50" s="23" t="s">
         <v>10</v>
       </c>
       <c r="M50" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N50" s="24" t="s">
         <v>10</v>
@@ -4803,13 +4803,13 @@
         <v>46</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L52" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M52" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N52" s="26" t="s">
         <v>104</v>
@@ -5002,13 +5002,13 @@
         <v>46</v>
       </c>
       <c r="K55" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L55" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M55" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N55" s="26" t="s">
         <v>104</v>
@@ -5068,13 +5068,13 @@
         <v>104</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L56" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M56" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N56" s="26" t="s">
         <v>104</v>
@@ -5136,10 +5136,10 @@
         <v>46</v>
       </c>
       <c r="L57" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M57" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N57" s="26" t="s">
         <v>46</v>
@@ -5204,13 +5204,13 @@
         <v>46</v>
       </c>
       <c r="K58" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L58" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N58" s="26" t="s">
         <v>46</v>
@@ -5253,11 +5253,15 @@
       <c r="D59" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
+      <c r="E59" s="16">
+        <v>3</v>
+      </c>
+      <c r="F59" s="16">
+        <v>1</v>
+      </c>
       <c r="G59" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="H59" s="25" t="s">
         <v>46</v>
@@ -5272,10 +5276,10 @@
         <v>46</v>
       </c>
       <c r="L59" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M59" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N59" s="26" t="s">
         <v>46</v>
@@ -5399,13 +5403,13 @@
         <v>46</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L61" s="25" t="s">
         <v>10</v>
       </c>
       <c r="M61" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N61" s="26" t="s">
         <v>10</v>
@@ -5464,10 +5468,10 @@
         <v>104</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L62" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M62" s="25" t="s">
         <v>10</v>
@@ -5580,11 +5584,15 @@
       <c r="D64" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
+      <c r="E64" s="17">
+        <v>1</v>
+      </c>
+      <c r="F64" s="17">
+        <v>1</v>
+      </c>
       <c r="G64" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="H64" s="25" t="s">
         <v>46</v>
@@ -5645,11 +5653,15 @@
       <c r="D65" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
+      <c r="E65" s="17">
+        <v>1</v>
+      </c>
+      <c r="F65" s="17">
+        <v>3</v>
+      </c>
       <c r="G65" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>V</v>
       </c>
       <c r="H65" s="25" t="s">
         <v>104</v>
@@ -5856,13 +5868,13 @@
         <v>10</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L68" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M68" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N68" s="26" t="s">
         <v>104</v>
@@ -5921,13 +5933,13 @@
         <v>104</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L69" s="25" t="s">
         <v>10</v>
       </c>
       <c r="M69" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="N69" s="26" t="s">
         <v>104</v>
@@ -5972,11 +5984,15 @@
       <c r="D70" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E70" s="18"/>
-      <c r="F70" s="18"/>
+      <c r="E70" s="18">
+        <v>4</v>
+      </c>
+      <c r="F70" s="18">
+        <v>2</v>
+      </c>
       <c r="G70" s="7" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="H70" s="25" t="s">
         <v>10</v>
@@ -5988,10 +6004,10 @@
         <v>46</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L70" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M70" s="25" t="s">
         <v>46</v>
@@ -6037,11 +6053,15 @@
       <c r="D71" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
+      <c r="E71" s="18">
+        <v>1</v>
+      </c>
+      <c r="F71" s="18">
+        <v>0</v>
+      </c>
       <c r="G71" s="7" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="H71" s="25" t="s">
         <v>10</v>
@@ -6053,13 +6073,13 @@
         <v>104</v>
       </c>
       <c r="K71" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L71" s="25" t="s">
         <v>10</v>
       </c>
       <c r="M71" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N71" s="26" t="s">
         <v>104</v>
@@ -6118,13 +6138,13 @@
         <v>46</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L72" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N72" s="26" t="s">
         <v>46</v>
@@ -6248,13 +6268,13 @@
         <v>104</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L74" s="25" t="s">
         <v>104</v>
       </c>
       <c r="M74" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="N74" s="26" t="s">
         <v>46</v>
@@ -6313,13 +6333,13 @@
         <v>10</v>
       </c>
       <c r="K75" s="25" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L75" s="25" t="s">
         <v>46</v>
       </c>
       <c r="M75" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N75" s="26" t="s">
         <v>46</v>
@@ -6362,7 +6382,7 @@
       <c r="F76" s="44"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H76" s="25">
         <v>222</v>
@@ -6374,13 +6394,13 @@
         <v>201</v>
       </c>
       <c r="K76" s="25">
+        <v>186</v>
+      </c>
+      <c r="L76" s="25">
         <v>172</v>
       </c>
-      <c r="L76" s="25">
+      <c r="M76" s="25">
         <v>190</v>
-      </c>
-      <c r="M76" s="25">
-        <v>186</v>
       </c>
       <c r="N76" s="26">
         <v>185</v>
@@ -6423,104 +6443,104 @@
       <c r="F77" s="43"/>
       <c r="G77" s="44"/>
       <c r="H77" s="28">
-        <f>SUM(H78:H81)</f>
+        <f t="shared" ref="H77:R77" si="3">SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
-        <f>SUM(I78:I81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J77" s="28">
-        <f>SUM(J78:J81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K77" s="28">
-        <f>SUM(K78:K81)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L77" s="28">
-        <f>SUM(L78:L81)</f>
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M77" s="28">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M77" s="28">
-        <f>SUM(M78:M81)</f>
+      <c r="N77" s="28">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N77" s="28">
-        <f>SUM(N78:N81)</f>
+      <c r="O77" s="28">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="P77" s="28">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="Q77" s="28">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O77" s="28">
-        <f>SUM(O78:O81)</f>
+      <c r="R77" s="28">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P77" s="28">
-        <f>SUM(P78:P81)</f>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="28">
-        <f>SUM(Q78:Q81)</f>
-        <v>0</v>
-      </c>
-      <c r="R77" s="28">
-        <f>SUM(R78:R81)</f>
-        <v>0</v>
-      </c>
       <c r="S77" s="28">
-        <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
-        <v>43</v>
+        <f t="shared" ref="S77:AF77" si="4">SUM(S78:S81)</f>
+        <v>26</v>
       </c>
       <c r="T77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="U77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="V77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="W77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="X77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="Y77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="Z77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="AA77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="AB77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="AC77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="AD77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="AE77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="AF77" s="28">
-        <f t="shared" si="3"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6532,103 +6552,103 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="5">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -6641,104 +6661,104 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="6">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="5"/>
-        <v>43</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6750,104 +6770,104 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="7">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="P80" s="3">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q80" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P80" s="3">
-        <f t="shared" si="6"/>
+      <c r="R80" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="S80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6859,103 +6879,103 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="8">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="M81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M81" s="3">
-        <f t="shared" si="7"/>
+      <c r="N81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N81" s="3">
-        <f t="shared" si="7"/>
+      <c r="O81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O81" s="3">
-        <f t="shared" si="7"/>
+      <c r="P81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P81" s="3">
-        <f t="shared" si="7"/>
+      <c r="Q81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q81" s="3">
-        <f t="shared" si="7"/>
+      <c r="R81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R81" s="3">
-        <f t="shared" si="7"/>
+      <c r="S81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S81" s="3">
-        <f t="shared" si="7"/>
+      <c r="T81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T81" s="3">
-        <f t="shared" si="7"/>
+      <c r="U81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U81" s="3">
-        <f t="shared" si="7"/>
+      <c r="V81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V81" s="3">
-        <f t="shared" si="7"/>
+      <c r="W81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W81" s="3">
-        <f t="shared" si="7"/>
+      <c r="X81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X81" s="3">
-        <f t="shared" si="7"/>
+      <c r="Y81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Y81" s="3">
-        <f t="shared" si="7"/>
+      <c r="Z81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Z81" s="3">
-        <f t="shared" si="7"/>
+      <c r="AA81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA81" s="3">
-        <f t="shared" si="7"/>
+      <c r="AB81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AB81" s="3">
-        <f t="shared" si="7"/>
+      <c r="AC81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AC81" s="3">
-        <f t="shared" si="7"/>
+      <c r="AD81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AD81" s="3">
-        <f t="shared" si="7"/>
+      <c r="AE81" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AE81" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0515CD9-3561-4DE0-9CAA-E6558E43F67B}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A93EAD76-B957-4A92-9CE4-2B338ED12165}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
@@ -873,58 +873,11 @@
     <xf numFmtId="0" fontId="6" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -932,6 +885,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -964,6 +919,51 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1288,31 +1288,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.6640625" customWidth="1"/>
-    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="5.6640625" customWidth="1"/>
-    <col min="19" max="32" width="5.6640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.7109375" customWidth="1"/>
+    <col min="19" max="32" width="5.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="35"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1389,47 +1389,47 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+    <row r="2" spans="1:32" ht="143.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="64" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="66"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51"/>
       <c r="H2" s="29" t="s">
         <v>111</v>
       </c>
       <c r="I2" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L2" s="30" t="s">
         <v>108</v>
-      </c>
-      <c r="K2" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>102</v>
       </c>
       <c r="M2" s="29" t="s">
         <v>114</v>
       </c>
       <c r="N2" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="O2" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="O2" s="30" t="s">
-        <v>109</v>
-      </c>
       <c r="P2" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q2" s="29" t="s">
         <v>112</v>
-      </c>
-      <c r="Q2" s="29" t="s">
-        <v>115</v>
       </c>
       <c r="R2" s="30" t="s">
         <v>105</v>
@@ -1449,7 +1449,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1462,24 +1462,24 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="54"/>
+      <c r="F3" s="37"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$75=H4:H75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I3" s="14" cm="1">
         <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$75=I4:I75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" s="14" cm="1">
         <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$75=J4:J75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" s="14" cm="1">
         <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$75=K4:K75)*($G$4:$G$75&lt;&gt;""))</f>
@@ -1487,23 +1487,23 @@
       </c>
       <c r="L3" s="14" cm="1">
         <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$75=L4:L75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M3" s="14" cm="1">
         <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$75=M4:M75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N3" s="14" cm="1">
         <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$75=N4:N75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O3" s="14" cm="1">
         <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$75=O4:O75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P3" s="14" cm="1">
         <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$75=P4:P75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="14" cm="1">
         <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$75=Q4:Q75)*($G$4:$G$75&lt;&gt;""))</f>
@@ -1515,63 +1515,63 @@
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="W3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="X3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AD3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF3" s="14">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1599,13 +1599,13 @@
       <c r="I4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="23" t="s">
+      <c r="L4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M4" s="23" t="s">
@@ -1641,8 +1641,8 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="40"/>
+    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="39"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1668,13 +1668,13 @@
       <c r="I5" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M5" s="23" t="s">
@@ -1710,8 +1710,8 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="40"/>
+    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="39"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1721,11 +1721,15 @@
       <c r="D6" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>10</v>
@@ -1733,23 +1737,23 @@
       <c r="I6" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="24" t="s">
-        <v>104</v>
+      <c r="J6" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="23" t="s">
-        <v>46</v>
+      <c r="L6" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M6" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N6" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="O6" s="24" t="s">
         <v>110</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>10</v>
       </c>
       <c r="P6" s="23" t="s">
         <v>46</v>
@@ -1775,8 +1779,8 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="40"/>
+    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="39"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1798,14 +1802,14 @@
       <c r="I7" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L7" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M7" s="23" t="s">
         <v>46</v>
@@ -1840,8 +1844,8 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="40"/>
+    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="39"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1863,23 +1867,23 @@
       <c r="I8" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J8" s="24" t="s">
-        <v>104</v>
+      <c r="J8" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M8" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="P8" s="23" t="s">
         <v>104</v>
@@ -1905,8 +1909,8 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="41"/>
+    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="40"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1928,13 +1932,13 @@
       <c r="I9" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="24" t="s">
-        <v>104</v>
+      <c r="J9" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L9" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M9" s="23" t="s">
@@ -1947,10 +1951,10 @@
         <v>104</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R9" s="24" t="s">
         <v>104</v>
@@ -1970,8 +1974,8 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="60" t="s">
+    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1999,29 +2003,29 @@
       <c r="I10" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="24" t="s">
-        <v>46</v>
+      <c r="J10" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M10" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="P10" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R10" s="24" t="s">
         <v>46</v>
@@ -2041,8 +2045,8 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
+    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="39"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2068,23 +2072,23 @@
       <c r="I11" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="24" t="s">
-        <v>104</v>
+      <c r="J11" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L11" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M11" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N11" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="P11" s="23" t="s">
         <v>104</v>
@@ -2110,8 +2114,8 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="40"/>
+    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="39"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2121,11 +2125,15 @@
       <c r="D12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="8">
+        <v>4</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
       <c r="G12" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="H12" s="23" t="s">
         <v>46</v>
@@ -2133,14 +2141,14 @@
       <c r="I12" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="24" t="s">
-        <v>10</v>
+      <c r="J12" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="23" t="s">
-        <v>46</v>
+      <c r="L12" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M12" s="23" t="s">
         <v>46</v>
@@ -2152,10 +2160,10 @@
         <v>46</v>
       </c>
       <c r="P12" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="R12" s="24" t="s">
         <v>10</v>
@@ -2175,8 +2183,8 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="40"/>
+    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="39"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2198,14 +2206,14 @@
       <c r="I13" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J13" s="24" t="s">
-        <v>10</v>
+      <c r="J13" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="23" t="s">
-        <v>46</v>
+      <c r="L13" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M13" s="23" t="s">
         <v>46</v>
@@ -2240,8 +2248,8 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="40"/>
+    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="39"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2263,29 +2271,29 @@
       <c r="I14" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="24" t="s">
-        <v>46</v>
+      <c r="J14" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L14" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M14" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="P14" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R14" s="24" t="s">
         <v>104</v>
@@ -2305,8 +2313,8 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="41"/>
+    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="40"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2328,29 +2336,29 @@
       <c r="I15" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J15" s="24" t="s">
+      <c r="J15" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L15" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L15" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M15" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N15" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="P15" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="Q15" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="R15" s="24" t="s">
         <v>46</v>
@@ -2370,8 +2378,8 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="61" t="s">
+    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2399,13 +2407,13 @@
       <c r="I16" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="23" t="s">
+      <c r="L16" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M16" s="23" t="s">
@@ -2441,8 +2449,8 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="39"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2468,13 +2476,13 @@
       <c r="I17" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="23" t="s">
+      <c r="L17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -2510,8 +2518,8 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="39"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2533,14 +2541,14 @@
       <c r="I18" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J18" s="24" t="s">
-        <v>10</v>
+      <c r="J18" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="23" t="s">
-        <v>104</v>
+      <c r="L18" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M18" s="23" t="s">
         <v>46</v>
@@ -2575,8 +2583,8 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
+    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="39"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2598,13 +2606,13 @@
       <c r="I19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="23" t="s">
+      <c r="L19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M19" s="23" t="s">
@@ -2640,8 +2648,8 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="40"/>
+    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="39"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2663,23 +2671,23 @@
       <c r="I20" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L20" s="23" t="s">
+      <c r="L20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N20" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="P20" s="23" t="s">
         <v>104</v>
@@ -2705,8 +2713,8 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="41"/>
+    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="40"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2728,13 +2736,13 @@
       <c r="I21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="23" t="s">
+      <c r="L21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M21" s="23" t="s">
@@ -2770,8 +2778,8 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="58" t="s">
+    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="43" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2799,29 +2807,29 @@
       <c r="I22" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J22" s="24" t="s">
-        <v>46</v>
+      <c r="J22" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L22" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M22" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N22" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="P22" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="Q22" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R22" s="24" t="s">
         <v>46</v>
@@ -2841,8 +2849,8 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
+    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="39"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2868,29 +2876,29 @@
       <c r="I23" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J23" s="24" t="s">
+      <c r="J23" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L23" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L23" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N23" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="O23" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="P23" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="Q23" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R23" s="24" t="s">
         <v>104</v>
@@ -2910,8 +2918,8 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
+    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="39"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2933,14 +2941,14 @@
       <c r="I24" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J24" s="24" t="s">
-        <v>10</v>
+      <c r="J24" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L24" s="23" t="s">
-        <v>46</v>
+      <c r="L24" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M24" s="23" t="s">
         <v>46</v>
@@ -2975,8 +2983,8 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
+    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="39"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2998,23 +3006,23 @@
       <c r="I25" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J25" s="24" t="s">
-        <v>104</v>
+      <c r="J25" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="23" t="s">
-        <v>10</v>
+      <c r="L25" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M25" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N25" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="O25" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="P25" s="23" t="s">
         <v>10</v>
@@ -3040,8 +3048,8 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
+    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="39"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3063,14 +3071,14 @@
       <c r="I26" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="24" t="s">
-        <v>104</v>
+      <c r="J26" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="23" t="s">
-        <v>10</v>
+      <c r="L26" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M26" s="23" t="s">
         <v>104</v>
@@ -3082,10 +3090,10 @@
         <v>104</v>
       </c>
       <c r="P26" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R26" s="24" t="s">
         <v>10</v>
@@ -3105,8 +3113,8 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="41"/>
+    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="40"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3128,23 +3136,23 @@
       <c r="I27" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J27" s="24" t="s">
-        <v>104</v>
+      <c r="J27" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K27" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L27" s="23" t="s">
-        <v>46</v>
+      <c r="L27" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M27" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N27" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="O27" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="P27" s="23" t="s">
         <v>46</v>
@@ -3170,8 +3178,8 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="59" t="s">
+    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3199,13 +3207,13 @@
       <c r="I28" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="24" t="s">
+      <c r="J28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="23" t="s">
+      <c r="L28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M28" s="23" t="s">
@@ -3241,8 +3249,8 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
+    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="39"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3268,14 +3276,14 @@
       <c r="I29" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J29" s="24" t="s">
-        <v>10</v>
+      <c r="J29" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L29" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L29" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M29" s="23" t="s">
         <v>10</v>
@@ -3310,8 +3318,8 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
+    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="39"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3333,13 +3341,13 @@
       <c r="I30" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J30" s="24" t="s">
+      <c r="J30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="23" t="s">
+      <c r="L30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M30" s="23" t="s">
@@ -3375,8 +3383,8 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
+    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="39"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3398,13 +3406,13 @@
       <c r="I31" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J31" s="24" t="s">
-        <v>46</v>
+      <c r="J31" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M31" s="23" t="s">
@@ -3440,8 +3448,8 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
+    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="39"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3463,23 +3471,23 @@
       <c r="I32" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="24" t="s">
+      <c r="J32" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L32" s="23" t="s">
+      <c r="L32" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M32" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N32" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="O32" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="P32" s="23" t="s">
         <v>104</v>
@@ -3505,8 +3513,8 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="41"/>
+    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="40"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3528,23 +3536,23 @@
       <c r="I33" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="24" t="s">
+      <c r="J33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L33" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L33" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N33" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="O33" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="P33" s="23" t="s">
         <v>104</v>
@@ -3570,8 +3578,8 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="57" t="s">
+    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="42" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3599,29 +3607,29 @@
       <c r="I34" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J34" s="24" t="s">
-        <v>10</v>
+      <c r="J34" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K34" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L34" s="24" t="s">
         <v>10</v>
       </c>
       <c r="M34" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N34" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="O34" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="P34" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="Q34" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R34" s="24" t="s">
         <v>46</v>
@@ -3641,8 +3649,8 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="40"/>
+    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="39"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3668,13 +3676,13 @@
       <c r="I35" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J35" s="24" t="s">
+      <c r="J35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L35" s="23" t="s">
+      <c r="L35" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M35" s="23" t="s">
@@ -3687,10 +3695,10 @@
         <v>46</v>
       </c>
       <c r="P35" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="Q35" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R35" s="24" t="s">
         <v>46</v>
@@ -3710,8 +3718,8 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="40"/>
+    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="39"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3733,23 +3741,23 @@
       <c r="I36" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J36" s="24" t="s">
-        <v>10</v>
+      <c r="J36" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L36" s="23" t="s">
-        <v>46</v>
+      <c r="L36" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M36" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N36" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="O36" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="P36" s="23" t="s">
         <v>46</v>
@@ -3775,8 +3783,8 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="40"/>
+    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="39"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3798,13 +3806,13 @@
       <c r="I37" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J37" s="24" t="s">
+      <c r="J37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L37" s="23" t="s">
+      <c r="L37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M37" s="23" t="s">
@@ -3817,10 +3825,10 @@
         <v>104</v>
       </c>
       <c r="P37" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Q37" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R37" s="24" t="s">
         <v>104</v>
@@ -3840,8 +3848,8 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="40"/>
+    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="39"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3863,29 +3871,29 @@
       <c r="I38" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="24" t="s">
+      <c r="J38" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L38" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L38" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M38" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N38" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="O38" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="P38" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="Q38" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R38" s="24" t="s">
         <v>10</v>
@@ -3905,8 +3913,8 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="41"/>
+    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="40"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3928,29 +3936,29 @@
       <c r="I39" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J39" s="24" t="s">
-        <v>104</v>
+      <c r="J39" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K39" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L39" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M39" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N39" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="O39" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="P39" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Q39" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R39" s="24" t="s">
         <v>104</v>
@@ -3970,8 +3978,8 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="56" t="s">
+    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="41" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3999,14 +4007,14 @@
       <c r="I40" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J40" s="24" t="s">
+      <c r="J40" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L40" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L40" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M40" s="23" t="s">
         <v>46</v>
@@ -4041,8 +4049,8 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="40"/>
+    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="39"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4068,14 +4076,14 @@
       <c r="I41" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J41" s="24" t="s">
-        <v>10</v>
+      <c r="J41" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L41" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M41" s="23" t="s">
         <v>10</v>
@@ -4110,8 +4118,8 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="40"/>
+    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="39"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4133,13 +4141,13 @@
       <c r="I42" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J42" s="24" t="s">
-        <v>46</v>
+      <c r="J42" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M42" s="23" t="s">
@@ -4175,8 +4183,8 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="40"/>
+    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="39"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4198,23 +4206,23 @@
       <c r="I43" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J43" s="24" t="s">
-        <v>46</v>
+      <c r="J43" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L43" s="23" t="s">
-        <v>104</v>
+      <c r="L43" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="M43" s="23" t="s">
         <v>46</v>
       </c>
       <c r="N43" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="O43" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="P43" s="23" t="s">
         <v>104</v>
@@ -4240,8 +4248,8 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="40"/>
+    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="39"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4263,23 +4271,23 @@
       <c r="I44" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J44" s="24" t="s">
+      <c r="J44" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L44" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L44" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="M44" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N44" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="O44" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="P44" s="23" t="s">
         <v>10</v>
@@ -4305,8 +4313,8 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="41"/>
+    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="40"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4328,13 +4336,13 @@
       <c r="I45" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J45" s="24" t="s">
+      <c r="J45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L45" s="23" t="s">
+      <c r="L45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M45" s="23" t="s">
@@ -4370,8 +4378,8 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="39" t="s">
+    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="58" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4399,13 +4407,13 @@
       <c r="I46" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J46" s="24" t="s">
+      <c r="J46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="23" t="s">
+      <c r="L46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M46" s="23" t="s">
@@ -4441,8 +4449,8 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="40"/>
+    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="39"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4468,13 +4476,13 @@
       <c r="I47" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J47" s="24" t="s">
+      <c r="J47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L47" s="23" t="s">
+      <c r="L47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="M47" s="23" t="s">
@@ -4510,8 +4518,8 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="40"/>
+    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="39"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4533,13 +4541,13 @@
       <c r="I48" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J48" s="24" t="s">
+      <c r="J48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L48" s="23" t="s">
+      <c r="L48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M48" s="23" t="s">
@@ -4575,8 +4583,8 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="40"/>
+    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="39"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4598,13 +4606,13 @@
       <c r="I49" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J49" s="24" t="s">
-        <v>46</v>
+      <c r="J49" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="M49" s="23" t="s">
@@ -4640,8 +4648,8 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="40"/>
+    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="39"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4663,23 +4671,23 @@
       <c r="I50" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J50" s="24" t="s">
-        <v>10</v>
+      <c r="J50" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K50" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L50" s="24" t="s">
         <v>10</v>
       </c>
       <c r="M50" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N50" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="O50" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="P50" s="23" t="s">
         <v>10</v>
@@ -4705,8 +4713,8 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="41"/>
+    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="40"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4728,23 +4736,23 @@
       <c r="I51" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J51" s="24" t="s">
-        <v>10</v>
+      <c r="J51" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L51" s="23" t="s">
-        <v>104</v>
+      <c r="L51" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="M51" s="23" t="s">
         <v>104</v>
       </c>
       <c r="N51" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="O51" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="P51" s="23" t="s">
         <v>104</v>
@@ -4770,8 +4778,8 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="46" t="s">
+    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="61" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4799,23 +4807,23 @@
       <c r="I52" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J52" s="26" t="s">
-        <v>46</v>
+      <c r="J52" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L52" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M52" s="25" t="s">
         <v>46</v>
       </c>
       <c r="N52" s="26" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="O52" s="26" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="P52" s="25" t="s">
         <v>46</v>
@@ -4841,8 +4849,8 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="47"/>
+    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="62"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4868,14 +4876,14 @@
       <c r="I53" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J53" s="26" t="s">
-        <v>46</v>
+      <c r="J53" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L53" s="25" t="s">
-        <v>104</v>
+      <c r="L53" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="M53" s="25" t="s">
         <v>104</v>
@@ -4910,8 +4918,8 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="47"/>
+    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="62"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4933,13 +4941,13 @@
       <c r="I54" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J54" s="26" t="s">
+      <c r="J54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L54" s="25" t="s">
+      <c r="L54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M54" s="25" t="s">
@@ -4975,8 +4983,8 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="47"/>
+    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="62"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4998,29 +5006,29 @@
       <c r="I55" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J55" s="26" t="s">
-        <v>46</v>
+      <c r="J55" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L55" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M55" s="25" t="s">
         <v>46</v>
       </c>
       <c r="N55" s="26" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="O55" s="26" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="P55" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="Q55" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R55" s="26" t="s">
         <v>104</v>
@@ -5041,8 +5049,8 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="47"/>
+    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="62"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5064,23 +5072,23 @@
       <c r="I56" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J56" s="26" t="s">
-        <v>104</v>
+      <c r="J56" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L56" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M56" s="25" t="s">
         <v>104</v>
       </c>
       <c r="N56" s="26" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="O56" s="26" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="P56" s="25" t="s">
         <v>104</v>
@@ -5106,8 +5114,8 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="48"/>
+    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="63"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5129,29 +5137,29 @@
       <c r="I57" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J57" s="26" t="s">
-        <v>104</v>
+      <c r="J57" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K57" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L57" s="25" t="s">
-        <v>46</v>
+      <c r="L57" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M57" s="25" t="s">
         <v>10</v>
       </c>
       <c r="N57" s="26" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="O57" s="26" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="P57" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="Q57" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R57" s="26" t="s">
         <v>46</v>
@@ -5171,8 +5179,8 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="49" t="s">
+    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="64" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5200,13 +5208,13 @@
       <c r="I58" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J58" s="26" t="s">
-        <v>46</v>
+      <c r="J58" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K58" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M58" s="25" t="s">
@@ -5242,8 +5250,8 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="50"/>
+    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="65"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5269,13 +5277,13 @@
       <c r="I59" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J59" s="26" t="s">
+      <c r="J59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L59" s="25" t="s">
+      <c r="L59" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M59" s="25" t="s">
@@ -5311,8 +5319,8 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="50"/>
+    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="65"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5334,14 +5342,14 @@
       <c r="I60" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J60" s="26" t="s">
-        <v>10</v>
+      <c r="J60" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L60" s="25" t="s">
-        <v>46</v>
+      <c r="L60" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="M60" s="25" t="s">
         <v>46</v>
@@ -5376,8 +5384,8 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="50"/>
+    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="65"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5399,23 +5407,23 @@
       <c r="I61" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J61" s="26" t="s">
-        <v>46</v>
+      <c r="J61" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L61" s="25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L61" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="M61" s="25" t="s">
         <v>10</v>
       </c>
       <c r="N61" s="26" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="O61" s="26" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="P61" s="25" t="s">
         <v>104</v>
@@ -5441,8 +5449,8 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="50"/>
+    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="65"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5464,13 +5472,13 @@
       <c r="I62" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J62" s="26" t="s">
-        <v>104</v>
+      <c r="J62" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L62" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L62" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M62" s="25" t="s">
@@ -5483,10 +5491,10 @@
         <v>104</v>
       </c>
       <c r="P62" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Q62" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R62" s="26" t="s">
         <v>10</v>
@@ -5506,8 +5514,8 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="51"/>
+    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="66"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5529,13 +5537,13 @@
       <c r="I63" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J63" s="26" t="s">
+      <c r="J63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L63" s="25" t="s">
+      <c r="L63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M63" s="25" t="s">
@@ -5571,8 +5579,8 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33" t="s">
+    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="52" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5600,13 +5608,13 @@
       <c r="I64" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J64" s="26" t="s">
+      <c r="J64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L64" s="25" t="s">
+      <c r="L64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M64" s="25" t="s">
@@ -5642,8 +5650,8 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="34"/>
+    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="53"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5669,13 +5677,13 @@
       <c r="I65" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J65" s="26" t="s">
+      <c r="J65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L65" s="25" t="s">
+      <c r="L65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M65" s="25" t="s">
@@ -5711,8 +5719,8 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="34"/>
+    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="53"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5734,13 +5742,13 @@
       <c r="I66" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J66" s="26" t="s">
+      <c r="J66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L66" s="25" t="s">
+      <c r="L66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M66" s="25" t="s">
@@ -5776,8 +5784,8 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="34"/>
+    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="53"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5799,13 +5807,13 @@
       <c r="I67" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J67" s="26" t="s">
+      <c r="J67" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L67" s="25" t="s">
+      <c r="L67" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M67" s="25" t="s">
@@ -5841,8 +5849,8 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="34"/>
+    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="53"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5864,14 +5872,14 @@
       <c r="I68" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J68" s="26" t="s">
+      <c r="J68" s="25" t="s">
         <v>10</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L68" s="25" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L68" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="M68" s="25" t="s">
         <v>104</v>
@@ -5883,10 +5891,10 @@
         <v>104</v>
       </c>
       <c r="P68" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Q68" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R68" s="26" t="s">
         <v>46</v>
@@ -5906,8 +5914,8 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="35"/>
+    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="54"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5929,14 +5937,14 @@
       <c r="I69" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J69" s="26" t="s">
+      <c r="J69" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L69" s="25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L69" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M69" s="25" t="s">
         <v>10</v>
@@ -5971,8 +5979,8 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="36" t="s">
+    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="55" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -6000,29 +6008,29 @@
       <c r="I70" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J70" s="26" t="s">
+      <c r="J70" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L70" s="25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L70" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="M70" s="25" t="s">
         <v>46</v>
       </c>
       <c r="N70" s="26" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="O70" s="26" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="P70" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="Q70" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R70" s="26" t="s">
         <v>104</v>
@@ -6042,8 +6050,8 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
+    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="56"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6069,14 +6077,14 @@
       <c r="I71" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J71" s="26" t="s">
-        <v>104</v>
+      <c r="J71" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K71" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L71" s="25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L71" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="M71" s="25" t="s">
         <v>10</v>
@@ -6088,10 +6096,10 @@
         <v>104</v>
       </c>
       <c r="P71" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="Q71" s="25" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="R71" s="26" t="s">
         <v>10</v>
@@ -6111,8 +6119,8 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="56"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6134,13 +6142,13 @@
       <c r="I72" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J72" s="26" t="s">
-        <v>46</v>
+      <c r="J72" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="M72" s="25" t="s">
@@ -6176,8 +6184,8 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="56"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6199,14 +6207,14 @@
       <c r="I73" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J73" s="26" t="s">
-        <v>46</v>
+      <c r="J73" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L73" s="25" t="s">
-        <v>104</v>
+      <c r="L73" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="M73" s="25" t="s">
         <v>104</v>
@@ -6218,10 +6226,10 @@
         <v>104</v>
       </c>
       <c r="P73" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Q73" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R73" s="26" t="s">
         <v>10</v>
@@ -6241,8 +6249,8 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
+    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="56"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6264,23 +6272,23 @@
       <c r="I74" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J74" s="26" t="s">
-        <v>104</v>
+      <c r="J74" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="M74" s="25" t="s">
         <v>104</v>
       </c>
       <c r="N74" s="26" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="O74" s="26" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="P74" s="25" t="s">
         <v>104</v>
@@ -6306,8 +6314,8 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="38"/>
+    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="57"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6329,14 +6337,14 @@
       <c r="I75" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J75" s="26" t="s">
-        <v>10</v>
+      <c r="J75" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K75" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L75" s="25" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L75" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="M75" s="25" t="s">
         <v>46</v>
@@ -6348,10 +6356,10 @@
         <v>46</v>
       </c>
       <c r="P75" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="Q75" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R75" s="26" t="s">
         <v>46</v>
@@ -6371,18 +6379,18 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="42" t="s">
+      <c r="D76" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="43"/>
-      <c r="F76" s="44"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="35"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H76" s="25">
         <v>222</v>
@@ -6390,29 +6398,29 @@
       <c r="I76" s="26">
         <v>179</v>
       </c>
-      <c r="J76" s="26">
+      <c r="J76" s="25">
+        <v>186</v>
+      </c>
+      <c r="K76" s="25">
+        <v>172</v>
+      </c>
+      <c r="L76" s="26">
         <v>201</v>
-      </c>
-      <c r="K76" s="25">
-        <v>186</v>
-      </c>
-      <c r="L76" s="25">
-        <v>172</v>
       </c>
       <c r="M76" s="25">
         <v>190</v>
       </c>
       <c r="N76" s="26">
+        <v>162</v>
+      </c>
+      <c r="O76" s="26">
         <v>185</v>
       </c>
-      <c r="O76" s="26">
-        <v>162</v>
-      </c>
       <c r="P76" s="25">
+        <v>197</v>
+      </c>
+      <c r="Q76" s="25">
         <v>169</v>
-      </c>
-      <c r="Q76" s="25">
-        <v>197</v>
       </c>
       <c r="R76" s="26">
         <v>180</v>
@@ -6432,118 +6440,118 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="45" t="s">
+      <c r="D77" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="44"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="35"/>
       <c r="H77" s="28">
-        <f t="shared" ref="H77:R77" si="3">SUM(H78:H81)</f>
+        <f>SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
+        <f>SUM(I78:I81)</f>
+        <v>2</v>
+      </c>
+      <c r="J77" s="28">
+        <f>SUM(J78:J81)</f>
+        <v>0</v>
+      </c>
+      <c r="K77" s="28">
+        <f>SUM(K78:K81)</f>
+        <v>9</v>
+      </c>
+      <c r="L77" s="28">
+        <f>SUM(L78:L81)</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="28">
+        <f>SUM(M78:M81)</f>
+        <v>0</v>
+      </c>
+      <c r="N77" s="28">
+        <f>SUM(N78:N81)</f>
+        <v>19</v>
+      </c>
+      <c r="O77" s="28">
+        <f>SUM(O78:O81)</f>
+        <v>0</v>
+      </c>
+      <c r="P77" s="28">
+        <f>SUM(P78:P81)</f>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="28">
+        <f>SUM(Q78:Q81)</f>
+        <v>12</v>
+      </c>
+      <c r="R77" s="28">
+        <f>SUM(R78:R81)</f>
+        <v>1</v>
+      </c>
+      <c r="S77" s="28">
+        <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
+        <v>19</v>
+      </c>
+      <c r="T77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="28">
+        <v>19</v>
+      </c>
+      <c r="U77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="28">
+        <v>19</v>
+      </c>
+      <c r="V77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L77" s="28">
+        <v>19</v>
+      </c>
+      <c r="W77" s="28">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="M77" s="28">
+        <v>19</v>
+      </c>
+      <c r="X77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="28">
+        <v>19</v>
+      </c>
+      <c r="Y77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="28">
+        <v>19</v>
+      </c>
+      <c r="Z77" s="28">
         <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="P77" s="28">
+        <v>19</v>
+      </c>
+      <c r="AA77" s="28">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="Q77" s="28">
+        <v>19</v>
+      </c>
+      <c r="AB77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="28">
+        <v>19</v>
+      </c>
+      <c r="AC77" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S77" s="28">
-        <f t="shared" ref="S77:AF77" si="4">SUM(S78:S81)</f>
-        <v>26</v>
-      </c>
-      <c r="T77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="U77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="V77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="W77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="X77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="Y77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="Z77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="AA77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="AB77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="AC77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AD77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="AE77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="AF77" s="28">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6552,107 +6560,107 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="5">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6661,107 +6669,107 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="6">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6770,107 +6778,107 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="7">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="L80" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L80" s="3">
-        <f t="shared" si="7"/>
+      <c r="M80" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M80" s="3">
-        <f t="shared" si="7"/>
+      <c r="N80" s="3">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="O80" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N80" s="3">
-        <f t="shared" si="7"/>
+      <c r="P80" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O80" s="3">
-        <f t="shared" si="7"/>
+      <c r="Q80" s="3">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="P80" s="3">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="Q80" s="3">
-        <f t="shared" si="7"/>
+      <c r="R80" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R80" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
       <c r="S80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6879,107 +6887,107 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="8">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="J81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J81" s="3">
-        <f t="shared" si="8"/>
+      <c r="K81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K81" s="3">
-        <f t="shared" si="8"/>
+      <c r="L81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L81" s="3">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
       <c r="M81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S81" s="3">
-        <f t="shared" si="8"/>
+      <c r="T81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T81" s="3">
-        <f t="shared" si="8"/>
+      <c r="U81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U81" s="3">
-        <f t="shared" si="8"/>
+      <c r="V81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="V81" s="3">
-        <f t="shared" si="8"/>
+      <c r="W81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W81" s="3">
-        <f t="shared" si="8"/>
+      <c r="X81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="X81" s="3">
-        <f t="shared" si="8"/>
+      <c r="Y81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Y81" s="3">
-        <f t="shared" si="8"/>
+      <c r="Z81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Z81" s="3">
-        <f t="shared" si="8"/>
+      <c r="AA81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA81" s="3">
-        <f t="shared" si="8"/>
+      <c r="AB81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB81" s="3">
-        <f t="shared" si="8"/>
+      <c r="AC81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AC81" s="3">
-        <f t="shared" si="8"/>
+      <c r="AD81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD81" s="3">
-        <f t="shared" si="8"/>
+      <c r="AE81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AE81" s="3">
-        <f t="shared" si="8"/>
+      <c r="AF81" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF81" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7013,7 +7021,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7047,7 +7055,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7081,7 +7089,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7115,7 +7123,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7149,7 +7157,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7183,7 +7191,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7217,7 +7225,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7251,7 +7259,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7285,7 +7293,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7319,7 +7327,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7353,7 +7361,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7387,7 +7395,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7421,7 +7429,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7455,7 +7463,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7489,7 +7497,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7523,7 +7531,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7557,7 +7565,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7591,7 +7599,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7625,7 +7633,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7634,7 +7642,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7643,7 +7651,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7652,7 +7660,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7661,7 +7669,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7670,7 +7678,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7679,7 +7687,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7688,7 +7696,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7697,7 +7705,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7706,7 +7714,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7715,7 +7723,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7724,7 +7732,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7733,7 +7741,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7742,7 +7750,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7751,7 +7759,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7760,7 +7768,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7769,7 +7777,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7778,7 +7786,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7787,7 +7795,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7796,7 +7804,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7805,7 +7813,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7814,7 +7822,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7823,7 +7831,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7832,7 +7840,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7847,6 +7855,13 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7858,13 +7873,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -7879,14 +7887,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="15" width="11.44140625" customWidth="1"/>
+    <col min="1" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="15" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>16</v>
@@ -7933,7 +7941,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -7978,7 +7986,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -8023,7 +8031,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -8068,7 +8076,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -8113,7 +8121,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -8158,7 +8166,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -8203,7 +8211,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -8248,7 +8256,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -8293,7 +8301,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -8338,7 +8346,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -8383,7 +8391,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>16</v>
@@ -8428,7 +8436,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>16</v>
@@ -8473,7 +8481,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
@@ -8518,7 +8526,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -8563,7 +8571,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
@@ -8608,7 +8616,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>16</v>
@@ -8653,7 +8661,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
@@ -8698,7 +8706,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>16</v>
@@ -8743,7 +8751,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>16</v>
@@ -8788,7 +8796,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>16</v>
@@ -8833,7 +8841,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -8878,7 +8886,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -8923,7 +8931,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>16</v>
@@ -8968,7 +8976,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>16</v>
@@ -9013,7 +9021,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -9058,7 +9066,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>16</v>
@@ -9103,7 +9111,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>16</v>
@@ -9148,7 +9156,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>16</v>
@@ -9193,7 +9201,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>16</v>
@@ -9238,7 +9246,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>16</v>
@@ -9283,7 +9291,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>16</v>
@@ -9328,7 +9336,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>16</v>
@@ -9373,7 +9381,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>16</v>
@@ -9418,7 +9426,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>16</v>
@@ -9463,7 +9471,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>16</v>
@@ -9508,7 +9516,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>16</v>
@@ -9553,7 +9561,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>16</v>
@@ -9598,7 +9606,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>16</v>
@@ -9643,7 +9651,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>16</v>
@@ -9688,7 +9696,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>16</v>
@@ -9733,7 +9741,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>16</v>
@@ -9778,7 +9786,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>16</v>
@@ -9823,7 +9831,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>16</v>
@@ -9868,7 +9876,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>16</v>
@@ -9913,7 +9921,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>16</v>
@@ -9958,7 +9966,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>16</v>
@@ -10003,7 +10011,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>16</v>
@@ -10048,7 +10056,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>16</v>
@@ -10093,7 +10101,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>16</v>
@@ -10138,7 +10146,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>16</v>
@@ -10183,7 +10191,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>16</v>
@@ -10228,7 +10236,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>16</v>
@@ -10273,7 +10281,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>16</v>
@@ -10318,7 +10326,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>16</v>
@@ -10363,7 +10371,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>16</v>
@@ -10408,7 +10416,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>16</v>
@@ -10453,7 +10461,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>16</v>
@@ -10498,7 +10506,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>16</v>
@@ -10543,7 +10551,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>16</v>
@@ -10588,7 +10596,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>16</v>
@@ -10633,7 +10641,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>16</v>
@@ -10678,7 +10686,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>16</v>
@@ -10723,7 +10731,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>16</v>
@@ -10768,7 +10776,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>16</v>
@@ -10813,7 +10821,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>16</v>
@@ -10858,7 +10866,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>16</v>
@@ -10903,7 +10911,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>16</v>
@@ -10948,7 +10956,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>16</v>
@@ -10993,7 +11001,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>16</v>
@@ -11038,7 +11046,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>16</v>
@@ -11083,7 +11091,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>16</v>
@@ -11128,7 +11136,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>16</v>
@@ -11173,7 +11181,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>16</v>
@@ -11218,7 +11226,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>16</v>
@@ -11263,7 +11271,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>16</v>
@@ -11308,7 +11316,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>16</v>
@@ -11353,7 +11361,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>16</v>
@@ -11398,7 +11406,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>16</v>
@@ -11443,7 +11451,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>16</v>
@@ -11488,7 +11496,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>16</v>
@@ -11533,7 +11541,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>16</v>
@@ -11578,7 +11586,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>16</v>
@@ -11623,7 +11631,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>16</v>
@@ -11668,7 +11676,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>16</v>
@@ -11713,7 +11721,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>16</v>
@@ -11758,7 +11766,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>16</v>
@@ -11803,7 +11811,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>16</v>
@@ -11848,7 +11856,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>16</v>
@@ -11893,7 +11901,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>16</v>
@@ -11938,7 +11946,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>16</v>
@@ -11983,7 +11991,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>16</v>
@@ -12028,7 +12036,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>16</v>
@@ -12073,7 +12081,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>16</v>
@@ -12118,7 +12126,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>16</v>
@@ -12163,7 +12171,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>16</v>
@@ -12208,7 +12216,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>16</v>
@@ -12253,7 +12261,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>16</v>
@@ -12298,7 +12306,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>16</v>
@@ -12343,7 +12351,7 @@
         <v>SI(G28-H28=-100;0;</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12369,9 +12377,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="11" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12382,26 +12390,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" customWidth="1"/>
-    <col min="2" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="2" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="11" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -12409,61 +12417,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -12471,7 +12479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -12479,19 +12487,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -12499,19 +12507,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -12519,19 +12527,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -12539,13 +12547,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -12553,229 +12561,229 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="1"/>
     </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="1"/>
     </row>
-    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="1"/>
     </row>
-    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="1"/>
     </row>
-    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="1"/>
     </row>
-    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="1"/>
     </row>
-    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="1"/>
     </row>
-    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="1"/>
     </row>
-    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="1"/>
     </row>
-    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="1"/>
     </row>
   </sheetData>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A93EAD76-B957-4A92-9CE4-2B338ED12165}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F234A566-2F22-46DE-BB66-542666453219}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
@@ -873,11 +873,58 @@
     <xf numFmtId="0" fontId="6" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -885,8 +932,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -919,51 +964,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1288,31 +1288,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.7109375" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="5.7109375" customWidth="1"/>
-    <col min="19" max="32" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.6640625" customWidth="1"/>
+    <col min="19" max="32" width="5.6640625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1389,47 +1389,47 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="143.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49" t="s">
+      <c r="B2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="29" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="30" t="s">
-        <v>106</v>
-      </c>
       <c r="J2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="K2" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="O2" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>108</v>
-      </c>
-      <c r="M2" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="N2" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="O2" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="P2" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q2" s="29" t="s">
-        <v>112</v>
       </c>
       <c r="R2" s="30" t="s">
         <v>105</v>
@@ -1449,7 +1449,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1462,116 +1462,116 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="37"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$75=H4:H75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="14" cm="1">
         <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$75=I4:I75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J3" s="14" cm="1">
         <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$75=J4:J75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K3" s="14" cm="1">
         <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$75=K4:K75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L3" s="14" cm="1">
         <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$75=L4:L75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M3" s="14" cm="1">
         <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$75=M4:M75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N3" s="14" cm="1">
         <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$75=N4:N75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O3" s="14" cm="1">
         <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$75=O4:O75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="P3" s="14" cm="1">
         <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$75=P4:P75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q3" s="14" cm="1">
         <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$75=Q4:Q75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R3" s="14" cm="1">
         <f t="array" ref="R3">SUMPRODUCT(($G$4:$G$75=R4:R75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="T3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="U3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="W3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="X3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Y3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Z3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AA3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AB3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AC3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AD3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AE3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AF3" s="14">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="55" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1593,10 +1593,10 @@
         <f>IF(OR(E4="",F4=""),"",IF(E4&gt;F4,"L",IF(E4&lt;F4,"V","E")))</f>
         <v>L</v>
       </c>
-      <c r="H4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="24" t="s">
+      <c r="H4" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="23" t="s">
@@ -1605,22 +1605,22 @@
       <c r="K4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="23" t="s">
+      <c r="L4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R4" s="24" t="s">
@@ -1641,8 +1641,8 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="39"/>
+    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="40"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1662,10 +1662,10 @@
         <f t="shared" ref="G5:G68" si="1">IF(OR(E5="",F5=""),"",IF(E5&gt;F5,"L",IF(E5&lt;F5,"V","E")))</f>
         <v>L</v>
       </c>
-      <c r="H5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="24" t="s">
+      <c r="H5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J5" s="23" t="s">
@@ -1674,23 +1674,23 @@
       <c r="K5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="23" t="s">
-        <v>10</v>
+      <c r="L5" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R5" s="24" t="s">
         <v>10</v>
@@ -1710,8 +1710,8 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="39"/>
+    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="40"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1731,11 +1731,11 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>46</v>
+      <c r="H6" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J6" s="23" t="s">
         <v>46</v>
@@ -1743,23 +1743,23 @@
       <c r="K6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O6" s="24" t="s">
+      <c r="L6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="P6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>46</v>
+      <c r="Q6" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R6" s="24" t="s">
         <v>46</v>
@@ -1779,8 +1779,8 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
+    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="40"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1790,41 +1790,45 @@
       <c r="D7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>10</v>
+        <v>L</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q7" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R7" s="24" t="s">
         <v>104</v>
@@ -1844,8 +1848,8 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
+    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="40"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1861,34 +1865,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I8" s="24" t="s">
+      <c r="H8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N8" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q8" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R8" s="24" t="s">
@@ -1909,8 +1913,8 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="40"/>
+    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="41"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1926,35 +1930,35 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>46</v>
+      <c r="H9" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q9" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R9" s="24" t="s">
         <v>104</v>
@@ -1974,8 +1978,8 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="60" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1997,35 +2001,35 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="24" t="s">
+      <c r="H10" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>10</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q10" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R10" s="24" t="s">
         <v>46</v>
@@ -2045,8 +2049,8 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="39"/>
+    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="40"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2066,34 +2070,34 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>10</v>
+      <c r="H11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N11" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P11" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R11" s="24" t="s">
@@ -2114,8 +2118,8 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="39"/>
+    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="40"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2135,10 +2139,10 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="24" t="s">
+      <c r="H12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="23" t="s">
@@ -2147,23 +2151,23 @@
       <c r="K12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q12" s="23" t="s">
-        <v>104</v>
+      <c r="L12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O12" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R12" s="24" t="s">
         <v>10</v>
@@ -2183,8 +2187,8 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
+    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="40"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2194,16 +2198,20 @@
       <c r="D13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="8">
+        <v>6</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
       <c r="G13" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="24" t="s">
+        <v>L</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J13" s="23" t="s">
@@ -2212,23 +2220,23 @@
       <c r="K13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="23" t="s">
-        <v>46</v>
+      <c r="L13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R13" s="24" t="s">
         <v>46</v>
@@ -2248,8 +2256,8 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
+    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="40"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2265,35 +2273,35 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="24" t="s">
+      <c r="H14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N14" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q14" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q14" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R14" s="24" t="s">
         <v>104</v>
@@ -2313,8 +2321,8 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
+    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="41"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2330,34 +2338,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>46</v>
+      <c r="H15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O15" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P15" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q15" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P15" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R15" s="24" t="s">
@@ -2378,8 +2386,8 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="61" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2401,11 +2409,11 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H16" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>46</v>
+      <c r="H16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J16" s="23" t="s">
         <v>46</v>
@@ -2413,22 +2421,22 @@
       <c r="K16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q16" s="23" t="s">
+      <c r="L16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q16" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R16" s="24" t="s">
@@ -2449,8 +2457,8 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="39"/>
+    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="40"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2470,10 +2478,10 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="24" t="s">
+      <c r="H17" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J17" s="23" t="s">
@@ -2482,22 +2490,22 @@
       <c r="K17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q17" s="23" t="s">
+      <c r="L17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P17" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R17" s="24" t="s">
@@ -2518,8 +2526,8 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="39"/>
+    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="40"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2529,16 +2537,20 @@
       <c r="D18" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>1</v>
+      </c>
       <c r="G18" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="24" t="s">
+        <v>V</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J18" s="23" t="s">
@@ -2547,23 +2559,23 @@
       <c r="K18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M18" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q18" s="23" t="s">
-        <v>104</v>
+      <c r="L18" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M18" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q18" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R18" s="24" t="s">
         <v>104</v>
@@ -2583,8 +2595,8 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="39"/>
+    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="40"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2594,16 +2606,20 @@
       <c r="D19" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="E19" s="9">
+        <v>3</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
       <c r="G19" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="24" t="s">
+        <v>L</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J19" s="23" t="s">
@@ -2612,22 +2628,22 @@
       <c r="K19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q19" s="23" t="s">
+      <c r="L19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R19" s="24" t="s">
@@ -2648,8 +2664,8 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
+    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="40"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2665,10 +2681,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I20" s="24" t="s">
+      <c r="H20" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J20" s="23" t="s">
@@ -2677,22 +2693,22 @@
       <c r="K20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O20" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q20" s="23" t="s">
+      <c r="L20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R20" s="24" t="s">
@@ -2713,8 +2729,8 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="40"/>
+    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="41"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2730,10 +2746,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" s="24" t="s">
+      <c r="H21" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J21" s="23" t="s">
@@ -2742,22 +2758,22 @@
       <c r="K21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M21" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q21" s="23" t="s">
+      <c r="L21" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M21" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R21" s="24" t="s">
@@ -2778,8 +2794,8 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
+    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="58" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2801,35 +2817,35 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H22" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>46</v>
+      <c r="H22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N22" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q22" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="L22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M22" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O22" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q22" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R22" s="24" t="s">
         <v>46</v>
@@ -2849,8 +2865,8 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="39"/>
+    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="40"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2870,35 +2886,35 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H23" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>104</v>
+      <c r="H23" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J23" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M23" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P23" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q23" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="L23" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M23" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P23" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q23" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R23" s="24" t="s">
         <v>104</v>
@@ -2918,8 +2934,8 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="39"/>
+    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="40"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2929,17 +2945,21 @@
       <c r="D24" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
+      <c r="E24" s="10">
+        <v>2</v>
+      </c>
+      <c r="F24" s="10">
+        <v>0</v>
+      </c>
       <c r="G24" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>46</v>
+        <v>L</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J24" s="23" t="s">
         <v>46</v>
@@ -2947,23 +2967,23 @@
       <c r="K24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q24" s="23" t="s">
-        <v>46</v>
+      <c r="L24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M24" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q24" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R24" s="24" t="s">
         <v>10</v>
@@ -2983,8 +3003,8 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
+    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="40"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2994,17 +3014,21 @@
       <c r="D25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
+      <c r="E25" s="10">
+        <v>0</v>
+      </c>
+      <c r="F25" s="10">
+        <v>1</v>
+      </c>
       <c r="G25" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>10</v>
+        <v>V</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J25" s="23" t="s">
         <v>10</v>
@@ -3012,23 +3036,23 @@
       <c r="K25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O25" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q25" s="23" t="s">
-        <v>10</v>
+      <c r="L25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M25" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P25" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q25" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R25" s="24" t="s">
         <v>46</v>
@@ -3048,8 +3072,8 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="39"/>
+    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="40"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3065,10 +3089,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26" s="24" t="s">
+      <c r="H26" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="23" t="s">
         <v>10</v>
       </c>
       <c r="J26" s="23" t="s">
@@ -3077,23 +3101,23 @@
       <c r="K26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M26" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q26" s="23" t="s">
-        <v>46</v>
+      <c r="L26" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M26" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N26" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O26" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P26" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q26" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R26" s="24" t="s">
         <v>10</v>
@@ -3113,8 +3137,8 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="40"/>
+    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="41"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3130,10 +3154,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H27" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I27" s="24" t="s">
+      <c r="H27" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="23" t="s">
         <v>10</v>
       </c>
       <c r="J27" s="23" t="s">
@@ -3142,23 +3166,23 @@
       <c r="K27" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M27" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N27" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q27" s="23" t="s">
-        <v>46</v>
+      <c r="L27" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M27" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N27" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O27" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P27" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q27" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R27" s="24" t="s">
         <v>104</v>
@@ -3178,8 +3202,8 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="44" t="s">
+    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="59" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3201,10 +3225,10 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" s="24" t="s">
+      <c r="H28" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J28" s="23" t="s">
@@ -3213,22 +3237,22 @@
       <c r="K28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q28" s="23" t="s">
+      <c r="L28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M28" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P28" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R28" s="24" t="s">
@@ -3249,8 +3273,8 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="39"/>
+    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="40"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3270,34 +3294,34 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="24" t="s">
+      <c r="H29" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="23" t="s">
         <v>10</v>
       </c>
       <c r="J29" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q29" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M29" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q29" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R29" s="24" t="s">
@@ -3318,8 +3342,8 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="39"/>
+    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="40"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3329,16 +3353,20 @@
       <c r="D30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+      <c r="E30" s="11">
+        <v>2</v>
+      </c>
+      <c r="F30" s="11">
+        <v>1</v>
+      </c>
       <c r="G30" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I30" s="24" t="s">
+        <v>L</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J30" s="23" t="s">
@@ -3347,22 +3375,22 @@
       <c r="K30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q30" s="23" t="s">
+      <c r="L30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M30" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P30" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R30" s="24" t="s">
@@ -3383,8 +3411,8 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
+    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="40"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3394,40 +3422,44 @@
       <c r="D31" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="E31" s="11">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11">
+        <v>0</v>
+      </c>
       <c r="G31" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>10</v>
+        <v>E</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J31" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M31" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q31" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L31" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M31" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P31" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q31" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R31" s="24" t="s">
@@ -3448,8 +3480,8 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="39"/>
+    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="40"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3465,11 +3497,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" s="24" t="s">
-        <v>10</v>
+      <c r="H32" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J32" s="23" t="s">
         <v>104</v>
@@ -3477,22 +3509,22 @@
       <c r="K32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L32" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M32" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O32" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q32" s="23" t="s">
+      <c r="L32" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M32" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P32" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q32" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R32" s="24" t="s">
@@ -3513,8 +3545,8 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="40"/>
+    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="41"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3530,34 +3562,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I33" s="24" t="s">
+      <c r="H33" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J33" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L33" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O33" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P33" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q33" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R33" s="24" t="s">
@@ -3578,8 +3610,8 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="42" t="s">
+    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="57" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3601,34 +3633,34 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" s="24" t="s">
+      <c r="H34" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" s="23" t="s">
         <v>10</v>
       </c>
       <c r="J34" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L34" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M34" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N34" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O34" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P34" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q34" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L34" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M34" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N34" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P34" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q34" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R34" s="24" t="s">
@@ -3649,8 +3681,8 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="39"/>
+    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="40"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3661,7 +3693,7 @@
         <v>98</v>
       </c>
       <c r="E35" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" s="12">
         <v>1</v>
@@ -3670,10 +3702,10 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="24" t="s">
+      <c r="H35" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J35" s="23" t="s">
@@ -3682,23 +3714,23 @@
       <c r="K35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q35" s="23" t="s">
-        <v>10</v>
+      <c r="L35" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M35" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N35" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O35" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q35" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R35" s="24" t="s">
         <v>46</v>
@@ -3718,8 +3750,8 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="39"/>
+    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="40"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3729,16 +3761,20 @@
       <c r="D36" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
+      <c r="E36" s="12">
+        <v>5</v>
+      </c>
+      <c r="F36" s="12">
+        <v>1</v>
+      </c>
       <c r="G36" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I36" s="24" t="s">
+        <v>L</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J36" s="23" t="s">
@@ -3747,23 +3783,23 @@
       <c r="K36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L36" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O36" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q36" s="23" t="s">
-        <v>46</v>
+      <c r="L36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M36" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P36" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q36" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R36" s="24" t="s">
         <v>46</v>
@@ -3783,8 +3819,8 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="39"/>
+    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="40"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3800,10 +3836,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I37" s="24" t="s">
+      <c r="H37" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J37" s="23" t="s">
@@ -3812,23 +3848,23 @@
       <c r="K37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q37" s="23" t="s">
-        <v>10</v>
+      <c r="L37" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M37" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N37" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O37" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P37" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q37" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R37" s="24" t="s">
         <v>104</v>
@@ -3848,8 +3884,8 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="39"/>
+    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="40"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3865,35 +3901,35 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" s="24" t="s">
+      <c r="H38" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I38" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J38" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N38" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q38" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="L38" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M38" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N38" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P38" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q38" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R38" s="24" t="s">
         <v>10</v>
@@ -3913,8 +3949,8 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="40"/>
+    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="41"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3930,35 +3966,35 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I39" s="24" t="s">
+      <c r="H39" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J39" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q39" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O39" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P39" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R39" s="24" t="s">
         <v>104</v>
@@ -3978,8 +4014,8 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="41" t="s">
+    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="56" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -4001,34 +4037,34 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I40" s="24" t="s">
-        <v>104</v>
+      <c r="H40" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J40" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M40" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P40" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q40" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R40" s="24" t="s">
@@ -4049,8 +4085,8 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="39"/>
+    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="40"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4070,35 +4106,35 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H41" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>104</v>
+      <c r="H41" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J41" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L41" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M41" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q41" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M41" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N41" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O41" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P41" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q41" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R41" s="24" t="s">
         <v>104</v>
@@ -4118,8 +4154,8 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
+    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="40"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4135,34 +4171,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="24" t="s">
+      <c r="H42" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I42" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J42" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q42" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M42" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P42" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R42" s="24" t="s">
@@ -4183,8 +4219,8 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="39"/>
+    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="40"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4200,10 +4236,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H43" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I43" s="24" t="s">
+      <c r="H43" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="23" t="s">
         <v>10</v>
       </c>
       <c r="J43" s="23" t="s">
@@ -4212,23 +4248,23 @@
       <c r="K43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L43" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M43" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O43" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q43" s="23" t="s">
-        <v>104</v>
+      <c r="L43" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M43" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N43" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O43" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P43" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q43" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="R43" s="24" t="s">
         <v>10</v>
@@ -4248,8 +4284,8 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="39"/>
+    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="40"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4265,35 +4301,35 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H44" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>46</v>
+      <c r="H44" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L44" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M44" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O44" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P44" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="L44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M44" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q44" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="R44" s="24" t="s">
         <v>10</v>
@@ -4313,8 +4349,8 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="40"/>
+    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="41"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4330,10 +4366,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I45" s="24" t="s">
+      <c r="H45" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J45" s="23" t="s">
@@ -4342,22 +4378,22 @@
       <c r="K45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q45" s="23" t="s">
+      <c r="L45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P45" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R45" s="24" t="s">
@@ -4378,8 +4414,8 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="58" t="s">
+    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="39" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4401,10 +4437,10 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="24" t="s">
+      <c r="H46" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J46" s="23" t="s">
@@ -4413,22 +4449,22 @@
       <c r="K46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q46" s="23" t="s">
+      <c r="L46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M46" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P46" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R46" s="24" t="s">
@@ -4449,8 +4485,8 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="39"/>
+    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="40"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4470,10 +4506,10 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I47" s="24" t="s">
+      <c r="H47" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J47" s="23" t="s">
@@ -4482,22 +4518,22 @@
       <c r="K47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M47" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q47" s="23" t="s">
+      <c r="L47" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M47" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P47" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="R47" s="24" t="s">
@@ -4518,8 +4554,8 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="39"/>
+    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="40"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4535,10 +4571,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I48" s="24" t="s">
+      <c r="H48" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J48" s="23" t="s">
@@ -4547,22 +4583,22 @@
       <c r="K48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q48" s="23" t="s">
+      <c r="L48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M48" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P48" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R48" s="24" t="s">
@@ -4583,8 +4619,8 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="39"/>
+    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="40"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4600,34 +4636,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I49" s="24" t="s">
+      <c r="H49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="O49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q49" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="R49" s="24" t="s">
@@ -4648,8 +4684,8 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="39"/>
+    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="40"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4665,34 +4701,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H50" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I50" s="24" t="s">
-        <v>10</v>
+      <c r="H50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I50" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J50" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N50" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="O50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q50" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M50" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R50" s="24" t="s">
@@ -4713,8 +4749,8 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="40"/>
+    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="41"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4730,11 +4766,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I51" s="24" t="s">
-        <v>10</v>
+      <c r="H51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I51" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J51" s="23" t="s">
         <v>104</v>
@@ -4742,23 +4778,23 @@
       <c r="K51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="O51" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q51" s="23" t="s">
-        <v>104</v>
+      <c r="L51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q51" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="R51" s="24" t="s">
         <v>104</v>
@@ -4778,8 +4814,8 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="61" t="s">
+    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="46" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4801,34 +4837,34 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I52" s="26" t="s">
+      <c r="H52" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I52" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J52" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O52" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q52" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M52" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P52" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q52" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R52" s="26" t="s">
@@ -4849,8 +4885,8 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="62"/>
+    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="47"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4870,11 +4906,11 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I53" s="26" t="s">
-        <v>10</v>
+      <c r="H53" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="J53" s="25" t="s">
         <v>104</v>
@@ -4882,23 +4918,23 @@
       <c r="K53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L53" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="N53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q53" s="25" t="s">
-        <v>104</v>
+      <c r="L53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M53" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P53" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q53" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="R53" s="26" t="s">
         <v>104</v>
@@ -4918,8 +4954,8 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="62"/>
+    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="47"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4935,10 +4971,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I54" s="26" t="s">
+      <c r="H54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J54" s="25" t="s">
@@ -4947,22 +4983,22 @@
       <c r="K54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q54" s="25" t="s">
+      <c r="L54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R54" s="26" t="s">
@@ -4983,8 +5019,8 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="62"/>
+    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="47"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -5000,34 +5036,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I55" s="26" t="s">
-        <v>46</v>
+      <c r="H55" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="J55" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K55" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M55" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O55" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q55" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M55" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N55" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="O55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P55" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q55" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R55" s="26" t="s">
@@ -5049,8 +5085,8 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="62"/>
+    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="47"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5066,34 +5102,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H56" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I56" s="26" t="s">
-        <v>104</v>
+      <c r="H56" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I56" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="N56" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="O56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q56" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M56" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="N56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P56" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q56" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R56" s="26" t="s">
@@ -5114,8 +5150,8 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="63"/>
+    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="48"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5131,10 +5167,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H57" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I57" s="26" t="s">
+      <c r="H57" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="25" t="s">
         <v>10</v>
       </c>
       <c r="J57" s="25" t="s">
@@ -5143,23 +5179,23 @@
       <c r="K57" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L57" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M57" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N57" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="O57" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P57" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q57" s="25" t="s">
-        <v>10</v>
+      <c r="L57" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M57" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="N57" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O57" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P57" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q57" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="R57" s="26" t="s">
         <v>46</v>
@@ -5179,8 +5215,8 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="64" t="s">
+    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="49" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5202,34 +5238,34 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I58" s="26" t="s">
+      <c r="H58" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J58" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q58" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M58" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P58" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R58" s="26" t="s">
@@ -5250,8 +5286,8 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="65"/>
+    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="50"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5271,10 +5307,10 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I59" s="26" t="s">
+      <c r="H59" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J59" s="25" t="s">
@@ -5283,22 +5319,22 @@
       <c r="K59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M59" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q59" s="25" t="s">
+      <c r="L59" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M59" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P59" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q59" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R59" s="26" t="s">
@@ -5319,8 +5355,8 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="65"/>
+    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="50"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5336,10 +5372,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I60" s="26" t="s">
+      <c r="H60" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I60" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J60" s="25" t="s">
@@ -5348,23 +5384,23 @@
       <c r="K60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L60" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q60" s="25" t="s">
-        <v>46</v>
+      <c r="L60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M60" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P60" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q60" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="R60" s="26" t="s">
         <v>46</v>
@@ -5384,8 +5420,8 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="65"/>
+    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="50"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5401,35 +5437,35 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I61" s="26" t="s">
-        <v>10</v>
+      <c r="H61" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I61" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M61" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O61" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="P61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q61" s="25" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L61" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P61" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q61" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="R61" s="26" t="s">
         <v>46</v>
@@ -5449,8 +5485,8 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="65"/>
+    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="50"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5466,35 +5502,35 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I62" s="26" t="s">
-        <v>10</v>
+      <c r="H62" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="J62" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q62" s="25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L62" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M62" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N62" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O62" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P62" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q62" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="R62" s="26" t="s">
         <v>10</v>
@@ -5514,8 +5550,8 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
+    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="51"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5531,10 +5567,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I63" s="26" t="s">
+      <c r="H63" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="J63" s="25" t="s">
@@ -5543,22 +5579,22 @@
       <c r="K63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="N63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q63" s="25" t="s">
+      <c r="L63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M63" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P63" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R63" s="26" t="s">
@@ -5579,8 +5615,8 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="52" t="s">
+    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="33" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5602,10 +5638,10 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I64" s="26" t="s">
+      <c r="H64" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J64" s="25" t="s">
@@ -5614,22 +5650,22 @@
       <c r="K64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q64" s="25" t="s">
+      <c r="L64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M64" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P64" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R64" s="26" t="s">
@@ -5650,8 +5686,8 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="53"/>
+    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="34"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5671,10 +5707,10 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I65" s="26" t="s">
+      <c r="H65" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="J65" s="25" t="s">
@@ -5683,22 +5719,22 @@
       <c r="K65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="N65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q65" s="25" t="s">
+      <c r="L65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M65" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P65" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R65" s="26" t="s">
@@ -5719,8 +5755,8 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="53"/>
+    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="34"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5736,10 +5772,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I66" s="26" t="s">
+      <c r="H66" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J66" s="25" t="s">
@@ -5748,22 +5784,22 @@
       <c r="K66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q66" s="25" t="s">
+      <c r="L66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M66" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P66" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R66" s="26" t="s">
@@ -5784,8 +5820,8 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="53"/>
+    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="34"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5801,11 +5837,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H67" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I67" s="26" t="s">
-        <v>46</v>
+      <c r="H67" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I67" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="J67" s="25" t="s">
         <v>46</v>
@@ -5813,22 +5849,22 @@
       <c r="K67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q67" s="25" t="s">
+      <c r="L67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M67" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P67" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q67" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R67" s="26" t="s">
@@ -5849,8 +5885,8 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="53"/>
+    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="34"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5866,34 +5902,34 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H68" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I68" s="26" t="s">
-        <v>10</v>
+      <c r="H68" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I68" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="J68" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L68" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M68" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="N68" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O68" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P68" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q68" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L68" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M68" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N68" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O68" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P68" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q68" s="26" t="s">
         <v>10</v>
       </c>
       <c r="R68" s="26" t="s">
@@ -5914,8 +5950,8 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
+    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="35"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5931,35 +5967,35 @@
         <f t="shared" ref="G69:G75" si="2">IF(OR(E69="",F69=""),"",IF(E69&gt;F69,"L",IF(E69&lt;F69,"V","E")))</f>
         <v/>
       </c>
-      <c r="H69" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I69" s="26" t="s">
-        <v>10</v>
+      <c r="H69" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I69" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="J69" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q69" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="L69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="O69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P69" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q69" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="R69" s="26" t="s">
         <v>46</v>
@@ -5979,8 +6015,8 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="55" t="s">
+    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="36" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -6002,34 +6038,34 @@
         <f t="shared" si="2"/>
         <v>L</v>
       </c>
-      <c r="H70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I70" s="26" t="s">
-        <v>104</v>
+      <c r="H70" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I70" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="J70" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L70" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M70" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N70" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O70" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q70" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L70" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M70" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N70" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="O70" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P70" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q70" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R70" s="26" t="s">
@@ -6050,8 +6086,8 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="56"/>
+    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="37"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6071,34 +6107,34 @@
         <f t="shared" si="2"/>
         <v>L</v>
       </c>
-      <c r="H71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I71" s="26" t="s">
-        <v>46</v>
+      <c r="H71" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I71" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="J71" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P71" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q71" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L71" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M71" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N71" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O71" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P71" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q71" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R71" s="26" t="s">
@@ -6119,8 +6155,8 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="56"/>
+    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="37"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6136,34 +6172,34 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I72" s="26" t="s">
+      <c r="H72" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I72" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J72" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q72" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M72" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P72" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="R72" s="26" t="s">
@@ -6184,8 +6220,8 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="56"/>
+    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="37"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6201,10 +6237,10 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I73" s="26" t="s">
+      <c r="H73" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I73" s="25" t="s">
         <v>104</v>
       </c>
       <c r="J73" s="25" t="s">
@@ -6213,23 +6249,23 @@
       <c r="K73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="L73" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="N73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q73" s="25" t="s">
-        <v>10</v>
+      <c r="L73" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M73" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N73" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O73" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P73" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q73" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="R73" s="26" t="s">
         <v>10</v>
@@ -6249,8 +6285,8 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="56"/>
+    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="37"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6266,34 +6302,34 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I74" s="26" t="s">
+      <c r="H74" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I74" s="25" t="s">
         <v>104</v>
       </c>
       <c r="J74" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="N74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="O74" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q74" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M74" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="O74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P74" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="R74" s="26" t="s">
@@ -6314,8 +6350,8 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="57"/>
+    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="38"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6331,34 +6367,34 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I75" s="26" t="s">
+      <c r="H75" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I75" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J75" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L75" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="O75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q75" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M75" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="N75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O75" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P75" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q75" s="26" t="s">
         <v>10</v>
       </c>
       <c r="R75" s="26" t="s">
@@ -6379,48 +6415,48 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="59" t="s">
+      <c r="D76" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="34"/>
-      <c r="F76" s="35"/>
+      <c r="E76" s="43"/>
+      <c r="F76" s="44"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>81</v>
-      </c>
-      <c r="H76" s="25">
+        <v>105</v>
+      </c>
+      <c r="H76" s="26">
+        <v>179</v>
+      </c>
+      <c r="I76" s="25">
         <v>222</v>
       </c>
-      <c r="I76" s="26">
-        <v>179</v>
-      </c>
       <c r="J76" s="25">
+        <v>172</v>
+      </c>
+      <c r="K76" s="25">
         <v>186</v>
       </c>
-      <c r="K76" s="25">
-        <v>172</v>
-      </c>
-      <c r="L76" s="26">
+      <c r="L76" s="25">
+        <v>190</v>
+      </c>
+      <c r="M76" s="26">
+        <v>162</v>
+      </c>
+      <c r="N76" s="25">
+        <v>197</v>
+      </c>
+      <c r="O76" s="25">
+        <v>169</v>
+      </c>
+      <c r="P76" s="26">
+        <v>185</v>
+      </c>
+      <c r="Q76" s="26">
         <v>201</v>
-      </c>
-      <c r="M76" s="25">
-        <v>190</v>
-      </c>
-      <c r="N76" s="26">
-        <v>162</v>
-      </c>
-      <c r="O76" s="26">
-        <v>185</v>
-      </c>
-      <c r="P76" s="25">
-        <v>197</v>
-      </c>
-      <c r="Q76" s="25">
-        <v>169</v>
       </c>
       <c r="R76" s="26">
         <v>180</v>
@@ -6440,118 +6476,118 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="60" t="s">
+      <c r="D77" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="35"/>
+      <c r="E77" s="43"/>
+      <c r="F77" s="43"/>
+      <c r="G77" s="44"/>
       <c r="H77" s="28">
         <f>SUM(H78:H81)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I77" s="28">
         <f>SUM(I78:I81)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" s="28">
         <f>SUM(J78:J81)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K77" s="28">
         <f>SUM(K78:K81)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L77" s="28">
         <f>SUM(L78:L81)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M77" s="28">
         <f>SUM(M78:M81)</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="N77" s="28">
         <f>SUM(N78:N81)</f>
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O77" s="28">
         <f>SUM(O78:O81)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P77" s="28">
         <f>SUM(P78:P81)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q77" s="28">
         <f>SUM(Q78:Q81)</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R77" s="28">
         <f>SUM(R78:R81)</f>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="S77" s="28">
         <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="T77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="U77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="V77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="W77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="X77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AB77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AC77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AD77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AE77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AF77" s="28">
         <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6564,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="4"/>
+        <f>IF(I76=$G$76,100,IF($G$76-I76=1,99,IF($G$76-I76=-1,99,IF($G$76-I76=2,98,IF($G$76-I76=-2,98,IF($G$76-I76=3,97,IF($G$76-I76=-3,97,IF($G$76-I76=4,96,IF($G$76-I76=-4,96,IF($G$76-I76=5,95,IF($G$76-I76=-5,95,IF($G$76-I76=6,94,IF($G$76-I76=-6,94,IF($G$76-I76=7,93,IF($G$76-I76=-7,93,IF($G$76-I76=8,92,IF($G$76-I76=-8,92,IF($G$76-I76=9,91,IF($G$76-I76=-9,91,IF($G$76-I76=10,90,IF($G$76-I76=-10,90,IF($G$76-I76=11,89,IF($G$76-I76=-11,89,IF($G$76-I76=12,88,IF($G$76-I76=-12,88,IF($G$76-I76=13,87,IF($G$76-I76=-13,87,IF($G$76-I76=14,86,IF($G$76-I76=-14,86,IF($G$76-I76=15,85,IF($G$76-I76=-15,85,IF($G$76-I76=16,84,IF($G$76-I76=-16,84,IF($G$76-I76=17,83,IF($G$76-I76=-17,83,IF($G$76-I76=18,82,IF($G$76-I76=-18,82,IF($G$76-I76=19,81,IF($G$76-I76=-19,81,IF($G$76-I76=20,80,IF($G$76-I76=-20,80,IF($G$76-I76=21,79,IF($G$76-I76=-21,79,IF($G$76-I76=22,78,IF($G$76-I76=-22,78,IF($G$76-I76=23,77,IF($G$76-I76=-23,77,IF($G$76-I76=24,76,IF($G$76-I76=-24,76,IF($G$76-I76=25,75,IF($G$76-I76=-25,75,IF($G$76-I76=26,74,IF($G$76-I76=-26,74,IF($G$76-I76=27,73,IF($G$76-I76=-27,73,IF($G$76-I76=28,72,IF($G$76-I76=-28,72,IF($G$76-I76=29,71,IF($G$76-I76=-29,71,IF($G$76-I76=30,70,IF($G$76-I76=-30,70,IF($G$76-I76=31,69,IF($G$76-I76=-31,69,IF($G$76-I76=32,68,IF($G$76-I76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="J78" s="3">
@@ -6660,7 +6696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6690,7 +6726,7 @@
       </c>
       <c r="M79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="N79" s="3">
         <f t="shared" si="5"/>
@@ -6698,7 +6734,7 @@
       </c>
       <c r="O79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P79" s="3">
         <f t="shared" si="5"/>
@@ -6769,7 +6805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6779,7 +6815,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="3">
         <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I80" s="3">
         <f t="shared" si="6"/>
@@ -6787,15 +6823,15 @@
       </c>
       <c r="J80" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K80" s="3">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L80" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M80" s="3">
         <f t="shared" si="6"/>
@@ -6803,7 +6839,7 @@
       </c>
       <c r="N80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O80" s="3">
         <f t="shared" si="6"/>
@@ -6811,74 +6847,74 @@
       </c>
       <c r="P80" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q80" s="3">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R80" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="T80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="U80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="V80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="W80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="X80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AB80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AC80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AD80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AE80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AF80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6892,7 +6928,7 @@
       </c>
       <c r="I81" s="3">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
         <f t="shared" si="7"/>
@@ -6924,11 +6960,11 @@
       </c>
       <c r="Q81" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R81" s="3">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" s="3">
         <f t="shared" si="7"/>
@@ -6987,7 +7023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7021,7 +7057,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7055,7 +7091,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7089,7 +7125,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7123,7 +7159,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7157,7 +7193,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7191,7 +7227,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7225,7 +7261,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7259,7 +7295,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7293,7 +7329,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7327,7 +7363,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7361,7 +7397,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7395,7 +7431,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7429,7 +7465,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7463,7 +7499,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7497,7 +7533,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7531,7 +7567,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7565,7 +7601,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7599,7 +7635,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7633,7 +7669,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7642,7 +7678,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7651,7 +7687,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7660,7 +7696,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7669,7 +7705,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7678,7 +7714,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7687,7 +7723,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7696,7 +7732,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7705,7 +7741,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7714,7 +7750,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7723,7 +7759,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7732,7 +7768,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7741,7 +7777,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7750,7 +7786,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7759,7 +7795,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7768,7 +7804,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7777,7 +7813,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7786,7 +7822,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7795,7 +7831,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7804,7 +7840,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7813,7 +7849,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7822,7 +7858,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7831,7 +7867,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7840,7 +7876,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7855,13 +7891,6 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7873,6 +7902,13 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -7887,14 +7923,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="15" width="11.42578125" customWidth="1"/>
+    <col min="1" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="15" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>16</v>
@@ -7941,7 +7977,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -7986,7 +8022,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -8031,7 +8067,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -8076,7 +8112,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -8121,7 +8157,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -8166,7 +8202,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -8211,7 +8247,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -8256,7 +8292,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -8301,7 +8337,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -8346,7 +8382,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -8391,7 +8427,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>16</v>
@@ -8436,7 +8472,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>16</v>
@@ -8481,7 +8517,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
@@ -8526,7 +8562,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -8571,7 +8607,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
@@ -8616,7 +8652,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>16</v>
@@ -8661,7 +8697,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
@@ -8706,7 +8742,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>16</v>
@@ -8751,7 +8787,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>16</v>
@@ -8796,7 +8832,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>16</v>
@@ -8841,7 +8877,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -8886,7 +8922,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -8931,7 +8967,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>16</v>
@@ -8976,7 +9012,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>16</v>
@@ -9021,7 +9057,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -9066,7 +9102,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>16</v>
@@ -9111,7 +9147,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>16</v>
@@ -9156,7 +9192,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>16</v>
@@ -9201,7 +9237,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>16</v>
@@ -9246,7 +9282,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>16</v>
@@ -9291,7 +9327,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>16</v>
@@ -9336,7 +9372,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>16</v>
@@ -9381,7 +9417,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>16</v>
@@ -9426,7 +9462,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>16</v>
@@ -9471,7 +9507,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>16</v>
@@ -9516,7 +9552,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>16</v>
@@ -9561,7 +9597,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>16</v>
@@ -9606,7 +9642,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>16</v>
@@ -9651,7 +9687,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>16</v>
@@ -9696,7 +9732,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>16</v>
@@ -9741,7 +9777,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>16</v>
@@ -9786,7 +9822,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>16</v>
@@ -9831,7 +9867,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>16</v>
@@ -9876,7 +9912,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>16</v>
@@ -9921,7 +9957,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>16</v>
@@ -9966,7 +10002,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>16</v>
@@ -10011,7 +10047,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>16</v>
@@ -10056,7 +10092,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>16</v>
@@ -10101,7 +10137,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>16</v>
@@ -10146,7 +10182,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>16</v>
@@ -10191,7 +10227,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>16</v>
@@ -10236,7 +10272,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>16</v>
@@ -10281,7 +10317,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>16</v>
@@ -10326,7 +10362,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>16</v>
@@ -10371,7 +10407,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>16</v>
@@ -10416,7 +10452,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>16</v>
@@ -10461,7 +10497,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>16</v>
@@ -10506,7 +10542,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>16</v>
@@ -10551,7 +10587,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>16</v>
@@ -10596,7 +10632,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>16</v>
@@ -10641,7 +10677,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>16</v>
@@ -10686,7 +10722,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>16</v>
@@ -10731,7 +10767,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>16</v>
@@ -10776,7 +10812,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>16</v>
@@ -10821,7 +10857,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>16</v>
@@ -10866,7 +10902,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>16</v>
@@ -10911,7 +10947,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>16</v>
@@ -10956,7 +10992,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>16</v>
@@ -11001,7 +11037,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>16</v>
@@ -11046,7 +11082,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>16</v>
@@ -11091,7 +11127,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>16</v>
@@ -11136,7 +11172,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>16</v>
@@ -11181,7 +11217,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>16</v>
@@ -11226,7 +11262,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>16</v>
@@ -11271,7 +11307,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>16</v>
@@ -11316,7 +11352,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>16</v>
@@ -11361,7 +11397,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>16</v>
@@ -11406,7 +11442,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>16</v>
@@ -11451,7 +11487,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>16</v>
@@ -11496,7 +11532,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>16</v>
@@ -11541,7 +11577,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>16</v>
@@ -11586,7 +11622,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>16</v>
@@ -11631,7 +11667,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>16</v>
@@ -11676,7 +11712,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>16</v>
@@ -11721,7 +11757,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>16</v>
@@ -11766,7 +11802,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>16</v>
@@ -11811,7 +11847,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>16</v>
@@ -11856,7 +11892,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>16</v>
@@ -11901,7 +11937,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>16</v>
@@ -11946,7 +11982,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>16</v>
@@ -11991,7 +12027,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>16</v>
@@ -12036,7 +12072,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>16</v>
@@ -12081,7 +12117,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>16</v>
@@ -12126,7 +12162,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>16</v>
@@ -12171,7 +12207,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>16</v>
@@ -12216,7 +12252,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>16</v>
@@ -12261,7 +12297,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>16</v>
@@ -12306,7 +12342,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>16</v>
@@ -12351,7 +12387,7 @@
         <v>SI(G28-H28=-100;0;</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12377,9 +12413,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="11" width="10.7109375" customWidth="1"/>
+    <col min="1" max="11" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12390,26 +12426,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="11" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="11" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -12417,61 +12453,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -12479,7 +12515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -12487,19 +12523,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -12507,19 +12543,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -12527,19 +12563,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -12547,13 +12583,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -12561,229 +12597,229 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="1"/>
     </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1"/>
     </row>
-    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="1"/>
     </row>
-    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="1"/>
     </row>
-    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="1"/>
     </row>
-    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="1"/>
     </row>
-    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="1"/>
     </row>
-    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="1"/>
     </row>
-    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="1"/>
     </row>
-    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1"/>
     </row>
   </sheetData>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F234A566-2F22-46DE-BB66-542666453219}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DBA7491-98F2-4EB2-86BD-87C8414B93B8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -873,58 +873,11 @@
     <xf numFmtId="0" fontId="6" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -932,6 +885,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -964,6 +919,51 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1304,15 +1304,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="35"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1390,17 +1390,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="64" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="66"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51"/>
       <c r="H2" s="30" t="s">
         <v>106</v>
       </c>
@@ -1422,11 +1422,11 @@
       <c r="N2" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="O2" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="P2" s="29" t="s">
         <v>112</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>107</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>108</v>
@@ -1462,44 +1462,44 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="54"/>
+      <c r="F3" s="37"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$75=H4:H75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="14" cm="1">
         <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$75=I4:I75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="14" cm="1">
         <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$75=J4:J75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" s="14" cm="1">
         <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$75=K4:K75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" s="14" cm="1">
         <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$75=L4:L75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="14" cm="1">
         <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$75=M4:M75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" s="14" cm="1">
         <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$75=N4:N75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O3" s="14" cm="1">
         <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$75=O4:O75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P3" s="14" cm="1">
         <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$75=P4:P75)*($G$4:$G$75&lt;&gt;""))</f>
@@ -1507,71 +1507,71 @@
       </c>
       <c r="Q3" s="14" cm="1">
         <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$75=Q4:Q75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R3" s="14" cm="1">
         <f t="array" ref="R3">SUMPRODUCT(($G$4:$G$75=R4:R75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF3" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="38" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1614,10 +1614,10 @@
       <c r="N4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P4" s="24" t="s">
+      <c r="O4" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q4" s="24" t="s">
@@ -1642,7 +1642,7 @@
       <c r="AF4" s="23"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="40"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1683,11 +1683,11 @@
       <c r="N5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P5" s="24" t="s">
-        <v>46</v>
+      <c r="O5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q5" s="24" t="s">
         <v>46</v>
@@ -1711,7 +1711,7 @@
       <c r="AF5" s="23"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="40"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1752,11 +1752,11 @@
       <c r="N6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P6" s="24" t="s">
+      <c r="O6" s="24" t="s">
         <v>110</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="Q6" s="24" t="s">
         <v>104</v>
@@ -1780,7 +1780,7 @@
       <c r="AF6" s="23"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="40"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1821,10 +1821,10 @@
       <c r="N7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" s="24" t="s">
+      <c r="O7" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q7" s="24" t="s">
@@ -1849,7 +1849,7 @@
       <c r="AF7" s="23"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="40"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1886,10 +1886,10 @@
       <c r="N8" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P8" s="24" t="s">
+      <c r="O8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P8" s="23" t="s">
         <v>104</v>
       </c>
       <c r="Q8" s="24" t="s">
@@ -1914,7 +1914,7 @@
       <c r="AF8" s="23"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="41"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1951,11 +1951,11 @@
       <c r="N9" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P9" s="24" t="s">
-        <v>104</v>
+      <c r="O9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q9" s="24" t="s">
         <v>104</v>
@@ -1979,7 +1979,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="45" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -2022,11 +2022,11 @@
       <c r="N10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P10" s="24" t="s">
-        <v>46</v>
+      <c r="O10" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P10" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q10" s="24" t="s">
         <v>46</v>
@@ -2050,7 +2050,7 @@
       <c r="AF10" s="23"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2091,10 +2091,10 @@
       <c r="N11" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P11" s="24" t="s">
+      <c r="O11" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P11" s="23" t="s">
         <v>104</v>
       </c>
       <c r="Q11" s="24" t="s">
@@ -2119,7 +2119,7 @@
       <c r="AF11" s="23"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="40"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2160,11 +2160,11 @@
       <c r="N12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P12" s="24" t="s">
-        <v>46</v>
+      <c r="O12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P12" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="Q12" s="24" t="s">
         <v>10</v>
@@ -2188,7 +2188,7 @@
       <c r="AF12" s="23"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="40"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2229,10 +2229,10 @@
       <c r="N13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P13" s="24" t="s">
+      <c r="O13" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q13" s="24" t="s">
@@ -2257,7 +2257,7 @@
       <c r="AF13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="40"/>
+      <c r="A14" s="39"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2294,11 +2294,11 @@
       <c r="N14" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P14" s="24" t="s">
-        <v>46</v>
+      <c r="O14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P14" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="Q14" s="24" t="s">
         <v>46</v>
@@ -2322,7 +2322,7 @@
       <c r="AF14" s="23"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="41"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2359,11 +2359,11 @@
       <c r="N15" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O15" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P15" s="24" t="s">
-        <v>10</v>
+      <c r="O15" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="Q15" s="24" t="s">
         <v>104</v>
@@ -2387,7 +2387,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="61" t="s">
+      <c r="A16" s="46" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2430,10 +2430,10 @@
       <c r="N16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P16" s="24" t="s">
+      <c r="O16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P16" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q16" s="24" t="s">
@@ -2458,7 +2458,7 @@
       <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2499,10 +2499,10 @@
       <c r="N17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P17" s="24" t="s">
+      <c r="O17" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="Q17" s="24" t="s">
@@ -2527,7 +2527,7 @@
       <c r="AF17" s="23"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2568,11 +2568,11 @@
       <c r="N18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P18" s="24" t="s">
-        <v>46</v>
+      <c r="O18" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P18" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="Q18" s="24" t="s">
         <v>10</v>
@@ -2596,7 +2596,7 @@
       <c r="AF18" s="23"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2637,10 +2637,10 @@
       <c r="N19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P19" s="24" t="s">
+      <c r="O19" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q19" s="24" t="s">
@@ -2665,7 +2665,7 @@
       <c r="AF19" s="23"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="40"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2702,11 +2702,11 @@
       <c r="N20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P20" s="24" t="s">
-        <v>46</v>
+      <c r="O20" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P20" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="Q20" s="24" t="s">
         <v>104</v>
@@ -2730,7 +2730,7 @@
       <c r="AF20" s="23"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="41"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2767,10 +2767,10 @@
       <c r="N21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="24" t="s">
+      <c r="O21" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q21" s="24" t="s">
@@ -2795,7 +2795,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="43" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2838,11 +2838,11 @@
       <c r="N22" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O22" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P22" s="24" t="s">
-        <v>46</v>
+      <c r="O22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P22" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q22" s="24" t="s">
         <v>46</v>
@@ -2866,7 +2866,7 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2907,11 +2907,11 @@
       <c r="N23" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O23" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P23" s="24" t="s">
-        <v>46</v>
+      <c r="O23" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P23" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="Q23" s="24" t="s">
         <v>46</v>
@@ -2935,7 +2935,7 @@
       <c r="AF23" s="23"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2976,10 +2976,10 @@
       <c r="N24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P24" s="24" t="s">
+      <c r="O24" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q24" s="24" t="s">
@@ -3004,7 +3004,7 @@
       <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -3045,11 +3045,11 @@
       <c r="N25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P25" s="24" t="s">
-        <v>46</v>
+      <c r="O25" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P25" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q25" s="24" t="s">
         <v>104</v>
@@ -3073,7 +3073,7 @@
       <c r="AF25" s="23"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3110,11 +3110,11 @@
       <c r="N26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O26" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P26" s="24" t="s">
-        <v>104</v>
+      <c r="O26" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P26" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="Q26" s="24" t="s">
         <v>104</v>
@@ -3138,7 +3138,7 @@
       <c r="AF26" s="23"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="41"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3175,11 +3175,11 @@
       <c r="N27" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P27" s="24" t="s">
-        <v>104</v>
+      <c r="O27" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P27" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="Q27" s="24" t="s">
         <v>104</v>
@@ -3203,7 +3203,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3246,10 +3246,10 @@
       <c r="N28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P28" s="24" t="s">
+      <c r="O28" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q28" s="24" t="s">
@@ -3274,7 +3274,7 @@
       <c r="AF28" s="23"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3315,11 +3315,11 @@
       <c r="N29" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P29" s="24" t="s">
-        <v>104</v>
+      <c r="O29" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P29" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q29" s="24" t="s">
         <v>10</v>
@@ -3343,7 +3343,7 @@
       <c r="AF29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3384,10 +3384,10 @@
       <c r="N30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P30" s="24" t="s">
+      <c r="O30" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q30" s="24" t="s">
@@ -3412,7 +3412,7 @@
       <c r="AF30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3453,10 +3453,10 @@
       <c r="N31" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P31" s="24" t="s">
+      <c r="O31" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P31" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q31" s="24" t="s">
@@ -3481,7 +3481,7 @@
       <c r="AF31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3518,11 +3518,11 @@
       <c r="N32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P32" s="24" t="s">
-        <v>46</v>
+      <c r="O32" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P32" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="Q32" s="24" t="s">
         <v>104</v>
@@ -3546,7 +3546,7 @@
       <c r="AF32" s="23"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="41"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3583,10 +3583,10 @@
       <c r="N33" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P33" s="24" t="s">
+      <c r="O33" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="Q33" s="24" t="s">
@@ -3611,7 +3611,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="57" t="s">
+      <c r="A34" s="42" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3654,11 +3654,11 @@
       <c r="N34" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P34" s="24" t="s">
-        <v>46</v>
+      <c r="O34" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P34" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q34" s="24" t="s">
         <v>10</v>
@@ -3682,7 +3682,7 @@
       <c r="AF34" s="23"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="40"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3723,11 +3723,11 @@
       <c r="N35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O35" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P35" s="24" t="s">
-        <v>46</v>
+      <c r="O35" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P35" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q35" s="24" t="s">
         <v>46</v>
@@ -3751,7 +3751,7 @@
       <c r="AF35" s="23"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="40"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3792,11 +3792,11 @@
       <c r="N36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P36" s="24" t="s">
-        <v>104</v>
+      <c r="O36" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P36" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="Q36" s="24" t="s">
         <v>10</v>
@@ -3820,7 +3820,7 @@
       <c r="AF36" s="23"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="40"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3830,11 +3830,15 @@
       <c r="D37" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
+      <c r="E37" s="12">
+        <v>0</v>
+      </c>
+      <c r="F37" s="12">
+        <v>4</v>
+      </c>
       <c r="G37" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>V</v>
       </c>
       <c r="H37" s="24" t="s">
         <v>104</v>
@@ -3857,11 +3861,11 @@
       <c r="N37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O37" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P37" s="24" t="s">
-        <v>104</v>
+      <c r="O37" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P37" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q37" s="24" t="s">
         <v>104</v>
@@ -3885,7 +3889,7 @@
       <c r="AF37" s="23"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="40"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3922,11 +3926,11 @@
       <c r="N38" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P38" s="24" t="s">
-        <v>10</v>
+      <c r="O38" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="P38" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="Q38" s="24" t="s">
         <v>10</v>
@@ -3950,7 +3954,7 @@
       <c r="AF38" s="23"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="41"/>
+      <c r="A39" s="40"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3987,10 +3991,10 @@
       <c r="N39" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O39" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P39" s="24" t="s">
+      <c r="O39" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="P39" s="23" t="s">
         <v>10</v>
       </c>
       <c r="Q39" s="24" t="s">
@@ -4015,7 +4019,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="41" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -4058,10 +4062,10 @@
       <c r="N40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P40" s="24" t="s">
+      <c r="O40" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P40" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q40" s="24" t="s">
@@ -4086,7 +4090,7 @@
       <c r="AF40" s="23"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="40"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4127,11 +4131,11 @@
       <c r="N41" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P41" s="24" t="s">
-        <v>104</v>
+      <c r="O41" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P41" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="Q41" s="24" t="s">
         <v>10</v>
@@ -4155,7 +4159,7 @@
       <c r="AF41" s="23"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="40"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4192,10 +4196,10 @@
       <c r="N42" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P42" s="24" t="s">
+      <c r="O42" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P42" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q42" s="24" t="s">
@@ -4220,7 +4224,7 @@
       <c r="AF42" s="23"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="40"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4257,11 +4261,11 @@
       <c r="N43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P43" s="24" t="s">
-        <v>46</v>
+      <c r="O43" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P43" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="Q43" s="24" t="s">
         <v>46</v>
@@ -4285,7 +4289,7 @@
       <c r="AF43" s="23"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="40"/>
+      <c r="A44" s="39"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4322,11 +4326,11 @@
       <c r="N44" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O44" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P44" s="24" t="s">
-        <v>104</v>
+      <c r="O44" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P44" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="Q44" s="24" t="s">
         <v>104</v>
@@ -4350,7 +4354,7 @@
       <c r="AF44" s="23"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="41"/>
+      <c r="A45" s="40"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4387,10 +4391,10 @@
       <c r="N45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P45" s="24" t="s">
+      <c r="O45" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="Q45" s="24" t="s">
@@ -4415,7 +4419,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="39" t="s">
+      <c r="A46" s="58" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4458,10 +4462,10 @@
       <c r="N46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P46" s="24" t="s">
+      <c r="O46" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q46" s="24" t="s">
@@ -4486,7 +4490,7 @@
       <c r="AF46" s="23"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="40"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4527,10 +4531,10 @@
       <c r="N47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P47" s="24" t="s">
+      <c r="O47" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="Q47" s="24" t="s">
@@ -4555,7 +4559,7 @@
       <c r="AF47" s="23"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="40"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4592,10 +4596,10 @@
       <c r="N48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P48" s="24" t="s">
+      <c r="O48" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q48" s="24" t="s">
@@ -4620,7 +4624,7 @@
       <c r="AF48" s="23"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="40"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4657,10 +4661,10 @@
       <c r="N49" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P49" s="24" t="s">
+      <c r="O49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P49" s="23" t="s">
         <v>46</v>
       </c>
       <c r="Q49" s="24" t="s">
@@ -4685,7 +4689,7 @@
       <c r="AF49" s="23"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="40"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4722,10 +4726,10 @@
       <c r="N50" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P50" s="24" t="s">
+      <c r="O50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="P50" s="23" t="s">
         <v>10</v>
       </c>
       <c r="Q50" s="24" t="s">
@@ -4750,7 +4754,7 @@
       <c r="AF50" s="23"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="41"/>
+      <c r="A51" s="40"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4787,10 +4791,10 @@
       <c r="N51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P51" s="24" t="s">
+      <c r="O51" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="23" t="s">
         <v>104</v>
       </c>
       <c r="Q51" s="24" t="s">
@@ -4815,7 +4819,7 @@
       <c r="AF51" s="23"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="46" t="s">
+      <c r="A52" s="61" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4858,11 +4862,11 @@
       <c r="N52" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P52" s="26" t="s">
-        <v>104</v>
+      <c r="O52" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P52" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="Q52" s="26" t="s">
         <v>46</v>
@@ -4886,7 +4890,7 @@
       <c r="AF52" s="25"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="47"/>
+      <c r="A53" s="62"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4927,10 +4931,10 @@
       <c r="N53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P53" s="26" t="s">
+      <c r="O53" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P53" s="25" t="s">
         <v>104</v>
       </c>
       <c r="Q53" s="26" t="s">
@@ -4955,7 +4959,7 @@
       <c r="AF53" s="25"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="47"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4992,10 +4996,10 @@
       <c r="N54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P54" s="26" t="s">
+      <c r="O54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q54" s="26" t="s">
@@ -5020,7 +5024,7 @@
       <c r="AF54" s="25"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="47"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -5057,11 +5061,11 @@
       <c r="N55" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O55" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P55" s="26" t="s">
-        <v>104</v>
+      <c r="O55" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P55" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="Q55" s="26" t="s">
         <v>46</v>
@@ -5086,7 +5090,7 @@
       <c r="AK55" s="31"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="47"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5123,10 +5127,10 @@
       <c r="N56" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P56" s="26" t="s">
+      <c r="O56" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P56" s="25" t="s">
         <v>104</v>
       </c>
       <c r="Q56" s="26" t="s">
@@ -5151,7 +5155,7 @@
       <c r="AF56" s="25"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="48"/>
+      <c r="A57" s="63"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5188,11 +5192,11 @@
       <c r="N57" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O57" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P57" s="26" t="s">
-        <v>46</v>
+      <c r="O57" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P57" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="Q57" s="26" t="s">
         <v>104</v>
@@ -5216,7 +5220,7 @@
       <c r="AF57" s="25"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="49" t="s">
+      <c r="A58" s="64" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5259,10 +5263,10 @@
       <c r="N58" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P58" s="26" t="s">
+      <c r="O58" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P58" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q58" s="26" t="s">
@@ -5287,7 +5291,7 @@
       <c r="AF58" s="25"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="50"/>
+      <c r="A59" s="65"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5328,10 +5332,10 @@
       <c r="N59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P59" s="26" t="s">
+      <c r="O59" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q59" s="26" t="s">
@@ -5356,7 +5360,7 @@
       <c r="AF59" s="25"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="50"/>
+      <c r="A60" s="65"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5393,10 +5397,10 @@
       <c r="N60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P60" s="26" t="s">
+      <c r="O60" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P60" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q60" s="26" t="s">
@@ -5421,7 +5425,7 @@
       <c r="AF60" s="25"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="50"/>
+      <c r="A61" s="65"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5458,11 +5462,11 @@
       <c r="N61" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P61" s="26" t="s">
-        <v>10</v>
+      <c r="O61" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="P61" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="Q61" s="26" t="s">
         <v>46</v>
@@ -5486,7 +5490,7 @@
       <c r="AF61" s="25"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="50"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5523,11 +5527,11 @@
       <c r="N62" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P62" s="26" t="s">
-        <v>104</v>
+      <c r="O62" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P62" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="Q62" s="26" t="s">
         <v>104</v>
@@ -5551,7 +5555,7 @@
       <c r="AF62" s="25"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="51"/>
+      <c r="A63" s="66"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5588,10 +5592,10 @@
       <c r="N63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P63" s="26" t="s">
+      <c r="O63" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="Q63" s="26" t="s">
@@ -5616,7 +5620,7 @@
       <c r="AF63" s="25"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33" t="s">
+      <c r="A64" s="52" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5659,10 +5663,10 @@
       <c r="N64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P64" s="26" t="s">
+      <c r="O64" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q64" s="26" t="s">
@@ -5687,7 +5691,7 @@
       <c r="AF64" s="25"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="34"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5728,10 +5732,10 @@
       <c r="N65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P65" s="26" t="s">
+      <c r="O65" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="Q65" s="26" t="s">
@@ -5756,7 +5760,7 @@
       <c r="AF65" s="25"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="34"/>
+      <c r="A66" s="53"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5793,10 +5797,10 @@
       <c r="N66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P66" s="26" t="s">
+      <c r="O66" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q66" s="26" t="s">
@@ -5821,7 +5825,7 @@
       <c r="AF66" s="25"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="34"/>
+      <c r="A67" s="53"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5858,10 +5862,10 @@
       <c r="N67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P67" s="26" t="s">
+      <c r="O67" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P67" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q67" s="26" t="s">
@@ -5886,7 +5890,7 @@
       <c r="AF67" s="25"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="34"/>
+      <c r="A68" s="53"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5923,11 +5927,11 @@
       <c r="N68" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O68" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P68" s="26" t="s">
-        <v>104</v>
+      <c r="O68" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P68" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="Q68" s="26" t="s">
         <v>10</v>
@@ -5951,7 +5955,7 @@
       <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="35"/>
+      <c r="A69" s="54"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5988,11 +5992,11 @@
       <c r="N69" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P69" s="26" t="s">
-        <v>104</v>
+      <c r="O69" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P69" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="Q69" s="26" t="s">
         <v>104</v>
@@ -6016,7 +6020,7 @@
       <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="36" t="s">
+      <c r="A70" s="55" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -6059,10 +6063,10 @@
       <c r="N70" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O70" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P70" s="26" t="s">
+      <c r="O70" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P70" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q70" s="26" t="s">
@@ -6087,7 +6091,7 @@
       <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
+      <c r="A71" s="56"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6128,10 +6132,10 @@
       <c r="N71" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O71" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P71" s="26" t="s">
+      <c r="O71" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P71" s="25" t="s">
         <v>104</v>
       </c>
       <c r="Q71" s="26" t="s">
@@ -6156,7 +6160,7 @@
       <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+      <c r="A72" s="56"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6193,10 +6197,10 @@
       <c r="N72" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P72" s="26" t="s">
+      <c r="O72" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P72" s="25" t="s">
         <v>46</v>
       </c>
       <c r="Q72" s="26" t="s">
@@ -6221,7 +6225,7 @@
       <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+      <c r="A73" s="56"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6258,11 +6262,11 @@
       <c r="N73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O73" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P73" s="26" t="s">
-        <v>104</v>
+      <c r="O73" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P73" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="Q73" s="26" t="s">
         <v>46</v>
@@ -6286,7 +6290,7 @@
       <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
+      <c r="A74" s="56"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6323,11 +6327,11 @@
       <c r="N74" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P74" s="26" t="s">
-        <v>46</v>
+      <c r="O74" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P74" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="Q74" s="26" t="s">
         <v>104</v>
@@ -6351,7 +6355,7 @@
       <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="38"/>
+      <c r="A75" s="57"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6388,11 +6392,11 @@
       <c r="N75" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O75" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P75" s="26" t="s">
-        <v>46</v>
+      <c r="O75" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P75" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="Q75" s="26" t="s">
         <v>10</v>
@@ -6419,14 +6423,14 @@
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="42" t="s">
+      <c r="D76" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="43"/>
-      <c r="F76" s="44"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="35"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H76" s="26">
         <v>179</v>
@@ -6449,11 +6453,11 @@
       <c r="N76" s="25">
         <v>197</v>
       </c>
-      <c r="O76" s="25">
+      <c r="O76" s="26">
+        <v>185</v>
+      </c>
+      <c r="P76" s="25">
         <v>169</v>
-      </c>
-      <c r="P76" s="26">
-        <v>185</v>
       </c>
       <c r="Q76" s="26">
         <v>201</v>
@@ -6480,15 +6484,15 @@
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="45" t="s">
+      <c r="D77" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="44"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="35"/>
       <c r="H77" s="28">
         <f>SUM(H78:H81)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I77" s="28">
         <f>SUM(I78:I81)</f>
@@ -6496,39 +6500,39 @@
       </c>
       <c r="J77" s="28">
         <f>SUM(J78:J81)</f>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K77" s="28">
         <f>SUM(K78:K81)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L77" s="28">
         <f>SUM(L78:L81)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M77" s="28">
         <f>SUM(M78:M81)</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N77" s="28">
         <f>SUM(N78:N81)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O77" s="28">
         <f>SUM(O78:O81)</f>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P77" s="28">
         <f>SUM(P78:P81)</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q77" s="28">
         <f>SUM(Q78:Q81)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R77" s="28">
         <f>SUM(R78:R81)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S77" s="28">
         <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
@@ -6714,7 +6718,7 @@
       </c>
       <c r="J79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K79" s="3">
         <f t="shared" si="5"/>
@@ -6726,7 +6730,7 @@
       </c>
       <c r="M79" s="3">
         <f t="shared" si="5"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N79" s="3">
         <f t="shared" si="5"/>
@@ -6734,11 +6738,11 @@
       </c>
       <c r="O79" s="3">
         <f t="shared" si="5"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q79" s="3">
         <f t="shared" si="5"/>
@@ -6815,7 +6819,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="3">
         <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I80" s="3">
         <f t="shared" si="6"/>
@@ -6823,15 +6827,15 @@
       </c>
       <c r="J80" s="3">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L80" s="3">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M80" s="3">
         <f t="shared" si="6"/>
@@ -6839,23 +6843,23 @@
       </c>
       <c r="N80" s="3">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O80" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P80" s="3">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R80" s="3">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S80" s="3">
         <f t="shared" si="6"/>
@@ -6960,7 +6964,7 @@
       </c>
       <c r="Q81" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R81" s="3">
         <f t="shared" si="7"/>
@@ -7891,6 +7895,13 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7902,13 +7913,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DBA7491-98F2-4EB2-86BD-87C8414B93B8}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE6F4472-831C-4093-B49F-ED8990AE93E4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
@@ -873,11 +873,58 @@
     <xf numFmtId="0" fontId="6" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -885,8 +932,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -919,51 +964,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1288,31 +1288,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.6640625" customWidth="1"/>
-    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="5.6640625" customWidth="1"/>
-    <col min="19" max="32" width="5.6640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.7109375" customWidth="1"/>
+    <col min="19" max="32" width="5.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1389,29 +1389,29 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="47" t="s">
+    <row r="2" spans="1:32" ht="143.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49" t="s">
+      <c r="B2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="30" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="K2" s="29" t="s">
         <v>111</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2" s="29" t="s">
-        <v>113</v>
       </c>
       <c r="L2" s="29" t="s">
         <v>114</v>
@@ -1422,11 +1422,11 @@
       <c r="N2" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="O2" s="30" t="s">
+      <c r="O2" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="P2" s="30" t="s">
         <v>107</v>
-      </c>
-      <c r="P2" s="29" t="s">
-        <v>112</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>108</v>
@@ -1449,7 +1449,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1462,56 +1462,56 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="37"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$75=H4:H75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" s="14" cm="1">
         <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$75=I4:I75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="14" cm="1">
         <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$75=J4:J75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" s="14" cm="1">
         <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$75=K4:K75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L3" s="14" cm="1">
         <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$75=L4:L75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" s="14" cm="1">
         <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$75=M4:M75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" s="14" cm="1">
         <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$75=N4:N75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O3" s="14" cm="1">
         <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$75=O4:O75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P3" s="14" cm="1">
         <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$75=P4:P75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="14" cm="1">
         <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$75=Q4:Q75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R3" s="14" cm="1">
         <f t="array" ref="R3">SUMPRODUCT(($G$4:$G$75=R4:R75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
@@ -1570,8 +1570,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1593,13 +1593,13 @@
         <f>IF(OR(E4="",F4=""),"",IF(E4&gt;F4,"L",IF(E4&lt;F4,"V","E")))</f>
         <v>L</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K4" s="23" t="s">
@@ -1614,10 +1614,10 @@
       <c r="N4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P4" s="23" t="s">
+      <c r="O4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q4" s="24" t="s">
@@ -1641,8 +1641,8 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
+    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="40"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1662,13 +1662,13 @@
         <f t="shared" ref="G5:G68" si="1">IF(OR(E5="",F5=""),"",IF(E5&gt;F5,"L",IF(E5&lt;F5,"V","E")))</f>
         <v>L</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K5" s="23" t="s">
@@ -1683,11 +1683,11 @@
       <c r="N5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P5" s="23" t="s">
-        <v>10</v>
+      <c r="O5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q5" s="24" t="s">
         <v>46</v>
@@ -1710,8 +1710,8 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
+    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="40"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1731,17 +1731,17 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L6" s="23" t="s">
         <v>46</v>
@@ -1752,11 +1752,11 @@
       <c r="N6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="24" t="s">
+      <c r="O6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="24" t="s">
         <v>110</v>
-      </c>
-      <c r="P6" s="23" t="s">
-        <v>46</v>
       </c>
       <c r="Q6" s="24" t="s">
         <v>104</v>
@@ -1779,8 +1779,8 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
+    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="40"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1800,17 +1800,17 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>46</v>
+      <c r="J7" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>46</v>
@@ -1821,10 +1821,10 @@
       <c r="N7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" s="23" t="s">
+      <c r="O7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q7" s="24" t="s">
@@ -1848,8 +1848,8 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
+    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="40"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1865,17 +1865,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H8" s="24" t="s">
-        <v>104</v>
+      <c r="H8" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L8" s="23" t="s">
         <v>104</v>
@@ -1886,10 +1886,10 @@
       <c r="N8" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P8" s="23" t="s">
+      <c r="O8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P8" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q8" s="24" t="s">
@@ -1913,8 +1913,8 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="41"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1930,17 +1930,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H9" s="24" t="s">
-        <v>46</v>
+      <c r="H9" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I9" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J9" s="23" t="s">
-        <v>104</v>
+      <c r="J9" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L9" s="23" t="s">
         <v>10</v>
@@ -1951,11 +1951,11 @@
       <c r="N9" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P9" s="23" t="s">
-        <v>10</v>
+      <c r="O9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q9" s="24" t="s">
         <v>104</v>
@@ -1978,8 +1978,8 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="45" t="s">
+    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="60" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -2001,14 +2001,14 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K10" s="23" t="s">
         <v>10</v>
@@ -2022,11 +2022,11 @@
       <c r="N10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="23" t="s">
-        <v>10</v>
+      <c r="O10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q10" s="24" t="s">
         <v>46</v>
@@ -2049,8 +2049,8 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
+    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="40"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2070,17 +2070,17 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I11" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J11" s="23" t="s">
-        <v>104</v>
+      <c r="J11" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L11" s="23" t="s">
         <v>104</v>
@@ -2091,10 +2091,10 @@
       <c r="N11" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P11" s="23" t="s">
+      <c r="O11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P11" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q11" s="24" t="s">
@@ -2118,8 +2118,8 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
+    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="40"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2139,13 +2139,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J12" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -2160,11 +2160,11 @@
       <c r="N12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P12" s="23" t="s">
-        <v>104</v>
+      <c r="O12" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P12" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q12" s="24" t="s">
         <v>10</v>
@@ -2187,8 +2187,8 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
+    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="40"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2208,13 +2208,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K13" s="23" t="s">
@@ -2229,10 +2229,10 @@
       <c r="N13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P13" s="23" t="s">
+      <c r="O13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q13" s="24" t="s">
@@ -2256,8 +2256,8 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
+    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="40"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2273,17 +2273,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H14" s="24" t="s">
-        <v>46</v>
+      <c r="H14" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L14" s="23" t="s">
         <v>10</v>
@@ -2294,11 +2294,11 @@
       <c r="N14" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P14" s="23" t="s">
-        <v>104</v>
+      <c r="O14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P14" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q14" s="24" t="s">
         <v>46</v>
@@ -2321,8 +2321,8 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="41"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2338,17 +2338,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H15" s="24" t="s">
-        <v>46</v>
+      <c r="H15" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L15" s="23" t="s">
         <v>10</v>
@@ -2359,11 +2359,11 @@
       <c r="N15" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O15" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P15" s="23" t="s">
-        <v>104</v>
+      <c r="O15" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P15" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="Q15" s="24" t="s">
         <v>104</v>
@@ -2386,8 +2386,8 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="61" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2409,17 +2409,17 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L16" s="23" t="s">
         <v>46</v>
@@ -2430,10 +2430,10 @@
       <c r="N16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P16" s="23" t="s">
+      <c r="O16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P16" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q16" s="24" t="s">
@@ -2457,8 +2457,8 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
+    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="40"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2478,13 +2478,13 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="23" t="s">
+      <c r="J17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -2499,10 +2499,10 @@
       <c r="N17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P17" s="23" t="s">
+      <c r="O17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q17" s="24" t="s">
@@ -2526,8 +2526,8 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
+    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="40"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2547,13 +2547,13 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J18" s="23" t="s">
+      <c r="J18" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -2568,11 +2568,11 @@
       <c r="N18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P18" s="23" t="s">
-        <v>104</v>
+      <c r="O18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q18" s="24" t="s">
         <v>10</v>
@@ -2595,8 +2595,8 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
+    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="40"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2616,13 +2616,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J19" s="23" t="s">
+      <c r="J19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K19" s="23" t="s">
@@ -2637,10 +2637,10 @@
       <c r="N19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P19" s="23" t="s">
+      <c r="O19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q19" s="24" t="s">
@@ -2664,8 +2664,8 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
+    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="40"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2681,13 +2681,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H20" s="24" t="s">
+      <c r="H20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J20" s="23" t="s">
+      <c r="J20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -2702,11 +2702,11 @@
       <c r="N20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O20" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P20" s="23" t="s">
-        <v>104</v>
+      <c r="O20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q20" s="24" t="s">
         <v>104</v>
@@ -2729,8 +2729,8 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="41"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2746,13 +2746,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="23" t="s">
+      <c r="J21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K21" s="23" t="s">
@@ -2767,10 +2767,10 @@
       <c r="N21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="23" t="s">
+      <c r="O21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q21" s="24" t="s">
@@ -2794,8 +2794,8 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="43" t="s">
+    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="58" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2817,17 +2817,17 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H22" s="24" t="s">
-        <v>46</v>
+      <c r="H22" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L22" s="23" t="s">
         <v>46</v>
@@ -2838,11 +2838,11 @@
       <c r="N22" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P22" s="23" t="s">
-        <v>10</v>
+      <c r="O22" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q22" s="24" t="s">
         <v>46</v>
@@ -2865,8 +2865,8 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="40"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2886,17 +2886,17 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H23" s="24" t="s">
-        <v>104</v>
+      <c r="H23" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L23" s="23" t="s">
         <v>46</v>
@@ -2907,11 +2907,11 @@
       <c r="N23" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P23" s="23" t="s">
-        <v>104</v>
+      <c r="O23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P23" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q23" s="24" t="s">
         <v>46</v>
@@ -2934,8 +2934,8 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
+    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="40"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2955,17 +2955,17 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H24" s="24" t="s">
+      <c r="H24" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L24" s="23" t="s">
         <v>46</v>
@@ -2976,10 +2976,10 @@
       <c r="N24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P24" s="23" t="s">
+      <c r="O24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q24" s="24" t="s">
@@ -3003,8 +3003,8 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="40"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -3024,17 +3024,17 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H25" s="24" t="s">
+      <c r="H25" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="24" t="s">
         <v>10</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L25" s="23" t="s">
         <v>10</v>
@@ -3045,11 +3045,11 @@
       <c r="N25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O25" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P25" s="23" t="s">
-        <v>10</v>
+      <c r="O25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P25" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q25" s="24" t="s">
         <v>104</v>
@@ -3072,8 +3072,8 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="40"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3089,13 +3089,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H26" s="24" t="s">
+      <c r="H26" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="23" t="s">
+      <c r="J26" s="24" t="s">
         <v>10</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -3110,11 +3110,11 @@
       <c r="N26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P26" s="23" t="s">
-        <v>46</v>
+      <c r="O26" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P26" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q26" s="24" t="s">
         <v>104</v>
@@ -3137,8 +3137,8 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="41"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3154,17 +3154,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H27" s="24" t="s">
-        <v>10</v>
+      <c r="H27" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J27" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J27" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L27" s="23" t="s">
         <v>10</v>
@@ -3175,11 +3175,11 @@
       <c r="N27" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P27" s="23" t="s">
-        <v>46</v>
+      <c r="O27" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P27" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q27" s="24" t="s">
         <v>104</v>
@@ -3202,8 +3202,8 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="59" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3225,13 +3225,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="23" t="s">
+      <c r="J28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -3246,10 +3246,10 @@
       <c r="N28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P28" s="23" t="s">
+      <c r="O28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q28" s="24" t="s">
@@ -3273,8 +3273,8 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
+    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="40"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3294,17 +3294,17 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H29" s="24" t="s">
-        <v>10</v>
+      <c r="H29" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="J29" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L29" s="23" t="s">
         <v>10</v>
@@ -3315,11 +3315,11 @@
       <c r="N29" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P29" s="23" t="s">
-        <v>10</v>
+      <c r="O29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q29" s="24" t="s">
         <v>10</v>
@@ -3342,8 +3342,8 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
+    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="40"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3363,13 +3363,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H30" s="24" t="s">
+      <c r="H30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J30" s="23" t="s">
+      <c r="J30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -3384,10 +3384,10 @@
       <c r="N30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P30" s="23" t="s">
+      <c r="O30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q30" s="24" t="s">
@@ -3411,8 +3411,8 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
+    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="40"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3432,14 +3432,14 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H31" s="24" t="s">
-        <v>10</v>
+      <c r="H31" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J31" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J31" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K31" s="23" t="s">
         <v>104</v>
@@ -3453,10 +3453,10 @@
       <c r="N31" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P31" s="23" t="s">
+      <c r="O31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P31" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q31" s="24" t="s">
@@ -3480,8 +3480,8 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
+    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="40"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3497,14 +3497,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H32" s="24" t="s">
-        <v>10</v>
+      <c r="H32" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="23" t="s">
-        <v>104</v>
+      <c r="J32" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K32" s="23" t="s">
         <v>104</v>
@@ -3518,11 +3518,11 @@
       <c r="N32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O32" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P32" s="23" t="s">
-        <v>104</v>
+      <c r="O32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P32" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q32" s="24" t="s">
         <v>104</v>
@@ -3545,8 +3545,8 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="41"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3562,14 +3562,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H33" s="24" t="s">
+      <c r="H33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J33" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J33" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="K33" s="23" t="s">
         <v>104</v>
@@ -3583,10 +3583,10 @@
       <c r="N33" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O33" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P33" s="23" t="s">
+      <c r="O33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P33" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q33" s="24" t="s">
@@ -3610,8 +3610,8 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="57" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3633,17 +3633,17 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H34" s="24" t="s">
-        <v>10</v>
+      <c r="H34" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I34" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J34" s="23" t="s">
+      <c r="J34" s="24" t="s">
         <v>10</v>
       </c>
       <c r="K34" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L34" s="23" t="s">
         <v>104</v>
@@ -3654,11 +3654,11 @@
       <c r="N34" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O34" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P34" s="23" t="s">
-        <v>10</v>
+      <c r="O34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P34" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q34" s="24" t="s">
         <v>10</v>
@@ -3681,8 +3681,8 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
+    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="40"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3702,13 +3702,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H35" s="24" t="s">
+      <c r="H35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J35" s="23" t="s">
+      <c r="J35" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K35" s="23" t="s">
@@ -3723,11 +3723,11 @@
       <c r="N35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P35" s="23" t="s">
-        <v>10</v>
+      <c r="O35" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q35" s="24" t="s">
         <v>46</v>
@@ -3750,8 +3750,8 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
+    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="40"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3771,13 +3771,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H36" s="24" t="s">
+      <c r="H36" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J36" s="23" t="s">
+      <c r="J36" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -3792,11 +3792,11 @@
       <c r="N36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O36" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P36" s="23" t="s">
-        <v>46</v>
+      <c r="O36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P36" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q36" s="24" t="s">
         <v>10</v>
@@ -3819,8 +3819,8 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
+    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="40"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3840,13 +3840,13 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H37" s="24" t="s">
+      <c r="H37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J37" s="23" t="s">
+      <c r="J37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="23" t="s">
@@ -3861,11 +3861,11 @@
       <c r="N37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P37" s="23" t="s">
-        <v>10</v>
+      <c r="O37" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P37" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q37" s="24" t="s">
         <v>104</v>
@@ -3888,8 +3888,8 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
+    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="40"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3905,17 +3905,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H38" s="24" t="s">
-        <v>46</v>
+      <c r="H38" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I38" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="23" t="s">
+      <c r="J38" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L38" s="23" t="s">
         <v>10</v>
@@ -3926,11 +3926,11 @@
       <c r="N38" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P38" s="23" t="s">
-        <v>46</v>
+      <c r="O38" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P38" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="Q38" s="24" t="s">
         <v>10</v>
@@ -3953,8 +3953,8 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="40"/>
+    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="41"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3970,17 +3970,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H39" s="24" t="s">
-        <v>104</v>
+      <c r="H39" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I39" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J39" s="23" t="s">
+      <c r="J39" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K39" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L39" s="23" t="s">
         <v>104</v>
@@ -3991,10 +3991,10 @@
       <c r="N39" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P39" s="23" t="s">
+      <c r="O39" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P39" s="24" t="s">
         <v>10</v>
       </c>
       <c r="Q39" s="24" t="s">
@@ -4018,8 +4018,8 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="41" t="s">
+    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="56" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -4041,14 +4041,14 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H40" s="24" t="s">
-        <v>104</v>
+      <c r="H40" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J40" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="J40" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="K40" s="23" t="s">
         <v>46</v>
@@ -4062,10 +4062,10 @@
       <c r="N40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P40" s="23" t="s">
+      <c r="O40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P40" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q40" s="24" t="s">
@@ -4089,8 +4089,8 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
+    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="40"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4110,17 +4110,17 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H41" s="24" t="s">
-        <v>104</v>
+      <c r="H41" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J41" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="J41" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L41" s="23" t="s">
         <v>10</v>
@@ -4131,11 +4131,11 @@
       <c r="N41" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P41" s="23" t="s">
-        <v>46</v>
+      <c r="O41" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P41" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q41" s="24" t="s">
         <v>10</v>
@@ -4158,8 +4158,8 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
+    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="40"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4169,23 +4169,27 @@
       <c r="D42" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
+      <c r="E42" s="13">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13">
+        <v>0</v>
+      </c>
       <c r="G42" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>46</v>
+        <v>E</v>
+      </c>
+      <c r="H42" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="I42" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J42" s="23" t="s">
+      <c r="J42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L42" s="23" t="s">
         <v>46</v>
@@ -4196,10 +4200,10 @@
       <c r="N42" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P42" s="23" t="s">
+      <c r="O42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q42" s="24" t="s">
@@ -4223,8 +4227,8 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
+    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="40"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4234,23 +4238,27 @@
       <c r="D43" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="E43" s="13">
+        <v>1</v>
+      </c>
+      <c r="F43" s="13">
+        <v>3</v>
+      </c>
       <c r="G43" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H43" s="24" t="s">
-        <v>10</v>
+        <v>V</v>
+      </c>
+      <c r="H43" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J43" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="J43" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K43" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L43" s="23" t="s">
         <v>46</v>
@@ -4261,11 +4269,11 @@
       <c r="N43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O43" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P43" s="23" t="s">
-        <v>104</v>
+      <c r="O43" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P43" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q43" s="24" t="s">
         <v>46</v>
@@ -4288,8 +4296,8 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
+    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="40"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4305,13 +4313,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H44" s="24" t="s">
-        <v>46</v>
+      <c r="H44" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J44" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K44" s="23" t="s">
@@ -4326,11 +4334,11 @@
       <c r="N44" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O44" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P44" s="23" t="s">
-        <v>10</v>
+      <c r="O44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q44" s="24" t="s">
         <v>104</v>
@@ -4353,8 +4361,8 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="40"/>
+    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="41"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4370,13 +4378,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H45" s="24" t="s">
+      <c r="H45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J45" s="23" t="s">
+      <c r="J45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -4391,10 +4399,10 @@
       <c r="N45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P45" s="23" t="s">
+      <c r="O45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q45" s="24" t="s">
@@ -4418,8 +4426,8 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="58" t="s">
+    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="39" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4441,13 +4449,13 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H46" s="24" t="s">
+      <c r="H46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J46" s="23" t="s">
+      <c r="J46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K46" s="23" t="s">
@@ -4462,10 +4470,10 @@
       <c r="N46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P46" s="23" t="s">
+      <c r="O46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q46" s="24" t="s">
@@ -4489,8 +4497,8 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39"/>
+    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="40"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4510,13 +4518,13 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H47" s="24" t="s">
+      <c r="H47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J47" s="23" t="s">
+      <c r="J47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="K47" s="23" t="s">
@@ -4531,10 +4539,10 @@
       <c r="N47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P47" s="23" t="s">
+      <c r="O47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q47" s="24" t="s">
@@ -4558,8 +4566,8 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="40"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4569,19 +4577,23 @@
       <c r="D48" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
+      <c r="E48" s="14">
+        <v>4</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
       <c r="G48" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H48" s="24" t="s">
+        <v>L</v>
+      </c>
+      <c r="H48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J48" s="23" t="s">
+      <c r="J48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K48" s="23" t="s">
@@ -4596,10 +4608,10 @@
       <c r="N48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P48" s="23" t="s">
+      <c r="O48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q48" s="24" t="s">
@@ -4623,8 +4635,8 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="40"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4634,23 +4646,27 @@
       <c r="D49" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
+      <c r="E49" s="14">
+        <v>2</v>
+      </c>
+      <c r="F49" s="14">
+        <v>2</v>
+      </c>
       <c r="G49" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H49" s="24" t="s">
-        <v>46</v>
+        <v>E</v>
+      </c>
+      <c r="H49" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I49" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J49" s="23" t="s">
+      <c r="J49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L49" s="23" t="s">
         <v>46</v>
@@ -4661,10 +4677,10 @@
       <c r="N49" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P49" s="23" t="s">
+      <c r="O49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q49" s="24" t="s">
@@ -4688,8 +4704,8 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="40"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4705,13 +4721,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H50" s="24" t="s">
-        <v>10</v>
+      <c r="H50" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I50" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J50" s="24" t="s">
         <v>10</v>
       </c>
       <c r="K50" s="23" t="s">
@@ -4726,10 +4742,10 @@
       <c r="N50" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P50" s="23" t="s">
+      <c r="O50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P50" s="24" t="s">
         <v>10</v>
       </c>
       <c r="Q50" s="24" t="s">
@@ -4753,8 +4769,8 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="41"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4770,14 +4786,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H51" s="24" t="s">
-        <v>10</v>
+      <c r="H51" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="I51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J51" s="23" t="s">
-        <v>104</v>
+      <c r="J51" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="K51" s="23" t="s">
         <v>104</v>
@@ -4791,10 +4807,10 @@
       <c r="N51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O51" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="P51" s="23" t="s">
+      <c r="O51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q51" s="24" t="s">
@@ -4818,8 +4834,8 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="61" t="s">
+    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="46" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4841,17 +4857,17 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H52" s="26" t="s">
-        <v>46</v>
+      <c r="H52" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I52" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J52" s="25" t="s">
+      <c r="J52" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L52" s="25" t="s">
         <v>46</v>
@@ -4862,11 +4878,11 @@
       <c r="N52" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O52" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P52" s="25" t="s">
-        <v>46</v>
+      <c r="O52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P52" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="Q52" s="26" t="s">
         <v>46</v>
@@ -4889,8 +4905,8 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="62"/>
+    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="47"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4910,14 +4926,14 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H53" s="26" t="s">
-        <v>10</v>
+      <c r="H53" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="J53" s="25" t="s">
-        <v>104</v>
+      <c r="J53" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="K53" s="25" t="s">
         <v>104</v>
@@ -4931,10 +4947,10 @@
       <c r="N53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P53" s="25" t="s">
+      <c r="O53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P53" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q53" s="26" t="s">
@@ -4958,8 +4974,8 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="62"/>
+    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="47"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4975,13 +4991,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H54" s="26" t="s">
+      <c r="H54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J54" s="25" t="s">
+      <c r="J54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K54" s="25" t="s">
@@ -4996,10 +5012,10 @@
       <c r="N54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P54" s="25" t="s">
+      <c r="O54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q54" s="26" t="s">
@@ -5023,8 +5039,8 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="62"/>
+    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="47"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -5040,13 +5056,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H55" s="26" t="s">
-        <v>46</v>
+      <c r="H55" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J55" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K55" s="25" t="s">
@@ -5061,11 +5077,11 @@
       <c r="N55" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O55" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P55" s="25" t="s">
-        <v>46</v>
+      <c r="O55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P55" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="Q55" s="26" t="s">
         <v>46</v>
@@ -5089,8 +5105,8 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="62"/>
+    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="47"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5106,17 +5122,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H56" s="26" t="s">
-        <v>104</v>
+      <c r="H56" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I56" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="J56" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L56" s="25" t="s">
         <v>104</v>
@@ -5127,10 +5143,10 @@
       <c r="N56" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P56" s="25" t="s">
+      <c r="O56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P56" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q56" s="26" t="s">
@@ -5154,8 +5170,8 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="63"/>
+    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="48"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5171,17 +5187,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H57" s="26" t="s">
-        <v>10</v>
+      <c r="H57" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="I57" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J57" s="25" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="J57" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="K57" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L57" s="25" t="s">
         <v>10</v>
@@ -5192,11 +5208,11 @@
       <c r="N57" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O57" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P57" s="25" t="s">
-        <v>10</v>
+      <c r="O57" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P57" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="Q57" s="26" t="s">
         <v>104</v>
@@ -5219,8 +5235,8 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="64" t="s">
+    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="49" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5242,17 +5258,17 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H58" s="26" t="s">
-        <v>46</v>
+      <c r="H58" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I58" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J58" s="25" t="s">
+      <c r="J58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K58" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L58" s="25" t="s">
         <v>46</v>
@@ -5263,10 +5279,10 @@
       <c r="N58" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P58" s="25" t="s">
+      <c r="O58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q58" s="26" t="s">
@@ -5290,8 +5306,8 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="65"/>
+    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="50"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5311,13 +5327,13 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H59" s="26" t="s">
+      <c r="H59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J59" s="25" t="s">
+      <c r="J59" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K59" s="25" t="s">
@@ -5332,10 +5348,10 @@
       <c r="N59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P59" s="25" t="s">
+      <c r="O59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P59" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q59" s="26" t="s">
@@ -5359,8 +5375,8 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="65"/>
+    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="50"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5376,13 +5392,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H60" s="26" t="s">
+      <c r="H60" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J60" s="25" t="s">
+      <c r="J60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K60" s="25" t="s">
@@ -5397,10 +5413,10 @@
       <c r="N60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P60" s="25" t="s">
+      <c r="O60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q60" s="26" t="s">
@@ -5424,8 +5440,8 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="65"/>
+    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="50"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5441,13 +5457,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H61" s="26" t="s">
-        <v>10</v>
+      <c r="H61" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J61" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="J61" s="26" t="s">
         <v>10</v>
       </c>
       <c r="K61" s="25" t="s">
@@ -5462,11 +5478,11 @@
       <c r="N61" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O61" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="P61" s="25" t="s">
-        <v>104</v>
+      <c r="O61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P61" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="Q61" s="26" t="s">
         <v>46</v>
@@ -5489,8 +5505,8 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="65"/>
+    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="50"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5506,17 +5522,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H62" s="26" t="s">
+      <c r="H62" s="25" t="s">
         <v>10</v>
       </c>
       <c r="I62" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="J62" s="25" t="s">
-        <v>104</v>
+      <c r="J62" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L62" s="25" t="s">
         <v>10</v>
@@ -5527,11 +5543,11 @@
       <c r="N62" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P62" s="25" t="s">
-        <v>10</v>
+      <c r="O62" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P62" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="Q62" s="26" t="s">
         <v>104</v>
@@ -5554,8 +5570,8 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="66"/>
+    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="51"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5571,13 +5587,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H63" s="26" t="s">
+      <c r="H63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="I63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="J63" s="25" t="s">
+      <c r="J63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K63" s="25" t="s">
@@ -5592,10 +5608,10 @@
       <c r="N63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P63" s="25" t="s">
+      <c r="O63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q63" s="26" t="s">
@@ -5619,8 +5635,8 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="52" t="s">
+    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="33" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5642,13 +5658,13 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="H64" s="26" t="s">
+      <c r="H64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J64" s="25" t="s">
+      <c r="J64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K64" s="25" t="s">
@@ -5663,10 +5679,10 @@
       <c r="N64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P64" s="25" t="s">
+      <c r="O64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q64" s="26" t="s">
@@ -5690,8 +5706,8 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="53"/>
+    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="34"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5711,13 +5727,13 @@
         <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="H65" s="26" t="s">
+      <c r="H65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="I65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="J65" s="25" t="s">
+      <c r="J65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K65" s="25" t="s">
@@ -5732,10 +5748,10 @@
       <c r="N65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P65" s="25" t="s">
+      <c r="O65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q65" s="26" t="s">
@@ -5759,8 +5775,8 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="53"/>
+    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="34"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5776,13 +5792,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H66" s="26" t="s">
+      <c r="H66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J66" s="25" t="s">
+      <c r="J66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K66" s="25" t="s">
@@ -5797,10 +5813,10 @@
       <c r="N66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P66" s="25" t="s">
+      <c r="O66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q66" s="26" t="s">
@@ -5824,8 +5840,8 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="53"/>
+    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="34"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5841,17 +5857,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H67" s="26" t="s">
+      <c r="H67" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I67" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J67" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K67" s="25" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L67" s="25" t="s">
         <v>46</v>
@@ -5862,10 +5878,10 @@
       <c r="N67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P67" s="25" t="s">
+      <c r="O67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P67" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q67" s="26" t="s">
@@ -5889,8 +5905,8 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="53"/>
+    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="34"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5906,17 +5922,17 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H68" s="26" t="s">
+      <c r="H68" s="25" t="s">
         <v>10</v>
       </c>
       <c r="I68" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J68" s="25" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="J68" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L68" s="25" t="s">
         <v>104</v>
@@ -5927,11 +5943,11 @@
       <c r="N68" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O68" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P68" s="25" t="s">
-        <v>10</v>
+      <c r="O68" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P68" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="Q68" s="26" t="s">
         <v>10</v>
@@ -5954,8 +5970,8 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="54"/>
+    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="35"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5971,17 +5987,17 @@
         <f t="shared" ref="G69:G75" si="2">IF(OR(E69="",F69=""),"",IF(E69&gt;F69,"L",IF(E69&lt;F69,"V","E")))</f>
         <v/>
       </c>
-      <c r="H69" s="26" t="s">
-        <v>10</v>
+      <c r="H69" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I69" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="J69" s="26" t="s">
         <v>10</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L69" s="25" t="s">
         <v>10</v>
@@ -5992,11 +6008,11 @@
       <c r="N69" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P69" s="25" t="s">
-        <v>10</v>
+      <c r="O69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P69" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="Q69" s="26" t="s">
         <v>104</v>
@@ -6019,8 +6035,8 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="55" t="s">
+    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="36" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -6042,17 +6058,17 @@
         <f t="shared" si="2"/>
         <v>L</v>
       </c>
-      <c r="H70" s="26" t="s">
-        <v>104</v>
+      <c r="H70" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="I70" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="J70" s="25" t="s">
-        <v>10</v>
+      <c r="J70" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L70" s="25" t="s">
         <v>46</v>
@@ -6063,10 +6079,10 @@
       <c r="N70" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O70" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P70" s="25" t="s">
+      <c r="O70" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P70" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q70" s="26" t="s">
@@ -6090,8 +6106,8 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="56"/>
+    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="37"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -6111,17 +6127,17 @@
         <f t="shared" si="2"/>
         <v>L</v>
       </c>
-      <c r="H71" s="26" t="s">
+      <c r="H71" s="25" t="s">
         <v>46</v>
       </c>
       <c r="I71" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="25" t="s">
-        <v>10</v>
+      <c r="J71" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="K71" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L71" s="25" t="s">
         <v>10</v>
@@ -6132,10 +6148,10 @@
       <c r="N71" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P71" s="25" t="s">
+      <c r="O71" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P71" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q71" s="26" t="s">
@@ -6159,8 +6175,8 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="56"/>
+    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="37"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6176,17 +6192,17 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H72" s="26" t="s">
-        <v>46</v>
+      <c r="H72" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I72" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J72" s="25" t="s">
+      <c r="J72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L72" s="25" t="s">
         <v>46</v>
@@ -6197,10 +6213,10 @@
       <c r="N72" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P72" s="25" t="s">
+      <c r="O72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q72" s="26" t="s">
@@ -6224,8 +6240,8 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="56"/>
+    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="37"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6241,13 +6257,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H73" s="26" t="s">
+      <c r="H73" s="25" t="s">
         <v>104</v>
       </c>
       <c r="I73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="J73" s="25" t="s">
+      <c r="J73" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K73" s="25" t="s">
@@ -6262,11 +6278,11 @@
       <c r="N73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="P73" s="25" t="s">
-        <v>10</v>
+      <c r="O73" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P73" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="Q73" s="26" t="s">
         <v>46</v>
@@ -6289,8 +6305,8 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="56"/>
+    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="37"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6306,17 +6322,17 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H74" s="26" t="s">
-        <v>104</v>
+      <c r="H74" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="I74" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="J74" s="25" t="s">
+      <c r="J74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L74" s="25" t="s">
         <v>104</v>
@@ -6327,11 +6343,11 @@
       <c r="N74" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O74" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P74" s="25" t="s">
-        <v>104</v>
+      <c r="O74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P74" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="Q74" s="26" t="s">
         <v>104</v>
@@ -6354,8 +6370,8 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="57"/>
+    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="38"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6371,17 +6387,17 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H75" s="26" t="s">
-        <v>46</v>
+      <c r="H75" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="I75" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="J75" s="25" t="s">
+      <c r="J75" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K75" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L75" s="25" t="s">
         <v>46</v>
@@ -6392,11 +6408,11 @@
       <c r="N75" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P75" s="25" t="s">
-        <v>10</v>
+      <c r="O75" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P75" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="Q75" s="26" t="s">
         <v>10</v>
@@ -6419,30 +6435,30 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="59" t="s">
+      <c r="D76" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="34"/>
-      <c r="F76" s="35"/>
+      <c r="E76" s="43"/>
+      <c r="F76" s="44"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>109</v>
-      </c>
-      <c r="H76" s="26">
+        <v>121</v>
+      </c>
+      <c r="H76" s="25">
+        <v>186</v>
+      </c>
+      <c r="I76" s="25">
+        <v>172</v>
+      </c>
+      <c r="J76" s="26">
         <v>179</v>
       </c>
-      <c r="I76" s="25">
+      <c r="K76" s="25">
         <v>222</v>
-      </c>
-      <c r="J76" s="25">
-        <v>172</v>
-      </c>
-      <c r="K76" s="25">
-        <v>186</v>
       </c>
       <c r="L76" s="25">
         <v>190</v>
@@ -6453,11 +6469,11 @@
       <c r="N76" s="25">
         <v>197</v>
       </c>
-      <c r="O76" s="26">
+      <c r="O76" s="25">
+        <v>169</v>
+      </c>
+      <c r="P76" s="26">
         <v>185</v>
-      </c>
-      <c r="P76" s="25">
-        <v>169</v>
       </c>
       <c r="Q76" s="26">
         <v>201</v>
@@ -6480,59 +6496,59 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="60" t="s">
+      <c r="D77" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="35"/>
+      <c r="E77" s="43"/>
+      <c r="F77" s="43"/>
+      <c r="G77" s="44"/>
       <c r="H77" s="28">
         <f>SUM(H78:H81)</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I77" s="28">
         <f>SUM(I78:I81)</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J77" s="28">
         <f>SUM(J78:J81)</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K77" s="28">
         <f>SUM(K78:K81)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L77" s="28">
         <f>SUM(L78:L81)</f>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="M77" s="28">
         <f>SUM(M78:M81)</f>
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="N77" s="28">
         <f>SUM(N78:N81)</f>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O77" s="28">
         <f>SUM(O78:O81)</f>
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="P77" s="28">
         <f>SUM(P78:P81)</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Q77" s="28">
         <f>SUM(Q78:Q81)</f>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="R77" s="28">
         <f>SUM(R78:R81)</f>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="S77" s="28">
         <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
@@ -6591,7 +6607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6700,7 +6716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6714,11 +6730,11 @@
       </c>
       <c r="I79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J79" s="3">
         <f t="shared" si="5"/>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K79" s="3">
         <f t="shared" si="5"/>
@@ -6730,7 +6746,7 @@
       </c>
       <c r="M79" s="3">
         <f t="shared" si="5"/>
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="N79" s="3">
         <f t="shared" si="5"/>
@@ -6738,11 +6754,11 @@
       </c>
       <c r="O79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="P79" s="3">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Q79" s="3">
         <f t="shared" si="5"/>
@@ -6750,7 +6766,7 @@
       </c>
       <c r="R79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="S79" s="3">
         <f t="shared" si="5"/>
@@ -6809,7 +6825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6819,7 +6835,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="3">
         <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I80" s="3">
         <f t="shared" si="6"/>
@@ -6831,11 +6847,11 @@
       </c>
       <c r="K80" s="3">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L80" s="3">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="M80" s="3">
         <f t="shared" si="6"/>
@@ -6843,11 +6859,11 @@
       </c>
       <c r="N80" s="3">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O80" s="3">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P80" s="3">
         <f t="shared" si="6"/>
@@ -6855,11 +6871,11 @@
       </c>
       <c r="Q80" s="3">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="R80" s="3">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="S80" s="3">
         <f t="shared" si="6"/>
@@ -6918,7 +6934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -7027,7 +7043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7061,7 +7077,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7095,7 +7111,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7129,7 +7145,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7163,7 +7179,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7197,7 +7213,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7231,7 +7247,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7265,7 +7281,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7299,7 +7315,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7333,7 +7349,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7367,7 +7383,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7401,7 +7417,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7435,7 +7451,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7469,7 +7485,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7503,7 +7519,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7537,7 +7553,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7571,7 +7587,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7605,7 +7621,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7639,7 +7655,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7673,7 +7689,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7682,7 +7698,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7691,7 +7707,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7700,7 +7716,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7709,7 +7725,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7718,7 +7734,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7727,7 +7743,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7736,7 +7752,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7745,7 +7761,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7754,7 +7770,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7763,7 +7779,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7772,7 +7788,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7781,7 +7797,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7790,7 +7806,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7799,7 +7815,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7808,7 +7824,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7817,7 +7833,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7826,7 +7842,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7835,7 +7851,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7844,7 +7860,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7853,7 +7869,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7862,7 +7878,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7871,7 +7887,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7880,7 +7896,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7895,13 +7911,6 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7913,6 +7922,13 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -7927,14 +7943,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="15" width="11.44140625" customWidth="1"/>
+    <col min="1" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="15" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>16</v>
@@ -7981,7 +7997,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -8026,7 +8042,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -8071,7 +8087,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -8116,7 +8132,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -8161,7 +8177,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -8206,7 +8222,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -8251,7 +8267,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -8296,7 +8312,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -8341,7 +8357,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -8386,7 +8402,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -8431,7 +8447,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>16</v>
@@ -8476,7 +8492,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>16</v>
@@ -8521,7 +8537,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
@@ -8566,7 +8582,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -8611,7 +8627,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
@@ -8656,7 +8672,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>16</v>
@@ -8701,7 +8717,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
@@ -8746,7 +8762,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>16</v>
@@ -8791,7 +8807,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>16</v>
@@ -8836,7 +8852,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>16</v>
@@ -8881,7 +8897,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -8926,7 +8942,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -8971,7 +8987,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>16</v>
@@ -9016,7 +9032,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>16</v>
@@ -9061,7 +9077,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -9106,7 +9122,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>16</v>
@@ -9151,7 +9167,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>16</v>
@@ -9196,7 +9212,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>16</v>
@@ -9241,7 +9257,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>16</v>
@@ -9286,7 +9302,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>16</v>
@@ -9331,7 +9347,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>16</v>
@@ -9376,7 +9392,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>16</v>
@@ -9421,7 +9437,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>16</v>
@@ -9466,7 +9482,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>16</v>
@@ -9511,7 +9527,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>16</v>
@@ -9556,7 +9572,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>16</v>
@@ -9601,7 +9617,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>16</v>
@@ -9646,7 +9662,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>16</v>
@@ -9691,7 +9707,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>16</v>
@@ -9736,7 +9752,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>16</v>
@@ -9781,7 +9797,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>16</v>
@@ -9826,7 +9842,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>16</v>
@@ -9871,7 +9887,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>16</v>
@@ -9916,7 +9932,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>16</v>
@@ -9961,7 +9977,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>16</v>
@@ -10006,7 +10022,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>16</v>
@@ -10051,7 +10067,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>16</v>
@@ -10096,7 +10112,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>16</v>
@@ -10141,7 +10157,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>16</v>
@@ -10186,7 +10202,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>16</v>
@@ -10231,7 +10247,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>16</v>
@@ -10276,7 +10292,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>16</v>
@@ -10321,7 +10337,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>16</v>
@@ -10366,7 +10382,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>16</v>
@@ -10411,7 +10427,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>16</v>
@@ -10456,7 +10472,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>16</v>
@@ -10501,7 +10517,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>16</v>
@@ -10546,7 +10562,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>16</v>
@@ -10591,7 +10607,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>16</v>
@@ -10636,7 +10652,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>16</v>
@@ -10681,7 +10697,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>16</v>
@@ -10726,7 +10742,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>16</v>
@@ -10771,7 +10787,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>16</v>
@@ -10816,7 +10832,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>16</v>
@@ -10861,7 +10877,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>16</v>
@@ -10906,7 +10922,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>16</v>
@@ -10951,7 +10967,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>16</v>
@@ -10996,7 +11012,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>16</v>
@@ -11041,7 +11057,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>16</v>
@@ -11086,7 +11102,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>16</v>
@@ -11131,7 +11147,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>16</v>
@@ -11176,7 +11192,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>16</v>
@@ -11221,7 +11237,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>16</v>
@@ -11266,7 +11282,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>16</v>
@@ -11311,7 +11327,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>16</v>
@@ -11356,7 +11372,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>16</v>
@@ -11401,7 +11417,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>16</v>
@@ -11446,7 +11462,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>16</v>
@@ -11491,7 +11507,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>16</v>
@@ -11536,7 +11552,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>16</v>
@@ -11581,7 +11597,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>16</v>
@@ -11626,7 +11642,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>16</v>
@@ -11671,7 +11687,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>16</v>
@@ -11716,7 +11732,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>16</v>
@@ -11761,7 +11777,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>16</v>
@@ -11806,7 +11822,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>16</v>
@@ -11851,7 +11867,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>16</v>
@@ -11896,7 +11912,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>16</v>
@@ -11941,7 +11957,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>16</v>
@@ -11986,7 +12002,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>16</v>
@@ -12031,7 +12047,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>16</v>
@@ -12076,7 +12092,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>16</v>
@@ -12121,7 +12137,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>16</v>
@@ -12166,7 +12182,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>16</v>
@@ -12211,7 +12227,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>16</v>
@@ -12256,7 +12272,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>16</v>
@@ -12301,7 +12317,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>16</v>
@@ -12346,7 +12362,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>16</v>
@@ -12391,7 +12407,7 @@
         <v>SI(G28-H28=-100;0;</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12417,9 +12433,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="11" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12430,26 +12446,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" customWidth="1"/>
-    <col min="2" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="2" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="11" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -12457,61 +12473,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -12519,7 +12535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -12527,19 +12543,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -12547,19 +12563,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -12567,19 +12583,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -12587,13 +12603,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -12601,229 +12617,229 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="1"/>
     </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="1"/>
     </row>
-    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="1"/>
     </row>
-    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="1"/>
     </row>
-    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="1"/>
     </row>
-    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="1"/>
     </row>
-    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="1"/>
     </row>
-    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="1"/>
     </row>
-    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="1"/>
     </row>
-    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="1"/>
     </row>
   </sheetData>

--- a/quiniela_actualizada_2026.xlsx
+++ b/quiniela_actualizada_2026.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE6F4472-831C-4093-B49F-ED8990AE93E4}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{B808BCDA-0D93-4F95-9A36-65794598B9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16FAAD26-6334-4CB8-BE68-7A3B2D2AAEE1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="pagos" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="16os" sheetId="5" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="Hoja3" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="pagos" sheetId="4" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="118">
   <si>
     <t>GRUPOS</t>
   </si>
@@ -407,12 +408,18 @@
   <si>
     <t>Ivan</t>
   </si>
+  <si>
+    <t xml:space="preserve">LLAVE SUPERIOR </t>
+  </si>
+  <si>
+    <t>LLAVE INFERIOR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -478,6 +485,13 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="6"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="25">
@@ -626,7 +640,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -771,13 +785,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -965,13 +994,36 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CDE2DAD8-18C9-498B-94D4-DF142B136E21}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{E78B5277-1D27-424B-A76E-597236430B2A}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1288,22 +1340,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.7109375" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="5.7109375" customWidth="1"/>
-    <col min="19" max="32" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.6640625" customWidth="1"/>
+    <col min="19" max="32" width="5.6640625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
         <v>101</v>
       </c>
@@ -1389,7 +1441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="143.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
       <c r="A2" s="62" t="s">
         <v>47</v>
       </c>
@@ -1402,19 +1454,19 @@
       <c r="F2" s="65"/>
       <c r="G2" s="66"/>
       <c r="H2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="J2" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>106</v>
-      </c>
       <c r="K2" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="L2" s="29" t="s">
         <v>111</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>114</v>
       </c>
       <c r="M2" s="30" t="s">
         <v>109</v>
@@ -1449,7 +1501,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1471,47 +1523,47 @@
       </c>
       <c r="H3" s="14" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$75=H4:H75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="14" cm="1">
         <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$75=I4:I75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J3" s="14" cm="1">
         <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$75=J4:J75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K3" s="14" cm="1">
         <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$75=K4:K75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L3" s="14" cm="1">
         <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$75=L4:L75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M3" s="14" cm="1">
         <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$75=M4:M75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N3" s="14" cm="1">
         <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$75=N4:N75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O3" s="14" cm="1">
         <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$75=O4:O75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P3" s="14" cm="1">
         <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$75=P4:P75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="14" cm="1">
         <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$75=Q4:Q75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R3" s="14" cm="1">
         <f t="array" ref="R3">SUMPRODUCT(($G$4:$G$75=R4:R75)*($G$4:$G$75&lt;&gt;""))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
@@ -1570,7 +1622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="55" t="s">
         <v>6</v>
       </c>
@@ -1596,10 +1648,10 @@
       <c r="H4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="24" t="s">
+      <c r="I4" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K4" s="23" t="s">
@@ -1641,7 +1693,7 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="40"/>
       <c r="B5" s="7">
         <v>2</v>
@@ -1665,17 +1717,17 @@
       <c r="H5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="24" t="s">
+      <c r="I5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="M5" s="24" t="s">
         <v>46</v>
@@ -1710,7 +1762,7 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="40"/>
       <c r="B6" s="7">
         <v>3</v>
@@ -1734,17 +1786,17 @@
       <c r="H6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="24" t="s">
+      <c r="I6" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M6" s="24" t="s">
         <v>10</v>
@@ -1779,7 +1831,7 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="40"/>
       <c r="B7" s="7">
         <v>4</v>
@@ -1801,12 +1853,12 @@
         <v>L</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="23" t="s">
@@ -1848,7 +1900,7 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="40"/>
       <c r="B8" s="7">
         <v>5</v>
@@ -1866,13 +1918,13 @@
         <v/>
       </c>
       <c r="H8" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K8" s="23" t="s">
         <v>104</v>
@@ -1913,7 +1965,7 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="7">
         <v>6</v>
@@ -1931,19 +1983,19 @@
         <v/>
       </c>
       <c r="H9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M9" s="24" t="s">
         <v>104</v>
@@ -1978,7 +2030,7 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="60" t="s">
         <v>7</v>
       </c>
@@ -2002,19 +2054,19 @@
         <v>E</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M10" s="24" t="s">
         <v>10</v>
@@ -2049,7 +2101,7 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="40"/>
       <c r="B11" s="7">
         <v>8</v>
@@ -2071,12 +2123,12 @@
         <v>E</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J11" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K11" s="23" t="s">
@@ -2118,7 +2170,7 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="40"/>
       <c r="B12" s="7">
         <v>9</v>
@@ -2142,10 +2194,10 @@
       <c r="H12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J12" s="24" t="s">
+      <c r="I12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -2187,7 +2239,7 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="40"/>
       <c r="B13" s="7">
         <v>10</v>
@@ -2211,10 +2263,10 @@
       <c r="H13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="24" t="s">
+      <c r="I13" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K13" s="23" t="s">
@@ -2256,7 +2308,7 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="40"/>
       <c r="B14" s="7">
         <v>11</v>
@@ -2274,19 +2326,19 @@
         <v/>
       </c>
       <c r="H14" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>104</v>
@@ -2321,7 +2373,7 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="41"/>
       <c r="B15" s="7">
         <v>12</v>
@@ -2339,13 +2391,13 @@
         <v/>
       </c>
       <c r="H15" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K15" s="23" t="s">
         <v>10</v>
@@ -2386,7 +2438,7 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="61" t="s">
         <v>8</v>
       </c>
@@ -2412,17 +2464,17 @@
       <c r="H16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="24" t="s">
+      <c r="I16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M16" s="24" t="s">
         <v>46</v>
@@ -2457,7 +2509,7 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="40"/>
       <c r="B17" s="7">
         <v>14</v>
@@ -2481,10 +2533,10 @@
       <c r="H17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J17" s="24" t="s">
+      <c r="I17" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -2526,7 +2578,7 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="40"/>
       <c r="B18" s="7">
         <v>15</v>
@@ -2550,17 +2602,17 @@
       <c r="H18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" s="24" t="s">
+      <c r="I18" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="M18" s="24" t="s">
         <v>46</v>
@@ -2595,7 +2647,7 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="40"/>
       <c r="B19" s="7">
         <v>16</v>
@@ -2619,10 +2671,10 @@
       <c r="H19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="24" t="s">
+      <c r="I19" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K19" s="23" t="s">
@@ -2664,7 +2716,7 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="40"/>
       <c r="B20" s="7">
         <v>17</v>
@@ -2684,10 +2736,10 @@
       <c r="H20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J20" s="24" t="s">
+      <c r="I20" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -2729,7 +2781,7 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="41"/>
       <c r="B21" s="7">
         <v>18</v>
@@ -2749,17 +2801,17 @@
       <c r="H21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J21" s="24" t="s">
+      <c r="I21" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M21" s="24" t="s">
         <v>46</v>
@@ -2794,7 +2846,7 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="58" t="s">
         <v>9</v>
       </c>
@@ -2818,19 +2870,19 @@
         <v>L</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M22" s="24" t="s">
         <v>104</v>
@@ -2865,7 +2917,7 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
       <c r="B23" s="7">
         <v>20</v>
@@ -2887,19 +2939,19 @@
         <v>L</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M23" s="24" t="s">
         <v>10</v>
@@ -2934,7 +2986,7 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="40"/>
       <c r="B24" s="7">
         <v>21</v>
@@ -2958,17 +3010,17 @@
       <c r="H24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24" s="24" t="s">
+      <c r="I24" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="M24" s="24" t="s">
         <v>46</v>
@@ -3003,7 +3055,7 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="40"/>
       <c r="B25" s="7">
         <v>22</v>
@@ -3027,17 +3079,17 @@
       <c r="H25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="I25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J25" s="24" t="s">
+      <c r="I25" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M25" s="24" t="s">
         <v>104</v>
@@ -3072,7 +3124,7 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="40"/>
       <c r="B26" s="7">
         <v>23</v>
@@ -3092,17 +3144,17 @@
       <c r="H26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="I26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" s="24" t="s">
+      <c r="I26" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M26" s="24" t="s">
         <v>104</v>
@@ -3137,7 +3189,7 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="41"/>
       <c r="B27" s="7">
         <v>24</v>
@@ -3157,11 +3209,11 @@
       <c r="H27" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J27" s="24" t="s">
-        <v>10</v>
+      <c r="I27" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K27" s="23" t="s">
         <v>10</v>
@@ -3202,7 +3254,7 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="59" t="s">
         <v>10</v>
       </c>
@@ -3228,10 +3280,10 @@
       <c r="H28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J28" s="24" t="s">
+      <c r="I28" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -3273,7 +3325,7 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="40"/>
       <c r="B29" s="7">
         <v>26</v>
@@ -3295,13 +3347,13 @@
         <v>L</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J29" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="I29" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K29" s="23" t="s">
         <v>10</v>
@@ -3342,7 +3394,7 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="40"/>
       <c r="B30" s="7">
         <v>27</v>
@@ -3366,10 +3418,10 @@
       <c r="H30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J30" s="24" t="s">
+      <c r="I30" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -3411,7 +3463,7 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="40"/>
       <c r="B31" s="7">
         <v>28</v>
@@ -3433,19 +3485,19 @@
         <v>E</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J31" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="I31" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K31" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M31" s="24" t="s">
         <v>46</v>
@@ -3480,7 +3532,7 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="40"/>
       <c r="B32" s="7">
         <v>29</v>
@@ -3500,17 +3552,17 @@
       <c r="H32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J32" s="24" t="s">
-        <v>10</v>
+      <c r="I32" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K32" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M32" s="24" t="s">
         <v>10</v>
@@ -3545,7 +3597,7 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="41"/>
       <c r="B33" s="7">
         <v>30</v>
@@ -3563,12 +3615,12 @@
         <v/>
       </c>
       <c r="H33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J33" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K33" s="23" t="s">
@@ -3610,7 +3662,7 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="57" t="s">
         <v>11</v>
       </c>
@@ -3634,19 +3686,19 @@
         <v>E</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J34" s="24" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K34" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="M34" s="24" t="s">
         <v>104</v>
@@ -3681,7 +3733,7 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="40"/>
       <c r="B35" s="7">
         <v>32</v>
@@ -3705,10 +3757,10 @@
       <c r="H35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J35" s="24" t="s">
+      <c r="I35" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K35" s="23" t="s">
@@ -3750,7 +3802,7 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="40"/>
       <c r="B36" s="7">
         <v>33</v>
@@ -3774,10 +3826,10 @@
       <c r="H36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J36" s="24" t="s">
+      <c r="I36" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J36" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -3819,7 +3871,7 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="40"/>
       <c r="B37" s="7">
         <v>34</v>
@@ -3843,10 +3895,10 @@
       <c r="H37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J37" s="24" t="s">
+      <c r="I37" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="23" t="s">
@@ -3888,7 +3940,7 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="40"/>
       <c r="B38" s="7">
         <v>35</v>
@@ -3906,19 +3958,19 @@
         <v/>
       </c>
       <c r="H38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J38" s="24" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M38" s="24" t="s">
         <v>104</v>
@@ -3953,7 +4005,7 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="41"/>
       <c r="B39" s="7">
         <v>36</v>
@@ -3971,13 +4023,13 @@
         <v/>
       </c>
       <c r="H39" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J39" s="24" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K39" s="23" t="s">
         <v>104</v>
@@ -4018,7 +4070,7 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="56" t="s">
         <v>12</v>
       </c>
@@ -4042,13 +4094,13 @@
         <v>E</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J40" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J40" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K40" s="23" t="s">
         <v>46</v>
@@ -4089,7 +4141,7 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="40"/>
       <c r="B41" s="7">
         <v>38</v>
@@ -4111,13 +4163,13 @@
         <v>E</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J41" s="24" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J41" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K41" s="23" t="s">
         <v>10</v>
@@ -4158,7 +4210,7 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="40"/>
       <c r="B42" s="7">
         <v>39</v>
@@ -4180,13 +4232,13 @@
         <v>E</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I42" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="K42" s="23" t="s">
         <v>46</v>
@@ -4227,7 +4279,7 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="40"/>
       <c r="B43" s="7">
         <v>40</v>
@@ -4251,17 +4303,17 @@
       <c r="H43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J43" s="24" t="s">
-        <v>10</v>
+      <c r="I43" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K43" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M43" s="24" t="s">
         <v>10</v>
@@ -4296,7 +4348,7 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="40"/>
       <c r="B44" s="7">
         <v>41</v>
@@ -4314,19 +4366,19 @@
         <v/>
       </c>
       <c r="H44" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I44" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J44" s="24" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I44" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M44" s="24" t="s">
         <v>10</v>
@@ -4361,7 +4413,7 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="41"/>
       <c r="B45" s="7">
         <v>42</v>
@@ -4381,10 +4433,10 @@
       <c r="H45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J45" s="24" t="s">
+      <c r="I45" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K45" s="23" t="s">
@@ -4426,7 +4478,7 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="39" t="s">
         <v>13</v>
       </c>
@@ -4452,10 +4504,10 @@
       <c r="H46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J46" s="24" t="s">
+      <c r="I46" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K46" s="23" t="s">
@@ -4497,7 +4549,7 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="40"/>
       <c r="B47" s="7">
         <v>44</v>
@@ -4521,17 +4573,17 @@
       <c r="H47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J47" s="24" t="s">
+      <c r="I47" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="K47" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M47" s="24" t="s">
         <v>104</v>
@@ -4566,7 +4618,7 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="40"/>
       <c r="B48" s="7">
         <v>45</v>
@@ -4590,10 +4642,10 @@
       <c r="H48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J48" s="24" t="s">
+      <c r="I48" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="K48" s="23" t="s">
@@ -4635,7 +4687,7 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="40"/>
       <c r="B49" s="7">
         <v>46</v>
@@ -4657,13 +4709,13 @@
         <v>E</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J49" s="24" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J49" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K49" s="23" t="s">
         <v>46</v>
@@ -4704,7 +4756,7 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="40"/>
       <c r="B50" s="7">
         <v>47</v>
@@ -4722,19 +4774,19 @@
         <v/>
       </c>
       <c r="H50" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J50" s="24" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="I50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J50" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K50" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L50" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M50" s="24" t="s">
         <v>104</v>
@@ -4769,7 +4821,7 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="41"/>
       <c r="B51" s="7">
         <v>48</v>
@@ -4789,11 +4841,11 @@
       <c r="H51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="I51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J51" s="24" t="s">
-        <v>10</v>
+      <c r="I51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="K51" s="23" t="s">
         <v>104</v>
@@ -4834,7 +4886,7 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="46" t="s">
         <v>77</v>
       </c>
@@ -4858,13 +4910,13 @@
         <v>L</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J52" s="26" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I52" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J52" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K52" s="25" t="s">
         <v>46</v>
@@ -4905,7 +4957,7 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="47"/>
       <c r="B53" s="7">
         <v>50</v>
@@ -4929,11 +4981,11 @@
       <c r="H53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="I53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J53" s="26" t="s">
-        <v>10</v>
+      <c r="I53" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J53" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K53" s="25" t="s">
         <v>104</v>
@@ -4974,7 +5026,7 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="47"/>
       <c r="B54" s="7">
         <v>51</v>
@@ -4985,19 +5037,23 @@
       <c r="D54" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
+      <c r="E54" s="15">
+        <v>3</v>
+      </c>
+      <c r="F54" s="15">
+        <v>0</v>
+      </c>
       <c r="G54" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="H54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J54" s="26" t="s">
+      <c r="I54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K54" s="25" t="s">
@@ -5039,7 +5095,7 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="47"/>
       <c r="B55" s="7">
         <v>52</v>
@@ -5050,26 +5106,30 @@
       <c r="D55" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
+      <c r="E55" s="15">
+        <v>3</v>
+      </c>
+      <c r="F55" s="15">
+        <v>2</v>
+      </c>
       <c r="G55" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="H55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I55" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J55" s="26" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I55" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J55" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K55" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L55" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M55" s="26" t="s">
         <v>46</v>
@@ -5105,7 +5165,7 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="47"/>
       <c r="B56" s="7">
         <v>53</v>
@@ -5123,19 +5183,19 @@
         <v/>
       </c>
       <c r="H56" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J56" s="26" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="I56" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J56" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L56" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="M56" s="26" t="s">
         <v>10</v>
@@ -5170,7 +5230,7 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="48"/>
       <c r="B57" s="7">
         <v>54</v>
@@ -5190,11 +5250,11 @@
       <c r="H57" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I57" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J57" s="26" t="s">
-        <v>10</v>
+      <c r="I57" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J57" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K57" s="25" t="s">
         <v>10</v>
@@ -5235,7 +5295,7 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="49" t="s">
         <v>78</v>
       </c>
@@ -5259,13 +5319,13 @@
         <v>L</v>
       </c>
       <c r="H58" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J58" s="26" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I58" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J58" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K58" s="25" t="s">
         <v>46</v>
@@ -5306,7 +5366,7 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="50"/>
       <c r="B59" s="7">
         <v>56</v>
@@ -5330,17 +5390,17 @@
       <c r="H59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J59" s="26" t="s">
+      <c r="I59" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J59" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K59" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L59" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M59" s="26" t="s">
         <v>46</v>
@@ -5375,7 +5435,7 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="50"/>
       <c r="B60" s="7">
         <v>57</v>
@@ -5386,19 +5446,23 @@
       <c r="D60" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
+      <c r="E60" s="16">
+        <v>2</v>
+      </c>
+      <c r="F60" s="16">
+        <v>0</v>
+      </c>
       <c r="G60" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="H60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J60" s="26" t="s">
+      <c r="I60" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J60" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K60" s="25" t="s">
@@ -5440,7 +5504,7 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="50"/>
       <c r="B61" s="7">
         <v>58</v>
@@ -5458,19 +5522,19 @@
         <v/>
       </c>
       <c r="H61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I61" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J61" s="26" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="I61" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J61" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L61" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M61" s="26" t="s">
         <v>46</v>
@@ -5505,7 +5569,7 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="50"/>
       <c r="B62" s="7">
         <v>59</v>
@@ -5523,19 +5587,19 @@
         <v/>
       </c>
       <c r="H62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J62" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I62" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J62" s="25" t="s">
         <v>10</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="L62" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="M62" s="26" t="s">
         <v>104</v>
@@ -5570,7 +5634,7 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="51"/>
       <c r="B63" s="7">
         <v>60</v>
@@ -5590,10 +5654,10 @@
       <c r="H63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="I63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J63" s="26" t="s">
+      <c r="I63" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K63" s="25" t="s">
@@ -5635,7 +5699,7 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="33" t="s">
         <v>79</v>
       </c>
@@ -5661,10 +5725,10 @@
       <c r="H64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J64" s="26" t="s">
+      <c r="I64" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K64" s="25" t="s">
@@ -5706,7 +5770,7 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="34"/>
       <c r="B65" s="7">
         <v>62</v>
@@ -5730,10 +5794,10 @@
       <c r="H65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="I65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J65" s="26" t="s">
+      <c r="I65" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K65" s="25" t="s">
@@ -5775,7 +5839,7 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="34"/>
       <c r="B66" s="7">
         <v>63</v>
@@ -5795,10 +5859,10 @@
       <c r="H66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J66" s="26" t="s">
+      <c r="I66" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K66" s="25" t="s">
@@ -5840,7 +5904,7 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="34"/>
       <c r="B67" s="7">
         <v>64</v>
@@ -5860,17 +5924,17 @@
       <c r="H67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J67" s="26" t="s">
+      <c r="I67" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J67" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K67" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="L67" s="25" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="M67" s="26" t="s">
         <v>46</v>
@@ -5905,7 +5969,7 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="34"/>
       <c r="B68" s="7">
         <v>65</v>
@@ -5923,19 +5987,19 @@
         <v/>
       </c>
       <c r="H68" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I68" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J68" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I68" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J68" s="25" t="s">
         <v>10</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="L68" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="M68" s="26" t="s">
         <v>104</v>
@@ -5970,7 +6034,7 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="35"/>
       <c r="B69" s="7">
         <v>66</v>
@@ -5988,19 +6052,19 @@
         <v/>
       </c>
       <c r="H69" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J69" s="26" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="I69" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J69" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="L69" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M69" s="26" t="s">
         <v>104</v>
@@ -6035,7 +6099,7 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="36" t="s">
         <v>46</v>
       </c>
@@ -6059,19 +6123,19 @@
         <v>L</v>
       </c>
       <c r="H70" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J70" s="26" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="I70" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J70" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L70" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M70" s="26" t="s">
         <v>104</v>
@@ -6106,7 +6170,7 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="37"/>
       <c r="B71" s="7">
         <v>68</v>
@@ -6128,12 +6192,12 @@
         <v>L</v>
       </c>
       <c r="H71" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J71" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I71" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J71" s="25" t="s">
         <v>46</v>
       </c>
       <c r="K71" s="25" t="s">
@@ -6175,7 +6239,7 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="37"/>
       <c r="B72" s="7">
         <v>69</v>
@@ -6193,13 +6257,13 @@
         <v/>
       </c>
       <c r="H72" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J72" s="26" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I72" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J72" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K72" s="25" t="s">
         <v>46</v>
@@ -6240,7 +6304,7 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="37"/>
       <c r="B73" s="7">
         <v>70</v>
@@ -6260,10 +6324,10 @@
       <c r="H73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="I73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J73" s="26" t="s">
+      <c r="I73" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J73" s="25" t="s">
         <v>104</v>
       </c>
       <c r="K73" s="25" t="s">
@@ -6305,7 +6369,7 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="37"/>
       <c r="B74" s="7">
         <v>71</v>
@@ -6323,13 +6387,13 @@
         <v/>
       </c>
       <c r="H74" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J74" s="26" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="I74" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J74" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="K74" s="25" t="s">
         <v>104</v>
@@ -6370,7 +6434,7 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="38"/>
       <c r="B75" s="7">
         <v>72</v>
@@ -6388,13 +6452,13 @@
         <v/>
       </c>
       <c r="H75" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J75" s="26" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="I75" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J75" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="K75" s="25" t="s">
         <v>46</v>
@@ -6435,7 +6499,7 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
@@ -6446,22 +6510,22 @@
       <c r="F76" s="44"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H76" s="25">
+        <v>172</v>
+      </c>
+      <c r="I76" s="26">
+        <v>179</v>
+      </c>
+      <c r="J76" s="25">
         <v>186</v>
       </c>
-      <c r="I76" s="25">
-        <v>172</v>
-      </c>
-      <c r="J76" s="26">
-        <v>179</v>
-      </c>
       <c r="K76" s="25">
+        <v>190</v>
+      </c>
+      <c r="L76" s="25">
         <v>222</v>
-      </c>
-      <c r="L76" s="25">
-        <v>190</v>
       </c>
       <c r="M76" s="26">
         <v>162</v>
@@ -6496,7 +6560,7 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
@@ -6508,47 +6572,47 @@
       <c r="G77" s="44"/>
       <c r="H77" s="28">
         <f>SUM(H78:H81)</f>
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="I77" s="28">
         <f>SUM(I78:I81)</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J77" s="28">
         <f>SUM(J78:J81)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K77" s="28">
         <f>SUM(K78:K81)</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L77" s="28">
         <f>SUM(L78:L81)</f>
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="M77" s="28">
         <f>SUM(M78:M81)</f>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="N77" s="28">
         <f>SUM(N78:N81)</f>
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O77" s="28">
         <f>SUM(O78:O81)</f>
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="P77" s="28">
         <f>SUM(P78:P81)</f>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q77" s="28">
         <f>SUM(Q78:Q81)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R77" s="28">
         <f>SUM(R78:R81)</f>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="S77" s="28">
         <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
@@ -6607,7 +6671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6637,7 +6701,7 @@
       </c>
       <c r="M78" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N78" s="3">
         <f t="shared" si="4"/>
@@ -6716,7 +6780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6726,19 +6790,19 @@
       <c r="G79" s="1"/>
       <c r="H79" s="3">
         <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I79" s="3">
         <f t="shared" si="5"/>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J79" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L79" s="3">
         <f t="shared" si="5"/>
@@ -6746,7 +6810,7 @@
       </c>
       <c r="M79" s="3">
         <f t="shared" si="5"/>
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="N79" s="3">
         <f t="shared" si="5"/>
@@ -6754,11 +6818,11 @@
       </c>
       <c r="O79" s="3">
         <f t="shared" si="5"/>
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="P79" s="3">
         <f t="shared" si="5"/>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q79" s="3">
         <f t="shared" si="5"/>
@@ -6766,7 +6830,7 @@
       </c>
       <c r="R79" s="3">
         <f t="shared" si="5"/>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="S79" s="3">
         <f t="shared" si="5"/>
@@ -6825,7 +6889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6835,7 +6899,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="3">
         <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I80" s="3">
         <f t="shared" si="6"/>
@@ -6851,7 +6915,7 @@
       </c>
       <c r="L80" s="3">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="M80" s="3">
         <f t="shared" si="6"/>
@@ -6859,7 +6923,7 @@
       </c>
       <c r="N80" s="3">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O80" s="3">
         <f t="shared" si="6"/>
@@ -6871,7 +6935,7 @@
       </c>
       <c r="Q80" s="3">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R80" s="3">
         <f t="shared" si="6"/>
@@ -6934,7 +6998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -7043,7 +7107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7077,7 +7141,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7111,7 +7175,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7145,7 +7209,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7179,7 +7243,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7213,7 +7277,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7247,7 +7311,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7281,7 +7345,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7315,7 +7379,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7349,7 +7413,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7383,7 +7447,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7417,7 +7481,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7451,7 +7515,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7485,7 +7549,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7519,7 +7583,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7553,7 +7617,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7587,7 +7651,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7621,7 +7685,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7655,7 +7719,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7689,7 +7753,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7698,7 +7762,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7707,7 +7771,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7716,7 +7780,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7725,7 +7789,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7734,7 +7798,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7743,7 +7807,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7752,7 +7816,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7761,7 +7825,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7770,7 +7834,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7779,7 +7843,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7788,7 +7852,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7797,7 +7861,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7806,7 +7870,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7815,7 +7879,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7824,7 +7888,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7833,7 +7897,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7842,7 +7906,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7851,7 +7915,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7860,7 +7924,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7869,7 +7933,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7878,7 +7942,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7887,7 +7951,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7896,7 +7960,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7931,6 +7995,2388 @@
     <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>MAX($H$3:$AF$3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
+  <pageSetup scale="90" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24305812-5E9F-41C6-A63E-58E236EADEB5}">
+  <dimension ref="A1:AF68"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.6640625" customWidth="1"/>
+    <col min="19" max="32" width="5.6640625" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="19">
+        <v>1</v>
+      </c>
+      <c r="I1" s="19">
+        <v>2</v>
+      </c>
+      <c r="J1" s="19">
+        <v>3</v>
+      </c>
+      <c r="K1" s="32">
+        <v>4</v>
+      </c>
+      <c r="L1" s="32">
+        <v>5</v>
+      </c>
+      <c r="M1" s="32">
+        <v>6</v>
+      </c>
+      <c r="N1" s="32">
+        <v>7</v>
+      </c>
+      <c r="O1" s="32">
+        <v>8</v>
+      </c>
+      <c r="P1" s="32">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="32">
+        <v>10</v>
+      </c>
+      <c r="R1" s="32">
+        <v>11</v>
+      </c>
+      <c r="S1" s="20">
+        <v>12</v>
+      </c>
+      <c r="T1" s="20">
+        <v>13</v>
+      </c>
+      <c r="U1" s="20">
+        <v>14</v>
+      </c>
+      <c r="V1" s="20">
+        <v>15</v>
+      </c>
+      <c r="W1" s="20">
+        <v>16</v>
+      </c>
+      <c r="X1" s="20">
+        <v>17</v>
+      </c>
+      <c r="Y1" s="20">
+        <v>18</v>
+      </c>
+      <c r="Z1" s="20">
+        <v>19</v>
+      </c>
+      <c r="AA1" s="20">
+        <v>20</v>
+      </c>
+      <c r="AB1" s="20">
+        <v>21</v>
+      </c>
+      <c r="AC1" s="20">
+        <v>22</v>
+      </c>
+      <c r="AD1" s="20">
+        <v>23</v>
+      </c>
+      <c r="AE1" s="20">
+        <v>24</v>
+      </c>
+      <c r="AF1" s="21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="141.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="O2" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+    </row>
+    <row r="3" spans="1:32" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="54"/>
+      <c r="G3" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="14" cm="1">
+        <f t="array" ref="H3">SUMPRODUCT(($G$4:$G$19=H4:H19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="14" cm="1">
+        <f t="array" ref="I3">SUMPRODUCT(($G$4:$G$19=I4:I19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="14" cm="1">
+        <f t="array" ref="J3">SUMPRODUCT(($G$4:$G$19=J4:J19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="14" cm="1">
+        <f t="array" ref="K3">SUMPRODUCT(($G$4:$G$19=K4:K19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="14" cm="1">
+        <f t="array" ref="L3">SUMPRODUCT(($G$4:$G$19=L4:L19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="14" cm="1">
+        <f t="array" ref="M3">SUMPRODUCT(($G$4:$G$19=M4:M19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="14" cm="1">
+        <f t="array" ref="N3">SUMPRODUCT(($G$4:$G$19=N4:N19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="14" cm="1">
+        <f t="array" ref="O3">SUMPRODUCT(($G$4:$G$19=O4:O19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="14" cm="1">
+        <f t="array" ref="P3">SUMPRODUCT(($G$4:$G$19=P4:P19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="14" cm="1">
+        <f t="array" ref="Q3">SUMPRODUCT(($G$4:$G$19=Q4:Q19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="14" cm="1">
+        <f t="array" ref="R3">SUMPRODUCT(($G$4:$G$19=R4:R19)*($G$4:$G$19&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="14" t="e">
+        <f>SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T3" s="14" t="e">
+        <f>SUM(IF(T4=$G$4,1,0)+IF(T5=$G$5,1,0)+IF(T6=$G$6,1,0)+IF(T7=$G$7,1,0)+IF(T8=$G$8,1,0)+IF(T9=$G$9,1,0)+IF(T10=$G$10,1,0)+IF(T11=$G$11,1,0)+IF(T12=$G$12,1,0)+IF(T13=$G$13,1,0)+IF(T14=$G$14,1,0)+IF(T19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U3" s="14" t="e">
+        <f>SUM(IF(U4=$G$4,1,0)+IF(U5=$G$5,1,0)+IF(U6=$G$6,1,0)+IF(U7=$G$7,1,0)+IF(U8=$G$8,1,0)+IF(U9=$G$9,1,0)+IF(U10=$G$10,1,0)+IF(U11=$G$11,1,0)+IF(U12=$G$12,1,0)+IF(U13=$G$13,1,0)+IF(U14=$G$14,1,0)+IF(U19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V3" s="14" t="e">
+        <f>SUM(IF(V4=$G$4,1,0)+IF(V5=$G$5,1,0)+IF(V6=$G$6,1,0)+IF(V7=$G$7,1,0)+IF(V8=$G$8,1,0)+IF(V9=$G$9,1,0)+IF(V10=$G$10,1,0)+IF(V11=$G$11,1,0)+IF(V12=$G$12,1,0)+IF(V13=$G$13,1,0)+IF(V14=$G$14,1,0)+IF(V19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W3" s="14" t="e">
+        <f>SUM(IF(W4=$G$4,1,0)+IF(W5=$G$5,1,0)+IF(W6=$G$6,1,0)+IF(W7=$G$7,1,0)+IF(W8=$G$8,1,0)+IF(W9=$G$9,1,0)+IF(W10=$G$10,1,0)+IF(W11=$G$11,1,0)+IF(W12=$G$12,1,0)+IF(W13=$G$13,1,0)+IF(W14=$G$14,1,0)+IF(W19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X3" s="14" t="e">
+        <f>SUM(IF(X4=$G$4,1,0)+IF(X5=$G$5,1,0)+IF(X6=$G$6,1,0)+IF(X7=$G$7,1,0)+IF(X8=$G$8,1,0)+IF(X9=$G$9,1,0)+IF(X10=$G$10,1,0)+IF(X11=$G$11,1,0)+IF(X12=$G$12,1,0)+IF(X13=$G$13,1,0)+IF(X14=$G$14,1,0)+IF(X19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y3" s="14" t="e">
+        <f>SUM(IF(Y4=$G$4,1,0)+IF(Y5=$G$5,1,0)+IF(Y6=$G$6,1,0)+IF(Y7=$G$7,1,0)+IF(Y8=$G$8,1,0)+IF(Y9=$G$9,1,0)+IF(Y10=$G$10,1,0)+IF(Y11=$G$11,1,0)+IF(Y12=$G$12,1,0)+IF(Y13=$G$13,1,0)+IF(Y14=$G$14,1,0)+IF(Y19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Z3" s="14" t="e">
+        <f>SUM(IF(Z4=$G$4,1,0)+IF(Z5=$G$5,1,0)+IF(Z6=$G$6,1,0)+IF(Z7=$G$7,1,0)+IF(Z8=$G$8,1,0)+IF(Z9=$G$9,1,0)+IF(Z10=$G$10,1,0)+IF(Z11=$G$11,1,0)+IF(Z12=$G$12,1,0)+IF(Z13=$G$13,1,0)+IF(Z14=$G$14,1,0)+IF(Z19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA3" s="14" t="e">
+        <f>SUM(IF(AA4=$G$4,1,0)+IF(AA5=$G$5,1,0)+IF(AA6=$G$6,1,0)+IF(AA7=$G$7,1,0)+IF(AA8=$G$8,1,0)+IF(AA9=$G$9,1,0)+IF(AA10=$G$10,1,0)+IF(AA11=$G$11,1,0)+IF(AA12=$G$12,1,0)+IF(AA13=$G$13,1,0)+IF(AA14=$G$14,1,0)+IF(AA19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB3" s="14" t="e">
+        <f>SUM(IF(AB4=$G$4,1,0)+IF(AB5=$G$5,1,0)+IF(AB6=$G$6,1,0)+IF(AB7=$G$7,1,0)+IF(AB8=$G$8,1,0)+IF(AB9=$G$9,1,0)+IF(AB10=$G$10,1,0)+IF(AB11=$G$11,1,0)+IF(AB12=$G$12,1,0)+IF(AB13=$G$13,1,0)+IF(AB14=$G$14,1,0)+IF(AB19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AC3" s="14" t="e">
+        <f>SUM(IF(AC4=$G$4,1,0)+IF(AC5=$G$5,1,0)+IF(AC6=$G$6,1,0)+IF(AC7=$G$7,1,0)+IF(AC8=$G$8,1,0)+IF(AC9=$G$9,1,0)+IF(AC10=$G$10,1,0)+IF(AC11=$G$11,1,0)+IF(AC12=$G$12,1,0)+IF(AC13=$G$13,1,0)+IF(AC14=$G$14,1,0)+IF(AC19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AD3" s="14" t="e">
+        <f>SUM(IF(AD4=$G$4,1,0)+IF(AD5=$G$5,1,0)+IF(AD6=$G$6,1,0)+IF(AD7=$G$7,1,0)+IF(AD8=$G$8,1,0)+IF(AD9=$G$9,1,0)+IF(AD10=$G$10,1,0)+IF(AD11=$G$11,1,0)+IF(AD12=$G$12,1,0)+IF(AD13=$G$13,1,0)+IF(AD14=$G$14,1,0)+IF(AD19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AE3" s="14" t="e">
+        <f>SUM(IF(AE4=$G$4,1,0)+IF(AE5=$G$5,1,0)+IF(AE6=$G$6,1,0)+IF(AE7=$G$7,1,0)+IF(AE8=$G$8,1,0)+IF(AE9=$G$9,1,0)+IF(AE10=$G$10,1,0)+IF(AE11=$G$11,1,0)+IF(AE12=$G$12,1,0)+IF(AE13=$G$13,1,0)+IF(AE14=$G$14,1,0)+IF(AE19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AF3" s="14" t="e">
+        <f>SUM(IF(AF4=$G$4,1,0)+IF(AF5=$G$5,1,0)+IF(AF6=$G$6,1,0)+IF(AF7=$G$7,1,0)+IF(AF8=$G$8,1,0)+IF(AF9=$G$9,1,0)+IF(AF10=$G$10,1,0)+IF(AF11=$G$11,1,0)+IF(AF12=$G$12,1,0)+IF(AF13=$G$13,1,0)+IF(AF14=$G$14,1,0)+IF(AF19=$G$19,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0)+IF(#REF!=#REF!,1,0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="70" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="68">
+        <v>1</v>
+      </c>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69" t="str">
+        <f>IF(OR(E4="",F4=""),"",IF(E4&gt;F4,"L",IF(E4&lt;F4,"V","E")))</f>
+        <v/>
+      </c>
+      <c r="H4" s="23"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="23"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="23"/>
+      <c r="AC4" s="23"/>
+      <c r="AD4" s="23"/>
+      <c r="AE4" s="23"/>
+      <c r="AF4" s="23"/>
+    </row>
+    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="70"/>
+      <c r="B5" s="68">
+        <v>2</v>
+      </c>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69" t="str">
+        <f t="shared" ref="G5:G19" si="0">IF(OR(E5="",F5=""),"",IF(E5&gt;F5,"L",IF(E5&lt;F5,"V","E")))</f>
+        <v/>
+      </c>
+      <c r="H5" s="23"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="23"/>
+    </row>
+    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="70"/>
+      <c r="B6" s="68">
+        <v>3</v>
+      </c>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H6" s="23"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="23"/>
+      <c r="W6" s="23"/>
+      <c r="X6" s="23"/>
+      <c r="Y6" s="23"/>
+      <c r="Z6" s="23"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="23"/>
+      <c r="AC6" s="23"/>
+      <c r="AD6" s="23"/>
+      <c r="AE6" s="23"/>
+      <c r="AF6" s="23"/>
+    </row>
+    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="70"/>
+      <c r="B7" s="68">
+        <v>4</v>
+      </c>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H7" s="23"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="23"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="23"/>
+      <c r="Y7" s="23"/>
+      <c r="Z7" s="23"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="23"/>
+      <c r="AD7" s="23"/>
+      <c r="AE7" s="23"/>
+      <c r="AF7" s="23"/>
+    </row>
+    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="70"/>
+      <c r="B8" s="68">
+        <v>5</v>
+      </c>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H8" s="23"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="23"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="23"/>
+    </row>
+    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="70"/>
+      <c r="B9" s="68">
+        <v>6</v>
+      </c>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H9" s="23"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
+      <c r="AE9" s="23"/>
+      <c r="AF9" s="23"/>
+    </row>
+    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="70"/>
+      <c r="B10" s="68">
+        <v>7</v>
+      </c>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H10" s="23"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="23"/>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="23"/>
+      <c r="AC10" s="23"/>
+      <c r="AD10" s="23"/>
+      <c r="AE10" s="23"/>
+      <c r="AF10" s="23"/>
+    </row>
+    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="70"/>
+      <c r="B11" s="68">
+        <v>8</v>
+      </c>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="23"/>
+      <c r="V11" s="23"/>
+      <c r="W11" s="23"/>
+      <c r="X11" s="23"/>
+      <c r="Y11" s="23"/>
+      <c r="Z11" s="23"/>
+      <c r="AA11" s="23"/>
+      <c r="AB11" s="23"/>
+      <c r="AC11" s="23"/>
+      <c r="AD11" s="23"/>
+      <c r="AE11" s="23"/>
+      <c r="AF11" s="23"/>
+    </row>
+    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="68">
+        <v>9</v>
+      </c>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H12" s="23"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+      <c r="AC12" s="23"/>
+      <c r="AD12" s="23"/>
+      <c r="AE12" s="23"/>
+      <c r="AF12" s="23"/>
+    </row>
+    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="70"/>
+      <c r="B13" s="68">
+        <v>10</v>
+      </c>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H13" s="23"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="23"/>
+      <c r="X13" s="23"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="23"/>
+      <c r="AD13" s="23"/>
+      <c r="AE13" s="23"/>
+      <c r="AF13" s="23"/>
+    </row>
+    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="70"/>
+      <c r="B14" s="68">
+        <v>11</v>
+      </c>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H14" s="23"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+    </row>
+    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="70"/>
+      <c r="B15" s="68">
+        <v>12</v>
+      </c>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H15" s="23"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="23"/>
+      <c r="AD15" s="23"/>
+      <c r="AE15" s="23"/>
+      <c r="AF15" s="23"/>
+    </row>
+    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="70"/>
+      <c r="B16" s="68">
+        <v>13</v>
+      </c>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H16" s="23"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="23"/>
+      <c r="AC16" s="23"/>
+      <c r="AD16" s="23"/>
+      <c r="AE16" s="23"/>
+      <c r="AF16" s="23"/>
+    </row>
+    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
+      <c r="B17" s="68">
+        <v>14</v>
+      </c>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H17" s="23"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
+      <c r="AA17" s="23"/>
+      <c r="AB17" s="23"/>
+      <c r="AC17" s="23"/>
+      <c r="AD17" s="23"/>
+      <c r="AE17" s="23"/>
+      <c r="AF17" s="23"/>
+    </row>
+    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="70"/>
+      <c r="B18" s="68">
+        <v>15</v>
+      </c>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H18" s="23"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="23"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="23"/>
+      <c r="AD18" s="23"/>
+      <c r="AE18" s="23"/>
+      <c r="AF18" s="23"/>
+    </row>
+    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="70"/>
+      <c r="B19" s="68">
+        <v>16</v>
+      </c>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H19" s="23"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="23"/>
+      <c r="W19" s="23"/>
+      <c r="X19" s="23"/>
+      <c r="Y19" s="23"/>
+      <c r="Z19" s="23"/>
+      <c r="AA19" s="23"/>
+      <c r="AB19" s="23"/>
+      <c r="AC19" s="23"/>
+      <c r="AD19" s="23"/>
+      <c r="AE19" s="23"/>
+      <c r="AF19" s="23"/>
+    </row>
+    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="43"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="2">
+        <f>SUM(E4:F19)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="25"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
+    </row>
+    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="27"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="28">
+        <f>SUM(H22:H25)</f>
+        <v>100</v>
+      </c>
+      <c r="I21" s="28">
+        <f>SUM(I22:I25)</f>
+        <v>100</v>
+      </c>
+      <c r="J21" s="28">
+        <f>SUM(J22:J25)</f>
+        <v>100</v>
+      </c>
+      <c r="K21" s="28">
+        <f>SUM(K22:K25)</f>
+        <v>100</v>
+      </c>
+      <c r="L21" s="28">
+        <f>SUM(L22:L25)</f>
+        <v>100</v>
+      </c>
+      <c r="M21" s="28">
+        <f>SUM(M22:M25)</f>
+        <v>100</v>
+      </c>
+      <c r="N21" s="28">
+        <f>SUM(N22:N25)</f>
+        <v>100</v>
+      </c>
+      <c r="O21" s="28">
+        <f>SUM(O22:O25)</f>
+        <v>100</v>
+      </c>
+      <c r="P21" s="28">
+        <f>SUM(P22:P25)</f>
+        <v>100</v>
+      </c>
+      <c r="Q21" s="28">
+        <f>SUM(Q22:Q25)</f>
+        <v>100</v>
+      </c>
+      <c r="R21" s="28">
+        <f>SUM(R22:R25)</f>
+        <v>100</v>
+      </c>
+      <c r="S21" s="28">
+        <f t="shared" ref="S21:AF21" si="1">SUM(S22:S25)</f>
+        <v>100</v>
+      </c>
+      <c r="T21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="U21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="V21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="W21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="X21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Y21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Z21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="AA21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="AB21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="AC21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="AD21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="AE21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="AF21" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="3">
+        <f t="shared" ref="H22:AF22" si="2">IF(H20=$G$20,100,IF($G$20-H20=1,99,IF($G$20-H20=-1,99,IF($G$20-H20=2,98,IF($G$20-H20=-2,98,IF($G$20-H20=3,97,IF($G$20-H20=-3,97,IF($G$20-H20=4,96,IF($G$20-H20=-4,96,IF($G$20-H20=5,95,IF($G$20-H20=-5,95,IF($G$20-H20=6,94,IF($G$20-H20=-6,94,IF($G$20-H20=7,93,IF($G$20-H20=-7,93,IF($G$20-H20=8,92,IF($G$20-H20=-8,92,IF($G$20-H20=9,91,IF($G$20-H20=-9,91,IF($G$20-H20=10,90,IF($G$20-H20=-10,90,IF($G$20-H20=11,89,IF($G$20-H20=-11,89,IF($G$20-H20=12,88,IF($G$20-H20=-12,88,IF($G$20-H20=13,87,IF($G$20-H20=-13,87,IF($G$20-H20=14,86,IF($G$20-H20=-14,86,IF($G$20-H20=15,85,IF($G$20-H20=-15,85,IF($G$20-H20=16,84,IF($G$20-H20=-16,84,IF($G$20-H20=17,83,IF($G$20-H20=-17,83,IF($G$20-H20=18,82,IF($G$20-H20=-18,82,IF($G$20-H20=19,81,IF($G$20-H20=-19,81,IF($G$20-H20=20,80,IF($G$20-H20=-20,80,IF($G$20-H20=21,79,IF($G$20-H20=-21,79,IF($G$20-H20=22,78,IF($G$20-H20=-22,78,IF($G$20-H20=23,77,IF($G$20-H20=-23,77,IF($G$20-H20=24,76,IF($G$20-H20=-24,76,IF($G$20-H20=25,75,IF($G$20-H20=-25,75,IF($G$20-H20=26,74,IF($G$20-H20=-26,74,IF($G$20-H20=27,73,IF($G$20-H20=-27,73,IF($G$20-H20=28,72,IF($G$20-H20=-28,72,IF($G$20-H20=29,71,IF($G$20-H20=-29,71,IF($G$20-H20=30,70,IF($G$20-H20=-30,70,IF($G$20-H20=31,69,IF($G$20-H20=-31,69,IF($G$20-H20=32,68,IF($G$20-H20=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
+        <f>IF(I20=$G$20,100,IF($G$20-I20=1,99,IF($G$20-I20=-1,99,IF($G$20-I20=2,98,IF($G$20-I20=-2,98,IF($G$20-I20=3,97,IF($G$20-I20=-3,97,IF($G$20-I20=4,96,IF($G$20-I20=-4,96,IF($G$20-I20=5,95,IF($G$20-I20=-5,95,IF($G$20-I20=6,94,IF($G$20-I20=-6,94,IF($G$20-I20=7,93,IF($G$20-I20=-7,93,IF($G$20-I20=8,92,IF($G$20-I20=-8,92,IF($G$20-I20=9,91,IF($G$20-I20=-9,91,IF($G$20-I20=10,90,IF($G$20-I20=-10,90,IF($G$20-I20=11,89,IF($G$20-I20=-11,89,IF($G$20-I20=12,88,IF($G$20-I20=-12,88,IF($G$20-I20=13,87,IF($G$20-I20=-13,87,IF($G$20-I20=14,86,IF($G$20-I20=-14,86,IF($G$20-I20=15,85,IF($G$20-I20=-15,85,IF($G$20-I20=16,84,IF($G$20-I20=-16,84,IF($G$20-I20=17,83,IF($G$20-I20=-17,83,IF($G$20-I20=18,82,IF($G$20-I20=-18,82,IF($G$20-I20=19,81,IF($G$20-I20=-19,81,IF($G$20-I20=20,80,IF($G$20-I20=-20,80,IF($G$20-I20=21,79,IF($G$20-I20=-21,79,IF($G$20-I20=22,78,IF($G$20-I20=-22,78,IF($G$20-I20=23,77,IF($G$20-I20=-23,77,IF($G$20-I20=24,76,IF($G$20-I20=-24,76,IF($G$20-I20=25,75,IF($G$20-I20=-25,75,IF($G$20-I20=26,74,IF($G$20-I20=-26,74,IF($G$20-I20=27,73,IF($G$20-I20=-27,73,IF($G$20-I20=28,72,IF($G$20-I20=-28,72,IF($G$20-I20=29,71,IF($G$20-I20=-29,71,IF($G$20-I20=30,70,IF($G$20-I20=-30,70,IF($G$20-I20=31,69,IF($G$20-I20=-31,69,IF($G$20-I20=32,68,IF($G$20-I20=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <v>100</v>
+      </c>
+      <c r="J22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="K22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="R22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="U22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="V22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="W22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="X22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="Z22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="AA22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="AB22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="AC22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="AD22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="AE22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="AF22" s="3">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="3">
+        <f t="shared" ref="H23:AF23" si="3">IF($G$20-H20=33,67,IF($G$20-H20=-33,67,IF($G$20-H20=34,66,IF($G$20-H20=-34,66,IF($G$20-H20=35,65,IF($G$20-H20=-35,65,IF($G$20-H20=36,64,IF($G$20-H20=-36,64,IF($G$20-H20=37,63,IF($G$20-H20=-37,63,IF($G$20-H20=38,62,IF($G$20-H20=-38,62,IF($G$20-H20=39,61,IF($G$20-H20=-39,61,IF($G$20-H20=40,60,IF($G$20-H20=-40,60,IF($G$20-H20=41,59,IF($G$20-H20=-41,59,IF($G$20-H20=42,58,IF($G$20-H20=-42,58,IF($G$20-H20=43,57,IF($G$20-H20=-43,57,IF($G$20-H20=44,56,IF($G$20-H20=-44,56,IF($G$20-H20=45,55,IF($G$20-H20=-45,55,IF($G$20-H20=46,54,IF($G$20-H20=-46,54,IF($G$20-H20=47,53,IF($G$20-H20=-47,53,IF($G$20-H20=48,52,IF($G$20-H20=-48,52,IF($G$20-H20=49,51,IF($G$20-H20=-49,51,IF($G$20-H20=50,50,IF($G$20-H20=-50,50,IF($G$20-H20=51,49,IF($G$20-H20=-51,49,IF($G$20-H20=52,48,IF($G$20-H20=-52,48,IF($G$20-H20=53,47,IF($G$20-H20=-53,47,IF($G$20-H20=54,46,IF($G$20-H20=-54,46,IF($G$20-H20=55,45,IF($G$20-H20=-55,45,IF($G$20-H20=56,44,IF($G$20-H20=-56,44,IF($G$20-H20=57,43,IF($G$20-H20=-57,43,IF($G$20-H20=58,42,IF($G$20-H20=-58,42,IF($G$20-H20=59,41,IF($G$20-H20=-59,41,IF($G$20-H20=60,40,IF($G$20-H20=-60,40,IF($G$20-H20=61,39,IF($G$20-H20=-61,39,IF($G$20-H20=62,38,IF($G$20-H20=-62,38,IF($G$20-H20=63,37,IF($G$20-H20=-63,37,IF($G$20-H20=64,36,IF($G$20-H20=-64,36,IF($G$20-H20=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="3">
+        <f t="shared" ref="H24:AF24" si="4">IF($G$20-H20=-65,35,IF($G$20-H20=66,34,IF($G$20-H20=-66,34,IF($G$20-H20=67,33,IF($G$20-H20=-67,33,IF($G$20-H20=68,32,IF($G$20-H20=-68,32,IF($G$20-H20=69,31,IF($G$20-H20=-69,31,IF($G$20-H20=70,30,IF($G$20-H20=-70,30,IF($G$20-H20=71,29,IF($G$20-H20=-71,29,IF($G$20-H20=72,28,IF($G$20-H20=-72,28,IF($G$20-H20=73,27,IF($G$20-H20=-73,27,IF($G$20-H20=74,26,IF($G$20-H20=-74,26,IF($G$20-H20=75,25,IF($G$20-H20=-75,25,IF($G$20-H20=76,24,IF($G$20-H20=-76,24,IF($G$20-H20=77,23,IF($G$20-H20=-77,23,IF($G$20-H20=78,22,IF($G$20-H20=-78,22,IF($G$20-H20=79,21,IF($G$20-H20=-79,21,IF($G$20-H20=80,20,IF($G$20-H20=-80,20,IF($G$20-H20=81,19,IF($G$20-H20=-81,19,IF($G$20-H20=82,18,IF($G$20-H20=-82,18,IF($G$20-H20=83,17,IF($G$20-H20=-83,17,IF($G$20-H20=84,16,IF($G$20-H20=-84,16,IF($G$20-H20=85,15,IF($G$20-H20=-85,15,IF($G$20-H20=86,14,IF($G$20-H20=-86,14,IF($G$20-H20=87,13,IF($G$20-H20=-87,13,IF($G$20-H20=88,12,IF($G$20-H20=-88,12,IF($G$20-H20=89,11,IF($G$20-H20=-89,11,IF($G$20-H20=90,10,IF($G$20-H20=-90,10,IF($G$20-H20=91,9,IF($G$20-H20=-91,9,IF($G$20-H20=92,8,IF($G$20-H20=-92,8,IF($G$20-H20=93,7,IF($G$20-H20=-93,7,IF($G$20-H20=94,6,IF($G$20-H20=-94,6,IF($G$20-H20=95,5,IF($G$20-H20=-95,5,IF($G$20-H20=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="3">
+        <f t="shared" ref="H25:AF25" si="5">IF($G$20-H20=-96,4,IF($G$20-H20=97,3,IF($G$20-H20=-97,3,IF($G$20-H20=98,2,IF($G$20-H20=-98,2,IF($G$20-H20=99,1,IF($G$20-H20=-99,1,IF($G$20-H20=100,0,IF($G$20-H20=-100,0,0)))))))))</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+    </row>
+    <row r="27" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+    </row>
+    <row r="28" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+    </row>
+    <row r="29" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+    </row>
+    <row r="30" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+    </row>
+    <row r="31" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+    </row>
+    <row r="32" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+    </row>
+    <row r="33" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+    </row>
+    <row r="34" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+    </row>
+    <row r="35" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+    </row>
+    <row r="36" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+    </row>
+    <row r="37" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+    </row>
+    <row r="38" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1"/>
+    </row>
+    <row r="39" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1"/>
+    </row>
+    <row r="40" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1"/>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+    </row>
+    <row r="41" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1"/>
+      <c r="AF41" s="1"/>
+    </row>
+    <row r="42" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+    </row>
+    <row r="43" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+    </row>
+    <row r="44" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+    </row>
+    <row r="45" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+   